--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,58 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A59276A-149F-4386-8CDA-01D2E7F84618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B69CC0-2B92-49A8-BC0C-8DD26AC1EF94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12765" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
     <sheet name="편의성" sheetId="10" r:id="rId2"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -1111,7 +1100,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UI가 움직이지기 않게 수정</t>
+    <t>마테리얼 제거</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1500,12 +1489,117 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1518,57 +1612,24 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1587,83 +1648,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2136,36 +2125,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -2178,17 +2167,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41" t="s">
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -2207,17 +2196,17 @@
       <c r="D4" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
       <c r="L4" s="10" t="s">
         <v>164</v>
       </c>
@@ -2234,17 +2223,17 @@
       <c r="D5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39" t="s">
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
       <c r="L5" s="10" t="s">
         <v>164</v>
       </c>
@@ -2261,17 +2250,17 @@
       <c r="D6" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39" t="s">
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
       <c r="L6" s="10" t="s">
         <v>164</v>
       </c>
@@ -2288,17 +2277,17 @@
       <c r="D7" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="39" t="s">
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
       <c r="L7" s="10" t="s">
         <v>164</v>
       </c>
@@ -2315,17 +2304,17 @@
       <c r="D8" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="39" t="s">
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
       <c r="L8" s="10" t="s">
         <v>164</v>
       </c>
@@ -2342,17 +2331,17 @@
       <c r="D9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="39" t="s">
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
       <c r="L9" s="10" t="s">
         <v>164</v>
       </c>
@@ -2369,17 +2358,17 @@
       <c r="D10" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="39" t="s">
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
       <c r="L10" s="10" t="s">
         <v>164</v>
       </c>
@@ -2396,17 +2385,17 @@
       <c r="D11" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39" t="s">
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
       <c r="L11" s="10" t="s">
         <v>164</v>
       </c>
@@ -2423,17 +2412,17 @@
       <c r="D12" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39" t="s">
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="75"/>
       <c r="L12" s="10" t="s">
         <v>54</v>
       </c>
@@ -2450,17 +2439,17 @@
       <c r="D13" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39" t="s">
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
       <c r="L13" s="10" t="s">
         <v>52</v>
       </c>
@@ -2477,17 +2466,17 @@
       <c r="D14" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39" t="s">
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75"/>
       <c r="L14" s="10" t="s">
         <v>54</v>
       </c>
@@ -2504,17 +2493,17 @@
       <c r="D15" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39" t="s">
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
       <c r="L15" s="10" t="s">
         <v>164</v>
       </c>
@@ -2531,17 +2520,17 @@
       <c r="D16" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39" t="s">
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
       <c r="L16" s="10" t="s">
         <v>164</v>
       </c>
@@ -2558,17 +2547,17 @@
       <c r="D17" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="75"/>
       <c r="L17" s="10" t="s">
         <v>164</v>
       </c>
@@ -2585,17 +2574,17 @@
       <c r="D18" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39" t="s">
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
       <c r="L18" s="10" t="s">
         <v>164</v>
       </c>
@@ -2612,17 +2601,17 @@
       <c r="D19" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="47" t="s">
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
       <c r="L19" s="10" t="s">
         <v>52</v>
       </c>
@@ -2639,17 +2628,17 @@
       <c r="D20" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="47" t="s">
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
       <c r="L20" s="10" t="s">
         <v>52</v>
       </c>
@@ -2666,17 +2655,17 @@
       <c r="D21" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="47" t="s">
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
       <c r="L21" s="10" t="s">
         <v>164</v>
       </c>
@@ -2693,17 +2682,17 @@
       <c r="D22" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="47" t="s">
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
       <c r="L22" s="10" t="s">
         <v>164</v>
       </c>
@@ -2720,17 +2709,17 @@
       <c r="D23" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="45" t="s">
+      <c r="E23" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="47" t="s">
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="69" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
       <c r="L23" s="10" t="s">
         <v>52</v>
       </c>
@@ -2747,17 +2736,17 @@
       <c r="D24" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="E24" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="47" t="s">
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
       <c r="L24" s="10" t="s">
         <v>52</v>
       </c>
@@ -2774,17 +2763,17 @@
       <c r="D25" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="E25" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="47" t="s">
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
       <c r="L25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2801,17 +2790,17 @@
       <c r="D26" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46" t="s">
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
       <c r="L26" s="10" t="s">
         <v>54</v>
       </c>
@@ -2819,7 +2808,7 @@
       <c r="P26" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="Q26" s="87" t="s">
+      <c r="Q26" s="42" t="s">
         <v>193</v>
       </c>
       <c r="S26" s="18" t="s">
@@ -2843,17 +2832,17 @@
       <c r="D27" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="71" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="56" t="s">
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="57"/>
-      <c r="K27" s="58"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="50"/>
       <c r="L27" s="10" t="s">
         <v>164</v>
       </c>
@@ -2876,17 +2865,17 @@
       <c r="D28" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="71" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="56" t="s">
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="57"/>
-      <c r="K28" s="58"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="50"/>
       <c r="L28" s="10" t="s">
         <v>52</v>
       </c>
@@ -2906,17 +2895,17 @@
       <c r="D29" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="56" t="s">
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="57"/>
-      <c r="K29" s="58"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="50"/>
       <c r="L29" s="10" t="s">
         <v>52</v>
       </c>
@@ -2936,17 +2925,17 @@
       <c r="D30" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="46" t="s">
+      <c r="E30" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="59" t="s">
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
       <c r="L30" s="10" t="s">
         <v>52</v>
       </c>
@@ -2966,17 +2955,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="55" t="s">
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
       <c r="L31" s="10" t="s">
         <v>52</v>
       </c>
@@ -2993,17 +2982,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="48" t="s">
+      <c r="E32" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="55" t="s">
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
       <c r="L32" s="10" t="s">
         <v>52</v>
       </c>
@@ -3014,23 +3003,23 @@
       <c r="B33" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="74">
+      <c r="C33" s="39">
         <v>46122</v>
       </c>
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="48" t="s">
+      <c r="E33" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="55" t="s">
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
       <c r="L33" s="10" t="s">
         <v>52</v>
       </c>
@@ -3038,26 +3027,26 @@
     </row>
     <row r="34" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19"/>
-      <c r="B34" s="75" t="s">
+      <c r="B34" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="74">
+      <c r="C34" s="39">
         <v>46123</v>
       </c>
-      <c r="D34" s="76" t="s">
+      <c r="D34" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="77" t="s">
+      <c r="E34" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="80" t="s">
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="81"/>
-      <c r="K34" s="82"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="57"/>
       <c r="L34" s="10" t="s">
         <v>52</v>
       </c>
@@ -3065,26 +3054,26 @@
     </row>
     <row r="35" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19"/>
-      <c r="B35" s="75" t="s">
+      <c r="B35" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="74">
+      <c r="C35" s="39">
         <v>46123</v>
       </c>
-      <c r="D35" s="76" t="s">
+      <c r="D35" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="77" t="s">
+      <c r="E35" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="83" t="s">
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="55" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
       <c r="L35" s="10" t="s">
         <v>52</v>
       </c>
@@ -3092,26 +3081,26 @@
     </row>
     <row r="36" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19"/>
-      <c r="B36" s="75" t="s">
+      <c r="B36" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="74">
+      <c r="C36" s="39">
         <v>46126</v>
       </c>
-      <c r="D36" s="76" t="s">
+      <c r="D36" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="77" t="s">
+      <c r="E36" s="61" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="83" t="s">
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="55" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
       <c r="L36" s="10" t="s">
         <v>52</v>
       </c>
@@ -3119,26 +3108,26 @@
     </row>
     <row r="37" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19"/>
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="74">
+      <c r="C37" s="39">
         <v>46127</v>
       </c>
-      <c r="D37" s="76" t="s">
+      <c r="D37" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="84" t="s">
+      <c r="E37" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="85"/>
-      <c r="G37" s="85"/>
-      <c r="H37" s="86"/>
-      <c r="I37" s="83" t="s">
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
       <c r="L37" s="10" t="s">
         <v>52</v>
       </c>
@@ -3146,26 +3135,26 @@
     </row>
     <row r="38" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19"/>
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="74">
+      <c r="C38" s="39">
         <v>46127</v>
       </c>
-      <c r="D38" s="76" t="s">
+      <c r="D38" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="84" t="s">
+      <c r="E38" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="83" t="s">
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="81"/>
-      <c r="K38" s="82"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="57"/>
       <c r="L38" s="10" t="s">
         <v>52</v>
       </c>
@@ -3173,26 +3162,26 @@
     </row>
     <row r="39" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19"/>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="89">
+      <c r="C39" s="44">
         <v>46130</v>
       </c>
-      <c r="D39" s="90" t="s">
+      <c r="D39" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="91" t="s">
+      <c r="E39" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="92" t="s">
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="92"/>
-      <c r="K39" s="92"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
       <c r="L39" s="10" t="s">
         <v>52</v>
       </c>
@@ -3200,26 +3189,26 @@
     </row>
     <row r="40" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19"/>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="89">
+      <c r="C40" s="44">
         <v>46140</v>
       </c>
-      <c r="D40" s="90" t="s">
+      <c r="D40" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="91" t="s">
+      <c r="E40" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="92" t="s">
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
       <c r="L40" s="10" t="s">
         <v>52</v>
       </c>
@@ -3227,53 +3216,53 @@
     </row>
     <row r="41" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
-      <c r="B41" s="88" t="s">
+      <c r="B41" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="89">
+      <c r="C41" s="44">
         <v>46140</v>
       </c>
-      <c r="D41" s="90" t="s">
+      <c r="D41" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="91" t="s">
+      <c r="E41" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="92" t="s">
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
       <c r="L41" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M41" s="19"/>
     </row>
     <row r="42" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
-      <c r="B42" s="88" t="s">
+      <c r="B42" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="89">
+      <c r="C42" s="44">
         <v>46140</v>
       </c>
-      <c r="D42" s="90" t="s">
+      <c r="D42" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="91" t="s">
+      <c r="E42" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="91"/>
-      <c r="G42" s="91"/>
-      <c r="H42" s="91"/>
-      <c r="I42" s="92" t="s">
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
       <c r="L42" s="10" t="s">
         <v>52</v>
       </c>
@@ -3281,53 +3270,53 @@
     </row>
     <row r="43" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
-      <c r="B43" s="88" t="s">
+      <c r="B43" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="89">
+      <c r="C43" s="44">
         <v>46140</v>
       </c>
-      <c r="D43" s="90" t="s">
+      <c r="D43" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="91" t="s">
+      <c r="E43" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="91"/>
-      <c r="G43" s="91"/>
-      <c r="H43" s="91"/>
-      <c r="I43" s="91" t="s">
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="92"/>
-      <c r="K43" s="92"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
       <c r="L43" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M43" s="19"/>
     </row>
     <row r="44" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19"/>
-      <c r="B44" s="88" t="s">
+      <c r="B44" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="89">
+      <c r="C44" s="44">
         <v>46140</v>
       </c>
-      <c r="D44" s="90" t="s">
+      <c r="D44" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="91" t="s">
+      <c r="E44" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="91"/>
-      <c r="G44" s="91"/>
-      <c r="H44" s="91"/>
-      <c r="I44" s="92" t="s">
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="53" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="92"/>
-      <c r="K44" s="92"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
       <c r="L44" s="10" t="s">
         <v>52</v>
       </c>
@@ -3335,188 +3324,188 @@
     </row>
     <row r="45" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19"/>
-      <c r="B45" s="88" t="s">
+      <c r="B45" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="89">
+      <c r="C45" s="44">
         <v>46140</v>
       </c>
-      <c r="D45" s="90" t="s">
+      <c r="D45" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="91" t="s">
+      <c r="E45" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="91"/>
-      <c r="G45" s="91"/>
-      <c r="H45" s="91"/>
-      <c r="I45" s="92" t="s">
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="92"/>
-      <c r="K45" s="92"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
       <c r="L45" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M45" s="19"/>
     </row>
     <row r="46" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19"/>
-      <c r="B46" s="88" t="s">
+      <c r="B46" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="89">
+      <c r="C46" s="44">
         <v>46140</v>
       </c>
-      <c r="D46" s="90" t="s">
+      <c r="D46" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="91" t="s">
+      <c r="E46" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="91"/>
-      <c r="G46" s="91"/>
-      <c r="H46" s="91"/>
-      <c r="I46" s="92" t="s">
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="92"/>
-      <c r="K46" s="92"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
       <c r="L46" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M46" s="19"/>
     </row>
     <row r="47" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19"/>
-      <c r="B47" s="88" t="s">
+      <c r="B47" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="89">
+      <c r="C47" s="44">
         <v>46140</v>
       </c>
-      <c r="D47" s="90" t="s">
+      <c r="D47" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="91" t="s">
+      <c r="E47" s="54" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="91"/>
-      <c r="G47" s="91"/>
-      <c r="H47" s="91"/>
-      <c r="I47" s="92" t="s">
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="53" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="92"/>
-      <c r="K47" s="92"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
       <c r="L47" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M47" s="19"/>
     </row>
     <row r="48" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19"/>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="89">
+      <c r="C48" s="44">
         <v>46140</v>
       </c>
-      <c r="D48" s="90" t="s">
+      <c r="D48" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="91" t="s">
+      <c r="E48" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="91"/>
-      <c r="G48" s="91"/>
-      <c r="H48" s="91"/>
-      <c r="I48" s="92" t="s">
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="53" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="92"/>
-      <c r="K48" s="92"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
       <c r="L48" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M48" s="19"/>
     </row>
     <row r="49" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19"/>
-      <c r="B49" s="88" t="s">
+      <c r="B49" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="89">
+      <c r="C49" s="44">
         <v>46140</v>
       </c>
-      <c r="D49" s="90" t="s">
+      <c r="D49" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="91" t="s">
+      <c r="E49" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="91"/>
-      <c r="G49" s="91"/>
-      <c r="H49" s="91"/>
-      <c r="I49" s="92" t="s">
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="92"/>
-      <c r="K49" s="92"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
       <c r="L49" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M49" s="19"/>
     </row>
     <row r="50" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19"/>
-      <c r="B50" s="88" t="s">
+      <c r="B50" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="89">
+      <c r="C50" s="44">
         <v>46140</v>
       </c>
-      <c r="D50" s="90" t="s">
+      <c r="D50" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="91" t="s">
+      <c r="E50" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="91"/>
-      <c r="G50" s="91"/>
-      <c r="H50" s="91"/>
-      <c r="I50" s="92" t="s">
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="53" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="92"/>
-      <c r="K50" s="92"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
       <c r="L50" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M50" s="19"/>
     </row>
     <row r="51" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19"/>
-      <c r="B51" s="88" t="s">
+      <c r="B51" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="89">
+      <c r="C51" s="44">
         <v>46140</v>
       </c>
-      <c r="D51" s="90" t="s">
+      <c r="D51" s="45" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="91" t="s">
+      <c r="E51" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="91"/>
-      <c r="G51" s="91"/>
-      <c r="H51" s="91"/>
-      <c r="I51" s="92" t="s">
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="53" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="92"/>
-      <c r="K51" s="92"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
       <c r="L51" s="10" t="s">
         <v>52</v>
       </c>
@@ -3524,55 +3513,55 @@
     </row>
     <row r="52" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19"/>
-      <c r="B52" s="88" t="s">
+      <c r="B52" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="89">
+      <c r="C52" s="44">
         <v>46140</v>
       </c>
-      <c r="D52" s="93" t="s">
+      <c r="D52" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="91" t="s">
+      <c r="E52" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="91"/>
-      <c r="G52" s="91"/>
-      <c r="H52" s="91"/>
-      <c r="I52" s="92" t="s">
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="92"/>
-      <c r="K52" s="92"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
       <c r="L52" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M52" s="19"/>
     </row>
     <row r="53" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19"/>
-      <c r="B53" s="88" t="s">
+      <c r="B53" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="89">
+      <c r="C53" s="44">
         <v>46140</v>
       </c>
-      <c r="D53" s="90" t="s">
+      <c r="D53" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="91" t="s">
+      <c r="E53" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="91"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="92" t="s">
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="54"/>
+      <c r="I53" s="53" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="92"/>
-      <c r="K53" s="92"/>
+      <c r="J53" s="53"/>
+      <c r="K53" s="53"/>
       <c r="L53" s="10" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M53" s="19"/>
     </row>
@@ -3583,13 +3572,13 @@
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
-      <c r="I54" s="54"/>
-      <c r="J54" s="54"/>
-      <c r="K54" s="54"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="47"/>
+      <c r="K54" s="47"/>
       <c r="L54" s="10" t="s">
         <v>52</v>
       </c>
@@ -3602,13 +3591,13 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="47"/>
+      <c r="K55" s="47"/>
       <c r="L55" s="10" t="s">
         <v>52</v>
       </c>
@@ -3621,13 +3610,13 @@
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
-      <c r="H56" s="52"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="59"/>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="47"/>
+      <c r="K56" s="47"/>
       <c r="L56" s="10" t="s">
         <v>52</v>
       </c>
@@ -3640,13 +3629,13 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="52"/>
-      <c r="H57" s="52"/>
-      <c r="I57" s="54"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="54"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="47"/>
+      <c r="K57" s="47"/>
       <c r="L57" s="10" t="s">
         <v>52</v>
       </c>
@@ -3659,13 +3648,13 @@
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="54"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="54"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="47"/>
+      <c r="J58" s="47"/>
+      <c r="K58" s="47"/>
       <c r="L58" s="10" t="s">
         <v>52</v>
       </c>
@@ -3678,13 +3667,13 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="54"/>
-      <c r="K59" s="54"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="59"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
       <c r="L59" s="10" t="s">
         <v>52</v>
       </c>
@@ -3697,13 +3686,13 @@
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="52"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47"/>
       <c r="L60" s="10" t="s">
         <v>52</v>
       </c>
@@ -3716,13 +3705,13 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
-      <c r="E61" s="52"/>
-      <c r="F61" s="52"/>
-      <c r="G61" s="52"/>
-      <c r="H61" s="52"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54"/>
-      <c r="K61" s="54"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47"/>
+      <c r="K61" s="47"/>
       <c r="L61" s="10" t="s">
         <v>52</v>
       </c>
@@ -3735,13 +3724,13 @@
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="52"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
+      <c r="E62" s="59"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="47"/>
+      <c r="J62" s="47"/>
+      <c r="K62" s="47"/>
       <c r="L62" s="10" t="s">
         <v>52</v>
       </c>
@@ -3754,13 +3743,13 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="52"/>
-      <c r="H63" s="52"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="47"/>
+      <c r="J63" s="47"/>
+      <c r="K63" s="47"/>
       <c r="L63" s="10" t="s">
         <v>52</v>
       </c>
@@ -3773,13 +3762,13 @@
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
-      <c r="H64" s="52"/>
-      <c r="I64" s="54"/>
-      <c r="J64" s="54"/>
-      <c r="K64" s="54"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="47"/>
+      <c r="J64" s="47"/>
+      <c r="K64" s="47"/>
       <c r="L64" s="10" t="s">
         <v>52</v>
       </c>
@@ -3792,13 +3781,13 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-      <c r="H65" s="52"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="54"/>
-      <c r="K65" s="54"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="47"/>
+      <c r="K65" s="47"/>
       <c r="L65" s="10" t="s">
         <v>52</v>
       </c>
@@ -3811,13 +3800,13 @@
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="54"/>
-      <c r="J66" s="54"/>
-      <c r="K66" s="54"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="47"/>
+      <c r="J66" s="47"/>
+      <c r="K66" s="47"/>
       <c r="L66" s="10" t="s">
         <v>52</v>
       </c>
@@ -3830,13 +3819,13 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
-      <c r="E67" s="53"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="54"/>
-      <c r="J67" s="54"/>
-      <c r="K67" s="54"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="47"/>
+      <c r="J67" s="47"/>
+      <c r="K67" s="47"/>
       <c r="L67" s="10" t="s">
         <v>52</v>
       </c>
@@ -3849,13 +3838,13 @@
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="52"/>
-      <c r="H68" s="52"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="54"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="59"/>
+      <c r="G68" s="59"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="47"/>
+      <c r="J68" s="47"/>
+      <c r="K68" s="47"/>
       <c r="L68" s="10" t="s">
         <v>52</v>
       </c>
@@ -3868,13 +3857,13 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="52"/>
-      <c r="H69" s="52"/>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
+      <c r="E69" s="59"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="47"/>
+      <c r="K69" s="47"/>
       <c r="L69" s="10" t="s">
         <v>52</v>
       </c>
@@ -3887,13 +3876,13 @@
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="52"/>
-      <c r="G70" s="52"/>
-      <c r="H70" s="52"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
+      <c r="E70" s="59"/>
+      <c r="F70" s="59"/>
+      <c r="G70" s="59"/>
+      <c r="H70" s="59"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
       <c r="L70" s="10" t="s">
         <v>52</v>
       </c>
@@ -3906,13 +3895,13 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="52"/>
-      <c r="H71" s="52"/>
-      <c r="I71" s="54"/>
-      <c r="J71" s="54"/>
-      <c r="K71" s="54"/>
+      <c r="E71" s="59"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="47"/>
+      <c r="K71" s="47"/>
       <c r="L71" s="10" t="s">
         <v>52</v>
       </c>
@@ -3925,13 +3914,13 @@
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="54"/>
-      <c r="K72" s="54"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="59"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="47"/>
+      <c r="K72" s="47"/>
       <c r="L72" s="10" t="s">
         <v>52</v>
       </c>
@@ -3944,13 +3933,13 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="52"/>
-      <c r="G73" s="52"/>
-      <c r="H73" s="52"/>
-      <c r="I73" s="54"/>
-      <c r="J73" s="54"/>
-      <c r="K73" s="54"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="59"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47"/>
       <c r="L73" s="10" t="s">
         <v>52</v>
       </c>
@@ -3963,13 +3952,13 @@
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="54"/>
-      <c r="J74" s="54"/>
-      <c r="K74" s="54"/>
+      <c r="E74" s="59"/>
+      <c r="F74" s="59"/>
+      <c r="G74" s="59"/>
+      <c r="H74" s="59"/>
+      <c r="I74" s="47"/>
+      <c r="J74" s="47"/>
+      <c r="K74" s="47"/>
       <c r="L74" s="10" t="s">
         <v>52</v>
       </c>
@@ -3982,13 +3971,13 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="54"/>
-      <c r="J75" s="54"/>
-      <c r="K75" s="54"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="47"/>
+      <c r="K75" s="47"/>
       <c r="L75" s="10" t="s">
         <v>52</v>
       </c>
@@ -4001,13 +3990,13 @@
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="54"/>
-      <c r="J76" s="54"/>
-      <c r="K76" s="54"/>
+      <c r="E76" s="59"/>
+      <c r="F76" s="59"/>
+      <c r="G76" s="59"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="47"/>
+      <c r="J76" s="47"/>
+      <c r="K76" s="47"/>
       <c r="L76" s="10" t="s">
         <v>52</v>
       </c>
@@ -4020,13 +4009,13 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="52"/>
-      <c r="H77" s="52"/>
-      <c r="I77" s="54"/>
-      <c r="J77" s="54"/>
-      <c r="K77" s="54"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="59"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="47"/>
+      <c r="J77" s="47"/>
+      <c r="K77" s="47"/>
       <c r="L77" s="10" t="s">
         <v>52</v>
       </c>
@@ -4039,13 +4028,13 @@
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="52"/>
-      <c r="I78" s="54"/>
-      <c r="J78" s="54"/>
-      <c r="K78" s="54"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="47"/>
+      <c r="J78" s="47"/>
+      <c r="K78" s="47"/>
       <c r="L78" s="10" t="s">
         <v>52</v>
       </c>
@@ -4058,13 +4047,13 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="54"/>
-      <c r="J79" s="54"/>
-      <c r="K79" s="54"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="47"/>
+      <c r="J79" s="47"/>
+      <c r="K79" s="47"/>
       <c r="L79" s="10" t="s">
         <v>52</v>
       </c>
@@ -4077,13 +4066,13 @@
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="54"/>
-      <c r="J80" s="54"/>
-      <c r="K80" s="54"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="47"/>
+      <c r="J80" s="47"/>
+      <c r="K80" s="47"/>
       <c r="L80" s="10" t="s">
         <v>52</v>
       </c>
@@ -4096,13 +4085,13 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="52"/>
-      <c r="H81" s="52"/>
-      <c r="I81" s="54"/>
-      <c r="J81" s="54"/>
-      <c r="K81" s="54"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="47"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="47"/>
       <c r="L81" s="10" t="s">
         <v>52</v>
       </c>
@@ -4115,13 +4104,13 @@
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="52"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="54"/>
-      <c r="J82" s="54"/>
-      <c r="K82" s="54"/>
+      <c r="E82" s="59"/>
+      <c r="F82" s="59"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="47"/>
+      <c r="J82" s="47"/>
+      <c r="K82" s="47"/>
       <c r="L82" s="10" t="s">
         <v>52</v>
       </c>
@@ -4134,13 +4123,13 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="52"/>
-      <c r="I83" s="54"/>
-      <c r="J83" s="54"/>
-      <c r="K83" s="54"/>
+      <c r="E83" s="59"/>
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="47"/>
+      <c r="J83" s="47"/>
+      <c r="K83" s="47"/>
       <c r="L83" s="10" t="s">
         <v>52</v>
       </c>
@@ -4153,13 +4142,13 @@
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="54"/>
-      <c r="J84" s="54"/>
-      <c r="K84" s="54"/>
+      <c r="E84" s="59"/>
+      <c r="F84" s="59"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="47"/>
+      <c r="J84" s="47"/>
+      <c r="K84" s="47"/>
       <c r="L84" s="10" t="s">
         <v>52</v>
       </c>
@@ -4172,13 +4161,13 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
-      <c r="H85" s="52"/>
-      <c r="I85" s="54"/>
-      <c r="J85" s="54"/>
-      <c r="K85" s="54"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59"/>
+      <c r="I85" s="47"/>
+      <c r="J85" s="47"/>
+      <c r="K85" s="47"/>
       <c r="L85" s="10" t="s">
         <v>52</v>
       </c>
@@ -4191,13 +4180,13 @@
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="54"/>
-      <c r="J86" s="54"/>
-      <c r="K86" s="54"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="47"/>
+      <c r="J86" s="47"/>
+      <c r="K86" s="47"/>
       <c r="L86" s="10" t="s">
         <v>52</v>
       </c>
@@ -4210,13 +4199,13 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="54"/>
-      <c r="J87" s="54"/>
-      <c r="K87" s="54"/>
+      <c r="E87" s="59"/>
+      <c r="F87" s="59"/>
+      <c r="G87" s="59"/>
+      <c r="H87" s="59"/>
+      <c r="I87" s="47"/>
+      <c r="J87" s="47"/>
+      <c r="K87" s="47"/>
       <c r="L87" s="10" t="s">
         <v>52</v>
       </c>
@@ -4229,13 +4218,13 @@
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="54"/>
-      <c r="J88" s="54"/>
-      <c r="K88" s="54"/>
+      <c r="E88" s="59"/>
+      <c r="F88" s="59"/>
+      <c r="G88" s="59"/>
+      <c r="H88" s="59"/>
+      <c r="I88" s="47"/>
+      <c r="J88" s="47"/>
+      <c r="K88" s="47"/>
       <c r="L88" s="10" t="s">
         <v>52</v>
       </c>
@@ -4248,13 +4237,13 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
-      <c r="E89" s="52"/>
-      <c r="F89" s="52"/>
-      <c r="G89" s="52"/>
-      <c r="H89" s="52"/>
-      <c r="I89" s="54"/>
-      <c r="J89" s="54"/>
-      <c r="K89" s="54"/>
+      <c r="E89" s="59"/>
+      <c r="F89" s="59"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="47"/>
+      <c r="J89" s="47"/>
+      <c r="K89" s="47"/>
       <c r="L89" s="10" t="s">
         <v>52</v>
       </c>
@@ -4267,13 +4256,13 @@
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="52"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="54"/>
-      <c r="J90" s="54"/>
-      <c r="K90" s="54"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="59"/>
+      <c r="G90" s="59"/>
+      <c r="H90" s="59"/>
+      <c r="I90" s="47"/>
+      <c r="J90" s="47"/>
+      <c r="K90" s="47"/>
       <c r="L90" s="10" t="s">
         <v>52</v>
       </c>
@@ -4286,13 +4275,13 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
-      <c r="E91" s="52"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="52"/>
-      <c r="H91" s="52"/>
-      <c r="I91" s="54"/>
-      <c r="J91" s="54"/>
-      <c r="K91" s="54"/>
+      <c r="E91" s="59"/>
+      <c r="F91" s="59"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="59"/>
+      <c r="I91" s="47"/>
+      <c r="J91" s="47"/>
+      <c r="K91" s="47"/>
       <c r="L91" s="10" t="s">
         <v>52</v>
       </c>
@@ -4305,13 +4294,13 @@
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="52"/>
-      <c r="H92" s="52"/>
-      <c r="I92" s="54"/>
-      <c r="J92" s="54"/>
-      <c r="K92" s="54"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="59"/>
+      <c r="G92" s="59"/>
+      <c r="H92" s="59"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="47"/>
+      <c r="K92" s="47"/>
       <c r="L92" s="10" t="s">
         <v>52</v>
       </c>
@@ -4324,13 +4313,13 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="54"/>
-      <c r="J93" s="54"/>
-      <c r="K93" s="54"/>
+      <c r="E93" s="59"/>
+      <c r="F93" s="59"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="47"/>
+      <c r="J93" s="47"/>
+      <c r="K93" s="47"/>
       <c r="L93" s="10" t="s">
         <v>52</v>
       </c>
@@ -4343,13 +4332,13 @@
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="52"/>
-      <c r="I94" s="54"/>
-      <c r="J94" s="54"/>
-      <c r="K94" s="54"/>
+      <c r="E94" s="59"/>
+      <c r="F94" s="59"/>
+      <c r="G94" s="59"/>
+      <c r="H94" s="59"/>
+      <c r="I94" s="47"/>
+      <c r="J94" s="47"/>
+      <c r="K94" s="47"/>
       <c r="L94" s="10" t="s">
         <v>52</v>
       </c>
@@ -4362,13 +4351,13 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="54"/>
-      <c r="J95" s="54"/>
-      <c r="K95" s="54"/>
+      <c r="E95" s="59"/>
+      <c r="F95" s="59"/>
+      <c r="G95" s="59"/>
+      <c r="H95" s="59"/>
+      <c r="I95" s="47"/>
+      <c r="J95" s="47"/>
+      <c r="K95" s="47"/>
       <c r="L95" s="10" t="s">
         <v>52</v>
       </c>
@@ -4381,13 +4370,13 @@
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="52"/>
-      <c r="H96" s="52"/>
-      <c r="I96" s="54"/>
-      <c r="J96" s="54"/>
-      <c r="K96" s="54"/>
+      <c r="E96" s="59"/>
+      <c r="F96" s="59"/>
+      <c r="G96" s="59"/>
+      <c r="H96" s="59"/>
+      <c r="I96" s="47"/>
+      <c r="J96" s="47"/>
+      <c r="K96" s="47"/>
       <c r="L96" s="10" t="s">
         <v>52</v>
       </c>
@@ -4400,13 +4389,13 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="52"/>
-      <c r="H97" s="52"/>
-      <c r="I97" s="54"/>
-      <c r="J97" s="54"/>
-      <c r="K97" s="54"/>
+      <c r="E97" s="59"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="59"/>
+      <c r="H97" s="59"/>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+      <c r="K97" s="47"/>
       <c r="L97" s="10" t="s">
         <v>52</v>
       </c>
@@ -4419,13 +4408,13 @@
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="54"/>
-      <c r="J98" s="54"/>
-      <c r="K98" s="54"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="59"/>
+      <c r="H98" s="59"/>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="47"/>
       <c r="L98" s="10" t="s">
         <v>52</v>
       </c>
@@ -4438,13 +4427,13 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="52"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="54"/>
-      <c r="J99" s="54"/>
-      <c r="K99" s="54"/>
+      <c r="E99" s="59"/>
+      <c r="F99" s="59"/>
+      <c r="G99" s="59"/>
+      <c r="H99" s="59"/>
+      <c r="I99" s="47"/>
+      <c r="J99" s="47"/>
+      <c r="K99" s="47"/>
       <c r="L99" s="10" t="s">
         <v>52</v>
       </c>
@@ -4457,13 +4446,13 @@
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="52"/>
-      <c r="H100" s="52"/>
-      <c r="I100" s="54"/>
-      <c r="J100" s="54"/>
-      <c r="K100" s="54"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="59"/>
+      <c r="H100" s="59"/>
+      <c r="I100" s="47"/>
+      <c r="J100" s="47"/>
+      <c r="K100" s="47"/>
       <c r="L100" s="10" t="s">
         <v>52</v>
       </c>
@@ -4471,50 +4460,135 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -4539,135 +4613,50 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -4705,42 +4694,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -5077,148 +5066,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="21" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="E2" s="23"/>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="90"/>
       <c r="M2" s="23"/>
-      <c r="N2" s="63" t="s">
+      <c r="N2" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="62" t="e" vm="1">
+      <c r="B3" s="86" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
       <c r="E3" s="22"/>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="22"/>
-      <c r="J3" s="70" t="s">
+      <c r="J3" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
       <c r="M3" s="22"/>
-      <c r="N3" s="62" t="e" vm="2">
+      <c r="N3" s="86" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
       <c r="E4" s="22"/>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="22"/>
-      <c r="J4" s="70" t="s">
+      <c r="J4" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
       <c r="M4" s="22"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="69"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="22"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
     </row>
     <row r="6" spans="2:16" s="21" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="82" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71" t="s">
+      <c r="C8" s="82"/>
+      <c r="D8" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="68" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68" t="s">
+      <c r="C10" s="84"/>
+      <c r="D10" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="84"/>
+      <c r="D11" s="84" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5229,6 +5210,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,47 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B69CC0-2B92-49A8-BC0C-8DD26AC1EF94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F9A0A8-F106-49E9-AC86-7D525B44E433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12765" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
     <sheet name="편의성" sheetId="10" r:id="rId2"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -59,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="276">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1100,7 +1111,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>마테리얼 제거</t>
+    <t>UI가 움직이지기 않게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 홀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처음 입장 시 2중 대화창 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화창이 하나만 나오게 수정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아들 방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 스냅되는 4가지 목말만 배치가 되고 침대에서 열쇠를 가져갈 수 있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목말 4개 포함해서 추가적인 아이템으로 스냅을 3곳을 추가하고 올바른 배치시 침대가 움직여서 열쇠를 가져 갈 수 있게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망령</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복도에 1분 이상있을 시 망령이 복도에 출현함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복도에 1분 이상 있을 시 망령이 플레이어를 즉사 시킴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1371,7 +1418,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1652,6 +1699,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1703,8 +1756,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFBE2D5"/>
       <color rgb="FFDAE9F8"/>
-      <color rgb="FFFBE2D5"/>
       <color rgb="FFFFCC66"/>
       <color rgb="FFFF5050"/>
       <color rgb="FF99FF99"/>
@@ -2185,7 +2238,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="204.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="204.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="26" t="s">
         <v>3</v>
@@ -2212,7 +2265,7 @@
       </c>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" ht="173.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="173.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="26" t="s">
         <v>11</v>
@@ -2239,7 +2292,7 @@
       </c>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="258.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="258.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="26" t="s">
         <v>12</v>
@@ -2266,7 +2319,7 @@
       </c>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="36.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="36.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="26" t="s">
         <v>13</v>
@@ -2293,7 +2346,7 @@
       </c>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" ht="121.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="121.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="26" t="s">
         <v>14</v>
@@ -2320,7 +2373,7 @@
       </c>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="123.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="123.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="26" t="s">
         <v>15</v>
@@ -2347,7 +2400,7 @@
       </c>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="26" t="s">
         <v>16</v>
@@ -2374,7 +2427,7 @@
       </c>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="26" t="s">
         <v>17</v>
@@ -2401,7 +2454,7 @@
       </c>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="26" t="s">
         <v>18</v>
@@ -2428,7 +2481,7 @@
       </c>
       <c r="M12" s="8"/>
     </row>
-    <row r="13" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="26" t="s">
         <v>19</v>
@@ -2455,7 +2508,7 @@
       </c>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="26" t="s">
         <v>20</v>
@@ -2482,7 +2535,7 @@
       </c>
       <c r="M14" s="8"/>
     </row>
-    <row r="15" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="26" t="s">
         <v>21</v>
@@ -2509,7 +2562,7 @@
       </c>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="26" t="s">
         <v>22</v>
@@ -2536,7 +2589,7 @@
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:21" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="26" t="s">
         <v>23</v>
@@ -2563,7 +2616,7 @@
       </c>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19"/>
       <c r="B18" s="26" t="s">
         <v>24</v>
@@ -2590,7 +2643,7 @@
       </c>
       <c r="M18" s="19"/>
     </row>
-    <row r="19" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19"/>
       <c r="B19" s="26" t="s">
         <v>66</v>
@@ -2617,7 +2670,7 @@
       </c>
       <c r="M19" s="19"/>
     </row>
-    <row r="20" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19"/>
       <c r="B20" s="26" t="s">
         <v>67</v>
@@ -2644,7 +2697,7 @@
       </c>
       <c r="M20" s="19"/>
     </row>
-    <row r="21" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
       <c r="B21" s="26" t="s">
         <v>68</v>
@@ -2671,7 +2724,7 @@
       </c>
       <c r="M21" s="19"/>
     </row>
-    <row r="22" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19"/>
       <c r="B22" s="26" t="s">
         <v>69</v>
@@ -2698,7 +2751,7 @@
       </c>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19"/>
       <c r="B23" s="26" t="s">
         <v>70</v>
@@ -2725,7 +2778,7 @@
       </c>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19"/>
       <c r="B24" s="26" t="s">
         <v>71</v>
@@ -2752,7 +2805,7 @@
       </c>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19"/>
       <c r="B25" s="26" t="s">
         <v>72</v>
@@ -2779,7 +2832,7 @@
       </c>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19"/>
       <c r="B26" s="33" t="s">
         <v>73</v>
@@ -2821,7 +2874,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19"/>
       <c r="B27" s="33" t="s">
         <v>74</v>
@@ -2854,7 +2907,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19"/>
       <c r="B28" s="33" t="s">
         <v>75</v>
@@ -2884,7 +2937,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19"/>
       <c r="B29" s="33" t="s">
         <v>76</v>
@@ -2914,7 +2967,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19"/>
       <c r="B30" s="33" t="s">
         <v>77</v>
@@ -2944,7 +2997,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19"/>
       <c r="B31" s="33" t="s">
         <v>78</v>
@@ -2971,7 +3024,7 @@
       </c>
       <c r="M31" s="19"/>
     </row>
-    <row r="32" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19"/>
       <c r="B32" s="33" t="s">
         <v>79</v>
@@ -2998,7 +3051,7 @@
       </c>
       <c r="M32" s="19"/>
     </row>
-    <row r="33" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19"/>
       <c r="B33" s="33" t="s">
         <v>80</v>
@@ -3025,7 +3078,7 @@
       </c>
       <c r="M33" s="19"/>
     </row>
-    <row r="34" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19"/>
       <c r="B34" s="40" t="s">
         <v>81</v>
@@ -3052,7 +3105,7 @@
       </c>
       <c r="M34" s="19"/>
     </row>
-    <row r="35" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19"/>
       <c r="B35" s="40" t="s">
         <v>82</v>
@@ -3079,7 +3132,7 @@
       </c>
       <c r="M35" s="19"/>
     </row>
-    <row r="36" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19"/>
       <c r="B36" s="40" t="s">
         <v>83</v>
@@ -3106,7 +3159,7 @@
       </c>
       <c r="M36" s="19"/>
     </row>
-    <row r="37" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19"/>
       <c r="B37" s="40" t="s">
         <v>84</v>
@@ -3133,7 +3186,7 @@
       </c>
       <c r="M37" s="19"/>
     </row>
-    <row r="38" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19"/>
       <c r="B38" s="40" t="s">
         <v>85</v>
@@ -3160,7 +3213,7 @@
       </c>
       <c r="M38" s="19"/>
     </row>
-    <row r="39" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19"/>
       <c r="B39" s="43" t="s">
         <v>86</v>
@@ -3187,7 +3240,7 @@
       </c>
       <c r="M39" s="19"/>
     </row>
-    <row r="40" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19"/>
       <c r="B40" s="43" t="s">
         <v>87</v>
@@ -3237,7 +3290,7 @@
       <c r="J41" s="53"/>
       <c r="K41" s="53"/>
       <c r="L41" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M41" s="19"/>
     </row>
@@ -3291,7 +3344,7 @@
       <c r="J43" s="53"/>
       <c r="K43" s="53"/>
       <c r="L43" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M43" s="19"/>
     </row>
@@ -3345,7 +3398,7 @@
       <c r="J45" s="53"/>
       <c r="K45" s="53"/>
       <c r="L45" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M45" s="19"/>
     </row>
@@ -3372,7 +3425,7 @@
       <c r="J46" s="53"/>
       <c r="K46" s="53"/>
       <c r="L46" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M46" s="19"/>
     </row>
@@ -3399,7 +3452,7 @@
       <c r="J47" s="53"/>
       <c r="K47" s="53"/>
       <c r="L47" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M47" s="19"/>
     </row>
@@ -3426,7 +3479,7 @@
       <c r="J48" s="53"/>
       <c r="K48" s="53"/>
       <c r="L48" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M48" s="19"/>
     </row>
@@ -3453,7 +3506,7 @@
       <c r="J49" s="53"/>
       <c r="K49" s="53"/>
       <c r="L49" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M49" s="19"/>
     </row>
@@ -3480,7 +3533,7 @@
       <c r="J50" s="53"/>
       <c r="K50" s="53"/>
       <c r="L50" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M50" s="19"/>
     </row>
@@ -3534,7 +3587,7 @@
       <c r="J52" s="53"/>
       <c r="K52" s="53"/>
       <c r="L52" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M52" s="19"/>
     </row>
@@ -3561,24 +3614,32 @@
       <c r="J53" s="53"/>
       <c r="K53" s="53"/>
       <c r="L53" s="10" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M53" s="19"/>
     </row>
     <row r="54" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19"/>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="59"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="59"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="47"/>
+      <c r="C54" s="39">
+        <v>46146</v>
+      </c>
+      <c r="D54" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="E54" s="94" t="s">
+        <v>268</v>
+      </c>
+      <c r="F54" s="94"/>
+      <c r="G54" s="94"/>
+      <c r="H54" s="94"/>
+      <c r="I54" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
       <c r="L54" s="10" t="s">
         <v>52</v>
       </c>
@@ -3586,18 +3647,26 @@
     </row>
     <row r="55" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19"/>
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="47"/>
-      <c r="J55" s="47"/>
-      <c r="K55" s="47"/>
+      <c r="C55" s="39">
+        <v>46146</v>
+      </c>
+      <c r="D55" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="E55" s="94" t="s">
+        <v>271</v>
+      </c>
+      <c r="F55" s="94"/>
+      <c r="G55" s="94"/>
+      <c r="H55" s="94"/>
+      <c r="I55" s="94" t="s">
+        <v>272</v>
+      </c>
+      <c r="J55" s="94"/>
+      <c r="K55" s="94"/>
       <c r="L55" s="10" t="s">
         <v>52</v>
       </c>
@@ -3605,18 +3674,26 @@
     </row>
     <row r="56" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19"/>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="59"/>
-      <c r="F56" s="59"/>
-      <c r="G56" s="59"/>
-      <c r="H56" s="59"/>
-      <c r="I56" s="47"/>
-      <c r="J56" s="47"/>
-      <c r="K56" s="47"/>
+      <c r="C56" s="39">
+        <v>46146</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="94" t="s">
+        <v>274</v>
+      </c>
+      <c r="F56" s="94"/>
+      <c r="G56" s="94"/>
+      <c r="H56" s="94"/>
+      <c r="I56" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="J56" s="94"/>
+      <c r="K56" s="94"/>
       <c r="L56" s="10" t="s">
         <v>52</v>
       </c>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F9A0A8-F106-49E9-AC86-7D525B44E433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4404FDD7-2280-47C9-8BFE-CDE1C31DEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="20535" windowHeight="15585" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
@@ -42,7 +42,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -57,20 +57,30 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="353">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1148,6 +1158,319 @@
   </si>
   <si>
     <t>복도에 1분 이상 있을 시 망령이 플레이어를 즉사 시킴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화분에서 물통을 획득할려고 시도 할 시 획득이 불가능한 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화분에서 물통을 정상적으로 획득하게 변경될 에정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세면대에서 물통을 스냅시킬 경우 세면대 패널이 꺼져버리고 물통하고 수도꼭지만 붕 떠 있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세면대에 패널을 물통을 스냅시켜도 정상적으로 유지되게 수정 될 에정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복도 화분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화분을 클릭 한 후 물통을 얻기 전에 기존에 있던 지도 위치를 클릭 시 지도가 활성되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용 중인 상태에서 다른 기능 작동하지 않게 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인으로 돌아가기 버튼 클릭 시 설정에 모든 버튼이 사용 불가능하게 변경되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정 화면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인으로 돌아가기 버튼 누를 시 정상적으로 메인화면으로 돌아가게 수정하고 버튼이 정상적으로 작동하게 수정 될 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동 세이브가 되어 망령에서 당할 경우 정상적으로 가정부 방으로 돌아오지만 당하기 이전에 획득한 모든 아이템이 삭제되고 재 획득 불가능한 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동 세이브가 된 시점에서 현재가 획득 중인 아이템이나 그 이후 획득한 아이템을 계속 가지고 있게 유지하거나 혹은 아이템을 재 획득할 수 있게 수정 될 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템이 모두 삭제된 이후 재 획득을 위해 서랍을 클릭 시 투명한 패널이 작동하여 모든 화면을 가려 정상적인 플레이가 어려워지는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윗 내용과 연동하여 재 획득이 가능할 경우 서랍에 패널이 정상적으로 작동하게 수정될 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤로 돌아가기 플로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 가정부 방과 서재 방에 갈 때 일방통행만 가능한 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방에서 재입장 용도로 지도를 사용 시 이전 기록 재입장한 방이 되어서 버려서 이전으로 돌아가기가 정상적인 작동이 불가능해지는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방에서는 지도를 사용하지 못하도록 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대사창</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대사창이 나온 상태로 다른 상호작용 시 클릭이 지연되는 현상이 발생함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대사 창이 나올 시 다른 상호작용은 못하도록 수정 될 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방에 있는 어떠한 오브젝트라도 한 번이라도 클릭 한 이후에 종료하면 체셔 이외에는 아무것도 클릭이 안되는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭 이후 종료 하여도 다른 오브젝트도 정상적으로 동작 할 수 있게 수정할 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">클릭 오류 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 클릭이 오류나는 곳은 2층 전체와 지하실 다 오류나는 상태고 서재는 종이 문서에만 콜리전 빠져있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2층전체와 지하실에 모든 클릭 스크립트를 최신화 및 서재에 종이 문서에 콜리전을 추가 할 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방에서 체셔의 먹이를 굽기 위해 프라이팬을 클릭해도 반응이 없는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프라이팬으로 먹이를 구울 수 있게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책에 닫기 버튼이 아직 화면 밖에 있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책에서 힌트 기물 획득 후 뒤에 있는 책과 서랍장 클릭되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책에서 완전히 나가기 전까지 뒤에 있는 오브젝트 클릭 금지 상태로 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책에 닫기 버튼을 화면 안에 보이게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서재 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서류 문서에 아직 콜리전이 추가가 안되어 있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콜리전을 추가해서 오브젝트 기능이 사용 가능하게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서재에 있는 책을 연 상태에서 그 아래에 있는 이동 버튼이 클릭 가능한 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서재에 책을 열람 중인 상태일때 그 아래에 있는 버튼이 클릭되지 않게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2층에서 지도를 열람 시 아래로 내려가기 버튼이 위로 올라가기 버튼으로 변경되어 있는 상태 ( 조건: 1층에서 2층 올라갈 때 가기 직전에 지도를 펼쳐 본 후 버튼이 올라가기가 되어 있는 상태에서 2층 올라갈 시 버튼이 그대로 유지되어 있는 상태 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도 열람 시 버튼이 올바르게 배치되어 있게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방에 첫 입장 후 지도를 클릭 시 아래에 시계도 같이 클릭되는 현상 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아내 방에서 시계를 클릭 시 대사가 출력되고 지도/ 뒤로가기 이외에 클릭이 전혀 안되는 상태 발생
+첫 입장 -&gt; 지도 클릭 -&gt; 시계 대사창 발생 -&gt; 다른 오브젝트 클릭이 가능한 상태
+첫 입장 -&gt; 시계 클릭 -&gt; 시계 대사창 발생 -&gt; 다른 오브젝트 클릭 불가능 상태 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대사가 출력이 되어도 다른 오브젝트들이 정상적으로 클릭 할 수 있게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도를 클릭 할 때 아래에 있는 시계가 눌리지 않게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI ( 이전 공간 이동 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤로 가기 버튼을 누를 때 밑에 대사 창을 출력 시키는 오브젝트가 있을 시 무조건 대사 창 발생 ( 2층 왼쪽 복도에서 다시 2층 메인으로 돌아갈 때 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤로가기 버튼 밑에 있는 오브젝트가 클릭되지 않게 수정 ( 콜리전 위치변경? )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하실 열쇠 넣는 곳에 닫기 버튼의 위치 조정이 필요해보임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금은 단순하게 열쇠 넣는 곳 바로 옆에 있는 상태 다른 오브젝트와 동일하게 왼쪽 맨 위에 있게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 감옥에서 철창을 클릭해서 나가기가 안되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철창을 클릭하면 감옥을 다시 나갈 수 있게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인화면으로 나간 다음에 이어하기 할 경우 안방에 책장이 사라지는 현상 발생 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이어하기를 진행하여도 책장이 그대로 있게 수정 ( 지금은 이어하기 굳이 필요한가? )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71번과 동일한 수정 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열쇠를 획득 이후 서랍장을 클릭할 시 동일하게 오브젝트 클릭이 안되는 현상 (71번 현상과 거의 동일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택지 UI 변경 및 내용 정렬하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단순한 선택에 글자 정렬이 안되어 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 관련해서 설명이 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리에 관해서는 최초로 아이템을 획득할 경우 or 
+최초 아이템에 커서를 가져다가 될 경우 안내문 같은 글자를 띄우면서 
+" Tap 키를 누르는 것으로 아이템을 확인할 수 있습니다. " 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2층 복도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2층 복도 버튼에 위치와 크기가 정 가운데에서 아이콘이 조금 거대한 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1층과 동일하게 크기와 위치를 수정할 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아들 방 - 육망성을 기준으로 기물을 넣고 가운데 까지 다 채울 시 가운데 물품이 서서히 사라지고 
+열쇠하고 나무조각이 천천히 나타나게 변경 ( 침대는 배제 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템을 특정 위치에 지정하여 일관성 없이 지정되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체셔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 위치에 상관없이 뒷 패널의 모양이 모두 똑같은 패널이 발생함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 위치에 따라서 패널을 조정하도록 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 씬으로만 돌아가게 되어 있어서 이동에 불편함이 매우 강한 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동방식을 대폭 변경하여 돌아가는 버튼은 방에서만 사용가능하도록 수정하고 또한 복도 이동방식은 일방통행으로 고정함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭 관련되서 지속적으로 발생하는 문제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아내 방, 공부 방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭문제를 해결하고 추가적으로 이미 미션 혹은 자물쇠를 푼 이후일 경우에 아내 방은 이미 열쇠를 회득했다고 나오지만 공부방에는 없어서 내용을 추가 바람 ( 체셔가 "너는 이미 문제를 풀었어" )라는 형식의 메시지를 출력함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1418,7 +1741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1450,234 +1773,195 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1699,12 +1983,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1756,8 +2034,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDAE9F8"/>
       <color rgb="FFFBE2D5"/>
-      <color rgb="FFDAE9F8"/>
       <color rgb="FFFFCC66"/>
       <color rgb="FFFF5050"/>
       <color rgb="FF99FF99"/>
@@ -1817,13 +2095,17 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
     <v>0</v>
     <v>5</v>
   </rv>
   <rv s="0">
     <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1842,6 +2124,7 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -2166,52 +2449,52 @@
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.75" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="33.625" style="17" customWidth="1"/>
-    <col min="5" max="7" width="15.625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="30.625" style="18" customWidth="1"/>
-    <col min="12" max="12" width="18" style="24" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="33.625" style="16" customWidth="1"/>
+    <col min="5" max="7" width="15.625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="30.625" style="17" customWidth="1"/>
+    <col min="12" max="12" width="18" style="21" customWidth="1"/>
     <col min="13" max="13" width="44.875" customWidth="1"/>
     <col min="20" max="21" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -2220,17 +2503,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76" t="s">
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -2238,768 +2521,768 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="204.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="26" t="s">
+    <row r="4" spans="1:13" ht="204.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30"/>
+      <c r="B4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="22">
         <v>46088</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="E4" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75" t="s">
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="10" t="s">
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M4" s="8"/>
-    </row>
-    <row r="5" spans="1:13" ht="173.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="26" t="s">
+      <c r="M4" s="31"/>
+    </row>
+    <row r="5" spans="1:13" ht="173.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
+      <c r="B5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="22">
         <v>46088</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75" t="s">
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="10" t="s">
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M5" s="8"/>
-    </row>
-    <row r="6" spans="1:13" ht="258.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="26" t="s">
+      <c r="M5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" ht="258.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31"/>
+      <c r="B6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="22">
         <v>46090</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="75" t="s">
+      <c r="E6" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75" t="s">
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="10" t="s">
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M6" s="8"/>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="26" t="s">
+      <c r="M6" s="31"/>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="22">
         <v>46090</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="75" t="s">
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="10" t="s">
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" ht="121.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="26" t="s">
+      <c r="M7" s="31"/>
+    </row>
+    <row r="8" spans="1:13" ht="121.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31"/>
+      <c r="B8" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="22">
         <v>46092</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="75" t="s">
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="10" t="s">
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="1:13" ht="123.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="26" t="s">
+      <c r="M8" s="31"/>
+    </row>
+    <row r="9" spans="1:13" ht="123.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="31"/>
+      <c r="B9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="22">
         <v>46092</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="75" t="s">
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="10" t="s">
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="26" t="s">
+      <c r="M9" s="31"/>
+    </row>
+    <row r="10" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="B10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="22">
         <v>46095</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="75" t="s">
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="10" t="s">
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="26" t="s">
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31"/>
+      <c r="B11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="22">
         <v>46095</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75" t="s">
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="75"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="10" t="s">
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="26" t="s">
+      <c r="M11" s="31"/>
+    </row>
+    <row r="12" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="31"/>
+      <c r="B12" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="22">
         <v>46096</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75" t="s">
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="75"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="10" t="s">
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="8"/>
-    </row>
-    <row r="13" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="26" t="s">
+      <c r="M12" s="31"/>
+    </row>
+    <row r="13" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="22">
         <v>46096</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75" t="s">
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M13" s="8"/>
-    </row>
-    <row r="14" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="26" t="s">
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="31"/>
+    </row>
+    <row r="14" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <v>46098</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75" t="s">
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="75"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="10" t="s">
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="26" t="s">
+      <c r="M14" s="31"/>
+    </row>
+    <row r="15" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31"/>
+      <c r="B15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="33">
         <v>46103</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75" t="s">
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="10" t="s">
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:13" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="26" t="s">
+      <c r="M15" s="31"/>
+    </row>
+    <row r="16" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="B16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <v>46103</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75" t="s">
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="10" t="s">
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row r="17" spans="1:21" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="26" t="s">
+      <c r="M16" s="31"/>
+    </row>
+    <row r="17" spans="1:21" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31"/>
+      <c r="B17" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <v>46103</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75" t="s">
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="75"/>
-      <c r="K17" s="75"/>
-      <c r="L17" s="10" t="s">
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M17" s="8"/>
-    </row>
-    <row r="18" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="26" t="s">
+      <c r="M17" s="31"/>
+    </row>
+    <row r="18" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <v>46107</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75" t="s">
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="75"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="10" t="s">
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M18" s="19"/>
-    </row>
-    <row r="19" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="26" t="s">
+      <c r="M18" s="10"/>
+    </row>
+    <row r="19" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="33">
         <v>46107</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="67" t="s">
+      <c r="E19" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="69" t="s">
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19" s="19"/>
-    </row>
-    <row r="20" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="26" t="s">
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="33">
         <v>46107</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="67" t="s">
+      <c r="E20" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="69" t="s">
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="26" t="s">
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="10"/>
+    </row>
+    <row r="21" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>46107</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="67" t="s">
+      <c r="E21" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="69" t="s">
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="10" t="s">
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="26" t="s">
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>46113</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="67" t="s">
+      <c r="E22" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="69" t="s">
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="10" t="s">
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M22" s="19"/>
-    </row>
-    <row r="23" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="26" t="s">
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="33">
         <v>46117</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="67" t="s">
+      <c r="E23" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="69" t="s">
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M23" s="19"/>
-    </row>
-    <row r="24" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="26" t="s">
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>46117</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="E24" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="69" t="s">
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M24" s="19"/>
-    </row>
-    <row r="25" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="26" t="s">
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>46117</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="69" t="s">
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M25" s="19"/>
-    </row>
-    <row r="26" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="33" t="s">
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="35">
         <v>46120</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68" t="s">
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="68"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="10" t="s">
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="19"/>
-      <c r="P26" s="36" t="s">
+      <c r="M26" s="10"/>
+      <c r="P26" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="Q26" s="42" t="s">
+      <c r="Q26" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="S26" s="18" t="s">
+      <c r="S26" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="T26" s="18" t="s">
+      <c r="T26" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="U26" s="18" t="s">
+      <c r="U26" s="17" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="33" t="s">
+    <row r="27" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>46120</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="71" t="s">
+      <c r="E27" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="48" t="s">
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="49"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="10" t="s">
+      <c r="J27" s="51"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="M27" s="19"/>
-      <c r="T27" s="18" t="s">
+      <c r="M27" s="10"/>
+      <c r="T27" s="17" t="s">
         <v>207</v>
       </c>
       <c r="U27" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="33" t="s">
+    <row r="28" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>46120</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="71" t="s">
+      <c r="E28" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="48" t="s">
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="49"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M28" s="19"/>
-      <c r="T28" s="18" t="s">
+      <c r="J28" s="51"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="10"/>
+      <c r="T28" s="17" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="33" t="s">
+    <row r="29" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="35">
         <v>46120</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="71" t="s">
+      <c r="E29" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="48" t="s">
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M29" s="19"/>
-      <c r="T29" s="18" t="s">
+      <c r="J29" s="51"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="T29" s="17" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="33" t="s">
+    <row r="30" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>46121</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="68" t="s">
+      <c r="E30" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="51" t="s">
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M30" s="19"/>
-      <c r="T30" s="18" t="s">
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="10"/>
+      <c r="T30" s="17" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="33" t="s">
+    <row r="31" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10"/>
+      <c r="B31" s="34" t="s">
         <v>78</v>
       </c>
       <c r="C31" s="37">
@@ -3008,25 +3291,25 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="70" t="s">
+      <c r="E31" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="52" t="s">
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M31" s="19"/>
-    </row>
-    <row r="32" spans="1:21" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
-      <c r="B32" s="33" t="s">
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="10"/>
+    </row>
+    <row r="32" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="34" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="37">
@@ -3035,25 +3318,25 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="70" t="s">
+      <c r="E32" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="52" t="s">
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M32" s="19"/>
-    </row>
-    <row r="33" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="33" t="s">
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="10"/>
+    </row>
+    <row r="33" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="34" t="s">
         <v>80</v>
       </c>
       <c r="C33" s="39">
@@ -3062,1504 +3345,1729 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="70" t="s">
+      <c r="E33" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="52" t="s">
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M33" s="19"/>
-    </row>
-    <row r="34" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="10"/>
+    </row>
+    <row r="34" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
       <c r="B34" s="40" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="39">
         <v>46123</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="61" t="s">
+      <c r="E34" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="58" t="s">
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="56"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M34" s="19"/>
-    </row>
-    <row r="35" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="10"/>
+    </row>
+    <row r="35" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10"/>
       <c r="B35" s="40" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="39">
         <v>46123</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="61" t="s">
+      <c r="E35" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="55" t="s">
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="55"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M35" s="19"/>
-    </row>
-    <row r="36" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="19"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M35" s="10"/>
+    </row>
+    <row r="36" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10"/>
       <c r="B36" s="40" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="39">
         <v>46126</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="55" t="s">
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M36" s="19"/>
-    </row>
-    <row r="37" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M36" s="10"/>
+    </row>
+    <row r="37" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10"/>
       <c r="B37" s="40" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="39">
         <v>46127</v>
       </c>
-      <c r="D37" s="41" t="s">
+      <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="64" t="s">
+      <c r="E37" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="55" t="s">
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="46" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M37" s="19"/>
-    </row>
-    <row r="38" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="10"/>
+    </row>
+    <row r="38" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
       <c r="B38" s="40" t="s">
         <v>85</v>
       </c>
       <c r="C38" s="39">
         <v>46127</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="55" t="s">
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="56"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M38" s="19"/>
-    </row>
-    <row r="39" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="43" t="s">
+      <c r="J38" s="48"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="10"/>
+    </row>
+    <row r="39" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="42">
         <v>46130</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="54" t="s">
+      <c r="E39" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="53" t="s">
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M39" s="19"/>
-    </row>
-    <row r="40" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19"/>
-      <c r="B40" s="43" t="s">
+      <c r="J39" s="47"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M39" s="10"/>
+    </row>
+    <row r="40" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="42">
         <v>46140</v>
       </c>
-      <c r="D40" s="45" t="s">
+      <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="54" t="s">
+      <c r="E40" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="54"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="53" t="s">
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M40" s="19"/>
-    </row>
-    <row r="41" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="43" t="s">
+      <c r="J40" s="47"/>
+      <c r="K40" s="47"/>
+      <c r="L40" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M40" s="10"/>
+    </row>
+    <row r="41" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="44">
+      <c r="C41" s="42">
         <v>46140</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="54" t="s">
+      <c r="E41" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="53" t="s">
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M41" s="19"/>
-    </row>
-    <row r="42" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
-      <c r="B42" s="43" t="s">
+      <c r="J41" s="47"/>
+      <c r="K41" s="47"/>
+      <c r="L41" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="10"/>
+    </row>
+    <row r="42" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="44">
+      <c r="C42" s="42">
         <v>46140</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="54" t="s">
+      <c r="E42" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="53" t="s">
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="53"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M42" s="19"/>
-    </row>
-    <row r="43" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="43" t="s">
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M42" s="10"/>
+    </row>
+    <row r="43" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="42">
         <v>46140</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="54" t="s">
+      <c r="E43" s="47" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="54"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="54" t="s">
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M43" s="19"/>
-    </row>
-    <row r="44" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="43" t="s">
+      <c r="J43" s="47"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M43" s="10"/>
+    </row>
+    <row r="44" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="44">
+      <c r="C44" s="42">
         <v>46140</v>
       </c>
-      <c r="D44" s="45" t="s">
+      <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="54" t="s">
+      <c r="E44" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="54"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="53" t="s">
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M44" s="19"/>
-    </row>
-    <row r="45" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="43" t="s">
+      <c r="J44" s="47"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="10"/>
+    </row>
+    <row r="45" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="44">
+      <c r="C45" s="42">
         <v>46140</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="54" t="s">
+      <c r="E45" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="53" t="s">
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="53"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M45" s="19"/>
-    </row>
-    <row r="46" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="43" t="s">
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="10"/>
+    </row>
+    <row r="46" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="42">
         <v>46140</v>
       </c>
-      <c r="D46" s="45" t="s">
+      <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="54" t="s">
+      <c r="E46" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="53" t="s">
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="53"/>
-      <c r="K46" s="53"/>
-      <c r="L46" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M46" s="19"/>
-    </row>
-    <row r="47" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="43" t="s">
+      <c r="J46" s="47"/>
+      <c r="K46" s="47"/>
+      <c r="L46" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M46" s="10"/>
+    </row>
+    <row r="47" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="10"/>
+      <c r="B47" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="44">
+      <c r="C47" s="42">
         <v>46140</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="54" t="s">
+      <c r="E47" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="53" t="s">
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M47" s="19"/>
-    </row>
-    <row r="48" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
-      <c r="B48" s="43" t="s">
+      <c r="J47" s="47"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" s="10"/>
+    </row>
+    <row r="48" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="44">
+      <c r="C48" s="42">
         <v>46140</v>
       </c>
-      <c r="D48" s="45" t="s">
+      <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="54" t="s">
+      <c r="E48" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="53" t="s">
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M48" s="19"/>
-    </row>
-    <row r="49" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="43" t="s">
+      <c r="J48" s="47"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M48" s="10"/>
+    </row>
+    <row r="49" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="44">
+      <c r="C49" s="42">
         <v>46140</v>
       </c>
-      <c r="D49" s="45" t="s">
+      <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="54" t="s">
+      <c r="E49" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="53" t="s">
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M49" s="19"/>
-    </row>
-    <row r="50" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="19"/>
-      <c r="B50" s="43" t="s">
+      <c r="J49" s="47"/>
+      <c r="K49" s="47"/>
+      <c r="L49" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M49" s="10"/>
+    </row>
+    <row r="50" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="44">
+      <c r="C50" s="42">
         <v>46140</v>
       </c>
-      <c r="D50" s="45" t="s">
+      <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="54" t="s">
+      <c r="E50" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="53" t="s">
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M50" s="19"/>
-    </row>
-    <row r="51" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="43" t="s">
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M50" s="10"/>
+    </row>
+    <row r="51" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="10"/>
+      <c r="B51" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="44">
+      <c r="C51" s="42">
         <v>46140</v>
       </c>
-      <c r="D51" s="45" t="s">
+      <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="54" t="s">
+      <c r="E51" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="53" t="s">
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M51" s="19"/>
-    </row>
-    <row r="52" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="19"/>
-      <c r="B52" s="43" t="s">
+      <c r="J51" s="47"/>
+      <c r="K51" s="47"/>
+      <c r="L51" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M51" s="10"/>
+    </row>
+    <row r="52" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="10"/>
+      <c r="B52" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="44">
+      <c r="C52" s="42">
         <v>46140</v>
       </c>
-      <c r="D52" s="46" t="s">
+      <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="54" t="s">
+      <c r="E52" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="53" t="s">
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M52" s="19"/>
-    </row>
-    <row r="53" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="43" t="s">
+      <c r="J52" s="47"/>
+      <c r="K52" s="47"/>
+      <c r="L52" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M52" s="10"/>
+    </row>
+    <row r="53" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="10"/>
+      <c r="B53" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="44">
+      <c r="C53" s="42">
         <v>46140</v>
       </c>
-      <c r="D53" s="45" t="s">
+      <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="54" t="s">
+      <c r="E53" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="54"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="54"/>
-      <c r="I53" s="53" t="s">
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M53" s="19"/>
-    </row>
-    <row r="54" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="19"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="47"/>
+      <c r="L53" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M53" s="10"/>
+    </row>
+    <row r="54" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10"/>
       <c r="B54" s="40" t="s">
         <v>101</v>
       </c>
       <c r="C54" s="39">
         <v>46146</v>
       </c>
-      <c r="D54" s="41" t="s">
+      <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="94" t="s">
+      <c r="E54" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="94"/>
-      <c r="G54" s="94"/>
-      <c r="H54" s="94"/>
-      <c r="I54" s="55" t="s">
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="55"/>
-      <c r="K54" s="55"/>
-      <c r="L54" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M54" s="19"/>
-    </row>
-    <row r="55" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M54" s="10"/>
+    </row>
+    <row r="55" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="10"/>
       <c r="B55" s="40" t="s">
         <v>102</v>
       </c>
       <c r="C55" s="39">
         <v>46146</v>
       </c>
-      <c r="D55" s="95" t="s">
+      <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="94" t="s">
+      <c r="E55" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="94"/>
-      <c r="G55" s="94"/>
-      <c r="H55" s="94"/>
-      <c r="I55" s="94" t="s">
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="94"/>
-      <c r="K55" s="94"/>
-      <c r="L55" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M55" s="19"/>
-    </row>
-    <row r="56" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="19"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55" s="10"/>
+    </row>
+    <row r="56" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="10"/>
       <c r="B56" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C56" s="39">
         <v>46146</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="94" t="s">
+      <c r="E56" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="94"/>
-      <c r="G56" s="94"/>
-      <c r="H56" s="94"/>
-      <c r="I56" s="94" t="s">
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="94"/>
-      <c r="K56" s="94"/>
-      <c r="L56" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M56" s="19"/>
-    </row>
-    <row r="57" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="20" t="s">
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
+      <c r="L56" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M56" s="10"/>
+    </row>
+    <row r="57" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="10"/>
+      <c r="B57" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="59"/>
-      <c r="F57" s="59"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="47"/>
+      <c r="C57" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="E57" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47" t="s">
+        <v>277</v>
+      </c>
       <c r="J57" s="47"/>
       <c r="K57" s="47"/>
-      <c r="L57" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M57" s="19"/>
-    </row>
-    <row r="58" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="19"/>
-      <c r="B58" s="20" t="s">
+      <c r="L57" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M57" s="10"/>
+    </row>
+    <row r="58" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10"/>
+      <c r="B58" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="59"/>
-      <c r="F58" s="59"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="47"/>
+      <c r="C58" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="47"/>
+      <c r="I58" s="47" t="s">
+        <v>282</v>
+      </c>
       <c r="J58" s="47"/>
       <c r="K58" s="47"/>
-      <c r="L58" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M58" s="19"/>
-    </row>
-    <row r="59" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="20" t="s">
+      <c r="L58" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M58" s="10"/>
+    </row>
+    <row r="59" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="10"/>
+      <c r="B59" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="59"/>
-      <c r="F59" s="59"/>
-      <c r="G59" s="59"/>
-      <c r="H59" s="59"/>
-      <c r="I59" s="47"/>
+      <c r="C59" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47"/>
+      <c r="H59" s="47"/>
+      <c r="I59" s="47" t="s">
+        <v>279</v>
+      </c>
       <c r="J59" s="47"/>
       <c r="K59" s="47"/>
-      <c r="L59" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M59" s="19"/>
-    </row>
-    <row r="60" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="19"/>
-      <c r="B60" s="20" t="s">
+      <c r="L59" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M59" s="10"/>
+    </row>
+    <row r="60" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="10"/>
+      <c r="B60" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="59"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="47"/>
+      <c r="C60" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D60" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47" t="s">
+        <v>285</v>
+      </c>
       <c r="J60" s="47"/>
       <c r="K60" s="47"/>
-      <c r="L60" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M60" s="19"/>
-    </row>
-    <row r="61" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="20" t="s">
+      <c r="L60" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M60" s="10"/>
+    </row>
+    <row r="61" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="10"/>
+      <c r="B61" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="47"/>
+      <c r="C61" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E61" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="47" t="s">
+        <v>287</v>
+      </c>
       <c r="J61" s="47"/>
       <c r="K61" s="47"/>
-      <c r="L61" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M61" s="19"/>
-    </row>
-    <row r="62" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="19"/>
-      <c r="B62" s="20" t="s">
+      <c r="L61" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M61" s="10"/>
+    </row>
+    <row r="62" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="10"/>
+      <c r="B62" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="59"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="47"/>
+      <c r="C62" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="47" t="s">
+        <v>289</v>
+      </c>
       <c r="J62" s="47"/>
       <c r="K62" s="47"/>
-      <c r="L62" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M62" s="19"/>
-    </row>
-    <row r="63" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
-      <c r="B63" s="20" t="s">
+      <c r="L62" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M62" s="10"/>
+    </row>
+    <row r="63" spans="1:13" s="17" customFormat="1" ht="240" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="10"/>
+      <c r="B63" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="59"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="47"/>
+      <c r="C63" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D63" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="E63" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="F63" s="47"/>
+      <c r="G63" s="47"/>
+      <c r="H63" s="47"/>
+      <c r="I63" s="47" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="J63" s="47"/>
       <c r="K63" s="47"/>
-      <c r="L63" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M63" s="19"/>
-    </row>
-    <row r="64" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="19"/>
-      <c r="B64" s="20" t="s">
+      <c r="L63" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M63" s="10"/>
+    </row>
+    <row r="64" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="10"/>
+      <c r="B64" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="47"/>
+      <c r="C64" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D64" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="F64" s="47"/>
+      <c r="G64" s="47"/>
+      <c r="H64" s="47"/>
+      <c r="I64" s="47" t="s">
+        <v>294</v>
+      </c>
       <c r="J64" s="47"/>
       <c r="K64" s="47"/>
-      <c r="L64" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M64" s="19"/>
-    </row>
-    <row r="65" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="19"/>
-      <c r="B65" s="20" t="s">
+      <c r="L64" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M64" s="10"/>
+    </row>
+    <row r="65" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="10"/>
+      <c r="B65" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="59"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="47"/>
+      <c r="C65" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D65" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E65" s="47" t="s">
+        <v>296</v>
+      </c>
+      <c r="F65" s="47"/>
+      <c r="G65" s="47"/>
+      <c r="H65" s="47"/>
+      <c r="I65" s="47" t="s">
+        <v>297</v>
+      </c>
       <c r="J65" s="47"/>
       <c r="K65" s="47"/>
-      <c r="L65" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M65" s="19"/>
-    </row>
-    <row r="66" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="19"/>
-      <c r="B66" s="20" t="s">
+      <c r="L65" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M65" s="10"/>
+    </row>
+    <row r="66" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="10"/>
+      <c r="B66" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="47"/>
+      <c r="C66" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D66" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>298</v>
+      </c>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="47"/>
+      <c r="I66" s="47" t="s">
+        <v>299</v>
+      </c>
       <c r="J66" s="47"/>
       <c r="K66" s="47"/>
-      <c r="L66" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M66" s="19"/>
-    </row>
-    <row r="67" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="19"/>
-      <c r="B67" s="20" t="s">
+      <c r="L66" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M66" s="10"/>
+    </row>
+    <row r="67" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="10"/>
+      <c r="B67" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="47"/>
+      <c r="C67" s="42">
+        <v>46161</v>
+      </c>
+      <c r="D67" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="E67" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="F67" s="55"/>
+      <c r="G67" s="55"/>
+      <c r="H67" s="55"/>
+      <c r="I67" s="47" t="s">
+        <v>302</v>
+      </c>
       <c r="J67" s="47"/>
       <c r="K67" s="47"/>
-      <c r="L67" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M67" s="19"/>
-    </row>
-    <row r="68" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="19"/>
-      <c r="B68" s="20" t="s">
+      <c r="L67" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M67" s="10"/>
+    </row>
+    <row r="68" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="10"/>
+      <c r="B68" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="59"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="47"/>
-      <c r="J68" s="47"/>
-      <c r="K68" s="47"/>
-      <c r="L68" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M68" s="19"/>
-    </row>
-    <row r="69" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="19"/>
-      <c r="B69" s="20" t="s">
+      <c r="C68" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E68" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="F68" s="46"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="J68" s="46"/>
+      <c r="K68" s="46"/>
+      <c r="L68" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M68" s="10"/>
+    </row>
+    <row r="69" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="10"/>
+      <c r="B69" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="47"/>
-      <c r="J69" s="47"/>
-      <c r="K69" s="47"/>
-      <c r="L69" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M69" s="19"/>
-    </row>
-    <row r="70" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="19"/>
-      <c r="B70" s="20" t="s">
+      <c r="C69" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="E69" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="46"/>
+      <c r="I69" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="J69" s="46"/>
+      <c r="K69" s="46"/>
+      <c r="L69" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M69" s="10"/>
+    </row>
+    <row r="70" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="10"/>
+      <c r="B70" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="59"/>
-      <c r="F70" s="59"/>
-      <c r="G70" s="59"/>
-      <c r="H70" s="59"/>
-      <c r="I70" s="47"/>
-      <c r="J70" s="47"/>
-      <c r="K70" s="47"/>
-      <c r="L70" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M70" s="19"/>
-    </row>
-    <row r="71" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="19"/>
-      <c r="B71" s="20" t="s">
+      <c r="C70" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="E70" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="J70" s="46"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M70" s="10"/>
+    </row>
+    <row r="71" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="10"/>
+      <c r="B71" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="59"/>
-      <c r="F71" s="59"/>
-      <c r="G71" s="59"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="47"/>
-      <c r="J71" s="47"/>
-      <c r="K71" s="47"/>
-      <c r="L71" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M71" s="19"/>
-    </row>
-    <row r="72" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="19"/>
-      <c r="B72" s="20" t="s">
+      <c r="C71" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D71" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M71" s="10"/>
+    </row>
+    <row r="72" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="10"/>
+      <c r="B72" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="59"/>
-      <c r="F72" s="59"/>
-      <c r="G72" s="59"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="47"/>
-      <c r="J72" s="47"/>
-      <c r="K72" s="47"/>
-      <c r="L72" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M72" s="19"/>
-    </row>
-    <row r="73" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="19"/>
-      <c r="B73" s="20" t="s">
+      <c r="C72" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="E72" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="J72" s="46"/>
+      <c r="K72" s="46"/>
+      <c r="L72" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M72" s="10"/>
+    </row>
+    <row r="73" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="10"/>
+      <c r="B73" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="59"/>
-      <c r="F73" s="59"/>
-      <c r="G73" s="59"/>
-      <c r="H73" s="59"/>
-      <c r="I73" s="47"/>
-      <c r="J73" s="47"/>
-      <c r="K73" s="47"/>
-      <c r="L73" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M73" s="19"/>
-    </row>
-    <row r="74" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="19"/>
-      <c r="B74" s="20" t="s">
+      <c r="C73" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="E73" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="F73" s="46"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="J73" s="46"/>
+      <c r="K73" s="46"/>
+      <c r="L73" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M73" s="10"/>
+    </row>
+    <row r="74" spans="1:13" s="17" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="10"/>
+      <c r="B74" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="59"/>
-      <c r="F74" s="59"/>
-      <c r="G74" s="59"/>
-      <c r="H74" s="59"/>
-      <c r="I74" s="47"/>
-      <c r="J74" s="47"/>
-      <c r="K74" s="47"/>
-      <c r="L74" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M74" s="19"/>
-    </row>
-    <row r="75" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20" t="s">
+      <c r="C74" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="E74" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="F74" s="46"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="J74" s="46"/>
+      <c r="K74" s="46"/>
+      <c r="L74" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M74" s="10"/>
+    </row>
+    <row r="75" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="10"/>
+      <c r="B75" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="59"/>
-      <c r="F75" s="59"/>
-      <c r="G75" s="59"/>
-      <c r="H75" s="59"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="47"/>
-      <c r="K75" s="47"/>
-      <c r="L75" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M75" s="19"/>
-    </row>
-    <row r="76" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="19"/>
-      <c r="B76" s="20" t="s">
+      <c r="C75" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D75" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="E75" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
+      <c r="I75" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="J75" s="46"/>
+      <c r="K75" s="46"/>
+      <c r="L75" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M75" s="10"/>
+    </row>
+    <row r="76" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="10"/>
+      <c r="B76" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="59"/>
-      <c r="F76" s="59"/>
-      <c r="G76" s="59"/>
-      <c r="H76" s="59"/>
-      <c r="I76" s="47"/>
-      <c r="J76" s="47"/>
-      <c r="K76" s="47"/>
-      <c r="L76" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M76" s="19"/>
-    </row>
-    <row r="77" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="19"/>
-      <c r="B77" s="20" t="s">
+      <c r="C76" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D76" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="46" t="s">
+        <v>332</v>
+      </c>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M76" s="10"/>
+    </row>
+    <row r="77" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="10"/>
+      <c r="B77" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="59"/>
-      <c r="F77" s="59"/>
-      <c r="G77" s="59"/>
-      <c r="H77" s="59"/>
-      <c r="I77" s="47"/>
-      <c r="J77" s="47"/>
-      <c r="K77" s="47"/>
-      <c r="L77" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M77" s="19"/>
-    </row>
-    <row r="78" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="19"/>
-      <c r="B78" s="20" t="s">
+      <c r="C77" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D77" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="F77" s="46"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="46"/>
+      <c r="I77" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="J77" s="46"/>
+      <c r="K77" s="46"/>
+      <c r="L77" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M77" s="10"/>
+    </row>
+    <row r="78" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="10"/>
+      <c r="B78" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="59"/>
-      <c r="F78" s="59"/>
-      <c r="G78" s="59"/>
-      <c r="H78" s="59"/>
-      <c r="I78" s="47"/>
-      <c r="J78" s="47"/>
-      <c r="K78" s="47"/>
-      <c r="L78" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M78" s="19"/>
-    </row>
-    <row r="79" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="19"/>
-      <c r="B79" s="20" t="s">
+      <c r="C78" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D78" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="F78" s="46"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="46"/>
+      <c r="I78" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
+      <c r="L78" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M78" s="10"/>
+    </row>
+    <row r="79" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="10"/>
+      <c r="B79" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="59"/>
-      <c r="F79" s="59"/>
-      <c r="G79" s="59"/>
-      <c r="H79" s="59"/>
-      <c r="I79" s="47"/>
-      <c r="J79" s="47"/>
-      <c r="K79" s="47"/>
-      <c r="L79" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M79" s="19"/>
-    </row>
-    <row r="80" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="19"/>
-      <c r="B80" s="20" t="s">
+      <c r="C79" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="E79" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M79" s="10"/>
+    </row>
+    <row r="80" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="10"/>
+      <c r="B80" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="59"/>
-      <c r="F80" s="59"/>
-      <c r="G80" s="59"/>
-      <c r="H80" s="59"/>
-      <c r="I80" s="47"/>
-      <c r="J80" s="47"/>
-      <c r="K80" s="47"/>
-      <c r="L80" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M80" s="19"/>
-    </row>
-    <row r="81" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="19"/>
-      <c r="B81" s="20" t="s">
+      <c r="C80" s="39">
+        <v>46163</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="E80" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="F80" s="46"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
+      <c r="L80" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M80" s="10"/>
+    </row>
+    <row r="81" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="10"/>
+      <c r="B81" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="59"/>
-      <c r="F81" s="59"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="47"/>
+      <c r="C81" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D81" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="E81" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="F81" s="47"/>
+      <c r="G81" s="47"/>
+      <c r="H81" s="47"/>
+      <c r="I81" s="47" t="s">
+        <v>335</v>
+      </c>
       <c r="J81" s="47"/>
       <c r="K81" s="47"/>
-      <c r="L81" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M81" s="19"/>
-    </row>
-    <row r="82" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="19"/>
-      <c r="B82" s="20" t="s">
+      <c r="L81" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M81" s="10"/>
+    </row>
+    <row r="82" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="10"/>
+      <c r="B82" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="47"/>
+      <c r="C82" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D82" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="E82" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="F82" s="47"/>
+      <c r="G82" s="47"/>
+      <c r="H82" s="47"/>
+      <c r="I82" s="47" t="s">
+        <v>339</v>
+      </c>
       <c r="J82" s="47"/>
       <c r="K82" s="47"/>
-      <c r="L82" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M82" s="19"/>
-    </row>
-    <row r="83" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="19"/>
-      <c r="B83" s="20" t="s">
+      <c r="L82" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M82" s="10"/>
+    </row>
+    <row r="83" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="10"/>
+      <c r="B83" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="47"/>
+      <c r="C83" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D83" s="43" t="s">
+        <v>340</v>
+      </c>
+      <c r="E83" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="F83" s="47"/>
+      <c r="G83" s="47"/>
+      <c r="H83" s="47"/>
+      <c r="I83" s="47" t="s">
+        <v>342</v>
+      </c>
       <c r="J83" s="47"/>
       <c r="K83" s="47"/>
-      <c r="L83" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M83" s="19"/>
-    </row>
-    <row r="84" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="19"/>
-      <c r="B84" s="20" t="s">
+      <c r="L83" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M83" s="10"/>
+    </row>
+    <row r="84" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="10"/>
+      <c r="B84" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="59"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="47"/>
+      <c r="C84" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D84" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E84" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="F84" s="47"/>
+      <c r="G84" s="47"/>
+      <c r="H84" s="47"/>
+      <c r="I84" s="47" t="s">
+        <v>343</v>
+      </c>
       <c r="J84" s="47"/>
       <c r="K84" s="47"/>
-      <c r="L84" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M84" s="19"/>
-    </row>
-    <row r="85" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="19"/>
-      <c r="B85" s="20" t="s">
+      <c r="L84" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M84" s="10"/>
+    </row>
+    <row r="85" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="10"/>
+      <c r="B85" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="47"/>
+      <c r="C85" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D85" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="E85" s="47" t="s">
+        <v>346</v>
+      </c>
+      <c r="F85" s="47"/>
+      <c r="G85" s="47"/>
+      <c r="H85" s="47"/>
+      <c r="I85" s="47" t="s">
+        <v>347</v>
+      </c>
       <c r="J85" s="47"/>
       <c r="K85" s="47"/>
-      <c r="L85" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M85" s="19"/>
-    </row>
-    <row r="86" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="19"/>
-      <c r="B86" s="20" t="s">
+      <c r="L85" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M85" s="10"/>
+    </row>
+    <row r="86" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="10"/>
+      <c r="B86" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="47"/>
+      <c r="C86" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D86" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="E86" s="47" t="s">
+        <v>348</v>
+      </c>
+      <c r="F86" s="47"/>
+      <c r="G86" s="47"/>
+      <c r="H86" s="47"/>
+      <c r="I86" s="47" t="s">
+        <v>349</v>
+      </c>
       <c r="J86" s="47"/>
       <c r="K86" s="47"/>
-      <c r="L86" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M86" s="19"/>
-    </row>
-    <row r="87" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20" t="s">
+      <c r="L86" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M86" s="10"/>
+    </row>
+    <row r="87" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="10"/>
+      <c r="B87" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="47"/>
+      <c r="C87" s="42">
+        <v>46169</v>
+      </c>
+      <c r="D87" s="43" t="s">
+        <v>351</v>
+      </c>
+      <c r="E87" s="47" t="s">
+        <v>350</v>
+      </c>
+      <c r="F87" s="47"/>
+      <c r="G87" s="47"/>
+      <c r="H87" s="47"/>
+      <c r="I87" s="47" t="s">
+        <v>352</v>
+      </c>
       <c r="J87" s="47"/>
       <c r="K87" s="47"/>
-      <c r="L87" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M87" s="19"/>
-    </row>
-    <row r="88" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="19"/>
-      <c r="B88" s="20" t="s">
+      <c r="L87" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M87" s="10"/>
+    </row>
+    <row r="88" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="10"/>
+      <c r="B88" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
+      <c r="C88" s="43"/>
+      <c r="D88" s="43"/>
+      <c r="E88" s="47"/>
+      <c r="F88" s="47"/>
+      <c r="G88" s="47"/>
+      <c r="H88" s="47"/>
       <c r="I88" s="47"/>
       <c r="J88" s="47"/>
       <c r="K88" s="47"/>
-      <c r="L88" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M88" s="19"/>
-    </row>
-    <row r="89" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="19"/>
-      <c r="B89" s="20" t="s">
+      <c r="L88" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M88" s="10"/>
+    </row>
+    <row r="89" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="10"/>
+      <c r="B89" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
+      <c r="C89" s="43"/>
+      <c r="D89" s="43"/>
+      <c r="E89" s="47"/>
+      <c r="F89" s="47"/>
+      <c r="G89" s="47"/>
+      <c r="H89" s="47"/>
       <c r="I89" s="47"/>
       <c r="J89" s="47"/>
       <c r="K89" s="47"/>
-      <c r="L89" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M89" s="19"/>
-    </row>
-    <row r="90" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="19"/>
-      <c r="B90" s="20" t="s">
+      <c r="L89" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="M89" s="10"/>
+    </row>
+    <row r="90" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="10"/>
+      <c r="B90" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="47"/>
-      <c r="K90" s="47"/>
-      <c r="L90" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M90" s="19"/>
-    </row>
-    <row r="91" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="19"/>
-      <c r="B91" s="20" t="s">
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="45"/>
+      <c r="J90" s="45"/>
+      <c r="K90" s="45"/>
+      <c r="L90" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M90" s="10"/>
+    </row>
+    <row r="91" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="10"/>
+      <c r="B91" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="47"/>
-      <c r="J91" s="47"/>
-      <c r="K91" s="47"/>
-      <c r="L91" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M91" s="19"/>
-    </row>
-    <row r="92" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="19"/>
-      <c r="B92" s="20" t="s">
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="45"/>
+      <c r="K91" s="45"/>
+      <c r="L91" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M91" s="10"/>
+    </row>
+    <row r="92" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="10"/>
+      <c r="B92" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="47"/>
-      <c r="K92" s="47"/>
-      <c r="L92" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M92" s="19"/>
-    </row>
-    <row r="93" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="19"/>
-      <c r="B93" s="20" t="s">
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="45"/>
+      <c r="I92" s="45"/>
+      <c r="J92" s="45"/>
+      <c r="K92" s="45"/>
+      <c r="L92" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M92" s="10"/>
+    </row>
+    <row r="93" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="10"/>
+      <c r="B93" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="47"/>
-      <c r="J93" s="47"/>
-      <c r="K93" s="47"/>
-      <c r="L93" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M93" s="19"/>
-    </row>
-    <row r="94" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="19"/>
-      <c r="B94" s="20" t="s">
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="45"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="45"/>
+      <c r="H93" s="45"/>
+      <c r="I93" s="45"/>
+      <c r="J93" s="45"/>
+      <c r="K93" s="45"/>
+      <c r="L93" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M93" s="10"/>
+    </row>
+    <row r="94" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="10"/>
+      <c r="B94" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="59"/>
-      <c r="F94" s="59"/>
-      <c r="G94" s="59"/>
-      <c r="H94" s="59"/>
-      <c r="I94" s="47"/>
-      <c r="J94" s="47"/>
-      <c r="K94" s="47"/>
-      <c r="L94" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M94" s="19"/>
-    </row>
-    <row r="95" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="19"/>
-      <c r="B95" s="20" t="s">
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="45"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="45"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M94" s="10"/>
+    </row>
+    <row r="95" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="10"/>
+      <c r="B95" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="59"/>
-      <c r="F95" s="59"/>
-      <c r="G95" s="59"/>
-      <c r="H95" s="59"/>
-      <c r="I95" s="47"/>
-      <c r="J95" s="47"/>
-      <c r="K95" s="47"/>
-      <c r="L95" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M95" s="19"/>
-    </row>
-    <row r="96" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="19"/>
-      <c r="B96" s="20" t="s">
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45"/>
+      <c r="G95" s="45"/>
+      <c r="H95" s="45"/>
+      <c r="I95" s="45"/>
+      <c r="J95" s="45"/>
+      <c r="K95" s="45"/>
+      <c r="L95" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M95" s="10"/>
+    </row>
+    <row r="96" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="10"/>
+      <c r="B96" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="59"/>
-      <c r="F96" s="59"/>
-      <c r="G96" s="59"/>
-      <c r="H96" s="59"/>
-      <c r="I96" s="47"/>
-      <c r="J96" s="47"/>
-      <c r="K96" s="47"/>
-      <c r="L96" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M96" s="19"/>
-    </row>
-    <row r="97" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="19"/>
-      <c r="B97" s="20" t="s">
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="45"/>
+      <c r="F96" s="45"/>
+      <c r="G96" s="45"/>
+      <c r="H96" s="45"/>
+      <c r="I96" s="45"/>
+      <c r="J96" s="45"/>
+      <c r="K96" s="45"/>
+      <c r="L96" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M96" s="10"/>
+    </row>
+    <row r="97" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="10"/>
+      <c r="B97" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="59"/>
-      <c r="F97" s="59"/>
-      <c r="G97" s="59"/>
-      <c r="H97" s="59"/>
-      <c r="I97" s="47"/>
-      <c r="J97" s="47"/>
-      <c r="K97" s="47"/>
-      <c r="L97" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M97" s="19"/>
-    </row>
-    <row r="98" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="19"/>
-      <c r="B98" s="20" t="s">
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="45"/>
+      <c r="F97" s="45"/>
+      <c r="G97" s="45"/>
+      <c r="H97" s="45"/>
+      <c r="I97" s="45"/>
+      <c r="J97" s="45"/>
+      <c r="K97" s="45"/>
+      <c r="L97" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M97" s="10"/>
+    </row>
+    <row r="98" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="10"/>
+      <c r="B98" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="59"/>
-      <c r="F98" s="59"/>
-      <c r="G98" s="59"/>
-      <c r="H98" s="59"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="47"/>
-      <c r="K98" s="47"/>
-      <c r="L98" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M98" s="19"/>
-    </row>
-    <row r="99" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="19"/>
-      <c r="B99" s="20" t="s">
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="45"/>
+      <c r="F98" s="45"/>
+      <c r="G98" s="45"/>
+      <c r="H98" s="45"/>
+      <c r="I98" s="45"/>
+      <c r="J98" s="45"/>
+      <c r="K98" s="45"/>
+      <c r="L98" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M98" s="10"/>
+    </row>
+    <row r="99" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="10"/>
+      <c r="B99" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="59"/>
-      <c r="F99" s="59"/>
-      <c r="G99" s="59"/>
-      <c r="H99" s="59"/>
-      <c r="I99" s="47"/>
-      <c r="J99" s="47"/>
-      <c r="K99" s="47"/>
-      <c r="L99" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M99" s="19"/>
-    </row>
-    <row r="100" spans="1:13" s="18" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="19"/>
-      <c r="B100" s="20" t="s">
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="45"/>
+      <c r="F99" s="45"/>
+      <c r="G99" s="45"/>
+      <c r="H99" s="45"/>
+      <c r="I99" s="45"/>
+      <c r="J99" s="45"/>
+      <c r="K99" s="45"/>
+      <c r="L99" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M99" s="10"/>
+    </row>
+    <row r="100" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="10"/>
+      <c r="B100" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="59"/>
-      <c r="F100" s="59"/>
-      <c r="G100" s="59"/>
-      <c r="H100" s="59"/>
-      <c r="I100" s="47"/>
-      <c r="J100" s="47"/>
-      <c r="K100" s="47"/>
-      <c r="L100" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M100" s="19"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="45"/>
+      <c r="F100" s="45"/>
+      <c r="G100" s="45"/>
+      <c r="H100" s="45"/>
+      <c r="I100" s="45"/>
+      <c r="J100" s="45"/>
+      <c r="K100" s="45"/>
+      <c r="L100" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M100" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -4577,25 +5085,54 @@
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="E20:H20"/>
     <mergeCell ref="I20:K20"/>
     <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="E34:H34"/>
     <mergeCell ref="E35:H35"/>
     <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
     <mergeCell ref="E43:H43"/>
     <mergeCell ref="E44:H44"/>
     <mergeCell ref="E45:H45"/>
@@ -4605,7 +5142,6 @@
     <mergeCell ref="E40:H40"/>
     <mergeCell ref="E41:H41"/>
     <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E36:H36"/>
     <mergeCell ref="E52:H52"/>
     <mergeCell ref="E53:H53"/>
     <mergeCell ref="E54:H54"/>
@@ -4690,11 +5226,6 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
     <mergeCell ref="I43:K43"/>
     <mergeCell ref="I44:K44"/>
     <mergeCell ref="I45:K45"/>
@@ -4771,42 +5302,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4850,8 +5381,8 @@
         <v>3</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="12"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
@@ -4867,8 +5398,8 @@
         <v>11</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="7" t="s">
         <v>8</v>
       </c>
@@ -4884,8 +5415,8 @@
         <v>12</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="11"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
@@ -4901,8 +5432,8 @@
         <v>13</v>
       </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="7" t="s">
         <v>8</v>
       </c>
@@ -4918,8 +5449,8 @@
         <v>14</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
@@ -4935,8 +5466,8 @@
         <v>15</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="7" t="s">
         <v>8</v>
       </c>
@@ -4952,8 +5483,8 @@
         <v>16</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
@@ -4965,8 +5496,8 @@
         <v>17</v>
       </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -4978,8 +5509,8 @@
         <v>18</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -4991,8 +5522,8 @@
         <v>19</v>
       </c>
       <c r="C13" s="8"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -5004,8 +5535,8 @@
         <v>20</v>
       </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -5017,8 +5548,8 @@
         <v>21</v>
       </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -5030,8 +5561,8 @@
         <v>22</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -5043,8 +5574,8 @@
         <v>23</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -5056,8 +5587,8 @@
         <v>24</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -5065,44 +5596,44 @@
       <c r="J18" s="8"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5131,149 +5662,149 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="1.625" style="18" customWidth="1"/>
     <col min="2" max="4" width="30.625" customWidth="1"/>
     <col min="5" max="5" width="1.625" customWidth="1"/>
     <col min="6" max="8" width="9.625" customWidth="1"/>
     <col min="9" max="9" width="1.625" customWidth="1"/>
     <col min="13" max="13" width="1.625" customWidth="1"/>
     <col min="14" max="16" width="30.625" customWidth="1"/>
-    <col min="17" max="17" width="1.625" style="21" customWidth="1"/>
+    <col min="17" max="17" width="1.625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" s="21" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="88" t="s">
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="87" t="s">
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86" t="e" vm="1">
+      <c r="B3" s="73" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="93" t="s">
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="93" t="s">
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="86" t="e" vm="2">
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="73" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="93" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="93" t="s">
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="91" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-    </row>
-    <row r="6" spans="2:16" s="21" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+    </row>
+    <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82" t="s">
+      <c r="C8" s="69"/>
+      <c r="D8" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84" t="s">
+      <c r="C10" s="71"/>
+      <c r="D10" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84" t="s">
+      <c r="C11" s="71"/>
+      <c r="D11" s="71" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4404FDD7-2280-47C9-8BFE-CDE1C31DEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0E5FB7-0CCD-4568-A9A0-24794FBCE4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="20535" windowHeight="15585" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20535" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="363">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1471,6 +1471,51 @@
   </si>
   <si>
     <t>클릭문제를 해결하고 추가적으로 이미 미션 혹은 자물쇠를 푼 이후일 경우에 아내 방은 이미 열쇠를 회득했다고 나오지만 공부방에는 없어서 내용을 추가 바람 ( 체셔가 "너는 이미 문제를 풀었어" )라는 형식의 메시지를 출력함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인트로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아내방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 인트로 사운드 버그 발생
+워크 플로우에서 충돌이 발생 / 가장 가까운 이유는 오디오 컨트롤러에서 디스트로어와 리무브가 첨가되어있음 105줄 부터 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">주방 태그 좌표 오류 발생
+캔버스에서 랜더 모드를 오버레이로 수정 후 캔버스 스케일에서 UI부분을 스케일로 수정 후 레퍼런스 1980*1080으로 수정
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI에 태그 위치가 정확한 위치에 나오도록 수정 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사운드가 정상적으로 나올 수 있도록 수정 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방에서 체셔를 먹이로 불러낸 후 클릭이 안되는 버그 
+프라이팬에서 구운먹이로 체셔를 불러낼때 패널 자체를 닫게 수정됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방에서 체셔를 클릭하면 다시 클릭이 가능하고 힌트가 출력되게 수정 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아내방 시계 클릭 시 모든 클릭 정지 상태 버그 
+워크플로우에서 Wallclock_Clicked와 Drawer_Clicked에서 false부분이 빠져있어서 안되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아내방에 시계 혹은 열쇠를 얻은 이후 서랍을 클릭해도 모든 오브젝트가 클릭될 수 있게 수정 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1877,78 +1922,105 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1956,34 +2028,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2034,8 +2079,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFBE2D5"/>
       <color rgb="FFDAE9F8"/>
-      <color rgb="FFFBE2D5"/>
       <color rgb="FFFFCC66"/>
       <color rgb="FFFF5050"/>
       <color rgb="FF99FF99"/>
@@ -2461,36 +2506,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -2503,17 +2548,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -2532,17 +2577,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="E4" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -2559,17 +2604,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="61" t="s">
+      <c r="E5" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -2586,17 +2631,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -2613,17 +2658,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="61" t="s">
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -2640,17 +2685,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="61" t="s">
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -2667,17 +2712,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="E9" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="61" t="s">
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -2694,17 +2739,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="61" t="s">
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -2721,17 +2766,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="61" t="s">
+      <c r="E11" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -2748,17 +2793,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61" t="s">
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -2775,17 +2820,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61" t="s">
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -2802,17 +2847,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="61" t="s">
+      <c r="E14" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61" t="s">
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -2829,17 +2874,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="61" t="s">
+      <c r="E15" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61" t="s">
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -2856,17 +2901,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="61" t="s">
+      <c r="E16" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61" t="s">
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -2883,17 +2928,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61" t="s">
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -2910,17 +2955,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="61" t="s">
+      <c r="E18" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61" t="s">
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -2937,17 +2982,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56" t="s">
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -2964,17 +3009,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56" t="s">
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="56"/>
-      <c r="K20" s="56"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -2991,17 +3036,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56" t="s">
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3018,17 +3063,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56" t="s">
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3045,17 +3090,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56" t="s">
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="56"/>
-      <c r="K23" s="56"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3072,17 +3117,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56" t="s">
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3099,17 +3144,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56" t="s">
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3126,17 +3171,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57" t="s">
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3168,17 +3213,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="50" t="s">
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="51"/>
-      <c r="K27" s="52"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="59"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -3201,17 +3246,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="50" t="s">
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="51"/>
-      <c r="K28" s="52"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="59"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -3231,17 +3276,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="50" t="s">
+      <c r="E29" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="50" t="s">
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="51"/>
-      <c r="K29" s="52"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="59"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -3261,17 +3306,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57" t="s">
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -3291,17 +3336,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="60" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53" t="s">
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -3318,17 +3363,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53" t="s">
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -3345,17 +3390,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53" t="s">
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="60"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -3372,17 +3417,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="54" t="s">
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="61" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="48"/>
-      <c r="K34" s="49"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="63"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -3399,17 +3444,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="46" t="s">
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="64"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -3426,17 +3471,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="46" t="s">
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="64" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
+      <c r="J36" s="64"/>
+      <c r="K36" s="64"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -3453,17 +3498,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="54" t="s">
+      <c r="E37" s="61" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="46" t="s">
+      <c r="F37" s="62"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="64"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -3480,17 +3525,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="54" t="s">
+      <c r="E38" s="61" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="46" t="s">
+      <c r="F38" s="62"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="64" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="48"/>
-      <c r="K38" s="49"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="63"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -3507,17 +3552,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="47" t="s">
+      <c r="E39" s="56" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="47" t="s">
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -3534,17 +3579,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="47" t="s">
+      <c r="E40" s="56" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
-      <c r="I40" s="47" t="s">
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="47"/>
-      <c r="K40" s="47"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -3561,17 +3606,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="47" t="s">
+      <c r="E41" s="56" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
-      <c r="I41" s="47" t="s">
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="47"/>
-      <c r="K41" s="47"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="56"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -3588,17 +3633,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="47" t="s">
+      <c r="E42" s="56" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47" t="s">
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -3615,17 +3660,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="47" t="s">
+      <c r="E43" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47" t="s">
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="56"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -3642,17 +3687,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="E44" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47" t="s">
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="56"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -3669,17 +3714,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="47" t="s">
+      <c r="E45" s="56" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47" t="s">
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="56"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -3696,17 +3741,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="47" t="s">
+      <c r="E46" s="56" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="47" t="s">
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
+      <c r="J46" s="56"/>
+      <c r="K46" s="56"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -3723,17 +3768,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="47" t="s">
+      <c r="E47" s="56" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
-      <c r="I47" s="47" t="s">
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
+      <c r="J47" s="56"/>
+      <c r="K47" s="56"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -3750,17 +3795,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="47" t="s">
+      <c r="E48" s="56" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47" t="s">
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
+      <c r="J48" s="56"/>
+      <c r="K48" s="56"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -3777,17 +3822,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="47" t="s">
+      <c r="E49" s="56" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47" t="s">
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="56"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -3804,17 +3849,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47" t="s">
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
+      <c r="J50" s="56"/>
+      <c r="K50" s="56"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -3831,17 +3876,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="47" t="s">
+      <c r="E51" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47" t="s">
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="47"/>
-      <c r="K51" s="47"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -3858,17 +3903,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="47" t="s">
+      <c r="E52" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
-      <c r="I52" s="47" t="s">
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="47"/>
-      <c r="K52" s="47"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="56"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -3885,17 +3930,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="47" t="s">
+      <c r="E53" s="56" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="47" t="s">
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="47"/>
-      <c r="K53" s="47"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -3912,17 +3957,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="46" t="s">
+      <c r="E54" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46" t="s">
+      <c r="F54" s="64"/>
+      <c r="G54" s="64"/>
+      <c r="H54" s="64"/>
+      <c r="I54" s="64" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
+      <c r="J54" s="64"/>
+      <c r="K54" s="64"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -3939,17 +3984,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="46" t="s">
+      <c r="E55" s="64" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46" t="s">
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
+      <c r="I55" s="64" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
+      <c r="J55" s="64"/>
+      <c r="K55" s="64"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -3966,17 +4011,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="46" t="s">
+      <c r="E56" s="64" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46" t="s">
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+      <c r="I56" s="64" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
+      <c r="J56" s="64"/>
+      <c r="K56" s="64"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -3993,17 +4038,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="47" t="s">
+      <c r="E57" s="56" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="47"/>
-      <c r="G57" s="47"/>
-      <c r="H57" s="47"/>
-      <c r="I57" s="47" t="s">
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="47"/>
-      <c r="K57" s="47"/>
+      <c r="J57" s="56"/>
+      <c r="K57" s="56"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4020,17 +4065,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="47" t="s">
+      <c r="E58" s="56" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="47"/>
-      <c r="I58" s="47" t="s">
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="47"/>
-      <c r="K58" s="47"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4047,17 +4092,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="47" t="s">
+      <c r="E59" s="56" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="47"/>
-      <c r="G59" s="47"/>
-      <c r="H59" s="47"/>
-      <c r="I59" s="47" t="s">
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
+      <c r="J59" s="56"/>
+      <c r="K59" s="56"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4074,17 +4119,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="47" t="s">
+      <c r="E60" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="47"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="47" t="s">
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="47"/>
-      <c r="K60" s="47"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="56"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4101,17 +4146,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="47" t="s">
+      <c r="E61" s="56" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47"/>
-      <c r="H61" s="47"/>
-      <c r="I61" s="47" t="s">
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="47"/>
-      <c r="K61" s="47"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4128,17 +4173,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="47" t="s">
+      <c r="E62" s="56" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="47"/>
-      <c r="G62" s="47"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="47" t="s">
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="47"/>
-      <c r="K62" s="47"/>
+      <c r="J62" s="56"/>
+      <c r="K62" s="56"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4155,17 +4200,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="47" t="s">
+      <c r="E63" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="47"/>
-      <c r="G63" s="47"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="47" t="e" vm="1">
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="47"/>
-      <c r="K63" s="47"/>
+      <c r="J63" s="56"/>
+      <c r="K63" s="56"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -4182,17 +4227,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="47" t="s">
+      <c r="E64" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="47"/>
-      <c r="G64" s="47"/>
-      <c r="H64" s="47"/>
-      <c r="I64" s="47" t="s">
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="56" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="47"/>
-      <c r="K64" s="47"/>
+      <c r="J64" s="56"/>
+      <c r="K64" s="56"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -4209,17 +4254,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="47" t="s">
+      <c r="E65" s="56" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="47"/>
-      <c r="G65" s="47"/>
-      <c r="H65" s="47"/>
-      <c r="I65" s="47" t="s">
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+      <c r="I65" s="56" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="47"/>
-      <c r="K65" s="47"/>
+      <c r="J65" s="56"/>
+      <c r="K65" s="56"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -4236,17 +4281,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="47" t="s">
+      <c r="E66" s="56" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="47"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="47"/>
-      <c r="I66" s="47" t="s">
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="47"/>
-      <c r="K66" s="47"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -4263,17 +4308,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="55" t="s">
+      <c r="E67" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="55"/>
-      <c r="G67" s="55"/>
-      <c r="H67" s="55"/>
-      <c r="I67" s="47" t="s">
+      <c r="F67" s="65"/>
+      <c r="G67" s="65"/>
+      <c r="H67" s="65"/>
+      <c r="I67" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="47"/>
-      <c r="K67" s="47"/>
+      <c r="J67" s="56"/>
+      <c r="K67" s="56"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -4290,17 +4335,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="46" t="s">
+      <c r="E68" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46" t="s">
+      <c r="F68" s="64"/>
+      <c r="G68" s="64"/>
+      <c r="H68" s="64"/>
+      <c r="I68" s="64" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
+      <c r="J68" s="64"/>
+      <c r="K68" s="64"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -4317,17 +4362,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="46" t="s">
+      <c r="E69" s="64" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46" t="s">
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
+      <c r="I69" s="64" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
+      <c r="J69" s="64"/>
+      <c r="K69" s="64"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -4344,17 +4389,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="46" t="s">
+      <c r="E70" s="64" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46" t="s">
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="64" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
+      <c r="J70" s="64"/>
+      <c r="K70" s="64"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -4371,17 +4416,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="46" t="s">
+      <c r="E71" s="64" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46" t="s">
+      <c r="F71" s="64"/>
+      <c r="G71" s="64"/>
+      <c r="H71" s="64"/>
+      <c r="I71" s="64" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
+      <c r="J71" s="64"/>
+      <c r="K71" s="64"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -4398,17 +4443,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="46" t="s">
+      <c r="E72" s="64" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46" t="s">
+      <c r="F72" s="64"/>
+      <c r="G72" s="64"/>
+      <c r="H72" s="64"/>
+      <c r="I72" s="64" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
+      <c r="J72" s="64"/>
+      <c r="K72" s="64"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -4425,17 +4470,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="46" t="s">
+      <c r="E73" s="64" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="46" t="s">
+      <c r="F73" s="64"/>
+      <c r="G73" s="64"/>
+      <c r="H73" s="64"/>
+      <c r="I73" s="64" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
+      <c r="J73" s="64"/>
+      <c r="K73" s="64"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -4452,17 +4497,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="46" t="s">
+      <c r="E74" s="64" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46" t="s">
+      <c r="F74" s="64"/>
+      <c r="G74" s="64"/>
+      <c r="H74" s="64"/>
+      <c r="I74" s="64" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
+      <c r="J74" s="64"/>
+      <c r="K74" s="64"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -4479,17 +4524,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="46" t="s">
+      <c r="E75" s="64" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46" t="s">
+      <c r="F75" s="64"/>
+      <c r="G75" s="64"/>
+      <c r="H75" s="64"/>
+      <c r="I75" s="64" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
+      <c r="J75" s="64"/>
+      <c r="K75" s="64"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -4506,17 +4551,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="46" t="s">
+      <c r="E76" s="64" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46" t="s">
+      <c r="F76" s="64"/>
+      <c r="G76" s="64"/>
+      <c r="H76" s="64"/>
+      <c r="I76" s="64" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
+      <c r="J76" s="64"/>
+      <c r="K76" s="64"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -4533,17 +4578,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="46" t="s">
+      <c r="E77" s="64" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="46" t="s">
+      <c r="F77" s="64"/>
+      <c r="G77" s="64"/>
+      <c r="H77" s="64"/>
+      <c r="I77" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
+      <c r="J77" s="64"/>
+      <c r="K77" s="64"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -4560,17 +4605,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="46" t="s">
+      <c r="E78" s="64" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46" t="s">
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="64"/>
+      <c r="I78" s="64" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
+      <c r="J78" s="64"/>
+      <c r="K78" s="64"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -4587,17 +4632,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="46" t="s">
+      <c r="E79" s="64" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="46" t="s">
+      <c r="F79" s="64"/>
+      <c r="G79" s="64"/>
+      <c r="H79" s="64"/>
+      <c r="I79" s="64" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
+      <c r="J79" s="64"/>
+      <c r="K79" s="64"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -4614,17 +4659,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="46" t="s">
+      <c r="E80" s="64" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46" t="s">
+      <c r="F80" s="64"/>
+      <c r="G80" s="64"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="64" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
+      <c r="J80" s="64"/>
+      <c r="K80" s="64"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -4641,17 +4686,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="47" t="s">
+      <c r="E81" s="56" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="47"/>
-      <c r="G81" s="47"/>
-      <c r="H81" s="47"/>
-      <c r="I81" s="47" t="s">
+      <c r="F81" s="56"/>
+      <c r="G81" s="56"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="56" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="47"/>
-      <c r="K81" s="47"/>
+      <c r="J81" s="56"/>
+      <c r="K81" s="56"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -4668,17 +4713,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="47" t="s">
+      <c r="E82" s="56" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="47"/>
-      <c r="G82" s="47"/>
-      <c r="H82" s="47"/>
-      <c r="I82" s="47" t="s">
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="47"/>
-      <c r="K82" s="47"/>
+      <c r="J82" s="56"/>
+      <c r="K82" s="56"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -4695,17 +4740,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="47" t="s">
+      <c r="E83" s="56" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="47"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="47"/>
-      <c r="I83" s="47" t="s">
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="47"/>
-      <c r="K83" s="47"/>
+      <c r="J83" s="56"/>
+      <c r="K83" s="56"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -4722,17 +4767,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="47" t="s">
+      <c r="E84" s="56" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="47"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47" t="s">
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="56" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="47"/>
-      <c r="K84" s="47"/>
+      <c r="J84" s="56"/>
+      <c r="K84" s="56"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -4749,17 +4794,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="47" t="s">
+      <c r="E85" s="56" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="47"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="47"/>
-      <c r="I85" s="47" t="s">
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="47"/>
-      <c r="K85" s="47"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -4776,17 +4821,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="47" t="s">
+      <c r="E86" s="56" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="47"/>
-      <c r="G86" s="47"/>
-      <c r="H86" s="47"/>
-      <c r="I86" s="47" t="s">
+      <c r="F86" s="56"/>
+      <c r="G86" s="56"/>
+      <c r="H86" s="56"/>
+      <c r="I86" s="56" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="47"/>
-      <c r="K86" s="47"/>
+      <c r="J86" s="56"/>
+      <c r="K86" s="56"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -4803,17 +4848,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="47" t="s">
+      <c r="E87" s="56" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47" t="s">
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="56"/>
+      <c r="I87" s="56" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="47"/>
-      <c r="K87" s="47"/>
+      <c r="J87" s="56"/>
+      <c r="K87" s="56"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -4821,76 +4866,108 @@
     </row>
     <row r="88" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
-      <c r="B88" s="41" t="s">
+      <c r="B88" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="C88" s="43"/>
-      <c r="D88" s="43"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
-      <c r="J88" s="47"/>
-      <c r="K88" s="47"/>
-      <c r="L88" s="43" t="s">
+      <c r="C88" s="39">
+        <v>46178</v>
+      </c>
+      <c r="D88" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="E88" s="64" t="s">
+        <v>355</v>
+      </c>
+      <c r="F88" s="64"/>
+      <c r="G88" s="64"/>
+      <c r="H88" s="64"/>
+      <c r="I88" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="J88" s="64"/>
+      <c r="K88" s="64"/>
+      <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
       <c r="M88" s="10"/>
     </row>
     <row r="89" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
-      <c r="B89" s="41" t="s">
+      <c r="B89" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C89" s="43"/>
-      <c r="D89" s="43"/>
-      <c r="E89" s="47"/>
-      <c r="F89" s="47"/>
-      <c r="G89" s="47"/>
-      <c r="H89" s="47"/>
-      <c r="I89" s="47"/>
-      <c r="J89" s="47"/>
-      <c r="K89" s="47"/>
-      <c r="L89" s="43" t="s">
+      <c r="C89" s="39">
+        <v>46178</v>
+      </c>
+      <c r="D89" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E89" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="F89" s="64"/>
+      <c r="G89" s="64"/>
+      <c r="H89" s="64"/>
+      <c r="I89" s="64" t="s">
+        <v>357</v>
+      </c>
+      <c r="J89" s="64"/>
+      <c r="K89" s="64"/>
+      <c r="L89" s="27" t="s">
         <v>52</v>
       </c>
       <c r="M89" s="10"/>
     </row>
     <row r="90" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="45"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="45"/>
-      <c r="J90" s="45"/>
-      <c r="K90" s="45"/>
-      <c r="L90" s="9" t="s">
+      <c r="C90" s="39">
+        <v>46178</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E90" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="F90" s="64"/>
+      <c r="G90" s="64"/>
+      <c r="H90" s="64"/>
+      <c r="I90" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="J90" s="64"/>
+      <c r="K90" s="64"/>
+      <c r="L90" s="27" t="s">
         <v>52</v>
       </c>
       <c r="M90" s="10"/>
     </row>
     <row r="91" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="45"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="45"/>
-      <c r="K91" s="45"/>
-      <c r="L91" s="9" t="s">
+      <c r="C91" s="39">
+        <v>46178</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="E91" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="F91" s="64"/>
+      <c r="G91" s="64"/>
+      <c r="H91" s="64"/>
+      <c r="I91" s="64" t="s">
+        <v>362</v>
+      </c>
+      <c r="J91" s="64"/>
+      <c r="K91" s="64"/>
+      <c r="L91" s="27" t="s">
         <v>52</v>
       </c>
       <c r="M91" s="10"/>
@@ -4902,13 +4979,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="45"/>
-      <c r="F92" s="45"/>
-      <c r="G92" s="45"/>
-      <c r="H92" s="45"/>
-      <c r="I92" s="45"/>
-      <c r="J92" s="45"/>
-      <c r="K92" s="45"/>
+      <c r="E92" s="66"/>
+      <c r="F92" s="66"/>
+      <c r="G92" s="66"/>
+      <c r="H92" s="66"/>
+      <c r="I92" s="66"/>
+      <c r="J92" s="66"/>
+      <c r="K92" s="66"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -4921,13 +4998,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="45"/>
-      <c r="F93" s="45"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="45"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="45"/>
-      <c r="K93" s="45"/>
+      <c r="E93" s="66"/>
+      <c r="F93" s="66"/>
+      <c r="G93" s="66"/>
+      <c r="H93" s="66"/>
+      <c r="I93" s="66"/>
+      <c r="J93" s="66"/>
+      <c r="K93" s="66"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -4940,13 +5017,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="45"/>
-      <c r="F94" s="45"/>
-      <c r="G94" s="45"/>
-      <c r="H94" s="45"/>
-      <c r="I94" s="45"/>
-      <c r="J94" s="45"/>
-      <c r="K94" s="45"/>
+      <c r="E94" s="66"/>
+      <c r="F94" s="66"/>
+      <c r="G94" s="66"/>
+      <c r="H94" s="66"/>
+      <c r="I94" s="66"/>
+      <c r="J94" s="66"/>
+      <c r="K94" s="66"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -4959,13 +5036,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="45"/>
-      <c r="F95" s="45"/>
-      <c r="G95" s="45"/>
-      <c r="H95" s="45"/>
-      <c r="I95" s="45"/>
-      <c r="J95" s="45"/>
-      <c r="K95" s="45"/>
+      <c r="E95" s="66"/>
+      <c r="F95" s="66"/>
+      <c r="G95" s="66"/>
+      <c r="H95" s="66"/>
+      <c r="I95" s="66"/>
+      <c r="J95" s="66"/>
+      <c r="K95" s="66"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -4978,13 +5055,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="45"/>
-      <c r="F96" s="45"/>
-      <c r="G96" s="45"/>
-      <c r="H96" s="45"/>
-      <c r="I96" s="45"/>
-      <c r="J96" s="45"/>
-      <c r="K96" s="45"/>
+      <c r="E96" s="66"/>
+      <c r="F96" s="66"/>
+      <c r="G96" s="66"/>
+      <c r="H96" s="66"/>
+      <c r="I96" s="66"/>
+      <c r="J96" s="66"/>
+      <c r="K96" s="66"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -4997,13 +5074,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="45"/>
-      <c r="F97" s="45"/>
-      <c r="G97" s="45"/>
-      <c r="H97" s="45"/>
-      <c r="I97" s="45"/>
-      <c r="J97" s="45"/>
-      <c r="K97" s="45"/>
+      <c r="E97" s="66"/>
+      <c r="F97" s="66"/>
+      <c r="G97" s="66"/>
+      <c r="H97" s="66"/>
+      <c r="I97" s="66"/>
+      <c r="J97" s="66"/>
+      <c r="K97" s="66"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5016,13 +5093,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="45"/>
-      <c r="F98" s="45"/>
-      <c r="G98" s="45"/>
-      <c r="H98" s="45"/>
-      <c r="I98" s="45"/>
-      <c r="J98" s="45"/>
-      <c r="K98" s="45"/>
+      <c r="E98" s="66"/>
+      <c r="F98" s="66"/>
+      <c r="G98" s="66"/>
+      <c r="H98" s="66"/>
+      <c r="I98" s="66"/>
+      <c r="J98" s="66"/>
+      <c r="K98" s="66"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -5035,13 +5112,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="45"/>
-      <c r="F99" s="45"/>
-      <c r="G99" s="45"/>
-      <c r="H99" s="45"/>
-      <c r="I99" s="45"/>
-      <c r="J99" s="45"/>
-      <c r="K99" s="45"/>
+      <c r="E99" s="66"/>
+      <c r="F99" s="66"/>
+      <c r="G99" s="66"/>
+      <c r="H99" s="66"/>
+      <c r="I99" s="66"/>
+      <c r="J99" s="66"/>
+      <c r="K99" s="66"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -5054,13 +5131,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
-      <c r="J100" s="45"/>
-      <c r="K100" s="45"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="66"/>
+      <c r="H100" s="66"/>
+      <c r="I100" s="66"/>
+      <c r="J100" s="66"/>
+      <c r="K100" s="66"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5068,6 +5145,179 @@
     </row>
   </sheetData>
   <mergeCells count="197">
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -5092,179 +5342,6 @@
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -5674,140 +5751,148 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="77"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="73"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="74" t="s">
+      <c r="N2" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="e" vm="2">
+      <c r="B3" s="69" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="73" t="e" vm="3">
+      <c r="N3" s="69" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="77" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="80" t="s">
+      <c r="J4" s="77" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="79"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="76"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69" t="s">
+      <c r="C8" s="78"/>
+      <c r="D8" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="71" t="s">
+      <c r="C9" s="79"/>
+      <c r="D9" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71" t="s">
+      <c r="C10" s="75"/>
+      <c r="D10" s="75" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71" t="s">
+      <c r="C11" s="75"/>
+      <c r="D11" s="75" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5818,14 +5903,6 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0E5FB7-0CCD-4568-A9A0-24794FBCE4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E7D9CA-FBA7-4019-8259-1503ADC7F22C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20535" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -17,49 +17,38 @@
     <sheet name="편의성" sheetId="10" r:id="rId2"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -1922,78 +1911,90 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2012,23 +2013,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2506,36 +2495,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -2548,17 +2537,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47" t="s">
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -2577,17 +2566,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46" t="s">
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -2604,17 +2593,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46" t="s">
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -2631,17 +2620,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46" t="s">
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -2658,17 +2647,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="46" t="s">
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -2685,17 +2674,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="46" t="s">
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -2712,17 +2701,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="46" t="s">
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -2739,17 +2728,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="46" t="s">
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -2766,17 +2755,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46" t="s">
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -2793,17 +2782,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46" t="s">
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -2820,17 +2809,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46" t="s">
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -2847,17 +2836,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46" t="s">
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -2874,17 +2863,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46" t="s">
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -2901,17 +2890,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46" t="s">
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -2928,17 +2917,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46" t="s">
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -2955,17 +2944,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46" t="s">
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -2982,17 +2971,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51" t="s">
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3009,17 +2998,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E20" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51" t="s">
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3036,17 +3025,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="E21" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51" t="s">
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3063,17 +3052,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51" t="s">
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3090,17 +3079,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="E23" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51" t="s">
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3117,17 +3106,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="51" t="s">
+      <c r="E24" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51" t="s">
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3144,17 +3133,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51" t="s">
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3171,17 +3160,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52" t="s">
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3213,17 +3202,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="49" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="57" t="s">
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="58"/>
-      <c r="K27" s="59"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="51"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -3246,17 +3235,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="57" t="s">
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="58"/>
-      <c r="K28" s="59"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="51"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -3276,17 +3265,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="57" t="s">
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="58"/>
-      <c r="K29" s="59"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="51"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -3306,17 +3295,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52" t="s">
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -3336,17 +3325,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="60" t="s">
+      <c r="E31" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="60"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60" t="s">
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -3363,17 +3352,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="60" t="s">
+      <c r="E32" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60" t="s">
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -3390,17 +3379,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60" t="s">
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="60"/>
-      <c r="K33" s="60"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -3417,17 +3406,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="53" t="s">
+      <c r="E34" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="61" t="s">
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="62"/>
-      <c r="K34" s="63"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="48"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -3444,17 +3433,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="53" t="s">
+      <c r="E35" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="64" t="s">
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -3471,17 +3460,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="53" t="s">
+      <c r="E36" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="64" t="s">
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -3498,17 +3487,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="61" t="s">
+      <c r="E37" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="62"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="64" t="s">
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="46" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -3525,17 +3514,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="61" t="s">
+      <c r="E38" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="64" t="s">
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="62"/>
-      <c r="K38" s="63"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="48"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -3552,17 +3541,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="56" t="s">
+      <c r="E39" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56" t="s">
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -3579,17 +3568,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="56" t="s">
+      <c r="E40" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56" t="s">
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -3606,17 +3595,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="56" t="s">
+      <c r="E41" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56" t="s">
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="56"/>
-      <c r="K41" s="56"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -3633,17 +3622,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="45" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56" t="s">
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -3660,17 +3649,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="56" t="s">
+      <c r="E43" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56" t="s">
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="56"/>
-      <c r="K43" s="56"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -3687,17 +3676,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="56" t="s">
+      <c r="E44" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56" t="s">
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="56"/>
-      <c r="K44" s="56"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="45"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -3714,17 +3703,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="56" t="s">
+      <c r="E45" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56" t="s">
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="56"/>
-      <c r="K45" s="56"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -3741,17 +3730,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56" t="s">
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -3768,17 +3757,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="56" t="s">
+      <c r="E47" s="45" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="56" t="s">
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="56"/>
-      <c r="K47" s="56"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -3795,17 +3784,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="56" t="s">
+      <c r="E48" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56" t="s">
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="56"/>
-      <c r="K48" s="56"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -3822,17 +3811,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="56" t="s">
+      <c r="E49" s="45" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56" t="s">
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="56"/>
-      <c r="K49" s="56"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -3849,17 +3838,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="45" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56" t="s">
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="56"/>
-      <c r="K50" s="56"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -3876,17 +3865,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="56" t="s">
+      <c r="E51" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="56" t="s">
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="56"/>
-      <c r="K51" s="56"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -3903,17 +3892,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="56" t="s">
+      <c r="E52" s="45" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="56" t="s">
+      <c r="F52" s="45"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="45"/>
+      <c r="I52" s="45" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="56"/>
-      <c r="K52" s="56"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="45"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -3930,17 +3919,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="56" t="s">
+      <c r="E53" s="45" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56" t="s">
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="45" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -3957,17 +3946,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="64" t="s">
+      <c r="E54" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="64"/>
-      <c r="G54" s="64"/>
-      <c r="H54" s="64"/>
-      <c r="I54" s="64" t="s">
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="46" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="64"/>
-      <c r="K54" s="64"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -3984,17 +3973,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="64" t="s">
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="64"/>
-      <c r="K55" s="64"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4011,17 +4000,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="64" t="s">
+      <c r="E56" s="46" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64" t="s">
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="64"/>
-      <c r="K56" s="64"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4038,17 +4027,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="56" t="s">
+      <c r="E57" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56" t="s">
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="45"/>
+      <c r="I57" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="56"/>
-      <c r="K57" s="56"/>
+      <c r="J57" s="45"/>
+      <c r="K57" s="45"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4065,17 +4054,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="56" t="s">
+      <c r="E58" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56" t="s">
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="56"/>
-      <c r="K58" s="56"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4092,17 +4081,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="56"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56" t="s">
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="45"/>
+      <c r="I59" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="56"/>
-      <c r="K59" s="56"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4119,17 +4108,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="56" t="s">
+      <c r="E60" s="45" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="56"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56" t="s">
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
+      <c r="H60" s="45"/>
+      <c r="I60" s="45" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="56"/>
-      <c r="K60" s="56"/>
+      <c r="J60" s="45"/>
+      <c r="K60" s="45"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4146,17 +4135,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="56" t="s">
+      <c r="E61" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="56"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56" t="s">
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="45"/>
+      <c r="I61" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="56"/>
-      <c r="K61" s="56"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="45"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4173,17 +4162,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="56" t="s">
+      <c r="E62" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="56"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="56" t="s">
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="45"/>
+      <c r="I62" s="45" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="56"/>
-      <c r="K62" s="56"/>
+      <c r="J62" s="45"/>
+      <c r="K62" s="45"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4200,17 +4189,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="56" t="s">
+      <c r="E63" s="45" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="56"/>
-      <c r="I63" s="56" t="e" vm="1">
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="56"/>
-      <c r="K63" s="56"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -4227,17 +4216,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="56" t="s">
+      <c r="E64" s="45" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="56"/>
-      <c r="I64" s="56" t="s">
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="56"/>
-      <c r="K64" s="56"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="45"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -4254,17 +4243,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="56" t="s">
+      <c r="E65" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="56" t="s">
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="56"/>
-      <c r="K65" s="56"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -4281,17 +4270,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="56" t="s">
+      <c r="E66" s="45" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-      <c r="I66" s="56" t="s">
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="56"/>
-      <c r="K66" s="56"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -4308,17 +4297,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="65" t="s">
+      <c r="E67" s="55" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="65"/>
-      <c r="G67" s="65"/>
-      <c r="H67" s="65"/>
-      <c r="I67" s="56" t="s">
+      <c r="F67" s="55"/>
+      <c r="G67" s="55"/>
+      <c r="H67" s="55"/>
+      <c r="I67" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="56"/>
-      <c r="K67" s="56"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="45"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -4335,17 +4324,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="64" t="s">
+      <c r="E68" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="64"/>
-      <c r="G68" s="64"/>
-      <c r="H68" s="64"/>
-      <c r="I68" s="64" t="s">
+      <c r="F68" s="46"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="64"/>
-      <c r="K68" s="64"/>
+      <c r="J68" s="46"/>
+      <c r="K68" s="46"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -4362,17 +4351,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="64" t="s">
+      <c r="E69" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="64"/>
-      <c r="G69" s="64"/>
-      <c r="H69" s="64"/>
-      <c r="I69" s="64" t="s">
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="46"/>
+      <c r="I69" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="64"/>
-      <c r="K69" s="64"/>
+      <c r="J69" s="46"/>
+      <c r="K69" s="46"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -4389,17 +4378,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="64" t="s">
+      <c r="E70" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="64"/>
-      <c r="G70" s="64"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="64" t="s">
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="64"/>
-      <c r="K70" s="64"/>
+      <c r="J70" s="46"/>
+      <c r="K70" s="46"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -4416,17 +4405,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="64" t="s">
+      <c r="E71" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="64"/>
-      <c r="G71" s="64"/>
-      <c r="H71" s="64"/>
-      <c r="I71" s="64" t="s">
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="64"/>
-      <c r="K71" s="64"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -4443,17 +4432,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="64" t="s">
+      <c r="E72" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="64"/>
-      <c r="G72" s="64"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="64" t="s">
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="64"/>
-      <c r="K72" s="64"/>
+      <c r="J72" s="46"/>
+      <c r="K72" s="46"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -4470,17 +4459,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="64" t="s">
+      <c r="E73" s="46" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="64"/>
-      <c r="G73" s="64"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="64" t="s">
+      <c r="F73" s="46"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="64"/>
-      <c r="K73" s="64"/>
+      <c r="J73" s="46"/>
+      <c r="K73" s="46"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -4497,17 +4486,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="64" t="s">
+      <c r="E74" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="64"/>
-      <c r="G74" s="64"/>
-      <c r="H74" s="64"/>
-      <c r="I74" s="64" t="s">
+      <c r="F74" s="46"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="64"/>
-      <c r="K74" s="64"/>
+      <c r="J74" s="46"/>
+      <c r="K74" s="46"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -4524,17 +4513,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="64" t="s">
+      <c r="E75" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="64"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="64"/>
-      <c r="I75" s="64" t="s">
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
+      <c r="I75" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="64"/>
-      <c r="K75" s="64"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="46"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -4551,17 +4540,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="64" t="s">
+      <c r="E76" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="64"/>
-      <c r="G76" s="64"/>
-      <c r="H76" s="64"/>
-      <c r="I76" s="64" t="s">
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="64"/>
-      <c r="K76" s="64"/>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -4578,17 +4567,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="64" t="s">
+      <c r="E77" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="64"/>
-      <c r="G77" s="64"/>
-      <c r="H77" s="64"/>
-      <c r="I77" s="64" t="s">
+      <c r="F77" s="46"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="46"/>
+      <c r="I77" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="64"/>
-      <c r="K77" s="64"/>
+      <c r="J77" s="46"/>
+      <c r="K77" s="46"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -4605,17 +4594,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="64" t="s">
+      <c r="E78" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="64"/>
-      <c r="G78" s="64"/>
-      <c r="H78" s="64"/>
-      <c r="I78" s="64" t="s">
+      <c r="F78" s="46"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="46"/>
+      <c r="I78" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="64"/>
-      <c r="K78" s="64"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -4632,17 +4621,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="64"/>
-      <c r="G79" s="64"/>
-      <c r="H79" s="64"/>
-      <c r="I79" s="64" t="s">
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="64"/>
-      <c r="K79" s="64"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -4659,17 +4648,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="64" t="s">
+      <c r="E80" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="64"/>
-      <c r="G80" s="64"/>
-      <c r="H80" s="64"/>
-      <c r="I80" s="64" t="s">
+      <c r="F80" s="46"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="64"/>
-      <c r="K80" s="64"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -4686,17 +4675,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="56" t="s">
+      <c r="E81" s="45" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="56"/>
-      <c r="I81" s="56" t="s">
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="56"/>
-      <c r="K81" s="56"/>
+      <c r="J81" s="45"/>
+      <c r="K81" s="45"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -4713,17 +4702,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="56" t="s">
+      <c r="E82" s="45" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="56"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="56"/>
-      <c r="I82" s="56" t="s">
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="45" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="56"/>
-      <c r="K82" s="56"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="45"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -4740,17 +4729,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="56" t="s">
+      <c r="E83" s="45" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="56"/>
-      <c r="G83" s="56"/>
-      <c r="H83" s="56"/>
-      <c r="I83" s="56" t="s">
+      <c r="F83" s="45"/>
+      <c r="G83" s="45"/>
+      <c r="H83" s="45"/>
+      <c r="I83" s="45" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="56"/>
-      <c r="K83" s="56"/>
+      <c r="J83" s="45"/>
+      <c r="K83" s="45"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -4767,17 +4756,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="56" t="s">
+      <c r="E84" s="45" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="56"/>
-      <c r="G84" s="56"/>
-      <c r="H84" s="56"/>
-      <c r="I84" s="56" t="s">
+      <c r="F84" s="45"/>
+      <c r="G84" s="45"/>
+      <c r="H84" s="45"/>
+      <c r="I84" s="45" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="56"/>
-      <c r="K84" s="56"/>
+      <c r="J84" s="45"/>
+      <c r="K84" s="45"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -4794,17 +4783,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="56" t="s">
+      <c r="E85" s="45" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="56"/>
-      <c r="G85" s="56"/>
-      <c r="H85" s="56"/>
-      <c r="I85" s="56" t="s">
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="56"/>
-      <c r="K85" s="56"/>
+      <c r="J85" s="45"/>
+      <c r="K85" s="45"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -4821,17 +4810,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="56" t="s">
+      <c r="E86" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="56"/>
-      <c r="G86" s="56"/>
-      <c r="H86" s="56"/>
-      <c r="I86" s="56" t="s">
+      <c r="F86" s="45"/>
+      <c r="G86" s="45"/>
+      <c r="H86" s="45"/>
+      <c r="I86" s="45" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="56"/>
-      <c r="K86" s="56"/>
+      <c r="J86" s="45"/>
+      <c r="K86" s="45"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -4848,17 +4837,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="56" t="s">
+      <c r="E87" s="45" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="56"/>
-      <c r="G87" s="56"/>
-      <c r="H87" s="56"/>
-      <c r="I87" s="56" t="s">
+      <c r="F87" s="45"/>
+      <c r="G87" s="45"/>
+      <c r="H87" s="45"/>
+      <c r="I87" s="45" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="56"/>
-      <c r="K87" s="56"/>
+      <c r="J87" s="45"/>
+      <c r="K87" s="45"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -4875,17 +4864,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="64" t="s">
+      <c r="E88" s="46" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="64"/>
-      <c r="G88" s="64"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="64" t="s">
+      <c r="F88" s="46"/>
+      <c r="G88" s="46"/>
+      <c r="H88" s="46"/>
+      <c r="I88" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="64"/>
-      <c r="K88" s="64"/>
+      <c r="J88" s="46"/>
+      <c r="K88" s="46"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -4902,19 +4891,19 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="64" t="s">
+      <c r="E89" s="46" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="64"/>
-      <c r="G89" s="64"/>
-      <c r="H89" s="64"/>
-      <c r="I89" s="64" t="s">
+      <c r="F89" s="46"/>
+      <c r="G89" s="46"/>
+      <c r="H89" s="46"/>
+      <c r="I89" s="46" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="64"/>
-      <c r="K89" s="64"/>
+      <c r="J89" s="46"/>
+      <c r="K89" s="46"/>
       <c r="L89" s="27" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M89" s="10"/>
     </row>
@@ -4929,19 +4918,19 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="46" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="64"/>
-      <c r="G90" s="64"/>
-      <c r="H90" s="64"/>
-      <c r="I90" s="64" t="s">
+      <c r="F90" s="46"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="46"/>
+      <c r="I90" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="64"/>
-      <c r="K90" s="64"/>
+      <c r="J90" s="46"/>
+      <c r="K90" s="46"/>
       <c r="L90" s="27" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M90" s="10"/>
     </row>
@@ -4956,19 +4945,19 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="64" t="s">
+      <c r="E91" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="64"/>
-      <c r="G91" s="64"/>
-      <c r="H91" s="64"/>
-      <c r="I91" s="64" t="s">
+      <c r="F91" s="46"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="46"/>
+      <c r="I91" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="64"/>
-      <c r="K91" s="64"/>
+      <c r="J91" s="46"/>
+      <c r="K91" s="46"/>
       <c r="L91" s="27" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M91" s="10"/>
     </row>
@@ -4979,13 +4968,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="66"/>
-      <c r="F92" s="66"/>
-      <c r="G92" s="66"/>
-      <c r="H92" s="66"/>
-      <c r="I92" s="66"/>
-      <c r="J92" s="66"/>
-      <c r="K92" s="66"/>
+      <c r="E92" s="52"/>
+      <c r="F92" s="52"/>
+      <c r="G92" s="52"/>
+      <c r="H92" s="52"/>
+      <c r="I92" s="52"/>
+      <c r="J92" s="52"/>
+      <c r="K92" s="52"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -4998,13 +4987,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="66"/>
-      <c r="F93" s="66"/>
-      <c r="G93" s="66"/>
-      <c r="H93" s="66"/>
-      <c r="I93" s="66"/>
-      <c r="J93" s="66"/>
-      <c r="K93" s="66"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="52"/>
+      <c r="G93" s="52"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -5017,13 +5006,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="66"/>
-      <c r="F94" s="66"/>
-      <c r="G94" s="66"/>
-      <c r="H94" s="66"/>
-      <c r="I94" s="66"/>
-      <c r="J94" s="66"/>
-      <c r="K94" s="66"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="52"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -5036,13 +5025,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="66"/>
-      <c r="F95" s="66"/>
-      <c r="G95" s="66"/>
-      <c r="H95" s="66"/>
-      <c r="I95" s="66"/>
-      <c r="J95" s="66"/>
-      <c r="K95" s="66"/>
+      <c r="E95" s="52"/>
+      <c r="F95" s="52"/>
+      <c r="G95" s="52"/>
+      <c r="H95" s="52"/>
+      <c r="I95" s="52"/>
+      <c r="J95" s="52"/>
+      <c r="K95" s="52"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -5055,13 +5044,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="66"/>
-      <c r="F96" s="66"/>
-      <c r="G96" s="66"/>
-      <c r="H96" s="66"/>
-      <c r="I96" s="66"/>
-      <c r="J96" s="66"/>
-      <c r="K96" s="66"/>
+      <c r="E96" s="52"/>
+      <c r="F96" s="52"/>
+      <c r="G96" s="52"/>
+      <c r="H96" s="52"/>
+      <c r="I96" s="52"/>
+      <c r="J96" s="52"/>
+      <c r="K96" s="52"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5074,13 +5063,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="66"/>
-      <c r="F97" s="66"/>
-      <c r="G97" s="66"/>
-      <c r="H97" s="66"/>
-      <c r="I97" s="66"/>
-      <c r="J97" s="66"/>
-      <c r="K97" s="66"/>
+      <c r="E97" s="52"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="52"/>
+      <c r="H97" s="52"/>
+      <c r="I97" s="52"/>
+      <c r="J97" s="52"/>
+      <c r="K97" s="52"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5093,13 +5082,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="66"/>
-      <c r="F98" s="66"/>
-      <c r="G98" s="66"/>
-      <c r="H98" s="66"/>
-      <c r="I98" s="66"/>
-      <c r="J98" s="66"/>
-      <c r="K98" s="66"/>
+      <c r="E98" s="52"/>
+      <c r="F98" s="52"/>
+      <c r="G98" s="52"/>
+      <c r="H98" s="52"/>
+      <c r="I98" s="52"/>
+      <c r="J98" s="52"/>
+      <c r="K98" s="52"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -5112,13 +5101,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="66"/>
-      <c r="F99" s="66"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="66"/>
-      <c r="I99" s="66"/>
-      <c r="J99" s="66"/>
-      <c r="K99" s="66"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="52"/>
+      <c r="I99" s="52"/>
+      <c r="J99" s="52"/>
+      <c r="K99" s="52"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -5131,13 +5120,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="66"/>
-      <c r="F100" s="66"/>
-      <c r="G100" s="66"/>
-      <c r="H100" s="66"/>
-      <c r="I100" s="66"/>
-      <c r="J100" s="66"/>
-      <c r="K100" s="66"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52"/>
+      <c r="I100" s="52"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="52"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5145,45 +5134,140 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -5208,140 +5292,45 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -5751,148 +5740,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="73"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="77"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="69" t="e" vm="2">
+      <c r="B3" s="73" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="77" t="s">
+      <c r="J3" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="69" t="e" vm="3">
+      <c r="N3" s="73" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="77" t="s">
+      <c r="J4" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="74" t="s">
+      <c r="F5" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="76"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="79"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78" t="s">
+      <c r="C8" s="69"/>
+      <c r="D8" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="75" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75" t="s">
+      <c r="C10" s="71"/>
+      <c r="D10" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75" t="s">
+      <c r="C11" s="71"/>
+      <c r="D11" s="71" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5903,6 +5884,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E7D9CA-FBA7-4019-8259-1503ADC7F22C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62083625-601E-425D-97C2-46038CAF7BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20535" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
-    <sheet name="피드백" sheetId="7" r:id="rId1"/>
-    <sheet name="편의성" sheetId="10" r:id="rId2"/>
-    <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId3"/>
+    <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
+    <sheet name="사운드피드백" sheetId="11" r:id="rId2"/>
+    <sheet name="편의성" sheetId="10" r:id="rId3"/>
+    <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -27,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="483">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1507,12 +1508,652 @@
     <t>아내방에 시계 혹은 열쇠를 얻은 이후 서랍을 클릭해도 모든 오브젝트가 클릭될 수 있게 수정 예정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>No.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.003</t>
+  </si>
+  <si>
+    <t>No.004</t>
+  </si>
+  <si>
+    <t>No.005</t>
+  </si>
+  <si>
+    <t>No.006</t>
+  </si>
+  <si>
+    <t>No.007</t>
+  </si>
+  <si>
+    <t>No.008</t>
+  </si>
+  <si>
+    <t>No.009</t>
+  </si>
+  <si>
+    <t>No.010</t>
+  </si>
+  <si>
+    <t>No.011</t>
+  </si>
+  <si>
+    <t>No.012</t>
+  </si>
+  <si>
+    <t>No.013</t>
+  </si>
+  <si>
+    <t>No.014</t>
+  </si>
+  <si>
+    <t>No.015</t>
+  </si>
+  <si>
+    <t>No.016</t>
+  </si>
+  <si>
+    <t>No.017</t>
+  </si>
+  <si>
+    <t>No.018</t>
+  </si>
+  <si>
+    <t>No.019</t>
+  </si>
+  <si>
+    <t>No.020</t>
+  </si>
+  <si>
+    <t>No.021</t>
+  </si>
+  <si>
+    <t>No.022</t>
+  </si>
+  <si>
+    <t>No.023</t>
+  </si>
+  <si>
+    <t>No.024</t>
+  </si>
+  <si>
+    <t>No.025</t>
+  </si>
+  <si>
+    <t>No.026</t>
+  </si>
+  <si>
+    <t>No.027</t>
+  </si>
+  <si>
+    <t>No.028</t>
+  </si>
+  <si>
+    <t>No.029</t>
+  </si>
+  <si>
+    <t>No.030</t>
+  </si>
+  <si>
+    <t>No.031</t>
+  </si>
+  <si>
+    <t>No.032</t>
+  </si>
+  <si>
+    <t>No.033</t>
+  </si>
+  <si>
+    <t>No.034</t>
+  </si>
+  <si>
+    <t>No.035</t>
+  </si>
+  <si>
+    <t>No.036</t>
+  </si>
+  <si>
+    <t>No.037</t>
+  </si>
+  <si>
+    <t>No.038</t>
+  </si>
+  <si>
+    <t>No.039</t>
+  </si>
+  <si>
+    <t>No.040</t>
+  </si>
+  <si>
+    <t>No.041</t>
+  </si>
+  <si>
+    <t>No.042</t>
+  </si>
+  <si>
+    <t>No.043</t>
+  </si>
+  <si>
+    <t>No.044</t>
+  </si>
+  <si>
+    <t>No.045</t>
+  </si>
+  <si>
+    <t>No.046</t>
+  </si>
+  <si>
+    <t>No.047</t>
+  </si>
+  <si>
+    <t>No.048</t>
+  </si>
+  <si>
+    <t>No.049</t>
+  </si>
+  <si>
+    <t>No.050</t>
+  </si>
+  <si>
+    <t>No.051</t>
+  </si>
+  <si>
+    <t>No.052</t>
+  </si>
+  <si>
+    <t>No.053</t>
+  </si>
+  <si>
+    <t>No.054</t>
+  </si>
+  <si>
+    <t>No.055</t>
+  </si>
+  <si>
+    <t>No.056</t>
+  </si>
+  <si>
+    <t>No.057</t>
+  </si>
+  <si>
+    <t>No.058</t>
+  </si>
+  <si>
+    <t>No.059</t>
+  </si>
+  <si>
+    <t>No.060</t>
+  </si>
+  <si>
+    <t>No.061</t>
+  </si>
+  <si>
+    <t>No.062</t>
+  </si>
+  <si>
+    <t>No.063</t>
+  </si>
+  <si>
+    <t>No.064</t>
+  </si>
+  <si>
+    <t>No.065</t>
+  </si>
+  <si>
+    <t>No.066</t>
+  </si>
+  <si>
+    <t>No.067</t>
+  </si>
+  <si>
+    <t>No.068</t>
+  </si>
+  <si>
+    <t>No.069</t>
+  </si>
+  <si>
+    <t>No.070</t>
+  </si>
+  <si>
+    <t>No.071</t>
+  </si>
+  <si>
+    <t>No.072</t>
+  </si>
+  <si>
+    <t>No.073</t>
+  </si>
+  <si>
+    <t>No.074</t>
+  </si>
+  <si>
+    <t>No.075</t>
+  </si>
+  <si>
+    <t>No.076</t>
+  </si>
+  <si>
+    <t>No.077</t>
+  </si>
+  <si>
+    <t>No.078</t>
+  </si>
+  <si>
+    <t>No.079</t>
+  </si>
+  <si>
+    <t>No.080</t>
+  </si>
+  <si>
+    <t>No.081</t>
+  </si>
+  <si>
+    <t>No.082</t>
+  </si>
+  <si>
+    <t>No.083</t>
+  </si>
+  <si>
+    <t>No.084</t>
+  </si>
+  <si>
+    <t>No.085</t>
+  </si>
+  <si>
+    <t>No.086</t>
+  </si>
+  <si>
+    <t>No.087</t>
+  </si>
+  <si>
+    <t>No.088</t>
+  </si>
+  <si>
+    <t>No.089</t>
+  </si>
+  <si>
+    <t>No.090</t>
+  </si>
+  <si>
+    <t>No.091</t>
+  </si>
+  <si>
+    <t>No.092</t>
+  </si>
+  <si>
+    <t>No.093</t>
+  </si>
+  <si>
+    <t>No.094</t>
+  </si>
+  <si>
+    <t>No.095</t>
+  </si>
+  <si>
+    <t>No.096</t>
+  </si>
+  <si>
+    <t>No.097</t>
+  </si>
+  <si>
+    <t>No.098</t>
+  </si>
+  <si>
+    <t>No.099</t>
+  </si>
+  <si>
+    <t>No.100</t>
+  </si>
+  <si>
+    <t>사운드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌드한 인트로 씬에서 전기톱에 사운드가 오프닝 씬까지 따라와서 전기톱 소리가 계속 울림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전기톱 사운드가 현재 10초 정도로 설정되있는 상태에서 3초 ~ 3.5초 사이로 수정 요청 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사운드 요청 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴물이 달려들 때 "빠빰!" 이외에는 크게 없는 상태이고 괴물의 직접적인 소리가 없음 확인함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 사항으로 괴물의 괴성 소리 혹은 비명 소리를 추가가 가능하면 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌드 할 경우 초인종 이후 철문이 열리는 소리가 없는 것을 확인
+그 다음에 열리는 저택 대문 사운드와 비교 바람 
+( 기존에 있던 문 사운드에 대문 사운드 추가된 것 처럼 들림 / 또한 철문과 대문의 사운드가 같음 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철문이 열리는 소리를 오디오 컨트롤에 추가 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다용도실에서 전기를 킬 때 나오는 사운드에 시간이 현재 8.5초 정도로 맞춰져있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기를 킬 때 사운드에 유지 시간을 3~4초 사이로 수정 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오프닝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다용도실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화 중 스탠딩 캐릭터에 크기가 일정하지 않음 " 저택관련 전화내용" 부분 ( 전화를 받고 대화 중 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스탠딩 일러스트에 크기를 동일하게 변경 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스위치를 조작하여 전원을 켠(ON) 상태에서 다른 씬으로 이동했다가 다시 원래 씬으로 돌아오면, 
+내부 전원 데이터는 켜짐(ON)으로 유지되나 스위치의 UI 그림은 꺼짐(OFF) 상태로 보임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">이미지의 변동을 유지되게 수정요청
+1단계: 시작 블록 만들기 ( 단순한 참조사항 AI가 알려준 방법 )
+플로우차트 창 빈 곳을 우클릭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Add Block을 눌러 새 블록을 하나 만듭니다. (이름은 Init_Switch 등으로 지어주세요)
+해당 블록을 클릭하고 인스펙터 창에서 Execute On Event 드롭다운을 눌러 Game Started로 설정합니다. (이렇게 하면 방에 들어오자마자 이 블록이 자동으로 1번 실행됩니다.)
+2단계: 그림 맞춰주는 명령어 조립하기
+블록의 명령어 칸에 + 버튼을 눌러 아래 순서대로 7개의 명령어를 조립해 줍니다. 아까 버튼 조작하실 때 쓰셨던 것과 똑같습니다.
+[Flow] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [If] (조건: ElectricOn == True로 설정)
+[Unity] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [Set Active] (on_switch 오브젝트 연결, True 체크 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+[Unity] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [Set Active] (off_Switch 오브젝트 연결, False 체크 해제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>❌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+[Flow] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [Else]
+[Unity] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [Set Active] (on_switch 오브젝트 연결, False 체크 해제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>❌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+[Unity] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [Set Active] (off_Switch 오브젝트 연결, True 체크 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+[Flow] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>➡️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [End]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수도꼭지 안보이는 상태 Faucet 에 들어있는 Canvas 에서 Sort Order를 3으로 올리면 다시 보임 수정 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단순하게 Sort Order를 3으로 올려도 해결이 되는 것 처럼 보이지만,
+전체적인 Canvas를 조정해야할 것 처럼 보이는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인홀 화면이 두번 나오는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frowchart가 이미 들어있는 상황에서 하나가 복제되어 재 생성되어 발생하는 현상 ( DestroyOnLoad가 안되고 생성되는 느낌 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1609,8 +2250,20 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1667,6 +2320,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDAE9F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1775,7 +2434,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1911,9 +2570,60 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1932,9 +2642,6 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1944,9 +2651,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1970,12 +2674,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2026,7 +2724,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="2" xr:uid="{E5ED1C55-8C74-49FF-A6AC-1A927F2C2FB4}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="8">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -2064,12 +2762,34 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC66"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDAE9F8"/>
+      <color rgb="FF6666FF"/>
       <color rgb="FFFBE2D5"/>
-      <color rgb="FFDAE9F8"/>
       <color rgb="FFFFCC66"/>
       <color rgb="FFFF5050"/>
       <color rgb="FF99FF99"/>
@@ -2495,36 +3215,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -2537,17 +3257,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66" t="s">
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -2566,17 +3286,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="E4" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61" t="s">
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -2593,17 +3313,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="61" t="s">
+      <c r="E5" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -2620,17 +3340,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61" t="s">
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -2647,17 +3367,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="61" t="s">
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -2674,17 +3394,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="61" t="s">
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -2701,17 +3421,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="E9" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="61" t="s">
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -2728,17 +3448,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="61" t="s">
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -2755,17 +3475,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="61" t="s">
+      <c r="E11" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61" t="s">
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
+      <c r="J11" s="76"/>
+      <c r="K11" s="76"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -2782,17 +3502,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61" t="s">
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="76"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -2809,17 +3529,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61" t="s">
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="76"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -2836,17 +3556,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="61" t="s">
+      <c r="E14" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61" t="s">
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -2863,17 +3583,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="61" t="s">
+      <c r="E15" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61" t="s">
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -2890,17 +3610,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="61" t="s">
+      <c r="E16" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61" t="s">
+      <c r="F16" s="76"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -2917,17 +3637,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61" t="s">
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -2944,17 +3664,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="61" t="s">
+      <c r="E18" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61" t="s">
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -2971,17 +3691,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56" t="s">
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -2998,17 +3718,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56" t="s">
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="56"/>
-      <c r="K20" s="56"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3025,17 +3745,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56" t="s">
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3052,17 +3772,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56" t="s">
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3079,17 +3799,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56" t="s">
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="56"/>
-      <c r="K23" s="56"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3106,17 +3826,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56" t="s">
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3133,17 +3853,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56" t="s">
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3160,17 +3880,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="72" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57" t="s">
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3202,17 +3922,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="66" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="49" t="s">
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="50"/>
-      <c r="K27" s="51"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="68"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -3235,17 +3955,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="49" t="s">
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="66" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="50"/>
-      <c r="K28" s="51"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="68"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -3265,17 +3985,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="66" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="49" t="s">
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="50"/>
-      <c r="K29" s="51"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="68"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -3295,17 +4015,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="72" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57" t="s">
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -3325,17 +4045,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53" t="s">
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -3352,17 +4072,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53" t="s">
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -3379,17 +4099,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53" t="s">
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -3406,17 +4126,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="54" t="s">
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="70" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="47"/>
-      <c r="K34" s="48"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="65"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -3433,17 +4153,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="46" t="s">
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -3460,17 +4180,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="46" t="s">
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="63" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -3487,17 +4207,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="54" t="s">
+      <c r="E37" s="70" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="46" t="s">
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="63" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -3514,17 +4234,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="54" t="s">
+      <c r="E38" s="70" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="46" t="s">
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="47"/>
-      <c r="K38" s="48"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="65"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -3541,17 +4261,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="56" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45" t="s">
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -3568,17 +4288,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="56" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45" t="s">
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -3595,17 +4315,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="45" t="s">
+      <c r="E41" s="56" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45" t="s">
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="56"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -3622,17 +4342,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="56" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45" t="s">
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -3649,17 +4369,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="45" t="s">
+      <c r="E43" s="56" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45" t="s">
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="45"/>
-      <c r="K43" s="45"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="56"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -3676,17 +4396,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="45" t="s">
+      <c r="E44" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45" t="s">
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="56"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -3703,17 +4423,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="45" t="s">
+      <c r="E45" s="56" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45" t="s">
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="56"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -3730,17 +4450,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="56" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45" t="s">
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
+      <c r="J46" s="56"/>
+      <c r="K46" s="56"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -3757,17 +4477,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="45" t="s">
+      <c r="E47" s="56" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45" t="s">
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
+      <c r="J47" s="56"/>
+      <c r="K47" s="56"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -3784,17 +4504,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="45" t="s">
+      <c r="E48" s="56" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45" t="s">
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
+      <c r="J48" s="56"/>
+      <c r="K48" s="56"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -3811,17 +4531,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="56" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45" t="s">
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="56"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -3838,17 +4558,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45" t="s">
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
+      <c r="J50" s="56"/>
+      <c r="K50" s="56"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -3865,17 +4585,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="45" t="s">
+      <c r="E51" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45" t="s">
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -3892,17 +4612,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="45" t="s">
+      <c r="E52" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45" t="s">
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="45"/>
-      <c r="K52" s="45"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="56"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -3919,17 +4639,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="45" t="s">
+      <c r="E53" s="56" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45" t="s">
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -3946,17 +4666,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="46" t="s">
+      <c r="E54" s="63" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46" t="s">
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="63"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -3973,17 +4693,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="46" t="s">
+      <c r="E55" s="63" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46" t="s">
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="63"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4000,17 +4720,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="46" t="s">
+      <c r="E56" s="63" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46" t="s">
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="63" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
+      <c r="J56" s="63"/>
+      <c r="K56" s="63"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4027,17 +4747,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="45" t="s">
+      <c r="E57" s="56" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45" t="s">
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45"/>
+      <c r="J57" s="56"/>
+      <c r="K57" s="56"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4054,17 +4774,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="45" t="s">
+      <c r="E58" s="56" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45" t="s">
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4081,17 +4801,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="56" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45" t="s">
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
+      <c r="J59" s="56"/>
+      <c r="K59" s="56"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4108,17 +4828,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="56" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45" t="s">
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="56"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4135,17 +4855,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="45" t="s">
+      <c r="E61" s="56" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45" t="s">
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4162,17 +4882,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="45" t="s">
+      <c r="E62" s="56" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="45"/>
-      <c r="G62" s="45"/>
-      <c r="H62" s="45"/>
-      <c r="I62" s="45" t="s">
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="45"/>
-      <c r="K62" s="45"/>
+      <c r="J62" s="56"/>
+      <c r="K62" s="56"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4189,17 +4909,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="45" t="s">
+      <c r="E63" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45" t="e" vm="1">
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45"/>
+      <c r="J63" s="56"/>
+      <c r="K63" s="56"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -4216,17 +4936,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="45" t="s">
+      <c r="E64" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="45" t="s">
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="56" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="45"/>
-      <c r="K64" s="45"/>
+      <c r="J64" s="56"/>
+      <c r="K64" s="56"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -4243,17 +4963,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="45" t="s">
+      <c r="E65" s="56" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45" t="s">
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+      <c r="I65" s="56" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="45"/>
-      <c r="K65" s="45"/>
+      <c r="J65" s="56"/>
+      <c r="K65" s="56"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -4270,17 +4990,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="45" t="s">
+      <c r="E66" s="56" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45"/>
-      <c r="H66" s="45"/>
-      <c r="I66" s="45" t="s">
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="45"/>
-      <c r="K66" s="45"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -4297,17 +5017,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="55" t="s">
+      <c r="E67" s="71" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="55"/>
-      <c r="G67" s="55"/>
-      <c r="H67" s="55"/>
-      <c r="I67" s="45" t="s">
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="45"/>
-      <c r="K67" s="45"/>
+      <c r="J67" s="56"/>
+      <c r="K67" s="56"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -4324,17 +5044,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="46" t="s">
+      <c r="E68" s="63" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46" t="s">
+      <c r="F68" s="63"/>
+      <c r="G68" s="63"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="63" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
+      <c r="J68" s="63"/>
+      <c r="K68" s="63"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -4351,17 +5071,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="46" t="s">
+      <c r="E69" s="63" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46" t="s">
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="63"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -4378,17 +5098,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="46" t="s">
+      <c r="E70" s="63" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46" t="s">
+      <c r="F70" s="63"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="63" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="63"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -4405,17 +5125,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="46" t="s">
+      <c r="E71" s="63" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46" t="s">
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="63"/>
+      <c r="I71" s="63" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
+      <c r="J71" s="63"/>
+      <c r="K71" s="63"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -4432,17 +5152,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="46" t="s">
+      <c r="E72" s="63" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46" t="s">
+      <c r="F72" s="63"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
+      <c r="J72" s="63"/>
+      <c r="K72" s="63"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -4459,17 +5179,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="46" t="s">
+      <c r="E73" s="63" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="46" t="s">
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="63"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -4486,17 +5206,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="46" t="s">
+      <c r="E74" s="63" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46" t="s">
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="63"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -4513,17 +5233,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="46" t="s">
+      <c r="E75" s="63" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46" t="s">
+      <c r="F75" s="63"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="63" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="63"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -4540,17 +5260,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="46" t="s">
+      <c r="E76" s="63" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46" t="s">
+      <c r="F76" s="63"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="63" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
+      <c r="J76" s="63"/>
+      <c r="K76" s="63"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -4567,17 +5287,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="46" t="s">
+      <c r="E77" s="63" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="46" t="s">
+      <c r="F77" s="63"/>
+      <c r="G77" s="63"/>
+      <c r="H77" s="63"/>
+      <c r="I77" s="63" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
+      <c r="J77" s="63"/>
+      <c r="K77" s="63"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -4594,17 +5314,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="46" t="s">
+      <c r="E78" s="63" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46" t="s">
+      <c r="F78" s="63"/>
+      <c r="G78" s="63"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="63" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
+      <c r="J78" s="63"/>
+      <c r="K78" s="63"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -4621,17 +5341,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="46" t="s">
+      <c r="E79" s="63" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="46" t="s">
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="63" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
+      <c r="J79" s="63"/>
+      <c r="K79" s="63"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -4648,17 +5368,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="46" t="s">
+      <c r="E80" s="63" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46" t="s">
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="63"/>
+      <c r="I80" s="63" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
+      <c r="J80" s="63"/>
+      <c r="K80" s="63"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -4675,17 +5395,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="45" t="s">
+      <c r="E81" s="56" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="45"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45"/>
-      <c r="I81" s="45" t="s">
+      <c r="F81" s="56"/>
+      <c r="G81" s="56"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="56" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="45"/>
-      <c r="K81" s="45"/>
+      <c r="J81" s="56"/>
+      <c r="K81" s="56"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -4702,17 +5422,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="45" t="s">
+      <c r="E82" s="56" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="45" t="s">
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="45"/>
-      <c r="K82" s="45"/>
+      <c r="J82" s="56"/>
+      <c r="K82" s="56"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -4729,17 +5449,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="45" t="s">
+      <c r="E83" s="56" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="45"/>
-      <c r="G83" s="45"/>
-      <c r="H83" s="45"/>
-      <c r="I83" s="45" t="s">
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="45"/>
-      <c r="K83" s="45"/>
+      <c r="J83" s="56"/>
+      <c r="K83" s="56"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -4756,17 +5476,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="45" t="s">
+      <c r="E84" s="56" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="45"/>
-      <c r="G84" s="45"/>
-      <c r="H84" s="45"/>
-      <c r="I84" s="45" t="s">
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="56" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="45"/>
-      <c r="K84" s="45"/>
+      <c r="J84" s="56"/>
+      <c r="K84" s="56"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -4783,17 +5503,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="45" t="s">
+      <c r="E85" s="56" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="45"/>
-      <c r="G85" s="45"/>
-      <c r="H85" s="45"/>
-      <c r="I85" s="45" t="s">
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="45"/>
-      <c r="K85" s="45"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -4810,17 +5530,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="45" t="s">
+      <c r="E86" s="56" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="45"/>
-      <c r="G86" s="45"/>
-      <c r="H86" s="45"/>
-      <c r="I86" s="45" t="s">
+      <c r="F86" s="56"/>
+      <c r="G86" s="56"/>
+      <c r="H86" s="56"/>
+      <c r="I86" s="56" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="45"/>
-      <c r="K86" s="45"/>
+      <c r="J86" s="56"/>
+      <c r="K86" s="56"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -4837,17 +5557,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="45" t="s">
+      <c r="E87" s="56" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="45"/>
-      <c r="G87" s="45"/>
-      <c r="H87" s="45"/>
-      <c r="I87" s="45" t="s">
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="56"/>
+      <c r="I87" s="56" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="45"/>
-      <c r="K87" s="45"/>
+      <c r="J87" s="56"/>
+      <c r="K87" s="56"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -4864,17 +5584,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="46" t="s">
+      <c r="E88" s="63" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46" t="s">
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="63" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="63"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -4891,17 +5611,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="46" t="s">
+      <c r="E89" s="63" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="46"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="46"/>
-      <c r="I89" s="46" t="s">
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="46"/>
-      <c r="K89" s="46"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="63"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -4918,17 +5638,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="46" t="s">
+      <c r="E90" s="63" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46" t="s">
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="63"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -4945,17 +5665,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="46" t="s">
+      <c r="E91" s="63" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46" t="s">
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="63" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
+      <c r="J91" s="63"/>
+      <c r="K91" s="63"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -4963,37 +5683,53 @@
     </row>
     <row r="92" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="52"/>
-      <c r="H92" s="52"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
+      <c r="C92" s="39">
+        <v>46179</v>
+      </c>
+      <c r="D92" s="38" t="s">
+        <v>473</v>
+      </c>
+      <c r="E92" s="69" t="s">
+        <v>475</v>
+      </c>
+      <c r="F92" s="69"/>
+      <c r="G92" s="69"/>
+      <c r="H92" s="69"/>
+      <c r="I92" s="69" t="s">
+        <v>476</v>
+      </c>
+      <c r="J92" s="69"/>
+      <c r="K92" s="69"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M92" s="10"/>
     </row>
-    <row r="93" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" s="17" customFormat="1" ht="302.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
+      <c r="C93" s="39">
+        <v>46179</v>
+      </c>
+      <c r="D93" s="38" t="s">
+        <v>474</v>
+      </c>
+      <c r="E93" s="69" t="s">
+        <v>477</v>
+      </c>
+      <c r="F93" s="69"/>
+      <c r="G93" s="69"/>
+      <c r="H93" s="69"/>
+      <c r="I93" s="69" t="s">
+        <v>478</v>
+      </c>
+      <c r="J93" s="69"/>
+      <c r="K93" s="69"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -5001,18 +5737,26 @@
     </row>
     <row r="94" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="52"/>
-      <c r="I94" s="52"/>
-      <c r="J94" s="52"/>
-      <c r="K94" s="52"/>
+      <c r="C94" s="39">
+        <v>46179</v>
+      </c>
+      <c r="D94" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="E94" s="69" t="s">
+        <v>479</v>
+      </c>
+      <c r="F94" s="69"/>
+      <c r="G94" s="69"/>
+      <c r="H94" s="69"/>
+      <c r="I94" s="69" t="s">
+        <v>480</v>
+      </c>
+      <c r="J94" s="69"/>
+      <c r="K94" s="69"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -5020,18 +5764,26 @@
     </row>
     <row r="95" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
+      <c r="C95" s="39">
+        <v>46179</v>
+      </c>
+      <c r="D95" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="E95" s="69" t="s">
+        <v>481</v>
+      </c>
+      <c r="F95" s="69"/>
+      <c r="G95" s="69"/>
+      <c r="H95" s="69"/>
+      <c r="I95" s="69" t="s">
+        <v>482</v>
+      </c>
+      <c r="J95" s="69"/>
+      <c r="K95" s="69"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -5044,13 +5796,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="52"/>
-      <c r="H96" s="52"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="48"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5063,13 +5815,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="52"/>
-      <c r="H97" s="52"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="48"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5082,13 +5834,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -5101,13 +5853,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="52"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="52"/>
-      <c r="J99" s="52"/>
-      <c r="K99" s="52"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -5120,13 +5872,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="52"/>
-      <c r="H100" s="52"/>
-      <c r="I100" s="52"/>
-      <c r="J100" s="52"/>
-      <c r="K100" s="52"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5334,13 +6086,13 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"검토 중"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"거부"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"승인"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5355,6 +6107,2270 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C11BA6-98B8-4AA9-B610-E12E1F0ACA2C}">
+  <dimension ref="A1:U103"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="7.625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="33.625" style="16" customWidth="1"/>
+    <col min="5" max="8" width="20.625" style="12" customWidth="1"/>
+    <col min="9" max="11" width="30.625" style="17" customWidth="1"/>
+    <col min="12" max="12" width="18" style="21" customWidth="1"/>
+    <col min="13" max="13" width="44.875" customWidth="1"/>
+    <col min="20" max="21" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+    </row>
+    <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+    </row>
+    <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30"/>
+      <c r="B4" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4" s="46">
+        <v>46179</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>463</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>464</v>
+      </c>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="59" t="s">
+        <v>465</v>
+      </c>
+      <c r="J4" s="60"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="31"/>
+    </row>
+    <row r="5" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
+      <c r="B5" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" s="46">
+        <v>46179</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>463</v>
+      </c>
+      <c r="E5" s="62" t="s">
+        <v>469</v>
+      </c>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62" t="s">
+        <v>470</v>
+      </c>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31"/>
+      <c r="B6" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C6" s="33">
+        <v>46179</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>467</v>
+      </c>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55" t="s">
+        <v>468</v>
+      </c>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="31"/>
+    </row>
+    <row r="7" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="B7" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="C7" s="46">
+        <v>46179</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>463</v>
+      </c>
+      <c r="E7" s="62" t="s">
+        <v>471</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62" t="s">
+        <v>472</v>
+      </c>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="31"/>
+    </row>
+    <row r="8" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31"/>
+      <c r="B8" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="31"/>
+    </row>
+    <row r="9" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="31"/>
+      <c r="B9" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="31"/>
+    </row>
+    <row r="10" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="B10" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="31"/>
+      <c r="B11" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="31"/>
+    </row>
+    <row r="12" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="31"/>
+      <c r="B12" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="31"/>
+    </row>
+    <row r="13" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="31"/>
+    </row>
+    <row r="14" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="31"/>
+    </row>
+    <row r="15" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31"/>
+      <c r="B15" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="31"/>
+    </row>
+    <row r="16" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="B16" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="31"/>
+    </row>
+    <row r="17" spans="1:21" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31"/>
+      <c r="B17" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="31"/>
+    </row>
+    <row r="18" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="10"/>
+    </row>
+    <row r="19" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="10"/>
+    </row>
+    <row r="21" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="26" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="10"/>
+      <c r="P26" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q26" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="S26" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="T26" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="U26" s="17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M27" s="10"/>
+      <c r="T27" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="U27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="10"/>
+      <c r="T28" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="T29" s="17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="10"/>
+      <c r="T30" s="17" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10"/>
+      <c r="B31" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="10"/>
+    </row>
+    <row r="32" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="10"/>
+    </row>
+    <row r="33" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="10"/>
+    </row>
+    <row r="34" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
+      <c r="B34" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="10"/>
+    </row>
+    <row r="35" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10"/>
+      <c r="B35" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M35" s="10"/>
+    </row>
+    <row r="36" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10"/>
+      <c r="B36" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M36" s="10"/>
+    </row>
+    <row r="37" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10"/>
+      <c r="B37" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="10"/>
+    </row>
+    <row r="38" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="10"/>
+    </row>
+    <row r="39" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M39" s="10"/>
+    </row>
+    <row r="40" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M40" s="10"/>
+    </row>
+    <row r="41" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
+      <c r="L41" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="10"/>
+    </row>
+    <row r="42" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M42" s="10"/>
+    </row>
+    <row r="43" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
+      <c r="L43" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M43" s="10"/>
+    </row>
+    <row r="44" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
+      <c r="L44" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="10"/>
+    </row>
+    <row r="45" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
+      <c r="L45" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="10"/>
+    </row>
+    <row r="46" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
+      <c r="L46" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M46" s="10"/>
+    </row>
+    <row r="47" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="10"/>
+      <c r="B47" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
+      <c r="L47" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" s="10"/>
+    </row>
+    <row r="48" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
+      <c r="L48" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M48" s="10"/>
+    </row>
+    <row r="49" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M49" s="10"/>
+    </row>
+    <row r="50" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M50" s="10"/>
+    </row>
+    <row r="51" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="10"/>
+      <c r="B51" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M51" s="10"/>
+    </row>
+    <row r="52" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="10"/>
+      <c r="B52" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
+      <c r="L52" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M52" s="10"/>
+    </row>
+    <row r="53" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="10"/>
+      <c r="B53" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
+      <c r="L53" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M53" s="10"/>
+    </row>
+    <row r="54" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10"/>
+      <c r="B54" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M54" s="10"/>
+    </row>
+    <row r="55" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="10"/>
+      <c r="B55" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
+      <c r="L55" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55" s="10"/>
+    </row>
+    <row r="56" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="10"/>
+      <c r="B56" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
+      <c r="L56" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M56" s="10"/>
+    </row>
+    <row r="57" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="10"/>
+      <c r="B57" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
+      <c r="L57" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M57" s="10"/>
+    </row>
+    <row r="58" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10"/>
+      <c r="B58" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M58" s="10"/>
+    </row>
+    <row r="59" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="10"/>
+      <c r="B59" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
+      <c r="L59" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M59" s="10"/>
+    </row>
+    <row r="60" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="10"/>
+      <c r="B60" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
+      <c r="L60" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M60" s="10"/>
+    </row>
+    <row r="61" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="10"/>
+      <c r="B61" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
+      <c r="L61" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M61" s="10"/>
+    </row>
+    <row r="62" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="10"/>
+      <c r="B62" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
+      <c r="L62" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M62" s="10"/>
+    </row>
+    <row r="63" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="10"/>
+      <c r="B63" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
+      <c r="L63" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M63" s="10"/>
+    </row>
+    <row r="64" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="10"/>
+      <c r="B64" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
+      <c r="L64" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M64" s="10"/>
+    </row>
+    <row r="65" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="10"/>
+      <c r="B65" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="52"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="54"/>
+      <c r="L65" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M65" s="10"/>
+    </row>
+    <row r="66" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="10"/>
+      <c r="B66" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
+      <c r="L66" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M66" s="10"/>
+    </row>
+    <row r="67" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="10"/>
+      <c r="B67" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
+      <c r="L67" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M67" s="10"/>
+    </row>
+    <row r="68" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="10"/>
+      <c r="B68" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
+      <c r="L68" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M68" s="10"/>
+    </row>
+    <row r="69" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="10"/>
+      <c r="B69" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="52"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="54"/>
+      <c r="L69" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M69" s="10"/>
+    </row>
+    <row r="70" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="10"/>
+      <c r="B70" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
+      <c r="L70" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M70" s="10"/>
+    </row>
+    <row r="71" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="10"/>
+      <c r="B71" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
+      <c r="L71" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M71" s="10"/>
+    </row>
+    <row r="72" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="10"/>
+      <c r="B72" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48"/>
+      <c r="L72" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M72" s="10"/>
+    </row>
+    <row r="73" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="10"/>
+      <c r="B73" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="52"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="54"/>
+      <c r="I73" s="52"/>
+      <c r="J73" s="53"/>
+      <c r="K73" s="54"/>
+      <c r="L73" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M73" s="10"/>
+    </row>
+    <row r="74" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="10"/>
+      <c r="B74" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="48"/>
+      <c r="L74" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M74" s="10"/>
+    </row>
+    <row r="75" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="10"/>
+      <c r="B75" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M75" s="10"/>
+    </row>
+    <row r="76" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="10"/>
+      <c r="B76" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48"/>
+      <c r="L76" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M76" s="10"/>
+    </row>
+    <row r="77" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="10"/>
+      <c r="B77" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="48"/>
+      <c r="K77" s="48"/>
+      <c r="L77" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M77" s="10"/>
+    </row>
+    <row r="78" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="10"/>
+      <c r="B78" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
+      <c r="L78" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M78" s="10"/>
+    </row>
+    <row r="79" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="10"/>
+      <c r="B79" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
+      <c r="L79" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M79" s="10"/>
+    </row>
+    <row r="80" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="10"/>
+      <c r="B80" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="51"/>
+      <c r="I80" s="49"/>
+      <c r="J80" s="50"/>
+      <c r="K80" s="51"/>
+      <c r="L80" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M80" s="10"/>
+    </row>
+    <row r="81" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="10"/>
+      <c r="B81" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="51"/>
+      <c r="I81" s="49"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="51"/>
+      <c r="L81" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M81" s="10"/>
+    </row>
+    <row r="82" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="10"/>
+      <c r="B82" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="51"/>
+      <c r="I82" s="49"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="51"/>
+      <c r="L82" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M82" s="10"/>
+    </row>
+    <row r="83" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="10"/>
+      <c r="B83" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="51"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="50"/>
+      <c r="K83" s="51"/>
+      <c r="L83" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M83" s="10"/>
+    </row>
+    <row r="84" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="10"/>
+      <c r="B84" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="51"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="51"/>
+      <c r="L84" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M84" s="10"/>
+    </row>
+    <row r="85" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="10"/>
+      <c r="B85" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="51"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="51"/>
+      <c r="L85" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M85" s="10"/>
+    </row>
+    <row r="86" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="10"/>
+      <c r="B86" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="49"/>
+      <c r="J86" s="50"/>
+      <c r="K86" s="51"/>
+      <c r="L86" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M86" s="10"/>
+    </row>
+    <row r="87" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="10"/>
+      <c r="B87" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="50"/>
+      <c r="K87" s="51"/>
+      <c r="L87" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M87" s="10"/>
+    </row>
+    <row r="88" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="10"/>
+      <c r="B88" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="50"/>
+      <c r="K88" s="51"/>
+      <c r="L88" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M88" s="10"/>
+    </row>
+    <row r="89" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="10"/>
+      <c r="B89" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="51"/>
+      <c r="I89" s="49"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M89" s="10"/>
+    </row>
+    <row r="90" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="10"/>
+      <c r="B90" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="49"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="51"/>
+      <c r="I90" s="49"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M90" s="10"/>
+    </row>
+    <row r="91" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="10"/>
+      <c r="B91" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
+      <c r="L91" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M91" s="10"/>
+    </row>
+    <row r="92" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="10"/>
+      <c r="B92" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="48"/>
+      <c r="L92" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M92" s="10"/>
+    </row>
+    <row r="93" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="10"/>
+      <c r="B93" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="48"/>
+      <c r="L93" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M93" s="10"/>
+    </row>
+    <row r="94" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="10"/>
+      <c r="B94" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="48"/>
+      <c r="L94" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M94" s="10"/>
+    </row>
+    <row r="95" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="10"/>
+      <c r="B95" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="48"/>
+      <c r="L95" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M95" s="10"/>
+    </row>
+    <row r="96" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="10"/>
+      <c r="B96" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="48"/>
+      <c r="L96" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M96" s="10"/>
+    </row>
+    <row r="97" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="10"/>
+      <c r="B97" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="48"/>
+      <c r="L97" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M97" s="10"/>
+    </row>
+    <row r="98" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="10"/>
+      <c r="B98" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
+      <c r="L98" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M98" s="10"/>
+    </row>
+    <row r="99" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="10"/>
+      <c r="B99" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
+      <c r="L99" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M99" s="10"/>
+    </row>
+    <row r="100" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="10"/>
+      <c r="B100" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
+      <c r="L100" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M100" s="10"/>
+    </row>
+    <row r="101" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
+      <c r="J101" s="48"/>
+      <c r="K101" s="48"/>
+      <c r="L101" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M101" s="10"/>
+    </row>
+    <row r="102" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="48"/>
+      <c r="F102" s="48"/>
+      <c r="G102" s="48"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="48"/>
+      <c r="K102" s="48"/>
+      <c r="L102" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M102" s="10"/>
+    </row>
+    <row r="103" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="48"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="48"/>
+      <c r="K103" s="48"/>
+      <c r="L103" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M103" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="203">
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="L4:L103">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"검토 중"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"거부"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"승인"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L103" xr:uid="{10783737-3001-4C6F-AA7E-C3D9F580A692}">
+      <formula1>"승인,거부,검토 중,-"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DE762C-FA58-405A-90C9-B76434EC7F3A}">
   <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5368,42 +8384,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -5723,7 +8739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282F01E4-329A-4637-8D03-08736FA999D7}">
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5740,137 +8756,137 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="77"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="90"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="74" t="s">
+      <c r="N2" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="e" vm="2">
+      <c r="B3" s="86" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="73" t="e" vm="3">
+      <c r="N3" s="86" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="80" t="s">
+      <c r="J4" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="79"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="82" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69" t="s">
+      <c r="C8" s="82"/>
+      <c r="D8" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="71" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71" t="s">
+      <c r="C10" s="84"/>
+      <c r="D10" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71" t="s">
+      <c r="C11" s="84"/>
+      <c r="D11" s="84" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62083625-601E-425D-97C2-46038CAF7BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F7DC94-ADBF-4374-AFC7-FBE8246C0095}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -2579,9 +2579,93 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2591,96 +2675,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2688,34 +2715,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3215,36 +3215,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3257,17 +3257,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58" t="s">
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3286,17 +3286,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76" t="s">
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3313,17 +3313,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76" t="s">
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3340,17 +3340,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="76" t="s">
+      <c r="E6" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76" t="s">
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3367,17 +3367,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="76" t="s">
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3394,17 +3394,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="76" t="s">
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3421,17 +3421,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="76" t="s">
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3448,17 +3448,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="76" t="s">
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3475,17 +3475,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="76" t="s">
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="76"/>
-      <c r="K11" s="76"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3502,17 +3502,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76" t="s">
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3529,17 +3529,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76" t="s">
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3556,17 +3556,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76" t="s">
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3583,17 +3583,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="76" t="s">
+      <c r="E15" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="76"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76" t="s">
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3610,17 +3610,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="76" t="s">
+      <c r="E16" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76" t="s">
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3637,17 +3637,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="76" t="s">
+      <c r="E17" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76" t="s">
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3664,17 +3664,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="76" t="s">
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3691,17 +3691,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="E19" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55" t="s">
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3718,17 +3718,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="55" t="s">
+      <c r="E20" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55" t="s">
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3745,17 +3745,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="55" t="s">
+      <c r="E21" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55" t="s">
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3772,17 +3772,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="55" t="s">
+      <c r="E22" s="54" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55" t="s">
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3799,17 +3799,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="55" t="s">
+      <c r="E23" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55" t="s">
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3826,17 +3826,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="55" t="s">
+      <c r="E24" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55" t="s">
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3853,17 +3853,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55" t="s">
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3880,17 +3880,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="72" t="s">
+      <c r="E26" s="55" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72" t="s">
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3922,17 +3922,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="66" t="s">
+      <c r="E27" s="60" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="68"/>
-      <c r="I27" s="66" t="s">
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="67"/>
-      <c r="K27" s="68"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="62"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -3955,17 +3955,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="66" t="s">
+      <c r="E28" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="66" t="s">
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="67"/>
-      <c r="K28" s="68"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="62"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -3985,17 +3985,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="66" t="s">
+      <c r="E29" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="66" t="s">
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="60" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="67"/>
-      <c r="K29" s="68"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="62"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4015,17 +4015,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="72" t="s">
+      <c r="E30" s="55" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72" t="s">
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4045,17 +4045,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="E31" s="63" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69" t="s">
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4072,17 +4072,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="69" t="s">
+      <c r="E32" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69" t="s">
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4099,17 +4099,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="69" t="s">
+      <c r="E33" s="63" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69" t="s">
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4126,17 +4126,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="73" t="s">
+      <c r="E34" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="70" t="s">
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="64"/>
-      <c r="K34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="66"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4153,17 +4153,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="73" t="s">
+      <c r="E35" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="63" t="s">
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="63"/>
-      <c r="K35" s="63"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4180,17 +4180,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="73" t="s">
+      <c r="E36" s="56" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="63" t="s">
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="67" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="63"/>
-      <c r="K36" s="63"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4207,17 +4207,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="70" t="s">
+      <c r="E37" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="63" t="s">
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="63"/>
-      <c r="K37" s="63"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4234,17 +4234,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="70" t="s">
+      <c r="E38" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="63" t="s">
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="67" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="64"/>
-      <c r="K38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="66"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4261,17 +4261,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="56" t="s">
+      <c r="E39" s="59" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56" t="s">
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="59"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4288,17 +4288,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="56" t="s">
+      <c r="E40" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56" t="s">
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="59"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4315,17 +4315,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="56" t="s">
+      <c r="E41" s="59" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56" t="s">
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="56"/>
-      <c r="K41" s="56"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="59"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4342,17 +4342,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56" t="s">
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
+      <c r="J42" s="59"/>
+      <c r="K42" s="59"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4369,17 +4369,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="56" t="s">
+      <c r="E43" s="59" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56" t="s">
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="56"/>
-      <c r="K43" s="56"/>
+      <c r="J43" s="59"/>
+      <c r="K43" s="59"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4396,17 +4396,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="56" t="s">
+      <c r="E44" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56" t="s">
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="56"/>
-      <c r="K44" s="56"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="59"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4423,17 +4423,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="56" t="s">
+      <c r="E45" s="59" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56" t="s">
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="56"/>
-      <c r="K45" s="56"/>
+      <c r="J45" s="59"/>
+      <c r="K45" s="59"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4450,17 +4450,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="59" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56" t="s">
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
+      <c r="J46" s="59"/>
+      <c r="K46" s="59"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4477,17 +4477,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="56" t="s">
+      <c r="E47" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="56" t="s">
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="56"/>
-      <c r="K47" s="56"/>
+      <c r="J47" s="59"/>
+      <c r="K47" s="59"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4504,17 +4504,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="56" t="s">
+      <c r="E48" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56" t="s">
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="56"/>
-      <c r="K48" s="56"/>
+      <c r="J48" s="59"/>
+      <c r="K48" s="59"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4531,17 +4531,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="56" t="s">
+      <c r="E49" s="59" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56" t="s">
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="56"/>
-      <c r="K49" s="56"/>
+      <c r="J49" s="59"/>
+      <c r="K49" s="59"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4558,17 +4558,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56" t="s">
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="56"/>
-      <c r="K50" s="56"/>
+      <c r="J50" s="59"/>
+      <c r="K50" s="59"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4585,17 +4585,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="56" t="s">
+      <c r="E51" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="56" t="s">
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="56"/>
-      <c r="K51" s="56"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="59"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4612,17 +4612,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="56" t="s">
+      <c r="E52" s="59" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="56" t="s">
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="56"/>
-      <c r="K52" s="56"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4639,17 +4639,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="56" t="s">
+      <c r="E53" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56" t="s">
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
+      <c r="J53" s="59"/>
+      <c r="K53" s="59"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4666,17 +4666,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="63" t="s">
+      <c r="E54" s="67" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="63"/>
-      <c r="G54" s="63"/>
-      <c r="H54" s="63"/>
-      <c r="I54" s="63" t="s">
+      <c r="F54" s="67"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="67"/>
+      <c r="I54" s="67" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="63"/>
-      <c r="K54" s="63"/>
+      <c r="J54" s="67"/>
+      <c r="K54" s="67"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4693,17 +4693,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="63" t="s">
+      <c r="E55" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
-      <c r="I55" s="63" t="s">
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="67" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="63"/>
-      <c r="K55" s="63"/>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4720,17 +4720,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="63" t="s">
+      <c r="E56" s="67" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="63"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="63"/>
-      <c r="I56" s="63" t="s">
+      <c r="F56" s="67"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="67" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="63"/>
-      <c r="K56" s="63"/>
+      <c r="J56" s="67"/>
+      <c r="K56" s="67"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4747,17 +4747,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="56" t="s">
+      <c r="E57" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56" t="s">
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="56"/>
-      <c r="K57" s="56"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="59"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4774,17 +4774,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="56" t="s">
+      <c r="E58" s="59" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56" t="s">
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="56"/>
-      <c r="K58" s="56"/>
+      <c r="J58" s="59"/>
+      <c r="K58" s="59"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4801,17 +4801,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="59" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="56"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56" t="s">
+      <c r="F59" s="59"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="59" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="56"/>
-      <c r="K59" s="56"/>
+      <c r="J59" s="59"/>
+      <c r="K59" s="59"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4828,17 +4828,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="56" t="s">
+      <c r="E60" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="56"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56" t="s">
+      <c r="F60" s="59"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="56"/>
-      <c r="K60" s="56"/>
+      <c r="J60" s="59"/>
+      <c r="K60" s="59"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4855,17 +4855,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="56" t="s">
+      <c r="E61" s="59" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="56"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56" t="s">
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="59" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="56"/>
-      <c r="K61" s="56"/>
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4882,17 +4882,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="56" t="s">
+      <c r="E62" s="59" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="56"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="56" t="s">
+      <c r="F62" s="59"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="59" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="56"/>
-      <c r="K62" s="56"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4909,17 +4909,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="56" t="s">
+      <c r="E63" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="56"/>
-      <c r="I63" s="56" t="e" vm="1">
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="56"/>
-      <c r="K63" s="56"/>
+      <c r="J63" s="59"/>
+      <c r="K63" s="59"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -4936,17 +4936,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="56" t="s">
+      <c r="E64" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="56"/>
-      <c r="I64" s="56" t="s">
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="56"/>
-      <c r="K64" s="56"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="59"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -4963,17 +4963,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="56" t="s">
+      <c r="E65" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="56" t="s">
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59"/>
+      <c r="I65" s="59" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="56"/>
-      <c r="K65" s="56"/>
+      <c r="J65" s="59"/>
+      <c r="K65" s="59"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -4990,17 +4990,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="56" t="s">
+      <c r="E66" s="59" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
-      <c r="H66" s="56"/>
-      <c r="I66" s="56" t="s">
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="59" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="56"/>
-      <c r="K66" s="56"/>
+      <c r="J66" s="59"/>
+      <c r="K66" s="59"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5017,17 +5017,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="71" t="s">
+      <c r="E67" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="56" t="s">
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
+      <c r="H67" s="68"/>
+      <c r="I67" s="59" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="56"/>
-      <c r="K67" s="56"/>
+      <c r="J67" s="59"/>
+      <c r="K67" s="59"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5044,17 +5044,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="63" t="s">
+      <c r="E68" s="67" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="63"/>
-      <c r="G68" s="63"/>
-      <c r="H68" s="63"/>
-      <c r="I68" s="63" t="s">
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
+      <c r="H68" s="67"/>
+      <c r="I68" s="67" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="63"/>
-      <c r="K68" s="63"/>
+      <c r="J68" s="67"/>
+      <c r="K68" s="67"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5071,17 +5071,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="63" t="s">
+      <c r="E69" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="63"/>
-      <c r="G69" s="63"/>
-      <c r="H69" s="63"/>
-      <c r="I69" s="63" t="s">
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="63"/>
-      <c r="K69" s="63"/>
+      <c r="J69" s="67"/>
+      <c r="K69" s="67"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5098,17 +5098,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="63" t="s">
+      <c r="E70" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="63"/>
-      <c r="G70" s="63"/>
-      <c r="H70" s="63"/>
-      <c r="I70" s="63" t="s">
+      <c r="F70" s="67"/>
+      <c r="G70" s="67"/>
+      <c r="H70" s="67"/>
+      <c r="I70" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="63"/>
-      <c r="K70" s="63"/>
+      <c r="J70" s="67"/>
+      <c r="K70" s="67"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5125,17 +5125,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="63" t="s">
+      <c r="E71" s="67" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="63"/>
-      <c r="G71" s="63"/>
-      <c r="H71" s="63"/>
-      <c r="I71" s="63" t="s">
+      <c r="F71" s="67"/>
+      <c r="G71" s="67"/>
+      <c r="H71" s="67"/>
+      <c r="I71" s="67" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="63"/>
-      <c r="K71" s="63"/>
+      <c r="J71" s="67"/>
+      <c r="K71" s="67"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5152,17 +5152,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="63" t="s">
+      <c r="E72" s="67" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="63"/>
-      <c r="G72" s="63"/>
-      <c r="H72" s="63"/>
-      <c r="I72" s="63" t="s">
+      <c r="F72" s="67"/>
+      <c r="G72" s="67"/>
+      <c r="H72" s="67"/>
+      <c r="I72" s="67" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="63"/>
-      <c r="K72" s="63"/>
+      <c r="J72" s="67"/>
+      <c r="K72" s="67"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5179,17 +5179,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="63" t="s">
+      <c r="E73" s="67" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="63"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="63"/>
-      <c r="I73" s="63" t="s">
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="63"/>
-      <c r="K73" s="63"/>
+      <c r="J73" s="67"/>
+      <c r="K73" s="67"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5206,17 +5206,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="63" t="s">
+      <c r="E74" s="67" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="63"/>
-      <c r="G74" s="63"/>
-      <c r="H74" s="63"/>
-      <c r="I74" s="63" t="s">
+      <c r="F74" s="67"/>
+      <c r="G74" s="67"/>
+      <c r="H74" s="67"/>
+      <c r="I74" s="67" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="63"/>
-      <c r="K74" s="63"/>
+      <c r="J74" s="67"/>
+      <c r="K74" s="67"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5233,17 +5233,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="63" t="s">
+      <c r="E75" s="67" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="63"/>
-      <c r="G75" s="63"/>
-      <c r="H75" s="63"/>
-      <c r="I75" s="63" t="s">
+      <c r="F75" s="67"/>
+      <c r="G75" s="67"/>
+      <c r="H75" s="67"/>
+      <c r="I75" s="67" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="63"/>
-      <c r="K75" s="63"/>
+      <c r="J75" s="67"/>
+      <c r="K75" s="67"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5260,17 +5260,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="63" t="s">
+      <c r="E76" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="63"/>
-      <c r="G76" s="63"/>
-      <c r="H76" s="63"/>
-      <c r="I76" s="63" t="s">
+      <c r="F76" s="67"/>
+      <c r="G76" s="67"/>
+      <c r="H76" s="67"/>
+      <c r="I76" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="63"/>
-      <c r="K76" s="63"/>
+      <c r="J76" s="67"/>
+      <c r="K76" s="67"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5287,17 +5287,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="63" t="s">
+      <c r="E77" s="67" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="63"/>
-      <c r="G77" s="63"/>
-      <c r="H77" s="63"/>
-      <c r="I77" s="63" t="s">
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="63"/>
-      <c r="K77" s="63"/>
+      <c r="J77" s="67"/>
+      <c r="K77" s="67"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5314,17 +5314,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="63" t="s">
+      <c r="E78" s="67" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="63"/>
-      <c r="G78" s="63"/>
-      <c r="H78" s="63"/>
-      <c r="I78" s="63" t="s">
+      <c r="F78" s="67"/>
+      <c r="G78" s="67"/>
+      <c r="H78" s="67"/>
+      <c r="I78" s="67" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="63"/>
-      <c r="K78" s="63"/>
+      <c r="J78" s="67"/>
+      <c r="K78" s="67"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5341,17 +5341,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="63" t="s">
+      <c r="E79" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="63"/>
-      <c r="G79" s="63"/>
-      <c r="H79" s="63"/>
-      <c r="I79" s="63" t="s">
+      <c r="F79" s="67"/>
+      <c r="G79" s="67"/>
+      <c r="H79" s="67"/>
+      <c r="I79" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="63"/>
-      <c r="K79" s="63"/>
+      <c r="J79" s="67"/>
+      <c r="K79" s="67"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5368,17 +5368,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="63" t="s">
+      <c r="E80" s="67" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="63"/>
-      <c r="G80" s="63"/>
-      <c r="H80" s="63"/>
-      <c r="I80" s="63" t="s">
+      <c r="F80" s="67"/>
+      <c r="G80" s="67"/>
+      <c r="H80" s="67"/>
+      <c r="I80" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="63"/>
-      <c r="K80" s="63"/>
+      <c r="J80" s="67"/>
+      <c r="K80" s="67"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5395,17 +5395,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="56" t="s">
+      <c r="E81" s="59" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="56"/>
-      <c r="I81" s="56" t="s">
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="56"/>
-      <c r="K81" s="56"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="59"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5422,17 +5422,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="56" t="s">
+      <c r="E82" s="59" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="56"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="56"/>
-      <c r="I82" s="56" t="s">
+      <c r="F82" s="59"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="56"/>
-      <c r="K82" s="56"/>
+      <c r="J82" s="59"/>
+      <c r="K82" s="59"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5449,17 +5449,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="56" t="s">
+      <c r="E83" s="59" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="56"/>
-      <c r="G83" s="56"/>
-      <c r="H83" s="56"/>
-      <c r="I83" s="56" t="s">
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="59" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="56"/>
-      <c r="K83" s="56"/>
+      <c r="J83" s="59"/>
+      <c r="K83" s="59"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5476,17 +5476,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="56" t="s">
+      <c r="E84" s="59" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="56"/>
-      <c r="G84" s="56"/>
-      <c r="H84" s="56"/>
-      <c r="I84" s="56" t="s">
+      <c r="F84" s="59"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="59" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="56"/>
-      <c r="K84" s="56"/>
+      <c r="J84" s="59"/>
+      <c r="K84" s="59"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5503,17 +5503,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="56" t="s">
+      <c r="E85" s="59" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="56"/>
-      <c r="G85" s="56"/>
-      <c r="H85" s="56"/>
-      <c r="I85" s="56" t="s">
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59"/>
+      <c r="I85" s="59" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="56"/>
-      <c r="K85" s="56"/>
+      <c r="J85" s="59"/>
+      <c r="K85" s="59"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5530,17 +5530,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="56" t="s">
+      <c r="E86" s="59" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="56"/>
-      <c r="G86" s="56"/>
-      <c r="H86" s="56"/>
-      <c r="I86" s="56" t="s">
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="59" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="56"/>
-      <c r="K86" s="56"/>
+      <c r="J86" s="59"/>
+      <c r="K86" s="59"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5557,17 +5557,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="56" t="s">
+      <c r="E87" s="59" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="56"/>
-      <c r="G87" s="56"/>
-      <c r="H87" s="56"/>
-      <c r="I87" s="56" t="s">
+      <c r="F87" s="59"/>
+      <c r="G87" s="59"/>
+      <c r="H87" s="59"/>
+      <c r="I87" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="56"/>
-      <c r="K87" s="56"/>
+      <c r="J87" s="59"/>
+      <c r="K87" s="59"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5584,17 +5584,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="63" t="s">
+      <c r="E88" s="67" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="63"/>
-      <c r="G88" s="63"/>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63" t="s">
+      <c r="F88" s="67"/>
+      <c r="G88" s="67"/>
+      <c r="H88" s="67"/>
+      <c r="I88" s="67" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="63"/>
-      <c r="K88" s="63"/>
+      <c r="J88" s="67"/>
+      <c r="K88" s="67"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5611,17 +5611,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="63" t="s">
+      <c r="E89" s="67" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63" t="s">
+      <c r="F89" s="67"/>
+      <c r="G89" s="67"/>
+      <c r="H89" s="67"/>
+      <c r="I89" s="67" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
+      <c r="J89" s="67"/>
+      <c r="K89" s="67"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5638,17 +5638,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="63" t="s">
+      <c r="E90" s="67" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="63"/>
-      <c r="G90" s="63"/>
-      <c r="H90" s="63"/>
-      <c r="I90" s="63" t="s">
+      <c r="F90" s="67"/>
+      <c r="G90" s="67"/>
+      <c r="H90" s="67"/>
+      <c r="I90" s="67" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="63"/>
-      <c r="K90" s="63"/>
+      <c r="J90" s="67"/>
+      <c r="K90" s="67"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5665,17 +5665,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="63" t="s">
+      <c r="E91" s="67" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="63"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63" t="s">
+      <c r="F91" s="67"/>
+      <c r="G91" s="67"/>
+      <c r="H91" s="67"/>
+      <c r="I91" s="67" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="63"/>
-      <c r="K91" s="63"/>
+      <c r="J91" s="67"/>
+      <c r="K91" s="67"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5692,19 +5692,19 @@
       <c r="D92" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E92" s="69" t="s">
+      <c r="E92" s="63" t="s">
         <v>475</v>
       </c>
-      <c r="F92" s="69"/>
-      <c r="G92" s="69"/>
-      <c r="H92" s="69"/>
-      <c r="I92" s="69" t="s">
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63" t="s">
         <v>476</v>
       </c>
-      <c r="J92" s="69"/>
-      <c r="K92" s="69"/>
+      <c r="J92" s="63"/>
+      <c r="K92" s="63"/>
       <c r="L92" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M92" s="10"/>
     </row>
@@ -5719,19 +5719,19 @@
       <c r="D93" s="38" t="s">
         <v>474</v>
       </c>
-      <c r="E93" s="69" t="s">
+      <c r="E93" s="63" t="s">
         <v>477</v>
       </c>
-      <c r="F93" s="69"/>
-      <c r="G93" s="69"/>
-      <c r="H93" s="69"/>
-      <c r="I93" s="69" t="s">
+      <c r="F93" s="63"/>
+      <c r="G93" s="63"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="63" t="s">
         <v>478</v>
       </c>
-      <c r="J93" s="69"/>
-      <c r="K93" s="69"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="63"/>
       <c r="L93" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M93" s="10"/>
     </row>
@@ -5746,19 +5746,19 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="69" t="s">
+      <c r="E94" s="63" t="s">
         <v>479</v>
       </c>
-      <c r="F94" s="69"/>
-      <c r="G94" s="69"/>
-      <c r="H94" s="69"/>
-      <c r="I94" s="69" t="s">
+      <c r="F94" s="63"/>
+      <c r="G94" s="63"/>
+      <c r="H94" s="63"/>
+      <c r="I94" s="63" t="s">
         <v>480</v>
       </c>
-      <c r="J94" s="69"/>
-      <c r="K94" s="69"/>
+      <c r="J94" s="63"/>
+      <c r="K94" s="63"/>
       <c r="L94" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M94" s="10"/>
     </row>
@@ -5773,19 +5773,19 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="69" t="s">
+      <c r="E95" s="63" t="s">
         <v>481</v>
       </c>
-      <c r="F95" s="69"/>
-      <c r="G95" s="69"/>
-      <c r="H95" s="69"/>
-      <c r="I95" s="69" t="s">
+      <c r="F95" s="63"/>
+      <c r="G95" s="63"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="63" t="s">
         <v>482</v>
       </c>
-      <c r="J95" s="69"/>
-      <c r="K95" s="69"/>
+      <c r="J95" s="63"/>
+      <c r="K95" s="63"/>
       <c r="L95" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M95" s="10"/>
     </row>
@@ -5796,13 +5796,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="48"/>
-      <c r="K96" s="48"/>
+      <c r="E96" s="69"/>
+      <c r="F96" s="69"/>
+      <c r="G96" s="69"/>
+      <c r="H96" s="69"/>
+      <c r="I96" s="69"/>
+      <c r="J96" s="69"/>
+      <c r="K96" s="69"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5815,13 +5815,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="48"/>
+      <c r="E97" s="69"/>
+      <c r="F97" s="69"/>
+      <c r="G97" s="69"/>
+      <c r="H97" s="69"/>
+      <c r="I97" s="69"/>
+      <c r="J97" s="69"/>
+      <c r="K97" s="69"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5834,13 +5834,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
+      <c r="E98" s="69"/>
+      <c r="F98" s="69"/>
+      <c r="G98" s="69"/>
+      <c r="H98" s="69"/>
+      <c r="I98" s="69"/>
+      <c r="J98" s="69"/>
+      <c r="K98" s="69"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -5853,13 +5853,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
+      <c r="E99" s="69"/>
+      <c r="F99" s="69"/>
+      <c r="G99" s="69"/>
+      <c r="H99" s="69"/>
+      <c r="I99" s="69"/>
+      <c r="J99" s="69"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -5872,13 +5872,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
+      <c r="E100" s="69"/>
+      <c r="F100" s="69"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="69"/>
+      <c r="I100" s="69"/>
+      <c r="J100" s="69"/>
+      <c r="K100" s="69"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5886,6 +5886,179 @@
     </row>
   </sheetData>
   <mergeCells count="197">
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -5910,179 +6083,6 @@
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -6123,36 +6123,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -6165,17 +6165,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58" t="s">
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -6194,17 +6194,17 @@
       <c r="D4" s="47" t="s">
         <v>463</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="74" t="s">
         <v>464</v>
       </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="59" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="74" t="s">
         <v>465</v>
       </c>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="76"/>
       <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
@@ -6221,17 +6221,17 @@
       <c r="D5" s="47" t="s">
         <v>463</v>
       </c>
-      <c r="E5" s="62" t="s">
+      <c r="E5" s="70" t="s">
         <v>469</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62" t="s">
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70" t="s">
         <v>470</v>
       </c>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -6248,17 +6248,17 @@
       <c r="D6" s="24" t="s">
         <v>466</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="54" t="s">
         <v>467</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55" t="s">
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54" t="s">
         <v>468</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -6275,17 +6275,17 @@
       <c r="D7" s="47" t="s">
         <v>463</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="70" t="s">
         <v>471</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62" t="s">
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70" t="s">
         <v>472</v>
       </c>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -6298,13 +6298,13 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="54"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="73"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -6317,13 +6317,13 @@
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -6336,13 +6336,13 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -6355,13 +6355,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -6374,13 +6374,13 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="54"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="73"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -6393,13 +6393,13 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -6412,13 +6412,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -6431,13 +6431,13 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -6450,13 +6450,13 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -6469,13 +6469,13 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -6488,13 +6488,13 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -6507,13 +6507,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="54"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -6526,13 +6526,13 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -6545,13 +6545,13 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -6564,13 +6564,13 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -6583,13 +6583,13 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="54"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -6602,13 +6602,13 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -6621,13 +6621,13 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -6640,13 +6640,13 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -6674,13 +6674,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="54"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -6699,13 +6699,13 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -6721,13 +6721,13 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -6743,13 +6743,13 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -6765,13 +6765,13 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -6784,13 +6784,13 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -6803,13 +6803,13 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -6822,13 +6822,13 @@
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="54"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -6841,13 +6841,13 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -6860,13 +6860,13 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -6879,13 +6879,13 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -6898,13 +6898,13 @@
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="54"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -6917,13 +6917,13 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -6936,13 +6936,13 @@
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -6955,13 +6955,13 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -6974,13 +6974,13 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="54"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -6993,13 +6993,13 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="69"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -7012,13 +7012,13 @@
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -7031,13 +7031,13 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -7050,13 +7050,13 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -7069,13 +7069,13 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -7088,13 +7088,13 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -7107,13 +7107,13 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -7126,13 +7126,13 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="54"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="72"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -7145,13 +7145,13 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="69"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -7164,13 +7164,13 @@
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -7183,13 +7183,13 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -7202,13 +7202,13 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="54"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="53"/>
-      <c r="K54" s="54"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="72"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -7221,13 +7221,13 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -7240,13 +7240,13 @@
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="69"/>
+      <c r="G56" s="69"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="69"/>
+      <c r="J56" s="69"/>
+      <c r="K56" s="69"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -7259,13 +7259,13 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -7278,13 +7278,13 @@
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="54"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="54"/>
+      <c r="E58" s="71"/>
+      <c r="F58" s="72"/>
+      <c r="G58" s="72"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="72"/>
+      <c r="K58" s="73"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -7297,13 +7297,13 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="69"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="69"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -7316,13 +7316,13 @@
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="E60" s="69"/>
+      <c r="F60" s="69"/>
+      <c r="G60" s="69"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="69"/>
+      <c r="J60" s="69"/>
+      <c r="K60" s="69"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -7335,13 +7335,13 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="69"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -7354,13 +7354,13 @@
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="E62" s="69"/>
+      <c r="F62" s="69"/>
+      <c r="G62" s="69"/>
+      <c r="H62" s="69"/>
+      <c r="I62" s="69"/>
+      <c r="J62" s="69"/>
+      <c r="K62" s="69"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -7373,13 +7373,13 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="69"/>
+      <c r="K63" s="69"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -7392,13 +7392,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="69"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="69"/>
+      <c r="K64" s="69"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -7411,13 +7411,13 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="52"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="54"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="72"/>
+      <c r="H65" s="73"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="72"/>
+      <c r="K65" s="73"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -7430,13 +7430,13 @@
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="69"/>
+      <c r="J66" s="69"/>
+      <c r="K66" s="69"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -7449,13 +7449,13 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="48"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="E67" s="69"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="69"/>
+      <c r="J67" s="69"/>
+      <c r="K67" s="69"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -7468,13 +7468,13 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="69"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="69"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -7487,13 +7487,13 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="54"/>
-      <c r="I69" s="52"/>
-      <c r="J69" s="53"/>
-      <c r="K69" s="54"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="72"/>
+      <c r="H69" s="73"/>
+      <c r="I69" s="71"/>
+      <c r="J69" s="72"/>
+      <c r="K69" s="73"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -7506,13 +7506,13 @@
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="69"/>
+      <c r="J70" s="69"/>
+      <c r="K70" s="69"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -7525,13 +7525,13 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="69"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="69"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -7544,13 +7544,13 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="48"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="69"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="69"/>
+      <c r="J72" s="69"/>
+      <c r="K72" s="69"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -7563,13 +7563,13 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="54"/>
-      <c r="I73" s="52"/>
-      <c r="J73" s="53"/>
-      <c r="K73" s="54"/>
+      <c r="E73" s="71"/>
+      <c r="F73" s="72"/>
+      <c r="G73" s="72"/>
+      <c r="H73" s="73"/>
+      <c r="I73" s="71"/>
+      <c r="J73" s="72"/>
+      <c r="K73" s="73"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -7582,13 +7582,13 @@
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="69"/>
+      <c r="J74" s="69"/>
+      <c r="K74" s="69"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -7601,13 +7601,13 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="69"/>
+      <c r="H75" s="69"/>
+      <c r="I75" s="69"/>
+      <c r="J75" s="69"/>
+      <c r="K75" s="69"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -7620,13 +7620,13 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-      <c r="K76" s="48"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="69"/>
+      <c r="I76" s="69"/>
+      <c r="J76" s="69"/>
+      <c r="K76" s="69"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -7639,13 +7639,13 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="69"/>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="69"/>
+      <c r="J77" s="69"/>
+      <c r="K77" s="69"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -7658,13 +7658,13 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
+      <c r="E78" s="69"/>
+      <c r="F78" s="69"/>
+      <c r="G78" s="69"/>
+      <c r="H78" s="69"/>
+      <c r="I78" s="69"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="69"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -7677,13 +7677,13 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
+      <c r="E79" s="69"/>
+      <c r="F79" s="69"/>
+      <c r="G79" s="69"/>
+      <c r="H79" s="69"/>
+      <c r="I79" s="69"/>
+      <c r="J79" s="69"/>
+      <c r="K79" s="69"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -7696,13 +7696,13 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="51"/>
-      <c r="I80" s="49"/>
-      <c r="J80" s="50"/>
-      <c r="K80" s="51"/>
+      <c r="E80" s="77"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="79"/>
+      <c r="I80" s="77"/>
+      <c r="J80" s="78"/>
+      <c r="K80" s="79"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -7715,13 +7715,13 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="51"/>
-      <c r="I81" s="49"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="51"/>
+      <c r="E81" s="77"/>
+      <c r="F81" s="78"/>
+      <c r="G81" s="78"/>
+      <c r="H81" s="79"/>
+      <c r="I81" s="77"/>
+      <c r="J81" s="78"/>
+      <c r="K81" s="79"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -7734,13 +7734,13 @@
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="51"/>
-      <c r="I82" s="49"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="51"/>
+      <c r="E82" s="77"/>
+      <c r="F82" s="78"/>
+      <c r="G82" s="78"/>
+      <c r="H82" s="79"/>
+      <c r="I82" s="77"/>
+      <c r="J82" s="78"/>
+      <c r="K82" s="79"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -7753,13 +7753,13 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="51"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="50"/>
-      <c r="K83" s="51"/>
+      <c r="E83" s="77"/>
+      <c r="F83" s="78"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="79"/>
+      <c r="I83" s="77"/>
+      <c r="J83" s="78"/>
+      <c r="K83" s="79"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -7772,13 +7772,13 @@
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
-      <c r="H84" s="51"/>
-      <c r="I84" s="49"/>
-      <c r="J84" s="50"/>
-      <c r="K84" s="51"/>
+      <c r="E84" s="77"/>
+      <c r="F84" s="78"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="79"/>
+      <c r="I84" s="77"/>
+      <c r="J84" s="78"/>
+      <c r="K84" s="79"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -7791,13 +7791,13 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
-      <c r="H85" s="51"/>
-      <c r="I85" s="49"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="51"/>
+      <c r="E85" s="77"/>
+      <c r="F85" s="78"/>
+      <c r="G85" s="78"/>
+      <c r="H85" s="79"/>
+      <c r="I85" s="77"/>
+      <c r="J85" s="78"/>
+      <c r="K85" s="79"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -7810,13 +7810,13 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="49"/>
-      <c r="J86" s="50"/>
-      <c r="K86" s="51"/>
+      <c r="E86" s="77"/>
+      <c r="F86" s="78"/>
+      <c r="G86" s="78"/>
+      <c r="H86" s="79"/>
+      <c r="I86" s="77"/>
+      <c r="J86" s="78"/>
+      <c r="K86" s="79"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -7829,13 +7829,13 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="49"/>
-      <c r="J87" s="50"/>
-      <c r="K87" s="51"/>
+      <c r="E87" s="77"/>
+      <c r="F87" s="78"/>
+      <c r="G87" s="78"/>
+      <c r="H87" s="79"/>
+      <c r="I87" s="77"/>
+      <c r="J87" s="78"/>
+      <c r="K87" s="79"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -7848,13 +7848,13 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="49"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="51"/>
+      <c r="E88" s="77"/>
+      <c r="F88" s="78"/>
+      <c r="G88" s="78"/>
+      <c r="H88" s="79"/>
+      <c r="I88" s="77"/>
+      <c r="J88" s="78"/>
+      <c r="K88" s="79"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -7867,13 +7867,13 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
-      <c r="H89" s="51"/>
-      <c r="I89" s="49"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="51"/>
+      <c r="E89" s="77"/>
+      <c r="F89" s="78"/>
+      <c r="G89" s="78"/>
+      <c r="H89" s="79"/>
+      <c r="I89" s="77"/>
+      <c r="J89" s="78"/>
+      <c r="K89" s="79"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -7886,13 +7886,13 @@
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="49"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50"/>
-      <c r="H90" s="51"/>
-      <c r="I90" s="49"/>
-      <c r="J90" s="50"/>
-      <c r="K90" s="51"/>
+      <c r="E90" s="77"/>
+      <c r="F90" s="78"/>
+      <c r="G90" s="78"/>
+      <c r="H90" s="79"/>
+      <c r="I90" s="77"/>
+      <c r="J90" s="78"/>
+      <c r="K90" s="79"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -7905,13 +7905,13 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
+      <c r="E91" s="69"/>
+      <c r="F91" s="69"/>
+      <c r="G91" s="69"/>
+      <c r="H91" s="69"/>
+      <c r="I91" s="69"/>
+      <c r="J91" s="69"/>
+      <c r="K91" s="69"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -7924,13 +7924,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="48"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="69"/>
+      <c r="H92" s="69"/>
+      <c r="I92" s="69"/>
+      <c r="J92" s="69"/>
+      <c r="K92" s="69"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -7943,13 +7943,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="48"/>
-      <c r="J93" s="48"/>
-      <c r="K93" s="48"/>
+      <c r="E93" s="69"/>
+      <c r="F93" s="69"/>
+      <c r="G93" s="69"/>
+      <c r="H93" s="69"/>
+      <c r="I93" s="69"/>
+      <c r="J93" s="69"/>
+      <c r="K93" s="69"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -7962,13 +7962,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="48"/>
+      <c r="E94" s="69"/>
+      <c r="F94" s="69"/>
+      <c r="G94" s="69"/>
+      <c r="H94" s="69"/>
+      <c r="I94" s="69"/>
+      <c r="J94" s="69"/>
+      <c r="K94" s="69"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -7981,13 +7981,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="48"/>
+      <c r="E95" s="69"/>
+      <c r="F95" s="69"/>
+      <c r="G95" s="69"/>
+      <c r="H95" s="69"/>
+      <c r="I95" s="69"/>
+      <c r="J95" s="69"/>
+      <c r="K95" s="69"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -8000,13 +8000,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="48"/>
-      <c r="K96" s="48"/>
+      <c r="E96" s="69"/>
+      <c r="F96" s="69"/>
+      <c r="G96" s="69"/>
+      <c r="H96" s="69"/>
+      <c r="I96" s="69"/>
+      <c r="J96" s="69"/>
+      <c r="K96" s="69"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -8019,13 +8019,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="48"/>
+      <c r="E97" s="69"/>
+      <c r="F97" s="69"/>
+      <c r="G97" s="69"/>
+      <c r="H97" s="69"/>
+      <c r="I97" s="69"/>
+      <c r="J97" s="69"/>
+      <c r="K97" s="69"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -8038,13 +8038,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
+      <c r="E98" s="69"/>
+      <c r="F98" s="69"/>
+      <c r="G98" s="69"/>
+      <c r="H98" s="69"/>
+      <c r="I98" s="69"/>
+      <c r="J98" s="69"/>
+      <c r="K98" s="69"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -8057,13 +8057,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
+      <c r="E99" s="69"/>
+      <c r="F99" s="69"/>
+      <c r="G99" s="69"/>
+      <c r="H99" s="69"/>
+      <c r="I99" s="69"/>
+      <c r="J99" s="69"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -8076,13 +8076,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
+      <c r="E100" s="69"/>
+      <c r="F100" s="69"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="69"/>
+      <c r="I100" s="69"/>
+      <c r="J100" s="69"/>
+      <c r="K100" s="69"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -8094,13 +8094,13 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
-      <c r="J101" s="48"/>
-      <c r="K101" s="48"/>
+      <c r="E101" s="69"/>
+      <c r="F101" s="69"/>
+      <c r="G101" s="69"/>
+      <c r="H101" s="69"/>
+      <c r="I101" s="69"/>
+      <c r="J101" s="69"/>
+      <c r="K101" s="69"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -8112,13 +8112,13 @@
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="48"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="48"/>
-      <c r="H102" s="48"/>
-      <c r="I102" s="48"/>
-      <c r="J102" s="48"/>
-      <c r="K102" s="48"/>
+      <c r="E102" s="69"/>
+      <c r="F102" s="69"/>
+      <c r="G102" s="69"/>
+      <c r="H102" s="69"/>
+      <c r="I102" s="69"/>
+      <c r="J102" s="69"/>
+      <c r="K102" s="69"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -8130,13 +8130,13 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="48"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="48"/>
-      <c r="K103" s="48"/>
+      <c r="E103" s="69"/>
+      <c r="F103" s="69"/>
+      <c r="G103" s="69"/>
+      <c r="H103" s="69"/>
+      <c r="I103" s="69"/>
+      <c r="J103" s="69"/>
+      <c r="K103" s="69"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -8144,6 +8144,196 @@
     </row>
   </sheetData>
   <mergeCells count="203">
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -8157,196 +8347,6 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -8756,140 +8756,148 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="83" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="90"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="86"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="87" t="s">
+      <c r="N2" s="83" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86" t="e" vm="2">
+      <c r="B3" s="82" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="86" t="e" vm="3">
+      <c r="N3" s="82" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="93" t="s">
+      <c r="F4" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="93" t="s">
+      <c r="J4" s="90" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="87" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="92"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="89"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82" t="s">
+      <c r="C8" s="91"/>
+      <c r="D8" s="91" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="92"/>
+      <c r="D9" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84" t="s">
+      <c r="C10" s="88"/>
+      <c r="D10" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84" t="s">
+      <c r="C11" s="88"/>
+      <c r="D11" s="88" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -8900,14 +8908,6 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F7DC94-ADBF-4374-AFC7-FBE8246C0095}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5891EC8E-9D93-439D-8958-B5477E7B6B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="494">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1521,9 +1521,6 @@
   </si>
   <si>
     <t>No.004</t>
-  </si>
-  <si>
-    <t>No.005</t>
   </si>
   <si>
     <t>No.006</t>
@@ -2146,6 +2143,57 @@
   </si>
   <si>
     <t>Frowchart가 이미 들어있는 상황에서 하나가 복제되어 재 생성되어 발생하는 현상 ( DestroyOnLoad가 안되고 생성되는 느낌 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌드 후 게임을 시작하면 메인화면에 브금이 없는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인화면에서 사용될 브금을 추가 요청 ( 레퍼런스(참고자료)가 필요하면 사유에 적어두기 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인트로 씬에서 아무런 소리가 없는 상태에서 전기톱 소리만 울리는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조용한 상태에 있다가 갑자기 전기톱 소리만 나는 건 좋지 않다고 생각됨
+이에 따른 살인마의 걸음 소리가 추가되면 보다 세련된 느낌을 줄 수 있다고 여겨짐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오프닝 주인공과 조수가 대화는 부분에서 브금이 없어짐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opening_Office씬에서 Flowchart을 열어서 Invoke Method가 2개가 있는 그 중 CallStopMusic (): void를 맨 아래 Wait 바로 아래오 옮기는 것으로 해결 가능함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화창이 나오면 화면이 어두워지는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opening_Mention에서 StandingDialogueCanvas 이 부분에서 화면을 전체적으로 어둡게 만드는 원인
+StandingDialogueCanvas -&gt; CharacterDimBackdrop 조정이 필요함 
+원래는 오프닝에서 캐릭터들에 대화를 강조하기 위해 추가된 것이 Opening_Mention까지 따라온 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 지도에는 다용도실에 있어도 주방에 위치가 표기가 되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다용도실도 표기위치 추가요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2434,7 +2482,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2579,84 +2627,93 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2666,21 +2723,24 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2699,23 +2759,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3215,36 +3272,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3257,17 +3314,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50" t="s">
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3286,17 +3343,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49" t="s">
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3313,17 +3370,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49" t="s">
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3340,17 +3397,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49" t="s">
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3367,17 +3424,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="49" t="s">
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3394,17 +3451,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="49" t="s">
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3421,17 +3478,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="49" t="s">
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3448,17 +3505,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="49" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3475,17 +3532,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49" t="s">
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3502,17 +3559,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49" t="s">
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3529,17 +3586,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="49" t="s">
+      <c r="E13" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49" t="s">
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3556,17 +3613,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49" t="s">
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3583,17 +3640,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49" t="s">
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3610,17 +3667,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49" t="s">
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3637,17 +3694,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="49" t="s">
+      <c r="E17" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3664,17 +3721,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49" t="s">
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3691,17 +3748,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="54" t="s">
+      <c r="E19" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54" t="s">
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3718,17 +3775,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54" t="s">
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="59"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3745,17 +3802,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="54" t="s">
+      <c r="E21" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54" t="s">
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3772,17 +3829,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="54" t="s">
+      <c r="E22" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54" t="s">
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3799,17 +3856,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="54" t="s">
+      <c r="E23" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54" t="s">
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3826,17 +3883,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54" t="s">
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3853,17 +3910,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="54" t="s">
+      <c r="E25" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54" t="s">
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3880,17 +3937,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="55" t="s">
+      <c r="E26" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55" t="s">
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3922,17 +3979,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="60" t="s">
+      <c r="E27" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="60" t="s">
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="61"/>
-      <c r="K27" s="62"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -3955,17 +4012,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="60" t="s">
+      <c r="E28" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="60" t="s">
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="61"/>
-      <c r="K28" s="62"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="54"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -3985,17 +4042,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="60" t="s">
+      <c r="E29" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="60" t="s">
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="61"/>
-      <c r="K29" s="62"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="54"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4015,17 +4072,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="55" t="s">
+      <c r="E30" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55" t="s">
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4045,17 +4102,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="63" t="s">
+      <c r="E31" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63" t="s">
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4072,17 +4129,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="63" t="s">
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4099,17 +4156,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="63" t="s">
+      <c r="E33" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="63" t="s">
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="63"/>
-      <c r="K33" s="63"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4126,17 +4183,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="56" t="s">
+      <c r="E34" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="64" t="s">
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="65"/>
-      <c r="K34" s="66"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="51"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4153,17 +4210,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="56" t="s">
+      <c r="E35" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="67" t="s">
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="49" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="67"/>
-      <c r="K35" s="67"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4180,17 +4237,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="61" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="67" t="s">
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4207,17 +4264,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="64" t="s">
+      <c r="E37" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="67" t="s">
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="67"/>
-      <c r="K37" s="67"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4234,17 +4291,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="67" t="s">
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="49" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="65"/>
-      <c r="K38" s="66"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="51"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4261,17 +4318,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="59" t="s">
+      <c r="E39" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59" t="s">
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="59"/>
-      <c r="K39" s="59"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4288,17 +4345,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59" t="s">
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="59"/>
-      <c r="K40" s="59"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4315,17 +4372,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="59" t="s">
+      <c r="E41" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="59" t="s">
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="59"/>
-      <c r="K41" s="59"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4342,17 +4399,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="59" t="s">
+      <c r="E42" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59" t="s">
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="59"/>
-      <c r="K42" s="59"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4369,17 +4426,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="59" t="s">
+      <c r="E43" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59" t="s">
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4396,17 +4453,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59" t="s">
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="59"/>
-      <c r="K44" s="59"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4423,17 +4480,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="59" t="s">
+      <c r="E45" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="59" t="s">
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="59"/>
-      <c r="K45" s="59"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4450,17 +4507,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="59" t="s">
+      <c r="E46" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="59" t="s">
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="59"/>
-      <c r="K46" s="59"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4477,17 +4534,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="59" t="s">
+      <c r="E47" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="59" t="s">
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="59"/>
-      <c r="K47" s="59"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4504,17 +4561,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="59" t="s">
+      <c r="E48" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="59" t="s">
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="59"/>
-      <c r="K48" s="59"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4531,17 +4588,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="59" t="s">
+      <c r="E49" s="48" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="59" t="s">
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="59"/>
-      <c r="K49" s="59"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4558,17 +4615,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="59" t="s">
+      <c r="E50" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="59"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="59" t="s">
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="59"/>
-      <c r="K50" s="59"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="48"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4585,17 +4642,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="59" t="s">
+      <c r="E51" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59" t="s">
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4612,17 +4669,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="59" t="s">
+      <c r="E52" s="48" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59" t="s">
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4639,17 +4696,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="59" t="s">
+      <c r="E53" s="48" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="59"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="59" t="s">
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="59"/>
-      <c r="K53" s="59"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4666,17 +4723,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="67" t="s">
+      <c r="E54" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="67"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="67" t="s">
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="67"/>
-      <c r="K54" s="67"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4693,17 +4750,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="67" t="s">
+      <c r="E55" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="67" t="s">
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="67"/>
-      <c r="K55" s="67"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4720,17 +4777,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="67" t="s">
+      <c r="E56" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="67" t="s">
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="67"/>
-      <c r="K56" s="67"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4747,17 +4804,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="59" t="s">
+      <c r="E57" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="59"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="59" t="s">
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="59"/>
-      <c r="K57" s="59"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4774,17 +4831,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="59"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="59" t="s">
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="59"/>
-      <c r="K58" s="59"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4801,17 +4858,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="59" t="s">
+      <c r="E59" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="59"/>
-      <c r="G59" s="59"/>
-      <c r="H59" s="59"/>
-      <c r="I59" s="59" t="s">
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="59"/>
-      <c r="K59" s="59"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4828,17 +4885,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="59" t="s">
+      <c r="E60" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="59"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="59" t="s">
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="59"/>
-      <c r="K60" s="59"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4855,17 +4912,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="59" t="s">
+      <c r="E61" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="59" t="s">
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="59"/>
-      <c r="K61" s="59"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4882,17 +4939,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="59" t="s">
+      <c r="E62" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="59"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="59" t="s">
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="59"/>
-      <c r="K62" s="59"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4909,17 +4966,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="59" t="s">
+      <c r="E63" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="59" t="e" vm="1">
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="59"/>
-      <c r="K63" s="59"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -4936,17 +4993,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="59" t="s">
+      <c r="E64" s="48" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59" t="s">
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -4963,17 +5020,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="59" t="s">
+      <c r="E65" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="59" t="s">
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="59"/>
-      <c r="K65" s="59"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -4990,17 +5047,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="59" t="s">
+      <c r="E66" s="48" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="59" t="s">
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="59"/>
-      <c r="K66" s="59"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5017,17 +5074,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="68" t="s">
+      <c r="E67" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="59" t="s">
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="59"/>
-      <c r="K67" s="59"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5044,17 +5101,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="67" t="s">
+      <c r="E68" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67" t="s">
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="67"/>
-      <c r="K68" s="67"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5071,17 +5128,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="67" t="s">
+      <c r="E69" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="67"/>
-      <c r="I69" s="67" t="s">
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="67"/>
-      <c r="K69" s="67"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5098,17 +5155,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="67" t="s">
+      <c r="E70" s="49" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="67"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="67"/>
-      <c r="I70" s="67" t="s">
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="67"/>
-      <c r="K70" s="67"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5125,17 +5182,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="67" t="s">
+      <c r="E71" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="67"/>
-      <c r="G71" s="67"/>
-      <c r="H71" s="67"/>
-      <c r="I71" s="67" t="s">
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="67"/>
-      <c r="K71" s="67"/>
+      <c r="J71" s="49"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5152,17 +5209,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="67" t="s">
+      <c r="E72" s="49" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="67"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="67"/>
-      <c r="I72" s="67" t="s">
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="67"/>
-      <c r="K72" s="67"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5179,17 +5236,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="67" t="s">
+      <c r="E73" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="67"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="67"/>
-      <c r="I73" s="67" t="s">
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="67"/>
-      <c r="K73" s="67"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5206,17 +5263,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="67" t="s">
+      <c r="E74" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="67"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="67"/>
-      <c r="I74" s="67" t="s">
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="67"/>
-      <c r="K74" s="67"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5233,17 +5290,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="67" t="s">
+      <c r="E75" s="49" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67" t="s">
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="67"/>
-      <c r="K75" s="67"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5260,17 +5317,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="67" t="s">
+      <c r="E76" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="67"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67"/>
-      <c r="I76" s="67" t="s">
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="67"/>
-      <c r="K76" s="67"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5287,17 +5344,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="67" t="s">
+      <c r="E77" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="67"/>
-      <c r="G77" s="67"/>
-      <c r="H77" s="67"/>
-      <c r="I77" s="67" t="s">
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="67"/>
-      <c r="K77" s="67"/>
+      <c r="J77" s="49"/>
+      <c r="K77" s="49"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5314,17 +5371,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="67" t="s">
+      <c r="E78" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="67"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="67"/>
-      <c r="I78" s="67" t="s">
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="67"/>
-      <c r="K78" s="67"/>
+      <c r="J78" s="49"/>
+      <c r="K78" s="49"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5341,17 +5398,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="67" t="s">
+      <c r="E79" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="67"/>
-      <c r="G79" s="67"/>
-      <c r="H79" s="67"/>
-      <c r="I79" s="67" t="s">
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="67"/>
-      <c r="K79" s="67"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5368,17 +5425,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="67" t="s">
+      <c r="E80" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="67" t="s">
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="67"/>
-      <c r="K80" s="67"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5395,17 +5452,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="59" t="s">
+      <c r="E81" s="48" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="59"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="59" t="s">
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="59"/>
-      <c r="K81" s="59"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5422,17 +5479,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="59" t="s">
+      <c r="E82" s="48" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59" t="s">
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="59"/>
-      <c r="K82" s="59"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5449,17 +5506,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="59" t="s">
+      <c r="E83" s="48" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="59" t="s">
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="59"/>
-      <c r="K83" s="59"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5476,17 +5533,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="59" t="s">
+      <c r="E84" s="48" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="59" t="s">
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="59"/>
-      <c r="K84" s="59"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5503,17 +5560,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="59" t="s">
+      <c r="E85" s="48" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59" t="s">
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="59"/>
-      <c r="K85" s="59"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5530,17 +5587,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="59" t="s">
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="59"/>
-      <c r="K86" s="59"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5557,17 +5614,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="59" t="s">
+      <c r="E87" s="48" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59" t="s">
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5584,17 +5641,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="67" t="s">
+      <c r="E88" s="49" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
-      <c r="H88" s="67"/>
-      <c r="I88" s="67" t="s">
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="67"/>
-      <c r="K88" s="67"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5611,17 +5668,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="67" t="s">
+      <c r="E89" s="49" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="67"/>
-      <c r="G89" s="67"/>
-      <c r="H89" s="67"/>
-      <c r="I89" s="67" t="s">
+      <c r="F89" s="49"/>
+      <c r="G89" s="49"/>
+      <c r="H89" s="49"/>
+      <c r="I89" s="49" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="67"/>
-      <c r="K89" s="67"/>
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5638,17 +5695,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="67" t="s">
+      <c r="E90" s="49" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
-      <c r="H90" s="67"/>
-      <c r="I90" s="67" t="s">
+      <c r="F90" s="49"/>
+      <c r="G90" s="49"/>
+      <c r="H90" s="49"/>
+      <c r="I90" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="67"/>
-      <c r="K90" s="67"/>
+      <c r="J90" s="49"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5665,17 +5722,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="67" t="s">
+      <c r="E91" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
-      <c r="H91" s="67"/>
-      <c r="I91" s="67" t="s">
+      <c r="F91" s="49"/>
+      <c r="G91" s="49"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="67"/>
-      <c r="K91" s="67"/>
+      <c r="J91" s="49"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5690,19 +5747,19 @@
         <v>46179</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>473</v>
-      </c>
-      <c r="E92" s="63" t="s">
+        <v>472</v>
+      </c>
+      <c r="E92" s="55" t="s">
+        <v>474</v>
+      </c>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55" t="s">
         <v>475</v>
       </c>
-      <c r="F92" s="63"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63" t="s">
-        <v>476</v>
-      </c>
-      <c r="J92" s="63"/>
-      <c r="K92" s="63"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
       <c r="L92" s="9" t="s">
         <v>164</v>
       </c>
@@ -5717,19 +5774,19 @@
         <v>46179</v>
       </c>
       <c r="D93" s="38" t="s">
-        <v>474</v>
-      </c>
-      <c r="E93" s="63" t="s">
+        <v>473</v>
+      </c>
+      <c r="E93" s="55" t="s">
+        <v>476</v>
+      </c>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55" t="s">
         <v>477</v>
       </c>
-      <c r="F93" s="63"/>
-      <c r="G93" s="63"/>
-      <c r="H93" s="63"/>
-      <c r="I93" s="63" t="s">
-        <v>478</v>
-      </c>
-      <c r="J93" s="63"/>
-      <c r="K93" s="63"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
       <c r="L93" s="9" t="s">
         <v>164</v>
       </c>
@@ -5746,17 +5803,17 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="63" t="s">
+      <c r="E94" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55" t="s">
         <v>479</v>
       </c>
-      <c r="F94" s="63"/>
-      <c r="G94" s="63"/>
-      <c r="H94" s="63"/>
-      <c r="I94" s="63" t="s">
-        <v>480</v>
-      </c>
-      <c r="J94" s="63"/>
-      <c r="K94" s="63"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
       <c r="L94" s="9" t="s">
         <v>164</v>
       </c>
@@ -5773,17 +5830,17 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="63" t="s">
+      <c r="E95" s="55" t="s">
+        <v>480</v>
+      </c>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55" t="s">
         <v>481</v>
       </c>
-      <c r="F95" s="63"/>
-      <c r="G95" s="63"/>
-      <c r="H95" s="63"/>
-      <c r="I95" s="63" t="s">
-        <v>482</v>
-      </c>
-      <c r="J95" s="63"/>
-      <c r="K95" s="63"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="55"/>
       <c r="L95" s="9" t="s">
         <v>164</v>
       </c>
@@ -5791,18 +5848,26 @@
     </row>
     <row r="96" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="69"/>
-      <c r="F96" s="69"/>
-      <c r="G96" s="69"/>
-      <c r="H96" s="69"/>
-      <c r="I96" s="69"/>
-      <c r="J96" s="69"/>
-      <c r="K96" s="69"/>
+      <c r="C96" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D96" s="38" t="s">
+        <v>489</v>
+      </c>
+      <c r="E96" s="55" t="s">
+        <v>490</v>
+      </c>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55" t="s">
+        <v>491</v>
+      </c>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5810,18 +5875,26 @@
     </row>
     <row r="97" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="69"/>
-      <c r="F97" s="69"/>
-      <c r="G97" s="69"/>
-      <c r="H97" s="69"/>
-      <c r="I97" s="69"/>
-      <c r="J97" s="69"/>
-      <c r="K97" s="69"/>
+      <c r="C97" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D97" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="E97" s="55" t="s">
+        <v>492</v>
+      </c>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55" t="s">
+        <v>493</v>
+      </c>
+      <c r="J97" s="55"/>
+      <c r="K97" s="55"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5834,13 +5907,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="69"/>
-      <c r="F98" s="69"/>
-      <c r="G98" s="69"/>
-      <c r="H98" s="69"/>
-      <c r="I98" s="69"/>
-      <c r="J98" s="69"/>
-      <c r="K98" s="69"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="57"/>
+      <c r="J98" s="57"/>
+      <c r="K98" s="57"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -5853,13 +5926,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="69"/>
-      <c r="F99" s="69"/>
-      <c r="G99" s="69"/>
-      <c r="H99" s="69"/>
-      <c r="I99" s="69"/>
-      <c r="J99" s="69"/>
-      <c r="K99" s="69"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="57"/>
+      <c r="J99" s="57"/>
+      <c r="K99" s="57"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -5872,13 +5945,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="69"/>
-      <c r="F100" s="69"/>
-      <c r="G100" s="69"/>
-      <c r="H100" s="69"/>
-      <c r="I100" s="69"/>
-      <c r="J100" s="69"/>
-      <c r="K100" s="69"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5886,45 +5959,140 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -5949,140 +6117,45 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -6123,36 +6196,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -6165,17 +6238,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50" t="s">
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -6192,19 +6265,19 @@
         <v>46179</v>
       </c>
       <c r="D4" s="47" t="s">
+        <v>462</v>
+      </c>
+      <c r="E4" s="77" t="s">
         <v>463</v>
       </c>
-      <c r="E4" s="74" t="s">
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="77" t="s">
         <v>464</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="74" t="s">
-        <v>465</v>
-      </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="76"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="79"/>
       <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
@@ -6219,19 +6292,19 @@
         <v>46179</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>463</v>
-      </c>
-      <c r="E5" s="70" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" s="76" t="s">
+        <v>468</v>
+      </c>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76" t="s">
         <v>469</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70" t="s">
-        <v>470</v>
-      </c>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -6246,19 +6319,19 @@
         <v>46179</v>
       </c>
       <c r="D6" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>466</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59" t="s">
         <v>467</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -6273,19 +6346,19 @@
         <v>46179</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>463</v>
-      </c>
-      <c r="E7" s="70" t="s">
+        <v>462</v>
+      </c>
+      <c r="E7" s="76" t="s">
+        <v>470</v>
+      </c>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76" t="s">
         <v>471</v>
       </c>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70" t="s">
-        <v>472</v>
-      </c>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -6293,18 +6366,26 @@
     </row>
     <row r="8" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="31"/>
-      <c r="B8" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="73"/>
+      <c r="B8" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <v>46182</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E8" s="94" t="s">
+        <v>483</v>
+      </c>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="94" t="s">
+        <v>484</v>
+      </c>
+      <c r="J8" s="95"/>
+      <c r="K8" s="96"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -6312,18 +6393,26 @@
     </row>
     <row r="9" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="31"/>
-      <c r="B9" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
+      <c r="B9" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" s="33">
+        <v>46182</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>485</v>
+      </c>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59" t="s">
+        <v>486</v>
+      </c>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -6331,18 +6420,26 @@
     </row>
     <row r="10" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="31"/>
-      <c r="B10" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
+      <c r="B10" s="45" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="46">
+        <v>46182</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>487</v>
+      </c>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76" t="s">
+        <v>488</v>
+      </c>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -6351,17 +6448,17 @@
     <row r="11" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="31"/>
       <c r="B11" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -6370,17 +6467,17 @@
     <row r="12" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="31"/>
       <c r="B12" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="75"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -6389,17 +6486,17 @@
     <row r="13" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31"/>
       <c r="B13" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -6408,17 +6505,17 @@
     <row r="14" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="31"/>
       <c r="B14" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -6427,17 +6524,17 @@
     <row r="15" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="31"/>
       <c r="B15" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -6446,17 +6543,17 @@
     <row r="16" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="31"/>
       <c r="B16" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -6465,17 +6562,17 @@
     <row r="17" spans="1:21" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31"/>
       <c r="B17" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -6484,17 +6581,17 @@
     <row r="18" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -6503,17 +6600,17 @@
     <row r="19" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="75"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -6522,17 +6619,17 @@
     <row r="20" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -6541,17 +6638,17 @@
     <row r="21" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -6560,17 +6657,17 @@
     <row r="22" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -6579,17 +6676,17 @@
     <row r="23" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="74"/>
+      <c r="K23" s="75"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -6598,17 +6695,17 @@
     <row r="24" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -6617,17 +6714,17 @@
     <row r="25" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -6636,17 +6733,17 @@
     <row r="26" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -6670,17 +6767,17 @@
     <row r="27" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="75"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -6695,17 +6792,17 @@
     <row r="28" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -6717,17 +6814,17 @@
     <row r="29" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -6739,17 +6836,17 @@
     <row r="30" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -6761,17 +6858,17 @@
     <row r="31" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -6780,17 +6877,17 @@
     <row r="32" spans="1:21" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -6799,17 +6896,17 @@
     <row r="33" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -6818,17 +6915,17 @@
     <row r="34" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="75"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -6837,17 +6934,17 @@
     <row r="35" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -6856,17 +6953,17 @@
     <row r="36" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -6875,17 +6972,17 @@
     <row r="37" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -6894,17 +6991,17 @@
     <row r="38" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="73"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="75"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -6913,17 +7010,17 @@
     <row r="39" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -6932,17 +7029,17 @@
     <row r="40" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="69"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -6951,17 +7048,17 @@
     <row r="41" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -6970,17 +7067,17 @@
     <row r="42" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
       <c r="B42" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="75"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -6989,17 +7086,17 @@
     <row r="43" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="69"/>
-      <c r="K43" s="69"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -7008,17 +7105,17 @@
     <row r="44" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="69"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="69"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -7027,17 +7124,17 @@
     <row r="45" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="69"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -7046,17 +7143,17 @@
     <row r="46" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -7065,17 +7162,17 @@
     <row r="47" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -7084,17 +7181,17 @@
     <row r="48" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="69"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -7103,17 +7200,17 @@
     <row r="49" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="57"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -7122,17 +7219,17 @@
     <row r="50" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="71"/>
-      <c r="F50" s="72"/>
-      <c r="G50" s="72"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="72"/>
-      <c r="K50" s="73"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="73"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="75"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -7141,17 +7238,17 @@
     <row r="51" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="69"/>
-      <c r="I51" s="69"/>
-      <c r="J51" s="69"/>
-      <c r="K51" s="69"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -7160,17 +7257,17 @@
     <row r="52" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="69"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="69"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -7179,17 +7276,17 @@
     <row r="53" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="69"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="69"/>
-      <c r="I53" s="69"/>
-      <c r="J53" s="69"/>
-      <c r="K53" s="69"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -7198,17 +7295,17 @@
     <row r="54" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="71"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="71"/>
-      <c r="J54" s="72"/>
-      <c r="K54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="75"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -7217,17 +7314,17 @@
     <row r="55" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="69"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="69"/>
-      <c r="J55" s="69"/>
-      <c r="K55" s="69"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -7236,17 +7333,17 @@
     <row r="56" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="69"/>
-      <c r="F56" s="69"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="69"/>
-      <c r="J56" s="69"/>
-      <c r="K56" s="69"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="57"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -7255,17 +7352,17 @@
     <row r="57" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="69"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="69"/>
-      <c r="J57" s="69"/>
-      <c r="K57" s="69"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="57"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -7274,17 +7371,17 @@
     <row r="58" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="71"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="72"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="71"/>
-      <c r="J58" s="72"/>
-      <c r="K58" s="73"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="75"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -7293,17 +7390,17 @@
     <row r="59" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="69"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="69"/>
-      <c r="I59" s="69"/>
-      <c r="J59" s="69"/>
-      <c r="K59" s="69"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -7312,17 +7409,17 @@
     <row r="60" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="69"/>
-      <c r="F60" s="69"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="69"/>
-      <c r="K60" s="69"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -7331,17 +7428,17 @@
     <row r="61" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="69"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57"/>
+      <c r="K61" s="57"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -7350,17 +7447,17 @@
     <row r="62" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="69"/>
-      <c r="K62" s="69"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="57"/>
+      <c r="K62" s="57"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -7369,17 +7466,17 @@
     <row r="63" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="69"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="69"/>
-      <c r="K63" s="69"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="57"/>
+      <c r="J63" s="57"/>
+      <c r="K63" s="57"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -7388,17 +7485,17 @@
     <row r="64" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="69"/>
-      <c r="F64" s="69"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="69"/>
-      <c r="K64" s="69"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -7407,17 +7504,17 @@
     <row r="65" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="71"/>
-      <c r="F65" s="72"/>
-      <c r="G65" s="72"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="71"/>
-      <c r="J65" s="72"/>
-      <c r="K65" s="73"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="73"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="75"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -7426,17 +7523,17 @@
     <row r="66" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="69"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -7445,17 +7542,17 @@
     <row r="67" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69"/>
-      <c r="H67" s="69"/>
-      <c r="I67" s="69"/>
-      <c r="J67" s="69"/>
-      <c r="K67" s="69"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="57"/>
+      <c r="K67" s="57"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -7464,17 +7561,17 @@
     <row r="68" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="69"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="69"/>
-      <c r="J68" s="69"/>
-      <c r="K68" s="69"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="57"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -7483,17 +7580,17 @@
     <row r="69" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="71"/>
-      <c r="J69" s="72"/>
-      <c r="K69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="73"/>
+      <c r="J69" s="74"/>
+      <c r="K69" s="75"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -7502,17 +7599,17 @@
     <row r="70" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="69"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="69"/>
-      <c r="K70" s="69"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="57"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -7521,17 +7618,17 @@
     <row r="71" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="69"/>
-      <c r="H71" s="69"/>
-      <c r="I71" s="69"/>
-      <c r="J71" s="69"/>
-      <c r="K71" s="69"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="57"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -7540,17 +7637,17 @@
     <row r="72" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="69"/>
-      <c r="K72" s="69"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -7559,17 +7656,17 @@
     <row r="73" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="71"/>
-      <c r="F73" s="72"/>
-      <c r="G73" s="72"/>
-      <c r="H73" s="73"/>
-      <c r="I73" s="71"/>
-      <c r="J73" s="72"/>
-      <c r="K73" s="73"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="73"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="75"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -7578,17 +7675,17 @@
     <row r="74" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="69"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="69"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
+      <c r="J74" s="57"/>
+      <c r="K74" s="57"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -7597,17 +7694,17 @@
     <row r="75" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="69"/>
-      <c r="H75" s="69"/>
-      <c r="I75" s="69"/>
-      <c r="J75" s="69"/>
-      <c r="K75" s="69"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="57"/>
+      <c r="K75" s="57"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -7616,17 +7713,17 @@
     <row r="76" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="69"/>
-      <c r="H76" s="69"/>
-      <c r="I76" s="69"/>
-      <c r="J76" s="69"/>
-      <c r="K76" s="69"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="57"/>
+      <c r="J76" s="57"/>
+      <c r="K76" s="57"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -7635,17 +7732,17 @@
     <row r="77" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="69"/>
-      <c r="H77" s="69"/>
-      <c r="I77" s="69"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="69"/>
+      <c r="E77" s="57"/>
+      <c r="F77" s="57"/>
+      <c r="G77" s="57"/>
+      <c r="H77" s="57"/>
+      <c r="I77" s="57"/>
+      <c r="J77" s="57"/>
+      <c r="K77" s="57"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -7654,17 +7751,17 @@
     <row r="78" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="69"/>
-      <c r="F78" s="69"/>
-      <c r="G78" s="69"/>
-      <c r="H78" s="69"/>
-      <c r="I78" s="69"/>
-      <c r="J78" s="69"/>
-      <c r="K78" s="69"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="57"/>
+      <c r="J78" s="57"/>
+      <c r="K78" s="57"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -7673,17 +7770,17 @@
     <row r="79" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="69"/>
-      <c r="F79" s="69"/>
-      <c r="G79" s="69"/>
-      <c r="H79" s="69"/>
-      <c r="I79" s="69"/>
-      <c r="J79" s="69"/>
-      <c r="K79" s="69"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="57"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -7692,17 +7789,17 @@
     <row r="80" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="77"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="78"/>
-      <c r="H80" s="79"/>
-      <c r="I80" s="77"/>
-      <c r="J80" s="78"/>
-      <c r="K80" s="79"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="70"/>
+      <c r="J80" s="71"/>
+      <c r="K80" s="72"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -7711,17 +7808,17 @@
     <row r="81" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="77"/>
-      <c r="F81" s="78"/>
-      <c r="G81" s="78"/>
-      <c r="H81" s="79"/>
-      <c r="I81" s="77"/>
-      <c r="J81" s="78"/>
-      <c r="K81" s="79"/>
+      <c r="E81" s="70"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="70"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="72"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -7730,17 +7827,17 @@
     <row r="82" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="78"/>
-      <c r="G82" s="78"/>
-      <c r="H82" s="79"/>
-      <c r="I82" s="77"/>
-      <c r="J82" s="78"/>
-      <c r="K82" s="79"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="72"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -7749,17 +7846,17 @@
     <row r="83" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="77"/>
-      <c r="F83" s="78"/>
-      <c r="G83" s="78"/>
-      <c r="H83" s="79"/>
-      <c r="I83" s="77"/>
-      <c r="J83" s="78"/>
-      <c r="K83" s="79"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="70"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="72"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -7768,17 +7865,17 @@
     <row r="84" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="77"/>
-      <c r="F84" s="78"/>
-      <c r="G84" s="78"/>
-      <c r="H84" s="79"/>
-      <c r="I84" s="77"/>
-      <c r="J84" s="78"/>
-      <c r="K84" s="79"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="71"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="71"/>
+      <c r="K84" s="72"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -7787,17 +7884,17 @@
     <row r="85" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="77"/>
-      <c r="F85" s="78"/>
-      <c r="G85" s="78"/>
-      <c r="H85" s="79"/>
-      <c r="I85" s="77"/>
-      <c r="J85" s="78"/>
-      <c r="K85" s="79"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="71"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="72"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -7806,17 +7903,17 @@
     <row r="86" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="77"/>
-      <c r="F86" s="78"/>
-      <c r="G86" s="78"/>
-      <c r="H86" s="79"/>
-      <c r="I86" s="77"/>
-      <c r="J86" s="78"/>
-      <c r="K86" s="79"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="71"/>
+      <c r="H86" s="72"/>
+      <c r="I86" s="70"/>
+      <c r="J86" s="71"/>
+      <c r="K86" s="72"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -7825,17 +7922,17 @@
     <row r="87" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="78"/>
-      <c r="G87" s="78"/>
-      <c r="H87" s="79"/>
-      <c r="I87" s="77"/>
-      <c r="J87" s="78"/>
-      <c r="K87" s="79"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="72"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -7844,17 +7941,17 @@
     <row r="88" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="77"/>
-      <c r="F88" s="78"/>
-      <c r="G88" s="78"/>
-      <c r="H88" s="79"/>
-      <c r="I88" s="77"/>
-      <c r="J88" s="78"/>
-      <c r="K88" s="79"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="71"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="70"/>
+      <c r="J88" s="71"/>
+      <c r="K88" s="72"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -7863,17 +7960,17 @@
     <row r="89" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="77"/>
-      <c r="F89" s="78"/>
-      <c r="G89" s="78"/>
-      <c r="H89" s="79"/>
-      <c r="I89" s="77"/>
-      <c r="J89" s="78"/>
-      <c r="K89" s="79"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="70"/>
+      <c r="J89" s="71"/>
+      <c r="K89" s="72"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -7882,17 +7979,17 @@
     <row r="90" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="77"/>
-      <c r="F90" s="78"/>
-      <c r="G90" s="78"/>
-      <c r="H90" s="79"/>
-      <c r="I90" s="77"/>
-      <c r="J90" s="78"/>
-      <c r="K90" s="79"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="71"/>
+      <c r="K90" s="72"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -7901,17 +7998,17 @@
     <row r="91" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="69"/>
-      <c r="F91" s="69"/>
-      <c r="G91" s="69"/>
-      <c r="H91" s="69"/>
-      <c r="I91" s="69"/>
-      <c r="J91" s="69"/>
-      <c r="K91" s="69"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="57"/>
+      <c r="J91" s="57"/>
+      <c r="K91" s="57"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -7920,17 +8017,17 @@
     <row r="92" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="69"/>
-      <c r="H92" s="69"/>
-      <c r="I92" s="69"/>
-      <c r="J92" s="69"/>
-      <c r="K92" s="69"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
+      <c r="K92" s="57"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -7939,17 +8036,17 @@
     <row r="93" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="69"/>
-      <c r="F93" s="69"/>
-      <c r="G93" s="69"/>
-      <c r="H93" s="69"/>
-      <c r="I93" s="69"/>
-      <c r="J93" s="69"/>
-      <c r="K93" s="69"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="57"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -7958,17 +8055,17 @@
     <row r="94" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="69"/>
-      <c r="F94" s="69"/>
-      <c r="G94" s="69"/>
-      <c r="H94" s="69"/>
-      <c r="I94" s="69"/>
-      <c r="J94" s="69"/>
-      <c r="K94" s="69"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
+      <c r="I94" s="57"/>
+      <c r="J94" s="57"/>
+      <c r="K94" s="57"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -7977,17 +8074,17 @@
     <row r="95" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="69"/>
-      <c r="F95" s="69"/>
-      <c r="G95" s="69"/>
-      <c r="H95" s="69"/>
-      <c r="I95" s="69"/>
-      <c r="J95" s="69"/>
-      <c r="K95" s="69"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="57"/>
+      <c r="J95" s="57"/>
+      <c r="K95" s="57"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -7996,17 +8093,17 @@
     <row r="96" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="69"/>
-      <c r="F96" s="69"/>
-      <c r="G96" s="69"/>
-      <c r="H96" s="69"/>
-      <c r="I96" s="69"/>
-      <c r="J96" s="69"/>
-      <c r="K96" s="69"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="57"/>
+      <c r="J96" s="57"/>
+      <c r="K96" s="57"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -8015,17 +8112,17 @@
     <row r="97" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="69"/>
-      <c r="F97" s="69"/>
-      <c r="G97" s="69"/>
-      <c r="H97" s="69"/>
-      <c r="I97" s="69"/>
-      <c r="J97" s="69"/>
-      <c r="K97" s="69"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="57"/>
+      <c r="J97" s="57"/>
+      <c r="K97" s="57"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -8034,17 +8131,17 @@
     <row r="98" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="69"/>
-      <c r="F98" s="69"/>
-      <c r="G98" s="69"/>
-      <c r="H98" s="69"/>
-      <c r="I98" s="69"/>
-      <c r="J98" s="69"/>
-      <c r="K98" s="69"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="57"/>
+      <c r="J98" s="57"/>
+      <c r="K98" s="57"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -8053,17 +8150,17 @@
     <row r="99" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="69"/>
-      <c r="F99" s="69"/>
-      <c r="G99" s="69"/>
-      <c r="H99" s="69"/>
-      <c r="I99" s="69"/>
-      <c r="J99" s="69"/>
-      <c r="K99" s="69"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="57"/>
+      <c r="J99" s="57"/>
+      <c r="K99" s="57"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -8072,17 +8169,17 @@
     <row r="100" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="69"/>
-      <c r="F100" s="69"/>
-      <c r="G100" s="69"/>
-      <c r="H100" s="69"/>
-      <c r="I100" s="69"/>
-      <c r="J100" s="69"/>
-      <c r="K100" s="69"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -8090,17 +8187,17 @@
     </row>
     <row r="101" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="69"/>
-      <c r="F101" s="69"/>
-      <c r="G101" s="69"/>
-      <c r="H101" s="69"/>
-      <c r="I101" s="69"/>
-      <c r="J101" s="69"/>
-      <c r="K101" s="69"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="57"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -8108,17 +8205,17 @@
     </row>
     <row r="102" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="69"/>
-      <c r="F102" s="69"/>
-      <c r="G102" s="69"/>
-      <c r="H102" s="69"/>
-      <c r="I102" s="69"/>
-      <c r="J102" s="69"/>
-      <c r="K102" s="69"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="57"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -8126,17 +8223,17 @@
     </row>
     <row r="103" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="69"/>
-      <c r="F103" s="69"/>
-      <c r="G103" s="69"/>
-      <c r="H103" s="69"/>
-      <c r="I103" s="69"/>
-      <c r="J103" s="69"/>
-      <c r="K103" s="69"/>
+      <c r="E103" s="57"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="57"/>
+      <c r="H103" s="57"/>
+      <c r="I103" s="57"/>
+      <c r="J103" s="57"/>
+      <c r="K103" s="57"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -8144,196 +8241,6 @@
     </row>
   </sheetData>
   <mergeCells count="203">
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -8347,6 +8254,196 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -8756,148 +8853,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="86"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="90"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="82" t="e" vm="2">
+      <c r="B3" s="86" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="90" t="s">
+      <c r="F3" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="90" t="s">
+      <c r="J3" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="82" t="e" vm="3">
+      <c r="N3" s="86" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="90" t="s">
+      <c r="F4" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="90" t="s">
+      <c r="J4" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="82"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="86"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="89"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="82" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91" t="s">
+      <c r="C8" s="82"/>
+      <c r="D8" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="88" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88" t="s">
+      <c r="C10" s="84"/>
+      <c r="D10" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88" t="s">
+      <c r="C11" s="84"/>
+      <c r="D11" s="84" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -8908,6 +8997,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5891EC8E-9D93-439D-8958-B5477E7B6B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FFA1F5-4F74-4758-8341-CCBCA12376E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="499">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2194,6 +2194,26 @@
   </si>
   <si>
     <t>다용도실도 표기위치 추가요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리가 싱크대 패널 밑으로 올라옴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해결방안으로 GlobalInventoryCanvas_Prefab에 있는 인스펙터 창에서 캔버스 부분에 Sort 부분을 4로 상승시면 해결가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 싱크대에 물통을 넣고 물을 넣을려고 하면 수도꼭지와 이미지가 사라지는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 또한 관련된 부분으로 Sink_Pannel에서 Sort 부분을 수정하는 것으로 해결 가능한 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2627,108 +2647,144 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2736,43 +2792,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3272,36 +3292,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3314,17 +3334,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3343,17 +3363,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64" t="s">
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3370,17 +3390,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="64" t="s">
+      <c r="E5" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64" t="s">
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3397,17 +3417,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64" t="s">
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3424,17 +3444,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="E7" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="64" t="s">
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3451,17 +3471,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="65" t="s">
+      <c r="E8" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="64" t="s">
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3478,17 +3498,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="65" t="s">
+      <c r="E9" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="64" t="s">
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3505,17 +3525,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="65" t="s">
+      <c r="E10" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="64" t="s">
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3532,17 +3552,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="64" t="s">
+      <c r="E11" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64" t="s">
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3559,17 +3579,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64" t="s">
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3586,17 +3606,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="64" t="s">
+      <c r="E13" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64" t="s">
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3613,17 +3633,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="64" t="s">
+      <c r="E14" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64" t="s">
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3640,17 +3660,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3667,17 +3687,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="64" t="s">
+      <c r="E16" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3694,17 +3714,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="64" t="s">
+      <c r="E17" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3721,17 +3741,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="64" t="s">
+      <c r="E18" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64" t="s">
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3748,17 +3768,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59" t="s">
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3775,17 +3795,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59" t="s">
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3802,17 +3822,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59" t="s">
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3829,17 +3849,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59" t="s">
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3856,17 +3876,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59" t="s">
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3883,17 +3903,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59" t="s">
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3910,17 +3930,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="59" t="s">
+      <c r="E25" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59" t="s">
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3937,17 +3957,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="60" t="s">
+      <c r="E26" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60" t="s">
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3979,17 +3999,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="52" t="s">
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="53"/>
-      <c r="K27" s="54"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="76"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -4012,17 +4032,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="74" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="52" t="s">
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="53"/>
-      <c r="K28" s="54"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="76"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -4042,17 +4062,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="74" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="52" t="s">
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="53"/>
-      <c r="K29" s="54"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="76"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4072,17 +4092,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60" t="s">
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4102,17 +4122,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="77" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55" t="s">
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4129,17 +4149,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55" t="s">
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4156,17 +4176,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55" t="s">
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4183,17 +4203,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="61" t="s">
+      <c r="E34" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="56" t="s">
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="50"/>
-      <c r="K34" s="51"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="80"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4210,17 +4230,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="61" t="s">
+      <c r="E35" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="49" t="s">
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="81" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4237,17 +4257,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="70" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="49" t="s">
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4264,17 +4284,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="49" t="s">
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="81" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4291,17 +4311,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="E38" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="49" t="s">
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="50"/>
-      <c r="K38" s="51"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="80"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4318,17 +4338,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="48" t="s">
+      <c r="E39" s="73" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48" t="s">
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4345,17 +4365,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48" t="s">
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="73"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4372,17 +4392,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="E41" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48" t="s">
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4399,17 +4419,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="48" t="s">
+      <c r="E42" s="73" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48" t="s">
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
+      <c r="J42" s="73"/>
+      <c r="K42" s="73"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4426,17 +4446,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="73" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48" t="s">
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="J43" s="73"/>
+      <c r="K43" s="73"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4453,17 +4473,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="73" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48" t="s">
+      <c r="F44" s="73"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="73" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="J44" s="73"/>
+      <c r="K44" s="73"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4480,17 +4500,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="48" t="s">
+      <c r="E45" s="73" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48" t="s">
+      <c r="F45" s="73"/>
+      <c r="G45" s="73"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="73" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="J45" s="73"/>
+      <c r="K45" s="73"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4507,17 +4527,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="73" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48" t="s">
+      <c r="F46" s="73"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="73" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="J46" s="73"/>
+      <c r="K46" s="73"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4534,17 +4554,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="48" t="s">
+      <c r="E47" s="73" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48" t="s">
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="J47" s="73"/>
+      <c r="K47" s="73"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4561,17 +4581,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="48" t="s">
+      <c r="E48" s="73" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48" t="s">
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="J48" s="73"/>
+      <c r="K48" s="73"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4588,17 +4608,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="73" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48" t="s">
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="J49" s="73"/>
+      <c r="K49" s="73"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4615,17 +4635,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48" t="s">
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="48"/>
-      <c r="K50" s="48"/>
+      <c r="J50" s="73"/>
+      <c r="K50" s="73"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4642,17 +4662,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="73" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48" t="s">
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="J51" s="73"/>
+      <c r="K51" s="73"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4669,17 +4689,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="48" t="s">
+      <c r="E52" s="73" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48" t="s">
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="73" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="J52" s="73"/>
+      <c r="K52" s="73"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4696,17 +4716,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="73" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48" t="s">
+      <c r="F53" s="73"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="J53" s="73"/>
+      <c r="K53" s="73"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4723,17 +4743,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="49" t="s">
+      <c r="E54" s="81" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="49"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="49" t="s">
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="49"/>
-      <c r="K54" s="49"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4750,17 +4770,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="49" t="s">
+      <c r="E55" s="81" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49" t="s">
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4777,17 +4797,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="49" t="s">
+      <c r="E56" s="81" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49" t="s">
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="49"/>
-      <c r="K56" s="49"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4804,17 +4824,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48" t="s">
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="J57" s="73"/>
+      <c r="K57" s="73"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4831,17 +4851,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="48" t="s">
+      <c r="E58" s="73" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48" t="s">
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="J58" s="73"/>
+      <c r="K58" s="73"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4858,17 +4878,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="48" t="s">
+      <c r="E59" s="73" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48" t="s">
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="J59" s="73"/>
+      <c r="K59" s="73"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4885,17 +4905,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="48" t="s">
+      <c r="E60" s="73" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48" t="s">
+      <c r="F60" s="73"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="73" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="J60" s="73"/>
+      <c r="K60" s="73"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4912,17 +4932,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="48" t="s">
+      <c r="E61" s="73" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48" t="s">
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="J61" s="73"/>
+      <c r="K61" s="73"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4939,17 +4959,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="73" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48" t="s">
+      <c r="F62" s="73"/>
+      <c r="G62" s="73"/>
+      <c r="H62" s="73"/>
+      <c r="I62" s="73" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="J62" s="73"/>
+      <c r="K62" s="73"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4966,17 +4986,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="48" t="s">
+      <c r="E63" s="73" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48" t="e" vm="1">
+      <c r="F63" s="73"/>
+      <c r="G63" s="73"/>
+      <c r="H63" s="73"/>
+      <c r="I63" s="73" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="J63" s="73"/>
+      <c r="K63" s="73"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -4993,17 +5013,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="73" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48" t="s">
+      <c r="F64" s="73"/>
+      <c r="G64" s="73"/>
+      <c r="H64" s="73"/>
+      <c r="I64" s="73" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="J64" s="73"/>
+      <c r="K64" s="73"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -5020,17 +5040,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="73" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48" t="s">
+      <c r="F65" s="73"/>
+      <c r="G65" s="73"/>
+      <c r="H65" s="73"/>
+      <c r="I65" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="J65" s="73"/>
+      <c r="K65" s="73"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -5047,17 +5067,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="73" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48" t="s">
+      <c r="F66" s="73"/>
+      <c r="G66" s="73"/>
+      <c r="H66" s="73"/>
+      <c r="I66" s="73" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="J66" s="73"/>
+      <c r="K66" s="73"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5074,17 +5094,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="58" t="s">
+      <c r="E67" s="82" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="48" t="s">
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
+      <c r="H67" s="82"/>
+      <c r="I67" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="J67" s="73"/>
+      <c r="K67" s="73"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5101,17 +5121,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="49" t="s">
+      <c r="E68" s="81" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="49" t="s">
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="49"/>
-      <c r="K68" s="49"/>
+      <c r="J68" s="81"/>
+      <c r="K68" s="81"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5128,17 +5148,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="49" t="s">
+      <c r="E69" s="81" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="49" t="s">
+      <c r="F69" s="81"/>
+      <c r="G69" s="81"/>
+      <c r="H69" s="81"/>
+      <c r="I69" s="81" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="49"/>
-      <c r="K69" s="49"/>
+      <c r="J69" s="81"/>
+      <c r="K69" s="81"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5155,17 +5175,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="49" t="s">
+      <c r="E70" s="81" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49" t="s">
+      <c r="F70" s="81"/>
+      <c r="G70" s="81"/>
+      <c r="H70" s="81"/>
+      <c r="I70" s="81" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
+      <c r="J70" s="81"/>
+      <c r="K70" s="81"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5182,17 +5202,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="49" t="s">
+      <c r="E71" s="81" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="49" t="s">
+      <c r="F71" s="81"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="81"/>
+      <c r="I71" s="81" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="49"/>
-      <c r="K71" s="49"/>
+      <c r="J71" s="81"/>
+      <c r="K71" s="81"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5209,17 +5229,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="49" t="s">
+      <c r="E72" s="81" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49" t="s">
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="49"/>
-      <c r="K72" s="49"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5236,17 +5256,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="49" t="s">
+      <c r="E73" s="81" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49" t="s">
+      <c r="F73" s="81"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="81" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="49"/>
-      <c r="K73" s="49"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="81"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5263,17 +5283,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="49" t="s">
+      <c r="E74" s="81" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49" t="s">
+      <c r="F74" s="81"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="81"/>
+      <c r="I74" s="81" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="49"/>
-      <c r="K74" s="49"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="81"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5290,17 +5310,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="49" t="s">
+      <c r="E75" s="81" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49" t="s">
+      <c r="F75" s="81"/>
+      <c r="G75" s="81"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="81" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="49"/>
-      <c r="K75" s="49"/>
+      <c r="J75" s="81"/>
+      <c r="K75" s="81"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5317,17 +5337,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="49" t="s">
+      <c r="E76" s="81" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49" t="s">
+      <c r="F76" s="81"/>
+      <c r="G76" s="81"/>
+      <c r="H76" s="81"/>
+      <c r="I76" s="81" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="49"/>
-      <c r="K76" s="49"/>
+      <c r="J76" s="81"/>
+      <c r="K76" s="81"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5344,17 +5364,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="49" t="s">
+      <c r="E77" s="81" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="49"/>
-      <c r="G77" s="49"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="49" t="s">
+      <c r="F77" s="81"/>
+      <c r="G77" s="81"/>
+      <c r="H77" s="81"/>
+      <c r="I77" s="81" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="49"/>
-      <c r="K77" s="49"/>
+      <c r="J77" s="81"/>
+      <c r="K77" s="81"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5371,17 +5391,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="49" t="s">
+      <c r="E78" s="81" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49" t="s">
+      <c r="F78" s="81"/>
+      <c r="G78" s="81"/>
+      <c r="H78" s="81"/>
+      <c r="I78" s="81" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="81"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5398,17 +5418,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="49" t="s">
+      <c r="E79" s="81" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49" t="s">
+      <c r="F79" s="81"/>
+      <c r="G79" s="81"/>
+      <c r="H79" s="81"/>
+      <c r="I79" s="81" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
+      <c r="J79" s="81"/>
+      <c r="K79" s="81"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5425,17 +5445,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="49" t="s">
+      <c r="E80" s="81" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49" t="s">
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="81"/>
+      <c r="I80" s="81" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="49"/>
-      <c r="K80" s="49"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="81"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5452,17 +5472,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="48" t="s">
+      <c r="E81" s="73" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48" t="s">
+      <c r="F81" s="73"/>
+      <c r="G81" s="73"/>
+      <c r="H81" s="73"/>
+      <c r="I81" s="73" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="J81" s="73"/>
+      <c r="K81" s="73"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5479,17 +5499,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="48" t="s">
+      <c r="E82" s="73" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48" t="s">
+      <c r="F82" s="73"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="73"/>
+      <c r="I82" s="73" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="J82" s="73"/>
+      <c r="K82" s="73"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5506,17 +5526,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="48" t="s">
+      <c r="E83" s="73" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48" t="s">
+      <c r="F83" s="73"/>
+      <c r="G83" s="73"/>
+      <c r="H83" s="73"/>
+      <c r="I83" s="73" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="J83" s="73"/>
+      <c r="K83" s="73"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5533,17 +5553,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="48" t="s">
+      <c r="E84" s="73" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48" t="s">
+      <c r="F84" s="73"/>
+      <c r="G84" s="73"/>
+      <c r="H84" s="73"/>
+      <c r="I84" s="73" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="J84" s="73"/>
+      <c r="K84" s="73"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5560,17 +5580,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="48" t="s">
+      <c r="E85" s="73" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48" t="s">
+      <c r="F85" s="73"/>
+      <c r="G85" s="73"/>
+      <c r="H85" s="73"/>
+      <c r="I85" s="73" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="J85" s="73"/>
+      <c r="K85" s="73"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5587,17 +5607,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="48" t="s">
+      <c r="E86" s="73" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48" t="s">
+      <c r="F86" s="73"/>
+      <c r="G86" s="73"/>
+      <c r="H86" s="73"/>
+      <c r="I86" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
+      <c r="J86" s="73"/>
+      <c r="K86" s="73"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5614,17 +5634,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="48" t="s">
+      <c r="E87" s="73" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48" t="s">
+      <c r="F87" s="73"/>
+      <c r="G87" s="73"/>
+      <c r="H87" s="73"/>
+      <c r="I87" s="73" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
+      <c r="J87" s="73"/>
+      <c r="K87" s="73"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5641,17 +5661,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="49" t="s">
+      <c r="E88" s="81" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49" t="s">
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
+      <c r="H88" s="81"/>
+      <c r="I88" s="81" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="49"/>
-      <c r="K88" s="49"/>
+      <c r="J88" s="81"/>
+      <c r="K88" s="81"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5668,17 +5688,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="49" t="s">
+      <c r="E89" s="81" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="49"/>
-      <c r="G89" s="49"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="49" t="s">
+      <c r="F89" s="81"/>
+      <c r="G89" s="81"/>
+      <c r="H89" s="81"/>
+      <c r="I89" s="81" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="49"/>
-      <c r="K89" s="49"/>
+      <c r="J89" s="81"/>
+      <c r="K89" s="81"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5695,17 +5715,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="49" t="s">
+      <c r="E90" s="81" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="49"/>
-      <c r="G90" s="49"/>
-      <c r="H90" s="49"/>
-      <c r="I90" s="49" t="s">
+      <c r="F90" s="81"/>
+      <c r="G90" s="81"/>
+      <c r="H90" s="81"/>
+      <c r="I90" s="81" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="49"/>
-      <c r="K90" s="49"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="81"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5722,17 +5742,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="49" t="s">
+      <c r="E91" s="81" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="49"/>
-      <c r="G91" s="49"/>
-      <c r="H91" s="49"/>
-      <c r="I91" s="49" t="s">
+      <c r="F91" s="81"/>
+      <c r="G91" s="81"/>
+      <c r="H91" s="81"/>
+      <c r="I91" s="81" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="49"/>
-      <c r="K91" s="49"/>
+      <c r="J91" s="81"/>
+      <c r="K91" s="81"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5749,17 +5769,17 @@
       <c r="D92" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="E92" s="55" t="s">
+      <c r="E92" s="77" t="s">
         <v>474</v>
       </c>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="55"/>
-      <c r="I92" s="55" t="s">
+      <c r="F92" s="77"/>
+      <c r="G92" s="77"/>
+      <c r="H92" s="77"/>
+      <c r="I92" s="77" t="s">
         <v>475</v>
       </c>
-      <c r="J92" s="55"/>
-      <c r="K92" s="55"/>
+      <c r="J92" s="77"/>
+      <c r="K92" s="77"/>
       <c r="L92" s="9" t="s">
         <v>164</v>
       </c>
@@ -5776,17 +5796,17 @@
       <c r="D93" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E93" s="55" t="s">
+      <c r="E93" s="77" t="s">
         <v>476</v>
       </c>
-      <c r="F93" s="55"/>
-      <c r="G93" s="55"/>
-      <c r="H93" s="55"/>
-      <c r="I93" s="55" t="s">
+      <c r="F93" s="77"/>
+      <c r="G93" s="77"/>
+      <c r="H93" s="77"/>
+      <c r="I93" s="77" t="s">
         <v>477</v>
       </c>
-      <c r="J93" s="55"/>
-      <c r="K93" s="55"/>
+      <c r="J93" s="77"/>
+      <c r="K93" s="77"/>
       <c r="L93" s="9" t="s">
         <v>164</v>
       </c>
@@ -5803,17 +5823,17 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="55" t="s">
+      <c r="E94" s="77" t="s">
         <v>478</v>
       </c>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55" t="s">
+      <c r="F94" s="77"/>
+      <c r="G94" s="77"/>
+      <c r="H94" s="77"/>
+      <c r="I94" s="77" t="s">
         <v>479</v>
       </c>
-      <c r="J94" s="55"/>
-      <c r="K94" s="55"/>
+      <c r="J94" s="77"/>
+      <c r="K94" s="77"/>
       <c r="L94" s="9" t="s">
         <v>164</v>
       </c>
@@ -5830,17 +5850,17 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="55" t="s">
+      <c r="E95" s="77" t="s">
         <v>480</v>
       </c>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="55"/>
-      <c r="I95" s="55" t="s">
+      <c r="F95" s="77"/>
+      <c r="G95" s="77"/>
+      <c r="H95" s="77"/>
+      <c r="I95" s="77" t="s">
         <v>481</v>
       </c>
-      <c r="J95" s="55"/>
-      <c r="K95" s="55"/>
+      <c r="J95" s="77"/>
+      <c r="K95" s="77"/>
       <c r="L95" s="9" t="s">
         <v>164</v>
       </c>
@@ -5857,17 +5877,17 @@
       <c r="D96" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E96" s="55" t="s">
+      <c r="E96" s="77" t="s">
         <v>490</v>
       </c>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="55"/>
-      <c r="I96" s="55" t="s">
+      <c r="F96" s="77"/>
+      <c r="G96" s="77"/>
+      <c r="H96" s="77"/>
+      <c r="I96" s="77" t="s">
         <v>491</v>
       </c>
-      <c r="J96" s="55"/>
-      <c r="K96" s="55"/>
+      <c r="J96" s="77"/>
+      <c r="K96" s="77"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5884,17 +5904,17 @@
       <c r="D97" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="E97" s="55" t="s">
+      <c r="E97" s="77" t="s">
         <v>492</v>
       </c>
-      <c r="F97" s="55"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="55"/>
-      <c r="I97" s="55" t="s">
+      <c r="F97" s="77"/>
+      <c r="G97" s="77"/>
+      <c r="H97" s="77"/>
+      <c r="I97" s="77" t="s">
         <v>493</v>
       </c>
-      <c r="J97" s="55"/>
-      <c r="K97" s="55"/>
+      <c r="J97" s="77"/>
+      <c r="K97" s="77"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5902,18 +5922,26 @@
     </row>
     <row r="98" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="57"/>
-      <c r="G98" s="57"/>
-      <c r="H98" s="57"/>
-      <c r="I98" s="57"/>
-      <c r="J98" s="57"/>
-      <c r="K98" s="57"/>
+      <c r="C98" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D98" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="E98" s="77" t="s">
+        <v>494</v>
+      </c>
+      <c r="F98" s="77"/>
+      <c r="G98" s="77"/>
+      <c r="H98" s="77"/>
+      <c r="I98" s="77" t="s">
+        <v>495</v>
+      </c>
+      <c r="J98" s="77"/>
+      <c r="K98" s="77"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -5921,18 +5949,26 @@
     </row>
     <row r="99" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="57"/>
-      <c r="F99" s="57"/>
-      <c r="G99" s="57"/>
-      <c r="H99" s="57"/>
-      <c r="I99" s="57"/>
-      <c r="J99" s="57"/>
-      <c r="K99" s="57"/>
+      <c r="C99" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D99" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="E99" s="77" t="s">
+        <v>497</v>
+      </c>
+      <c r="F99" s="77"/>
+      <c r="G99" s="77"/>
+      <c r="H99" s="77"/>
+      <c r="I99" s="77" t="s">
+        <v>498</v>
+      </c>
+      <c r="J99" s="77"/>
+      <c r="K99" s="77"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -5945,13 +5981,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="57"/>
-      <c r="G100" s="57"/>
-      <c r="H100" s="57"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="57"/>
-      <c r="K100" s="57"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="61"/>
+      <c r="G100" s="61"/>
+      <c r="H100" s="61"/>
+      <c r="I100" s="61"/>
+      <c r="J100" s="61"/>
+      <c r="K100" s="61"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5959,6 +5995,179 @@
     </row>
   </sheetData>
   <mergeCells count="197">
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -5983,179 +6192,6 @@
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -6196,36 +6232,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -6238,17 +6274,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -6267,17 +6303,17 @@
       <c r="D4" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="55" t="s">
         <v>463</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="77" t="s">
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="55" t="s">
         <v>464</v>
       </c>
-      <c r="J4" s="78"/>
-      <c r="K4" s="79"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
@@ -6294,17 +6330,17 @@
       <c r="D5" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="49" t="s">
         <v>468</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76" t="s">
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49" t="s">
         <v>469</v>
       </c>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -6321,17 +6357,17 @@
       <c r="D6" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="48" t="s">
         <v>466</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59" t="s">
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48" t="s">
         <v>467</v>
       </c>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -6348,17 +6384,17 @@
       <c r="D7" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76" t="s">
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49" t="s">
         <v>471</v>
       </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -6375,17 +6411,17 @@
       <c r="D8" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="50" t="s">
         <v>483</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="94" t="s">
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="50" t="s">
         <v>484</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="96"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="52"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -6402,17 +6438,17 @@
       <c r="D9" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="48" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59" t="s">
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48" t="s">
         <v>486</v>
       </c>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -6429,17 +6465,17 @@
       <c r="D10" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="49" t="s">
         <v>487</v>
       </c>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76" t="s">
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49" t="s">
         <v>488</v>
       </c>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -6452,13 +6488,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -6471,13 +6507,13 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="75"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="60"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -6490,13 +6526,13 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -6509,13 +6545,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -6528,13 +6564,13 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -6547,13 +6583,13 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -6566,13 +6602,13 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -6585,13 +6621,13 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -6604,13 +6640,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="75"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="60"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -6623,13 +6659,13 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -6642,13 +6678,13 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -6661,13 +6697,13 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -6680,13 +6716,13 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="75"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="60"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -6699,13 +6735,13 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -6718,13 +6754,13 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -6737,13 +6773,13 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -6771,13 +6807,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="75"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="60"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -6796,13 +6832,13 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -6818,13 +6854,13 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -6840,13 +6876,13 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -6862,13 +6898,13 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -6881,13 +6917,13 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="57"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -6900,13 +6936,13 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -6919,13 +6955,13 @@
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="75"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="59"/>
+      <c r="K34" s="60"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -6938,13 +6974,13 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -6957,13 +6993,13 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -6976,13 +7012,13 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -6995,13 +7031,13 @@
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="73"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="75"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="59"/>
+      <c r="K38" s="60"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -7014,13 +7050,13 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -7033,13 +7069,13 @@
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -7052,13 +7088,13 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -7071,13 +7107,13 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="75"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="59"/>
+      <c r="K42" s="60"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -7090,13 +7126,13 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -7109,13 +7145,13 @@
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="61"/>
+      <c r="J44" s="61"/>
+      <c r="K44" s="61"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -7128,13 +7164,13 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="61"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -7147,13 +7183,13 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -7166,13 +7202,13 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
+      <c r="E47" s="61"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -7185,13 +7221,13 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="57"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -7204,13 +7240,13 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="57"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -7223,13 +7259,13 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="73"/>
-      <c r="J50" s="74"/>
-      <c r="K50" s="75"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="59"/>
+      <c r="K50" s="60"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -7242,13 +7278,13 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
+      <c r="E51" s="61"/>
+      <c r="F51" s="61"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -7261,13 +7297,13 @@
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="57"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -7280,13 +7316,13 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="57"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61"/>
+      <c r="J53" s="61"/>
+      <c r="K53" s="61"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -7299,13 +7335,13 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="74"/>
-      <c r="K54" s="75"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="60"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="59"/>
+      <c r="K54" s="60"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -7318,13 +7354,13 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="57"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -7337,13 +7373,13 @@
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="57"/>
-      <c r="K56" s="57"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
+      <c r="J56" s="61"/>
+      <c r="K56" s="61"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -7356,13 +7392,13 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="57"/>
-      <c r="J57" s="57"/>
-      <c r="K57" s="57"/>
+      <c r="E57" s="61"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -7375,13 +7411,13 @@
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="74"/>
-      <c r="K58" s="75"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="58"/>
+      <c r="J58" s="59"/>
+      <c r="K58" s="60"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -7394,13 +7430,13 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="57"/>
-      <c r="J59" s="57"/>
-      <c r="K59" s="57"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -7413,13 +7449,13 @@
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="57"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="57"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="57"/>
-      <c r="K60" s="57"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -7432,13 +7468,13 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57"/>
-      <c r="K61" s="57"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61"/>
+      <c r="J61" s="61"/>
+      <c r="K61" s="61"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -7451,13 +7487,13 @@
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="57"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="57"/>
-      <c r="K62" s="57"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="61"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -7470,13 +7506,13 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="57"/>
-      <c r="K63" s="57"/>
+      <c r="E63" s="61"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -7489,13 +7525,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
-      <c r="K64" s="57"/>
+      <c r="E64" s="61"/>
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="61"/>
+      <c r="I64" s="61"/>
+      <c r="J64" s="61"/>
+      <c r="K64" s="61"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -7508,13 +7544,13 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="74"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="74"/>
-      <c r="K65" s="75"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="59"/>
+      <c r="K65" s="60"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -7527,13 +7563,13 @@
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="57"/>
-      <c r="J66" s="57"/>
-      <c r="K66" s="57"/>
+      <c r="E66" s="61"/>
+      <c r="F66" s="61"/>
+      <c r="G66" s="61"/>
+      <c r="H66" s="61"/>
+      <c r="I66" s="61"/>
+      <c r="J66" s="61"/>
+      <c r="K66" s="61"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -7546,13 +7582,13 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
-      <c r="J67" s="57"/>
-      <c r="K67" s="57"/>
+      <c r="E67" s="61"/>
+      <c r="F67" s="61"/>
+      <c r="G67" s="61"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="61"/>
+      <c r="K67" s="61"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -7565,13 +7601,13 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="57"/>
-      <c r="K68" s="57"/>
+      <c r="E68" s="61"/>
+      <c r="F68" s="61"/>
+      <c r="G68" s="61"/>
+      <c r="H68" s="61"/>
+      <c r="I68" s="61"/>
+      <c r="J68" s="61"/>
+      <c r="K68" s="61"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -7584,13 +7620,13 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="74"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="73"/>
-      <c r="J69" s="74"/>
-      <c r="K69" s="75"/>
+      <c r="E69" s="58"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="58"/>
+      <c r="J69" s="59"/>
+      <c r="K69" s="60"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -7603,13 +7639,13 @@
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
-      <c r="K70" s="57"/>
+      <c r="E70" s="61"/>
+      <c r="F70" s="61"/>
+      <c r="G70" s="61"/>
+      <c r="H70" s="61"/>
+      <c r="I70" s="61"/>
+      <c r="J70" s="61"/>
+      <c r="K70" s="61"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -7622,13 +7658,13 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
-      <c r="I71" s="57"/>
-      <c r="J71" s="57"/>
-      <c r="K71" s="57"/>
+      <c r="E71" s="61"/>
+      <c r="F71" s="61"/>
+      <c r="G71" s="61"/>
+      <c r="H71" s="61"/>
+      <c r="I71" s="61"/>
+      <c r="J71" s="61"/>
+      <c r="K71" s="61"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -7641,13 +7677,13 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
-      <c r="K72" s="57"/>
+      <c r="E72" s="61"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="61"/>
+      <c r="H72" s="61"/>
+      <c r="I72" s="61"/>
+      <c r="J72" s="61"/>
+      <c r="K72" s="61"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -7660,13 +7696,13 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="73"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="73"/>
-      <c r="J73" s="74"/>
-      <c r="K73" s="75"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="58"/>
+      <c r="J73" s="59"/>
+      <c r="K73" s="60"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -7679,13 +7715,13 @@
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
-      <c r="K74" s="57"/>
+      <c r="E74" s="61"/>
+      <c r="F74" s="61"/>
+      <c r="G74" s="61"/>
+      <c r="H74" s="61"/>
+      <c r="I74" s="61"/>
+      <c r="J74" s="61"/>
+      <c r="K74" s="61"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -7698,13 +7734,13 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
-      <c r="K75" s="57"/>
+      <c r="E75" s="61"/>
+      <c r="F75" s="61"/>
+      <c r="G75" s="61"/>
+      <c r="H75" s="61"/>
+      <c r="I75" s="61"/>
+      <c r="J75" s="61"/>
+      <c r="K75" s="61"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -7717,13 +7753,13 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="57"/>
-      <c r="K76" s="57"/>
+      <c r="E76" s="61"/>
+      <c r="F76" s="61"/>
+      <c r="G76" s="61"/>
+      <c r="H76" s="61"/>
+      <c r="I76" s="61"/>
+      <c r="J76" s="61"/>
+      <c r="K76" s="61"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -7736,13 +7772,13 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="57"/>
-      <c r="K77" s="57"/>
+      <c r="E77" s="61"/>
+      <c r="F77" s="61"/>
+      <c r="G77" s="61"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="61"/>
+      <c r="J77" s="61"/>
+      <c r="K77" s="61"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -7755,13 +7791,13 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="57"/>
-      <c r="K78" s="57"/>
+      <c r="E78" s="61"/>
+      <c r="F78" s="61"/>
+      <c r="G78" s="61"/>
+      <c r="H78" s="61"/>
+      <c r="I78" s="61"/>
+      <c r="J78" s="61"/>
+      <c r="K78" s="61"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -7774,13 +7810,13 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="57"/>
-      <c r="K79" s="57"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="61"/>
+      <c r="G79" s="61"/>
+      <c r="H79" s="61"/>
+      <c r="I79" s="61"/>
+      <c r="J79" s="61"/>
+      <c r="K79" s="61"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -7793,13 +7829,13 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="70"/>
-      <c r="J80" s="71"/>
-      <c r="K80" s="72"/>
+      <c r="E80" s="62"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="62"/>
+      <c r="J80" s="63"/>
+      <c r="K80" s="64"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -7812,13 +7848,13 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="72"/>
+      <c r="E81" s="62"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="64"/>
+      <c r="I81" s="62"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="64"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -7831,13 +7867,13 @@
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="70"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="72"/>
+      <c r="E82" s="62"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="64"/>
+      <c r="I82" s="62"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="64"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -7850,13 +7886,13 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="72"/>
+      <c r="E83" s="62"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="64"/>
+      <c r="I83" s="62"/>
+      <c r="J83" s="63"/>
+      <c r="K83" s="64"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -7869,13 +7905,13 @@
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="70"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="70"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="72"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="63"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="64"/>
+      <c r="I84" s="62"/>
+      <c r="J84" s="63"/>
+      <c r="K84" s="64"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -7888,13 +7924,13 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="70"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="72"/>
-      <c r="I85" s="70"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="72"/>
+      <c r="E85" s="62"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="64"/>
+      <c r="I85" s="62"/>
+      <c r="J85" s="63"/>
+      <c r="K85" s="64"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -7907,13 +7943,13 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="70"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="71"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="70"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="72"/>
+      <c r="E86" s="62"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="64"/>
+      <c r="I86" s="62"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="64"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -7926,13 +7962,13 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="70"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="70"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="72"/>
+      <c r="E87" s="62"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="64"/>
+      <c r="I87" s="62"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="64"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -7945,13 +7981,13 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="70"/>
-      <c r="F88" s="71"/>
-      <c r="G88" s="71"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="70"/>
-      <c r="J88" s="71"/>
-      <c r="K88" s="72"/>
+      <c r="E88" s="62"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="64"/>
+      <c r="I88" s="62"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="64"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -7964,13 +8000,13 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="70"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="71"/>
-      <c r="H89" s="72"/>
-      <c r="I89" s="70"/>
-      <c r="J89" s="71"/>
-      <c r="K89" s="72"/>
+      <c r="E89" s="62"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="64"/>
+      <c r="I89" s="62"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="64"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -7983,13 +8019,13 @@
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="71"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="70"/>
-      <c r="J90" s="71"/>
-      <c r="K90" s="72"/>
+      <c r="E90" s="62"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="64"/>
+      <c r="I90" s="62"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="64"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -8002,13 +8038,13 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="57"/>
-      <c r="G91" s="57"/>
-      <c r="H91" s="57"/>
-      <c r="I91" s="57"/>
-      <c r="J91" s="57"/>
-      <c r="K91" s="57"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="61"/>
+      <c r="G91" s="61"/>
+      <c r="H91" s="61"/>
+      <c r="I91" s="61"/>
+      <c r="J91" s="61"/>
+      <c r="K91" s="61"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -8021,13 +8057,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="57"/>
-      <c r="H92" s="57"/>
-      <c r="I92" s="57"/>
-      <c r="J92" s="57"/>
-      <c r="K92" s="57"/>
+      <c r="E92" s="61"/>
+      <c r="F92" s="61"/>
+      <c r="G92" s="61"/>
+      <c r="H92" s="61"/>
+      <c r="I92" s="61"/>
+      <c r="J92" s="61"/>
+      <c r="K92" s="61"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -8040,13 +8076,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="57"/>
+      <c r="E93" s="61"/>
+      <c r="F93" s="61"/>
+      <c r="G93" s="61"/>
+      <c r="H93" s="61"/>
+      <c r="I93" s="61"/>
+      <c r="J93" s="61"/>
+      <c r="K93" s="61"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -8059,13 +8095,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="57"/>
-      <c r="G94" s="57"/>
-      <c r="H94" s="57"/>
-      <c r="I94" s="57"/>
-      <c r="J94" s="57"/>
-      <c r="K94" s="57"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="61"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="61"/>
+      <c r="I94" s="61"/>
+      <c r="J94" s="61"/>
+      <c r="K94" s="61"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -8078,13 +8114,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="57"/>
-      <c r="F95" s="57"/>
-      <c r="G95" s="57"/>
-      <c r="H95" s="57"/>
-      <c r="I95" s="57"/>
-      <c r="J95" s="57"/>
-      <c r="K95" s="57"/>
+      <c r="E95" s="61"/>
+      <c r="F95" s="61"/>
+      <c r="G95" s="61"/>
+      <c r="H95" s="61"/>
+      <c r="I95" s="61"/>
+      <c r="J95" s="61"/>
+      <c r="K95" s="61"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -8097,13 +8133,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="57"/>
-      <c r="F96" s="57"/>
-      <c r="G96" s="57"/>
-      <c r="H96" s="57"/>
-      <c r="I96" s="57"/>
-      <c r="J96" s="57"/>
-      <c r="K96" s="57"/>
+      <c r="E96" s="61"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="61"/>
+      <c r="I96" s="61"/>
+      <c r="J96" s="61"/>
+      <c r="K96" s="61"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -8116,13 +8152,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="57"/>
-      <c r="J97" s="57"/>
-      <c r="K97" s="57"/>
+      <c r="E97" s="61"/>
+      <c r="F97" s="61"/>
+      <c r="G97" s="61"/>
+      <c r="H97" s="61"/>
+      <c r="I97" s="61"/>
+      <c r="J97" s="61"/>
+      <c r="K97" s="61"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -8135,13 +8171,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="57"/>
-      <c r="G98" s="57"/>
-      <c r="H98" s="57"/>
-      <c r="I98" s="57"/>
-      <c r="J98" s="57"/>
-      <c r="K98" s="57"/>
+      <c r="E98" s="61"/>
+      <c r="F98" s="61"/>
+      <c r="G98" s="61"/>
+      <c r="H98" s="61"/>
+      <c r="I98" s="61"/>
+      <c r="J98" s="61"/>
+      <c r="K98" s="61"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -8154,13 +8190,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="57"/>
-      <c r="F99" s="57"/>
-      <c r="G99" s="57"/>
-      <c r="H99" s="57"/>
-      <c r="I99" s="57"/>
-      <c r="J99" s="57"/>
-      <c r="K99" s="57"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="61"/>
+      <c r="J99" s="61"/>
+      <c r="K99" s="61"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -8173,13 +8209,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="57"/>
-      <c r="G100" s="57"/>
-      <c r="H100" s="57"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="57"/>
-      <c r="K100" s="57"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="61"/>
+      <c r="G100" s="61"/>
+      <c r="H100" s="61"/>
+      <c r="I100" s="61"/>
+      <c r="J100" s="61"/>
+      <c r="K100" s="61"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -8191,13 +8227,13 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="57"/>
-      <c r="F101" s="57"/>
-      <c r="G101" s="57"/>
-      <c r="H101" s="57"/>
-      <c r="I101" s="57"/>
-      <c r="J101" s="57"/>
-      <c r="K101" s="57"/>
+      <c r="E101" s="61"/>
+      <c r="F101" s="61"/>
+      <c r="G101" s="61"/>
+      <c r="H101" s="61"/>
+      <c r="I101" s="61"/>
+      <c r="J101" s="61"/>
+      <c r="K101" s="61"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -8209,13 +8245,13 @@
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="57"/>
-      <c r="I102" s="57"/>
-      <c r="J102" s="57"/>
-      <c r="K102" s="57"/>
+      <c r="E102" s="61"/>
+      <c r="F102" s="61"/>
+      <c r="G102" s="61"/>
+      <c r="H102" s="61"/>
+      <c r="I102" s="61"/>
+      <c r="J102" s="61"/>
+      <c r="K102" s="61"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -8227,13 +8263,13 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="57"/>
-      <c r="F103" s="57"/>
-      <c r="G103" s="57"/>
-      <c r="H103" s="57"/>
-      <c r="I103" s="57"/>
-      <c r="J103" s="57"/>
-      <c r="K103" s="57"/>
+      <c r="E103" s="61"/>
+      <c r="F103" s="61"/>
+      <c r="G103" s="61"/>
+      <c r="H103" s="61"/>
+      <c r="I103" s="61"/>
+      <c r="J103" s="61"/>
+      <c r="K103" s="61"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -8241,6 +8277,196 @@
     </row>
   </sheetData>
   <mergeCells count="203">
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -8254,196 +8480,6 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -8481,42 +8517,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -8853,34 +8889,34 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="90"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="89"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="87" t="s">
+      <c r="N2" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86" t="e" vm="2">
+      <c r="B3" s="85" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="19"/>
       <c r="F3" s="93" t="s">
         <v>156</v>
@@ -8894,16 +8930,16 @@
       <c r="K3" s="93"/>
       <c r="L3" s="93"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="86" t="e" vm="3">
+      <c r="N3" s="85" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="19"/>
       <c r="F4" s="93" t="s">
         <v>159</v>
@@ -8917,76 +8953,84 @@
       <c r="K4" s="93"/>
       <c r="L4" s="93"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
       <c r="L5" s="92"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82" t="s">
+      <c r="C8" s="94"/>
+      <c r="D8" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="95" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="95"/>
+      <c r="D9" s="91" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="91" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84" t="s">
+      <c r="C11" s="91"/>
+      <c r="D11" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -8997,14 +9041,6 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FFA1F5-4F74-4758-8341-CCBCA12376E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E57BD1-12D2-4945-9C1B-B3127A2AE17E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView minimized="1" xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -2647,9 +2647,90 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2662,12 +2743,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2677,87 +2752,24 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2776,23 +2788,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3292,36 +3292,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3334,17 +3334,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54" t="s">
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3363,17 +3363,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65" t="s">
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3390,17 +3390,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="65" t="s">
+      <c r="E5" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65" t="s">
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3417,17 +3417,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65" t="s">
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3444,17 +3444,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="66" t="s">
+      <c r="E7" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="65" t="s">
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3471,17 +3471,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="65" t="s">
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3498,17 +3498,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="66" t="s">
+      <c r="E9" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="65" t="s">
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3525,17 +3525,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="66" t="s">
+      <c r="E10" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="65" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3552,17 +3552,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65" t="s">
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3579,17 +3579,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65" t="s">
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3606,17 +3606,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65" t="s">
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3633,17 +3633,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65" t="s">
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3660,17 +3660,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65" t="s">
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3687,17 +3687,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65" t="s">
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="65"/>
-      <c r="K16" s="65"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3714,17 +3714,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65" t="s">
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3741,17 +3741,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65" t="s">
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3768,17 +3768,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48" t="s">
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3795,17 +3795,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="E20" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48" t="s">
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="59"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3822,17 +3822,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48" t="s">
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3849,17 +3849,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48" t="s">
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3876,17 +3876,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="48" t="s">
+      <c r="E23" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48" t="s">
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3903,17 +3903,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48" t="s">
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3930,17 +3930,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48" t="s">
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3957,17 +3957,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="69" t="s">
+      <c r="E26" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69" t="s">
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3999,17 +3999,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="74" t="s">
+      <c r="E27" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="74" t="s">
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="75"/>
-      <c r="K27" s="76"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -4032,17 +4032,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="74" t="s">
+      <c r="E28" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="74" t="s">
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="75"/>
-      <c r="K28" s="76"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="54"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -4062,17 +4062,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="74" t="s">
+      <c r="E29" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="74" t="s">
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="75"/>
-      <c r="K29" s="76"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="54"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4092,17 +4092,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="69" t="s">
+      <c r="E30" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69" t="s">
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4122,17 +4122,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="77" t="s">
+      <c r="E31" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77" t="s">
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="77"/>
-      <c r="K31" s="77"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4149,17 +4149,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="77" t="s">
+      <c r="E32" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77" t="s">
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4176,17 +4176,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="77" t="s">
+      <c r="E33" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77" t="s">
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="77"/>
-      <c r="K33" s="77"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4203,17 +4203,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="70" t="s">
+      <c r="E34" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="78" t="s">
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="79"/>
-      <c r="K34" s="80"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="51"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4230,17 +4230,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="70" t="s">
+      <c r="E35" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="81" t="s">
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="49" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4257,17 +4257,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="70" t="s">
+      <c r="E36" s="61" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="81" t="s">
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4284,17 +4284,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="78" t="s">
+      <c r="E37" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="81" t="s">
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4311,17 +4311,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="78" t="s">
+      <c r="E38" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="81" t="s">
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="49" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="79"/>
-      <c r="K38" s="80"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="51"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4338,17 +4338,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73" t="s">
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="73"/>
-      <c r="K39" s="73"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4365,17 +4365,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="73" t="s">
+      <c r="E40" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73" t="s">
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="73"/>
-      <c r="K40" s="73"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4392,17 +4392,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="E41" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73" t="s">
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="73"/>
-      <c r="K41" s="73"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4419,17 +4419,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="73" t="s">
+      <c r="E42" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73" t="s">
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="73"/>
-      <c r="K42" s="73"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4446,17 +4446,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="73" t="s">
+      <c r="E43" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73" t="s">
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="73"/>
-      <c r="K43" s="73"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4473,17 +4473,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="73" t="s">
+      <c r="E44" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="73"/>
-      <c r="G44" s="73"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="73" t="s">
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="73"/>
-      <c r="K44" s="73"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4500,17 +4500,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="73" t="s">
+      <c r="E45" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="73"/>
-      <c r="G45" s="73"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73" t="s">
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="73"/>
-      <c r="K45" s="73"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4527,17 +4527,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="73" t="s">
+      <c r="E46" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="73"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73" t="s">
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="73"/>
-      <c r="K46" s="73"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4554,17 +4554,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="E47" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73" t="s">
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="73"/>
-      <c r="K47" s="73"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4581,17 +4581,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="73" t="s">
+      <c r="E48" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73" t="s">
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4608,17 +4608,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="73" t="s">
+      <c r="E49" s="48" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="73"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73" t="s">
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="73"/>
-      <c r="K49" s="73"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4635,17 +4635,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="73" t="s">
+      <c r="E50" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="73"/>
-      <c r="G50" s="73"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="73" t="s">
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="73"/>
-      <c r="K50" s="73"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="48"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4662,17 +4662,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="73" t="s">
+      <c r="E51" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="73"/>
-      <c r="G51" s="73"/>
-      <c r="H51" s="73"/>
-      <c r="I51" s="73" t="s">
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="73"/>
-      <c r="K51" s="73"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4689,17 +4689,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="73" t="s">
+      <c r="E52" s="48" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="73"/>
-      <c r="G52" s="73"/>
-      <c r="H52" s="73"/>
-      <c r="I52" s="73" t="s">
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="73"/>
-      <c r="K52" s="73"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4716,17 +4716,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="73" t="s">
+      <c r="E53" s="48" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="73"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="73" t="s">
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="73"/>
-      <c r="K53" s="73"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4743,17 +4743,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="81" t="s">
+      <c r="E54" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="81"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81" t="s">
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="81"/>
-      <c r="K54" s="81"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4770,17 +4770,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="81" t="s">
+      <c r="E55" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81" t="s">
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="81"/>
-      <c r="K55" s="81"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4797,17 +4797,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="81" t="s">
+      <c r="E56" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81" t="s">
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="81"/>
-      <c r="K56" s="81"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4824,17 +4824,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="73" t="s">
+      <c r="E57" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="73"/>
-      <c r="G57" s="73"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73" t="s">
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="73"/>
-      <c r="K57" s="73"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4851,17 +4851,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="73" t="s">
+      <c r="E58" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="73"/>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73" t="s">
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="73"/>
-      <c r="K58" s="73"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4878,17 +4878,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="73" t="s">
+      <c r="E59" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73" t="s">
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="73"/>
-      <c r="K59" s="73"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4905,17 +4905,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="73" t="s">
+      <c r="E60" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="73"/>
-      <c r="G60" s="73"/>
-      <c r="H60" s="73"/>
-      <c r="I60" s="73" t="s">
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="73"/>
-      <c r="K60" s="73"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4932,17 +4932,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="73" t="s">
+      <c r="E61" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73" t="s">
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="73"/>
-      <c r="K61" s="73"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4959,17 +4959,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="73" t="s">
+      <c r="E62" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="73"/>
-      <c r="G62" s="73"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="73" t="s">
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="73"/>
-      <c r="K62" s="73"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4986,17 +4986,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="73" t="s">
+      <c r="E63" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="73"/>
-      <c r="G63" s="73"/>
-      <c r="H63" s="73"/>
-      <c r="I63" s="73" t="e" vm="1">
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="73"/>
-      <c r="K63" s="73"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -5013,17 +5013,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="73" t="s">
+      <c r="E64" s="48" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="73"/>
-      <c r="G64" s="73"/>
-      <c r="H64" s="73"/>
-      <c r="I64" s="73" t="s">
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="73"/>
-      <c r="K64" s="73"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -5040,17 +5040,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="73" t="s">
+      <c r="E65" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="73"/>
-      <c r="G65" s="73"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="73" t="s">
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="73"/>
-      <c r="K65" s="73"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -5067,17 +5067,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="73" t="s">
+      <c r="E66" s="48" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="73"/>
-      <c r="G66" s="73"/>
-      <c r="H66" s="73"/>
-      <c r="I66" s="73" t="s">
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="73"/>
-      <c r="K66" s="73"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5094,17 +5094,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="82" t="s">
+      <c r="E67" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="82"/>
-      <c r="G67" s="82"/>
-      <c r="H67" s="82"/>
-      <c r="I67" s="73" t="s">
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="73"/>
-      <c r="K67" s="73"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5121,17 +5121,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="81" t="s">
+      <c r="E68" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81"/>
-      <c r="H68" s="81"/>
-      <c r="I68" s="81" t="s">
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="81"/>
-      <c r="K68" s="81"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5148,17 +5148,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="81" t="s">
+      <c r="E69" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
-      <c r="H69" s="81"/>
-      <c r="I69" s="81" t="s">
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="81"/>
-      <c r="K69" s="81"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5175,17 +5175,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="81" t="s">
+      <c r="E70" s="49" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="81"/>
-      <c r="G70" s="81"/>
-      <c r="H70" s="81"/>
-      <c r="I70" s="81" t="s">
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="81"/>
-      <c r="K70" s="81"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5202,17 +5202,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="81" t="s">
+      <c r="E71" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="81"/>
-      <c r="G71" s="81"/>
-      <c r="H71" s="81"/>
-      <c r="I71" s="81" t="s">
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="81"/>
-      <c r="K71" s="81"/>
+      <c r="J71" s="49"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5229,17 +5229,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="81" t="s">
+      <c r="E72" s="49" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="81"/>
-      <c r="G72" s="81"/>
-      <c r="H72" s="81"/>
-      <c r="I72" s="81" t="s">
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="81"/>
-      <c r="K72" s="81"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5256,17 +5256,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="81" t="s">
+      <c r="E73" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81"/>
-      <c r="H73" s="81"/>
-      <c r="I73" s="81" t="s">
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="81"/>
-      <c r="K73" s="81"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5283,17 +5283,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="81" t="s">
+      <c r="E74" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="81"/>
-      <c r="G74" s="81"/>
-      <c r="H74" s="81"/>
-      <c r="I74" s="81" t="s">
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="81"/>
-      <c r="K74" s="81"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5310,17 +5310,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="81" t="s">
+      <c r="E75" s="49" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="81"/>
-      <c r="G75" s="81"/>
-      <c r="H75" s="81"/>
-      <c r="I75" s="81" t="s">
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="81"/>
-      <c r="K75" s="81"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5337,17 +5337,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="81" t="s">
+      <c r="E76" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="81"/>
-      <c r="G76" s="81"/>
-      <c r="H76" s="81"/>
-      <c r="I76" s="81" t="s">
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="81"/>
-      <c r="K76" s="81"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5364,17 +5364,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="81" t="s">
+      <c r="E77" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="81"/>
-      <c r="G77" s="81"/>
-      <c r="H77" s="81"/>
-      <c r="I77" s="81" t="s">
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="81"/>
-      <c r="K77" s="81"/>
+      <c r="J77" s="49"/>
+      <c r="K77" s="49"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5391,17 +5391,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="81" t="s">
+      <c r="E78" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="81"/>
-      <c r="G78" s="81"/>
-      <c r="H78" s="81"/>
-      <c r="I78" s="81" t="s">
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="81"/>
-      <c r="K78" s="81"/>
+      <c r="J78" s="49"/>
+      <c r="K78" s="49"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5418,17 +5418,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="81" t="s">
+      <c r="E79" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="81"/>
-      <c r="G79" s="81"/>
-      <c r="H79" s="81"/>
-      <c r="I79" s="81" t="s">
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="81"/>
-      <c r="K79" s="81"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5445,17 +5445,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="81" t="s">
+      <c r="E80" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="81"/>
-      <c r="G80" s="81"/>
-      <c r="H80" s="81"/>
-      <c r="I80" s="81" t="s">
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="81"/>
-      <c r="K80" s="81"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5472,17 +5472,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="73" t="s">
+      <c r="E81" s="48" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="73"/>
-      <c r="G81" s="73"/>
-      <c r="H81" s="73"/>
-      <c r="I81" s="73" t="s">
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="73"/>
-      <c r="K81" s="73"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5499,17 +5499,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="73" t="s">
+      <c r="E82" s="48" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="73"/>
-      <c r="G82" s="73"/>
-      <c r="H82" s="73"/>
-      <c r="I82" s="73" t="s">
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="73"/>
-      <c r="K82" s="73"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5526,17 +5526,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="73" t="s">
+      <c r="E83" s="48" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="73"/>
-      <c r="G83" s="73"/>
-      <c r="H83" s="73"/>
-      <c r="I83" s="73" t="s">
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="73"/>
-      <c r="K83" s="73"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5553,17 +5553,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="73" t="s">
+      <c r="E84" s="48" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="73"/>
-      <c r="G84" s="73"/>
-      <c r="H84" s="73"/>
-      <c r="I84" s="73" t="s">
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="73"/>
-      <c r="K84" s="73"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5580,17 +5580,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="73" t="s">
+      <c r="E85" s="48" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="73"/>
-      <c r="G85" s="73"/>
-      <c r="H85" s="73"/>
-      <c r="I85" s="73" t="s">
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="73"/>
-      <c r="K85" s="73"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5607,17 +5607,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="73" t="s">
+      <c r="E86" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="73"/>
-      <c r="G86" s="73"/>
-      <c r="H86" s="73"/>
-      <c r="I86" s="73" t="s">
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="73"/>
-      <c r="K86" s="73"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5634,17 +5634,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="73" t="s">
+      <c r="E87" s="48" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="73"/>
-      <c r="G87" s="73"/>
-      <c r="H87" s="73"/>
-      <c r="I87" s="73" t="s">
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="73"/>
-      <c r="K87" s="73"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5661,17 +5661,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="81" t="s">
+      <c r="E88" s="49" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="81"/>
-      <c r="G88" s="81"/>
-      <c r="H88" s="81"/>
-      <c r="I88" s="81" t="s">
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="81"/>
-      <c r="K88" s="81"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5688,17 +5688,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="81" t="s">
+      <c r="E89" s="49" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="81"/>
-      <c r="G89" s="81"/>
-      <c r="H89" s="81"/>
-      <c r="I89" s="81" t="s">
+      <c r="F89" s="49"/>
+      <c r="G89" s="49"/>
+      <c r="H89" s="49"/>
+      <c r="I89" s="49" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="81"/>
-      <c r="K89" s="81"/>
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5715,17 +5715,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="81" t="s">
+      <c r="E90" s="49" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="81"/>
-      <c r="G90" s="81"/>
-      <c r="H90" s="81"/>
-      <c r="I90" s="81" t="s">
+      <c r="F90" s="49"/>
+      <c r="G90" s="49"/>
+      <c r="H90" s="49"/>
+      <c r="I90" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="81"/>
-      <c r="K90" s="81"/>
+      <c r="J90" s="49"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5742,17 +5742,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="81" t="s">
+      <c r="E91" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="81"/>
-      <c r="G91" s="81"/>
-      <c r="H91" s="81"/>
-      <c r="I91" s="81" t="s">
+      <c r="F91" s="49"/>
+      <c r="G91" s="49"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="81"/>
-      <c r="K91" s="81"/>
+      <c r="J91" s="49"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5769,17 +5769,17 @@
       <c r="D92" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="E92" s="77" t="s">
+      <c r="E92" s="55" t="s">
         <v>474</v>
       </c>
-      <c r="F92" s="77"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="77"/>
-      <c r="I92" s="77" t="s">
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55" t="s">
         <v>475</v>
       </c>
-      <c r="J92" s="77"/>
-      <c r="K92" s="77"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
       <c r="L92" s="9" t="s">
         <v>164</v>
       </c>
@@ -5796,17 +5796,17 @@
       <c r="D93" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E93" s="77" t="s">
+      <c r="E93" s="55" t="s">
         <v>476</v>
       </c>
-      <c r="F93" s="77"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="77"/>
-      <c r="I93" s="77" t="s">
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55" t="s">
         <v>477</v>
       </c>
-      <c r="J93" s="77"/>
-      <c r="K93" s="77"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
       <c r="L93" s="9" t="s">
         <v>164</v>
       </c>
@@ -5823,17 +5823,17 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="77" t="s">
+      <c r="E94" s="55" t="s">
         <v>478</v>
       </c>
-      <c r="F94" s="77"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="77"/>
-      <c r="I94" s="77" t="s">
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55" t="s">
         <v>479</v>
       </c>
-      <c r="J94" s="77"/>
-      <c r="K94" s="77"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
       <c r="L94" s="9" t="s">
         <v>164</v>
       </c>
@@ -5850,17 +5850,17 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="77" t="s">
+      <c r="E95" s="55" t="s">
         <v>480</v>
       </c>
-      <c r="F95" s="77"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="77"/>
-      <c r="I95" s="77" t="s">
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55" t="s">
         <v>481</v>
       </c>
-      <c r="J95" s="77"/>
-      <c r="K95" s="77"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="55"/>
       <c r="L95" s="9" t="s">
         <v>164</v>
       </c>
@@ -5877,17 +5877,17 @@
       <c r="D96" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E96" s="77" t="s">
+      <c r="E96" s="55" t="s">
         <v>490</v>
       </c>
-      <c r="F96" s="77"/>
-      <c r="G96" s="77"/>
-      <c r="H96" s="77"/>
-      <c r="I96" s="77" t="s">
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55" t="s">
         <v>491</v>
       </c>
-      <c r="J96" s="77"/>
-      <c r="K96" s="77"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5904,17 +5904,17 @@
       <c r="D97" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="E97" s="77" t="s">
+      <c r="E97" s="55" t="s">
         <v>492</v>
       </c>
-      <c r="F97" s="77"/>
-      <c r="G97" s="77"/>
-      <c r="H97" s="77"/>
-      <c r="I97" s="77" t="s">
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55" t="s">
         <v>493</v>
       </c>
-      <c r="J97" s="77"/>
-      <c r="K97" s="77"/>
+      <c r="J97" s="55"/>
+      <c r="K97" s="55"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -5931,19 +5931,19 @@
       <c r="D98" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="E98" s="77" t="s">
+      <c r="E98" s="55" t="s">
         <v>494</v>
       </c>
-      <c r="F98" s="77"/>
-      <c r="G98" s="77"/>
-      <c r="H98" s="77"/>
-      <c r="I98" s="77" t="s">
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55" t="s">
         <v>495</v>
       </c>
-      <c r="J98" s="77"/>
-      <c r="K98" s="77"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
       <c r="L98" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M98" s="10"/>
     </row>
@@ -5958,19 +5958,19 @@
       <c r="D99" s="38" t="s">
         <v>496</v>
       </c>
-      <c r="E99" s="77" t="s">
+      <c r="E99" s="55" t="s">
         <v>497</v>
       </c>
-      <c r="F99" s="77"/>
-      <c r="G99" s="77"/>
-      <c r="H99" s="77"/>
-      <c r="I99" s="77" t="s">
+      <c r="F99" s="55"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="55"/>
+      <c r="I99" s="55" t="s">
         <v>498</v>
       </c>
-      <c r="J99" s="77"/>
-      <c r="K99" s="77"/>
+      <c r="J99" s="55"/>
+      <c r="K99" s="55"/>
       <c r="L99" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M99" s="10"/>
     </row>
@@ -5981,13 +5981,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="61"/>
-      <c r="I100" s="61"/>
-      <c r="J100" s="61"/>
-      <c r="K100" s="61"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -5995,45 +5995,140 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -6058,140 +6153,45 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -6232,36 +6232,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -6274,17 +6274,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54" t="s">
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -6303,17 +6303,17 @@
       <c r="D4" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="80" t="s">
         <v>463</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="55" t="s">
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="80" t="s">
         <v>464</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="82"/>
       <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
@@ -6330,17 +6330,17 @@
       <c r="D5" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="76" t="s">
         <v>468</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49" t="s">
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76" t="s">
         <v>469</v>
       </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -6357,17 +6357,17 @@
       <c r="D6" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="59" t="s">
         <v>466</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48" t="s">
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59" t="s">
         <v>467</v>
       </c>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -6384,17 +6384,17 @@
       <c r="D7" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="76" t="s">
         <v>470</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49" t="s">
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76" t="s">
         <v>471</v>
       </c>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -6411,17 +6411,17 @@
       <c r="D8" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="77" t="s">
         <v>483</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="50" t="s">
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="77" t="s">
         <v>484</v>
       </c>
-      <c r="J8" s="51"/>
-      <c r="K8" s="52"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="79"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -6438,17 +6438,17 @@
       <c r="D9" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="59" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48" t="s">
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59" t="s">
         <v>486</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -6465,17 +6465,17 @@
       <c r="D10" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="76" t="s">
         <v>487</v>
       </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49" t="s">
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76" t="s">
         <v>488</v>
       </c>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -6488,13 +6488,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -6507,13 +6507,13 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="60"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="75"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -6526,13 +6526,13 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -6545,13 +6545,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -6564,13 +6564,13 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -6583,13 +6583,13 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -6602,13 +6602,13 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -6621,13 +6621,13 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -6640,13 +6640,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="60"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="75"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -6659,13 +6659,13 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -6678,13 +6678,13 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -6697,13 +6697,13 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -6716,13 +6716,13 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="60"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="74"/>
+      <c r="K23" s="75"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -6735,13 +6735,13 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -6754,13 +6754,13 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -6773,13 +6773,13 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -6807,13 +6807,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="60"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="75"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -6832,13 +6832,13 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -6854,13 +6854,13 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="61"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -6876,13 +6876,13 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -6898,13 +6898,13 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -6917,13 +6917,13 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -6936,13 +6936,13 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -6955,13 +6955,13 @@
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="60"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="75"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -6974,13 +6974,13 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="61"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -6993,13 +6993,13 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -7012,13 +7012,13 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -7031,13 +7031,13 @@
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="60"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="75"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -7050,13 +7050,13 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -7069,13 +7069,13 @@
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -7088,13 +7088,13 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -7107,13 +7107,13 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="59"/>
-      <c r="K42" s="60"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="75"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -7126,13 +7126,13 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
-      <c r="J43" s="61"/>
-      <c r="K43" s="61"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -7145,13 +7145,13 @@
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="61"/>
-      <c r="J44" s="61"/>
-      <c r="K44" s="61"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -7164,13 +7164,13 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="61"/>
-      <c r="J45" s="61"/>
-      <c r="K45" s="61"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -7183,13 +7183,13 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61"/>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -7202,13 +7202,13 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="61"/>
-      <c r="J47" s="61"/>
-      <c r="K47" s="61"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -7221,13 +7221,13 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="61"/>
-      <c r="J48" s="61"/>
-      <c r="K48" s="61"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -7240,13 +7240,13 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="57"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -7259,13 +7259,13 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="59"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="60"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="59"/>
-      <c r="K50" s="60"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="73"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="75"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -7278,13 +7278,13 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="61"/>
-      <c r="J51" s="61"/>
-      <c r="K51" s="61"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -7297,13 +7297,13 @@
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -7316,13 +7316,13 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="61"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="61"/>
-      <c r="J53" s="61"/>
-      <c r="K53" s="61"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -7335,13 +7335,13 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="60"/>
-      <c r="I54" s="58"/>
-      <c r="J54" s="59"/>
-      <c r="K54" s="60"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="75"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -7354,13 +7354,13 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="61"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -7373,13 +7373,13 @@
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="61"/>
-      <c r="J56" s="61"/>
-      <c r="K56" s="61"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="57"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -7392,13 +7392,13 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="61"/>
-      <c r="J57" s="61"/>
-      <c r="K57" s="61"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="57"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -7411,13 +7411,13 @@
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="59"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="58"/>
-      <c r="J58" s="59"/>
-      <c r="K58" s="60"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="75"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -7430,13 +7430,13 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="61"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -7449,13 +7449,13 @@
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -7468,13 +7468,13 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57"/>
+      <c r="K61" s="57"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -7487,13 +7487,13 @@
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="61"/>
-      <c r="J62" s="61"/>
-      <c r="K62" s="61"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="57"/>
+      <c r="K62" s="57"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -7506,13 +7506,13 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61"/>
-      <c r="J63" s="61"/>
-      <c r="K63" s="61"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="57"/>
+      <c r="J63" s="57"/>
+      <c r="K63" s="57"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -7525,13 +7525,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="61"/>
-      <c r="I64" s="61"/>
-      <c r="J64" s="61"/>
-      <c r="K64" s="61"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -7544,13 +7544,13 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="60"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="60"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="73"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="75"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -7563,13 +7563,13 @@
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61"/>
-      <c r="I66" s="61"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -7582,13 +7582,13 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="61"/>
-      <c r="F67" s="61"/>
-      <c r="G67" s="61"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="61"/>
-      <c r="J67" s="61"/>
-      <c r="K67" s="61"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="57"/>
+      <c r="K67" s="57"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -7601,13 +7601,13 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="61"/>
-      <c r="F68" s="61"/>
-      <c r="G68" s="61"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="61"/>
-      <c r="J68" s="61"/>
-      <c r="K68" s="61"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="57"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -7620,13 +7620,13 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="60"/>
-      <c r="I69" s="58"/>
-      <c r="J69" s="59"/>
-      <c r="K69" s="60"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="73"/>
+      <c r="J69" s="74"/>
+      <c r="K69" s="75"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -7639,13 +7639,13 @@
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="61"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="61"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="61"/>
-      <c r="J70" s="61"/>
-      <c r="K70" s="61"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="57"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -7658,13 +7658,13 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="61"/>
-      <c r="G71" s="61"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
-      <c r="J71" s="61"/>
-      <c r="K71" s="61"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="57"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -7677,13 +7677,13 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
-      <c r="J72" s="61"/>
-      <c r="K72" s="61"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -7696,13 +7696,13 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="59"/>
-      <c r="G73" s="59"/>
-      <c r="H73" s="60"/>
-      <c r="I73" s="58"/>
-      <c r="J73" s="59"/>
-      <c r="K73" s="60"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="73"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="75"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -7715,13 +7715,13 @@
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="61"/>
-      <c r="K74" s="61"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
+      <c r="J74" s="57"/>
+      <c r="K74" s="57"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -7734,13 +7734,13 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-      <c r="J75" s="61"/>
-      <c r="K75" s="61"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="57"/>
+      <c r="K75" s="57"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -7753,13 +7753,13 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
-      <c r="J76" s="61"/>
-      <c r="K76" s="61"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="57"/>
+      <c r="J76" s="57"/>
+      <c r="K76" s="57"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -7772,13 +7772,13 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="61"/>
-      <c r="F77" s="61"/>
-      <c r="G77" s="61"/>
-      <c r="H77" s="61"/>
-      <c r="I77" s="61"/>
-      <c r="J77" s="61"/>
-      <c r="K77" s="61"/>
+      <c r="E77" s="57"/>
+      <c r="F77" s="57"/>
+      <c r="G77" s="57"/>
+      <c r="H77" s="57"/>
+      <c r="I77" s="57"/>
+      <c r="J77" s="57"/>
+      <c r="K77" s="57"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -7791,13 +7791,13 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="61"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="61"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="57"/>
+      <c r="J78" s="57"/>
+      <c r="K78" s="57"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -7810,13 +7810,13 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
-      <c r="J79" s="61"/>
-      <c r="K79" s="61"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="57"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -7829,13 +7829,13 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="62"/>
-      <c r="F80" s="63"/>
-      <c r="G80" s="63"/>
-      <c r="H80" s="64"/>
-      <c r="I80" s="62"/>
-      <c r="J80" s="63"/>
-      <c r="K80" s="64"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="70"/>
+      <c r="J80" s="71"/>
+      <c r="K80" s="72"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -7848,13 +7848,13 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="62"/>
-      <c r="F81" s="63"/>
-      <c r="G81" s="63"/>
-      <c r="H81" s="64"/>
-      <c r="I81" s="62"/>
-      <c r="J81" s="63"/>
-      <c r="K81" s="64"/>
+      <c r="E81" s="70"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="70"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="72"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -7867,13 +7867,13 @@
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="62"/>
-      <c r="F82" s="63"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="62"/>
-      <c r="J82" s="63"/>
-      <c r="K82" s="64"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="72"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -7886,13 +7886,13 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="62"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="64"/>
-      <c r="I83" s="62"/>
-      <c r="J83" s="63"/>
-      <c r="K83" s="64"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="70"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="72"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -7905,13 +7905,13 @@
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="64"/>
-      <c r="I84" s="62"/>
-      <c r="J84" s="63"/>
-      <c r="K84" s="64"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="71"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="71"/>
+      <c r="K84" s="72"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -7924,13 +7924,13 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="62"/>
-      <c r="F85" s="63"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="64"/>
-      <c r="I85" s="62"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="64"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="71"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="72"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -7943,13 +7943,13 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63"/>
-      <c r="H86" s="64"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="64"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="71"/>
+      <c r="H86" s="72"/>
+      <c r="I86" s="70"/>
+      <c r="J86" s="71"/>
+      <c r="K86" s="72"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -7962,13 +7962,13 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="62"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="64"/>
-      <c r="I87" s="62"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="64"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="72"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -7981,13 +7981,13 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="62"/>
-      <c r="F88" s="63"/>
-      <c r="G88" s="63"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="62"/>
-      <c r="J88" s="63"/>
-      <c r="K88" s="64"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="71"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="70"/>
+      <c r="J88" s="71"/>
+      <c r="K88" s="72"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -8000,13 +8000,13 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="62"/>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="64"/>
-      <c r="I89" s="62"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="64"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="70"/>
+      <c r="J89" s="71"/>
+      <c r="K89" s="72"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -8019,13 +8019,13 @@
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="62"/>
-      <c r="F90" s="63"/>
-      <c r="G90" s="63"/>
-      <c r="H90" s="64"/>
-      <c r="I90" s="62"/>
-      <c r="J90" s="63"/>
-      <c r="K90" s="64"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="71"/>
+      <c r="K90" s="72"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -8038,13 +8038,13 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="61"/>
-      <c r="F91" s="61"/>
-      <c r="G91" s="61"/>
-      <c r="H91" s="61"/>
-      <c r="I91" s="61"/>
-      <c r="J91" s="61"/>
-      <c r="K91" s="61"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="57"/>
+      <c r="J91" s="57"/>
+      <c r="K91" s="57"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -8057,13 +8057,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="61"/>
-      <c r="H92" s="61"/>
-      <c r="I92" s="61"/>
-      <c r="J92" s="61"/>
-      <c r="K92" s="61"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
+      <c r="K92" s="57"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -8076,13 +8076,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="61"/>
-      <c r="I93" s="61"/>
-      <c r="J93" s="61"/>
-      <c r="K93" s="61"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="57"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -8095,13 +8095,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="61"/>
-      <c r="J94" s="61"/>
-      <c r="K94" s="61"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
+      <c r="I94" s="57"/>
+      <c r="J94" s="57"/>
+      <c r="K94" s="57"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -8114,13 +8114,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="61"/>
-      <c r="I95" s="61"/>
-      <c r="J95" s="61"/>
-      <c r="K95" s="61"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="57"/>
+      <c r="J95" s="57"/>
+      <c r="K95" s="57"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -8133,13 +8133,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="61"/>
-      <c r="I96" s="61"/>
-      <c r="J96" s="61"/>
-      <c r="K96" s="61"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="57"/>
+      <c r="J96" s="57"/>
+      <c r="K96" s="57"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -8152,13 +8152,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="61"/>
-      <c r="F97" s="61"/>
-      <c r="G97" s="61"/>
-      <c r="H97" s="61"/>
-      <c r="I97" s="61"/>
-      <c r="J97" s="61"/>
-      <c r="K97" s="61"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="57"/>
+      <c r="J97" s="57"/>
+      <c r="K97" s="57"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -8171,13 +8171,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
-      <c r="I98" s="61"/>
-      <c r="J98" s="61"/>
-      <c r="K98" s="61"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="57"/>
+      <c r="J98" s="57"/>
+      <c r="K98" s="57"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -8190,13 +8190,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61"/>
-      <c r="G99" s="61"/>
-      <c r="H99" s="61"/>
-      <c r="I99" s="61"/>
-      <c r="J99" s="61"/>
-      <c r="K99" s="61"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="57"/>
+      <c r="J99" s="57"/>
+      <c r="K99" s="57"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -8209,13 +8209,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="61"/>
-      <c r="I100" s="61"/>
-      <c r="J100" s="61"/>
-      <c r="K100" s="61"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -8227,13 +8227,13 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="61"/>
-      <c r="F101" s="61"/>
-      <c r="G101" s="61"/>
-      <c r="H101" s="61"/>
-      <c r="I101" s="61"/>
-      <c r="J101" s="61"/>
-      <c r="K101" s="61"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="57"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -8245,13 +8245,13 @@
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="61"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="61"/>
-      <c r="I102" s="61"/>
-      <c r="J102" s="61"/>
-      <c r="K102" s="61"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="57"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -8263,13 +8263,13 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="61"/>
-      <c r="F103" s="61"/>
-      <c r="G103" s="61"/>
-      <c r="H103" s="61"/>
-      <c r="I103" s="61"/>
-      <c r="J103" s="61"/>
-      <c r="K103" s="61"/>
+      <c r="E103" s="57"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="57"/>
+      <c r="H103" s="57"/>
+      <c r="I103" s="57"/>
+      <c r="J103" s="57"/>
+      <c r="K103" s="57"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -8277,196 +8277,6 @@
     </row>
   </sheetData>
   <mergeCells count="203">
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -8480,6 +8290,196 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -8889,148 +8889,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="87" t="s">
+      <c r="F2" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="89"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="93"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="86" t="s">
+      <c r="N2" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="85" t="e" vm="2">
+      <c r="B3" s="89" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="85" t="e" vm="3">
+      <c r="N3" s="89" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="93" t="s">
+      <c r="F4" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="93" t="s">
+      <c r="J4" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="85"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="90" t="s">
+      <c r="F5" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="92"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="95"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="85" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94" t="s">
+      <c r="C8" s="85"/>
+      <c r="D8" s="85" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="95"/>
-      <c r="D9" s="91" t="s">
+      <c r="C9" s="86"/>
+      <c r="D9" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91" t="s">
+      <c r="C10" s="87"/>
+      <c r="D10" s="87" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="87" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -9041,6 +9033,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E57BD1-12D2-4945-9C1B-B3127A2AE17E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB1DB3F-1FFE-4E52-8877-C2A1DE399F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="546">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2214,6 +2214,159 @@
   </si>
   <si>
     <t>이 또한 관련된 부분으로 Sink_Pannel에서 Sort 부분을 수정하는 것으로 해결 가능한 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.98</t>
+  </si>
+  <si>
+    <t>No.99</t>
+  </si>
+  <si>
+    <t>No.101</t>
+  </si>
+  <si>
+    <t>No.102</t>
+  </si>
+  <si>
+    <t>No.103</t>
+  </si>
+  <si>
+    <t>No.104</t>
+  </si>
+  <si>
+    <t>No.105</t>
+  </si>
+  <si>
+    <t>No.106</t>
+  </si>
+  <si>
+    <t>No.107</t>
+  </si>
+  <si>
+    <t>No.108</t>
+  </si>
+  <si>
+    <t>No.109</t>
+  </si>
+  <si>
+    <t>No.110</t>
+  </si>
+  <si>
+    <t>No.111</t>
+  </si>
+  <si>
+    <t>No.112</t>
+  </si>
+  <si>
+    <t>No.113</t>
+  </si>
+  <si>
+    <t>No.114</t>
+  </si>
+  <si>
+    <t>No.115</t>
+  </si>
+  <si>
+    <t>No.116</t>
+  </si>
+  <si>
+    <t>No.117</t>
+  </si>
+  <si>
+    <t>No.118</t>
+  </si>
+  <si>
+    <t>No.119</t>
+  </si>
+  <si>
+    <t>No.120</t>
+  </si>
+  <si>
+    <t>No.121</t>
+  </si>
+  <si>
+    <t>No.122</t>
+  </si>
+  <si>
+    <t>No.123</t>
+  </si>
+  <si>
+    <t>No.124</t>
+  </si>
+  <si>
+    <t>No.125</t>
+  </si>
+  <si>
+    <t>No.126</t>
+  </si>
+  <si>
+    <t>No.127</t>
+  </si>
+  <si>
+    <t>No.128</t>
+  </si>
+  <si>
+    <t>No.129</t>
+  </si>
+  <si>
+    <t>No.130</t>
+  </si>
+  <si>
+    <t>No.131</t>
+  </si>
+  <si>
+    <t>No.132</t>
+  </si>
+  <si>
+    <t>No.133</t>
+  </si>
+  <si>
+    <t>No.134</t>
+  </si>
+  <si>
+    <t>No.135</t>
+  </si>
+  <si>
+    <t>No.136</t>
+  </si>
+  <si>
+    <t>No.137</t>
+  </si>
+  <si>
+    <t>No.138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">초인종을 누른 이후 철문을 열 때 클릭을 연타를 하면 화면이 어두워진 상태에서 진행이 불가능한 상태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">연속 클릭을 막거나 플로우 차트에서 1초를 센 이후에도 화면이 다시 출력하게 변경 요청
+첫 번째 클릭: isClicked가 True로 바뀌고, 화면이 까매집니다(Fade). 그리고 1초를 세기 시작합니다(Wait 1 seconds).
+두 번째 클릭 (연타): 1초를 기다리는 도중에 연타가 들어오면, 펑거스가 대기 상태와 그 밑에 있던 Load Scene 명령어를 강제로 취소
+재실행: 블록이 맨 위부터 다시 시작되지만, 이미 isClicked는 True 상태입니다. 조건문에 막혀서 아무것도 안 하고 곧바로 End로 가버립니다.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중복되는 내용을 계속해서 로그에 추가되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해결 방법으로 이전 로그 비교 로직 추가하여 중복되는 로그는 기록이 안되게 원천을 막아버리는 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서재 (구)이미지가 원래는 아래에 있었는데 무슨 영문인지 다시 위로 올라온 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 이미지가 다시 안보이게 변경
+해결방안으로 그림에 이미지 투명도(알파값)을 변동하는 것으로 해결이 가능함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2647,37 +2800,28 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2695,40 +2839,31 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2752,23 +2887,29 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2788,11 +2929,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3276,11 +3429,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB156A54-7967-4D1A-B536-B4953C786998}">
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:U141"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.75" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="5.875" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" style="16" customWidth="1"/>
     <col min="4" max="4" width="33.625" style="16" customWidth="1"/>
     <col min="5" max="7" width="15.625" style="12" customWidth="1"/>
@@ -3292,36 +3445,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3334,17 +3487,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3363,17 +3516,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3390,17 +3543,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="64" t="s">
+      <c r="E5" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64" t="s">
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3417,17 +3570,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64" t="s">
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3444,17 +3597,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="E7" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="64" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3471,17 +3624,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="65" t="s">
+      <c r="E8" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="64" t="s">
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3498,17 +3651,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="65" t="s">
+      <c r="E9" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="64" t="s">
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3525,17 +3678,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="65" t="s">
+      <c r="E10" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="64" t="s">
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3552,17 +3705,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="64" t="s">
+      <c r="E11" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3579,17 +3732,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64" t="s">
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3606,17 +3759,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="64" t="s">
+      <c r="E13" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3633,17 +3786,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="64" t="s">
+      <c r="E14" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64" t="s">
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3660,17 +3813,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3687,17 +3840,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="64" t="s">
+      <c r="E16" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64" t="s">
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3714,17 +3867,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="64" t="s">
+      <c r="E17" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3741,17 +3894,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="64" t="s">
+      <c r="E18" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64" t="s">
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3768,17 +3921,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59" t="s">
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3795,17 +3948,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59" t="s">
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3822,17 +3975,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59" t="s">
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -3849,17 +4002,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59" t="s">
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -3876,17 +4029,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59" t="s">
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -3903,17 +4056,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59" t="s">
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -3930,17 +4083,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="59" t="s">
+      <c r="E25" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59" t="s">
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -3957,17 +4110,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="60" t="s">
+      <c r="E26" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60" t="s">
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -3999,17 +4152,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="62" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="52" t="s">
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="62" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="53"/>
-      <c r="K27" s="54"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -4032,17 +4185,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="52" t="s">
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="53"/>
-      <c r="K28" s="54"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="64"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -4062,17 +4215,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="52" t="s">
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="62" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="53"/>
-      <c r="K29" s="54"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="64"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4092,17 +4245,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60" t="s">
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4122,17 +4275,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55" t="s">
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4149,17 +4302,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55" t="s">
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4176,17 +4329,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55" t="s">
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4203,17 +4356,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="61" t="s">
+      <c r="E34" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="56" t="s">
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="50"/>
-      <c r="K34" s="51"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="67"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4230,17 +4383,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="61" t="s">
+      <c r="E35" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="49" t="s">
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4257,17 +4410,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="49" t="s">
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="68"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4284,17 +4437,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="49" t="s">
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="68"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4311,17 +4464,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="E38" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="49" t="s">
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="50"/>
-      <c r="K38" s="51"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="67"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4338,17 +4491,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="48" t="s">
+      <c r="E39" s="61" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48" t="s">
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4365,17 +4518,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="61" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48" t="s">
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4392,17 +4545,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="E41" s="61" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48" t="s">
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4419,17 +4572,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="48" t="s">
+      <c r="E42" s="61" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48" t="s">
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4446,17 +4599,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="61" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48" t="s">
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4473,17 +4626,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48" t="s">
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="J44" s="61"/>
+      <c r="K44" s="61"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4500,17 +4653,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="48" t="s">
+      <c r="E45" s="61" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48" t="s">
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="61" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="61"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4527,17 +4680,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="61" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48" t="s">
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4554,17 +4707,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="48" t="s">
+      <c r="E47" s="61" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48" t="s">
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4581,17 +4734,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="48" t="s">
+      <c r="E48" s="61" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48" t="s">
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="61" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4608,17 +4761,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48" t="s">
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4635,17 +4788,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48" t="s">
+      <c r="F50" s="61"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="48"/>
-      <c r="K50" s="48"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4662,17 +4815,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="61" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48" t="s">
+      <c r="F51" s="61"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4689,17 +4842,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="48" t="s">
+      <c r="E52" s="61" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48" t="s">
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4716,17 +4869,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48" t="s">
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="J53" s="61"/>
+      <c r="K53" s="61"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4743,17 +4896,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="49" t="s">
+      <c r="E54" s="68" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="49"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="49" t="s">
+      <c r="F54" s="68"/>
+      <c r="G54" s="68"/>
+      <c r="H54" s="68"/>
+      <c r="I54" s="68" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="49"/>
-      <c r="K54" s="49"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="68"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4770,17 +4923,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="49" t="s">
+      <c r="E55" s="68" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49" t="s">
+      <c r="F55" s="68"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="68" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
+      <c r="J55" s="68"/>
+      <c r="K55" s="68"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4797,17 +4950,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="49" t="s">
+      <c r="E56" s="68" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49" t="s">
+      <c r="F56" s="68"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="68"/>
+      <c r="I56" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="49"/>
-      <c r="K56" s="49"/>
+      <c r="J56" s="68"/>
+      <c r="K56" s="68"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4824,17 +4977,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48" t="s">
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -4851,17 +5004,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="48" t="s">
+      <c r="E58" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48" t="s">
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -4878,17 +5031,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="48" t="s">
+      <c r="E59" s="61" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48" t="s">
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -4905,17 +5058,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="48" t="s">
+      <c r="E60" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48" t="s">
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -4932,17 +5085,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="48" t="s">
+      <c r="E61" s="61" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48" t="s">
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="J61" s="61"/>
+      <c r="K61" s="61"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -4959,17 +5112,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="61" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48" t="s">
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="61"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -4986,17 +5139,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="48" t="s">
+      <c r="E63" s="61" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48" t="e" vm="1">
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -5013,17 +5166,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48" t="s">
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="61"/>
+      <c r="I64" s="61" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="J64" s="61"/>
+      <c r="K64" s="61"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -5040,17 +5193,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48" t="s">
+      <c r="F65" s="61"/>
+      <c r="G65" s="61"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="61" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -5067,17 +5220,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48" t="s">
+      <c r="F66" s="61"/>
+      <c r="G66" s="61"/>
+      <c r="H66" s="61"/>
+      <c r="I66" s="61" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="J66" s="61"/>
+      <c r="K66" s="61"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5094,17 +5247,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="58" t="s">
+      <c r="E67" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="48" t="s">
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="61" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="J67" s="61"/>
+      <c r="K67" s="61"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5121,17 +5274,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="49" t="s">
+      <c r="E68" s="68" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="49" t="s">
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="49"/>
-      <c r="K68" s="49"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="68"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5148,17 +5301,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="49" t="s">
+      <c r="E69" s="68" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="49" t="s">
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="68" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="49"/>
-      <c r="K69" s="49"/>
+      <c r="J69" s="68"/>
+      <c r="K69" s="68"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5175,17 +5328,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="49" t="s">
+      <c r="E70" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49" t="s">
+      <c r="F70" s="68"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="68"/>
+      <c r="I70" s="68" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
+      <c r="J70" s="68"/>
+      <c r="K70" s="68"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5202,17 +5355,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="49" t="s">
+      <c r="E71" s="68" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="49" t="s">
+      <c r="F71" s="68"/>
+      <c r="G71" s="68"/>
+      <c r="H71" s="68"/>
+      <c r="I71" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="49"/>
-      <c r="K71" s="49"/>
+      <c r="J71" s="68"/>
+      <c r="K71" s="68"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5229,17 +5382,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="49" t="s">
+      <c r="E72" s="68" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49" t="s">
+      <c r="F72" s="68"/>
+      <c r="G72" s="68"/>
+      <c r="H72" s="68"/>
+      <c r="I72" s="68" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="49"/>
-      <c r="K72" s="49"/>
+      <c r="J72" s="68"/>
+      <c r="K72" s="68"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5256,17 +5409,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="49" t="s">
+      <c r="E73" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49" t="s">
+      <c r="F73" s="68"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="68" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="49"/>
-      <c r="K73" s="49"/>
+      <c r="J73" s="68"/>
+      <c r="K73" s="68"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5283,17 +5436,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="49" t="s">
+      <c r="E74" s="68" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49" t="s">
+      <c r="F74" s="68"/>
+      <c r="G74" s="68"/>
+      <c r="H74" s="68"/>
+      <c r="I74" s="68" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="49"/>
-      <c r="K74" s="49"/>
+      <c r="J74" s="68"/>
+      <c r="K74" s="68"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5310,17 +5463,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="49" t="s">
+      <c r="E75" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49" t="s">
+      <c r="F75" s="68"/>
+      <c r="G75" s="68"/>
+      <c r="H75" s="68"/>
+      <c r="I75" s="68" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="49"/>
-      <c r="K75" s="49"/>
+      <c r="J75" s="68"/>
+      <c r="K75" s="68"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5337,17 +5490,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="49" t="s">
+      <c r="E76" s="68" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49" t="s">
+      <c r="F76" s="68"/>
+      <c r="G76" s="68"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="68" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="49"/>
-      <c r="K76" s="49"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="68"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5364,17 +5517,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="49" t="s">
+      <c r="E77" s="68" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="49"/>
-      <c r="G77" s="49"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="49" t="s">
+      <c r="F77" s="68"/>
+      <c r="G77" s="68"/>
+      <c r="H77" s="68"/>
+      <c r="I77" s="68" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="49"/>
-      <c r="K77" s="49"/>
+      <c r="J77" s="68"/>
+      <c r="K77" s="68"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5391,17 +5544,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="49" t="s">
+      <c r="E78" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49" t="s">
+      <c r="F78" s="68"/>
+      <c r="G78" s="68"/>
+      <c r="H78" s="68"/>
+      <c r="I78" s="68" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
+      <c r="J78" s="68"/>
+      <c r="K78" s="68"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5418,17 +5571,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="49" t="s">
+      <c r="E79" s="68" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49" t="s">
+      <c r="F79" s="68"/>
+      <c r="G79" s="68"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="68" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
+      <c r="J79" s="68"/>
+      <c r="K79" s="68"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5445,17 +5598,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="49" t="s">
+      <c r="E80" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49" t="s">
+      <c r="F80" s="68"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="68" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="49"/>
-      <c r="K80" s="49"/>
+      <c r="J80" s="68"/>
+      <c r="K80" s="68"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5472,17 +5625,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="48" t="s">
+      <c r="E81" s="61" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48" t="s">
+      <c r="F81" s="61"/>
+      <c r="G81" s="61"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="61" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="J81" s="61"/>
+      <c r="K81" s="61"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5499,17 +5652,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="48" t="s">
+      <c r="E82" s="61" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48" t="s">
+      <c r="F82" s="61"/>
+      <c r="G82" s="61"/>
+      <c r="H82" s="61"/>
+      <c r="I82" s="61" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="J82" s="61"/>
+      <c r="K82" s="61"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5526,17 +5679,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="48" t="s">
+      <c r="E83" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48" t="s">
+      <c r="F83" s="61"/>
+      <c r="G83" s="61"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="J83" s="61"/>
+      <c r="K83" s="61"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5553,17 +5706,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="48" t="s">
+      <c r="E84" s="61" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48" t="s">
+      <c r="F84" s="61"/>
+      <c r="G84" s="61"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="J84" s="61"/>
+      <c r="K84" s="61"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5580,17 +5733,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="48" t="s">
+      <c r="E85" s="61" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48" t="s">
+      <c r="F85" s="61"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="61" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="J85" s="61"/>
+      <c r="K85" s="61"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5607,17 +5760,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="48" t="s">
+      <c r="E86" s="61" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48" t="s">
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
+      <c r="I86" s="61" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
+      <c r="J86" s="61"/>
+      <c r="K86" s="61"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5634,17 +5787,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="48" t="s">
+      <c r="E87" s="61" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48" t="s">
+      <c r="F87" s="61"/>
+      <c r="G87" s="61"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="61" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
+      <c r="J87" s="61"/>
+      <c r="K87" s="61"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5661,17 +5814,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="49" t="s">
+      <c r="E88" s="68" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49" t="s">
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
+      <c r="H88" s="68"/>
+      <c r="I88" s="68" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="49"/>
-      <c r="K88" s="49"/>
+      <c r="J88" s="68"/>
+      <c r="K88" s="68"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5688,17 +5841,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="49" t="s">
+      <c r="E89" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="49"/>
-      <c r="G89" s="49"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="49" t="s">
+      <c r="F89" s="68"/>
+      <c r="G89" s="68"/>
+      <c r="H89" s="68"/>
+      <c r="I89" s="68" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="49"/>
-      <c r="K89" s="49"/>
+      <c r="J89" s="68"/>
+      <c r="K89" s="68"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5715,17 +5868,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="49" t="s">
+      <c r="E90" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="49"/>
-      <c r="G90" s="49"/>
-      <c r="H90" s="49"/>
-      <c r="I90" s="49" t="s">
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
+      <c r="H90" s="68"/>
+      <c r="I90" s="68" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="49"/>
-      <c r="K90" s="49"/>
+      <c r="J90" s="68"/>
+      <c r="K90" s="68"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5742,17 +5895,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="49" t="s">
+      <c r="E91" s="68" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="49"/>
-      <c r="G91" s="49"/>
-      <c r="H91" s="49"/>
-      <c r="I91" s="49" t="s">
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
+      <c r="H91" s="68"/>
+      <c r="I91" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="49"/>
-      <c r="K91" s="49"/>
+      <c r="J91" s="68"/>
+      <c r="K91" s="68"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5769,17 +5922,17 @@
       <c r="D92" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="E92" s="55" t="s">
+      <c r="E92" s="49" t="s">
         <v>474</v>
       </c>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="55"/>
-      <c r="I92" s="55" t="s">
+      <c r="F92" s="49"/>
+      <c r="G92" s="49"/>
+      <c r="H92" s="49"/>
+      <c r="I92" s="49" t="s">
         <v>475</v>
       </c>
-      <c r="J92" s="55"/>
-      <c r="K92" s="55"/>
+      <c r="J92" s="49"/>
+      <c r="K92" s="49"/>
       <c r="L92" s="9" t="s">
         <v>164</v>
       </c>
@@ -5796,17 +5949,17 @@
       <c r="D93" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E93" s="55" t="s">
+      <c r="E93" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="F93" s="55"/>
-      <c r="G93" s="55"/>
-      <c r="H93" s="55"/>
-      <c r="I93" s="55" t="s">
+      <c r="F93" s="49"/>
+      <c r="G93" s="49"/>
+      <c r="H93" s="49"/>
+      <c r="I93" s="49" t="s">
         <v>477</v>
       </c>
-      <c r="J93" s="55"/>
-      <c r="K93" s="55"/>
+      <c r="J93" s="49"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="9" t="s">
         <v>164</v>
       </c>
@@ -5823,17 +5976,17 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="55" t="s">
+      <c r="E94" s="49" t="s">
         <v>478</v>
       </c>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55" t="s">
+      <c r="F94" s="49"/>
+      <c r="G94" s="49"/>
+      <c r="H94" s="49"/>
+      <c r="I94" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="J94" s="55"/>
-      <c r="K94" s="55"/>
+      <c r="J94" s="49"/>
+      <c r="K94" s="49"/>
       <c r="L94" s="9" t="s">
         <v>164</v>
       </c>
@@ -5850,17 +6003,17 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="55" t="s">
+      <c r="E95" s="49" t="s">
         <v>480</v>
       </c>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="55"/>
-      <c r="I95" s="55" t="s">
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="J95" s="55"/>
-      <c r="K95" s="55"/>
+      <c r="J95" s="49"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="9" t="s">
         <v>164</v>
       </c>
@@ -5877,17 +6030,17 @@
       <c r="D96" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E96" s="55" t="s">
+      <c r="E96" s="49" t="s">
         <v>490</v>
       </c>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="55"/>
-      <c r="I96" s="55" t="s">
+      <c r="F96" s="49"/>
+      <c r="G96" s="49"/>
+      <c r="H96" s="49"/>
+      <c r="I96" s="49" t="s">
         <v>491</v>
       </c>
-      <c r="J96" s="55"/>
-      <c r="K96" s="55"/>
+      <c r="J96" s="49"/>
+      <c r="K96" s="49"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -5904,19 +6057,19 @@
       <c r="D97" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="E97" s="55" t="s">
+      <c r="E97" s="49" t="s">
         <v>492</v>
       </c>
-      <c r="F97" s="55"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="55"/>
-      <c r="I97" s="55" t="s">
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
+      <c r="H97" s="49"/>
+      <c r="I97" s="49" t="s">
         <v>493</v>
       </c>
-      <c r="J97" s="55"/>
-      <c r="K97" s="55"/>
+      <c r="J97" s="49"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M97" s="10"/>
     </row>
@@ -5931,19 +6084,19 @@
       <c r="D98" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="E98" s="55" t="s">
+      <c r="E98" s="49" t="s">
         <v>494</v>
       </c>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="55"/>
-      <c r="I98" s="55" t="s">
+      <c r="F98" s="49"/>
+      <c r="G98" s="49"/>
+      <c r="H98" s="49"/>
+      <c r="I98" s="49" t="s">
         <v>495</v>
       </c>
-      <c r="J98" s="55"/>
-      <c r="K98" s="55"/>
+      <c r="J98" s="49"/>
+      <c r="K98" s="49"/>
       <c r="L98" s="9" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M98" s="10"/>
     </row>
@@ -5958,43 +6111,984 @@
       <c r="D99" s="38" t="s">
         <v>496</v>
       </c>
-      <c r="E99" s="55" t="s">
+      <c r="E99" s="49" t="s">
         <v>497</v>
       </c>
-      <c r="F99" s="55"/>
-      <c r="G99" s="55"/>
-      <c r="H99" s="55"/>
-      <c r="I99" s="55" t="s">
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
+      <c r="H99" s="49"/>
+      <c r="I99" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="J99" s="55"/>
-      <c r="K99" s="55"/>
+      <c r="J99" s="49"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="9" t="s">
-        <v>164</v>
+        <v>52</v>
       </c>
       <c r="M99" s="10"/>
     </row>
-    <row r="100" spans="1:13" s="17" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" s="17" customFormat="1" ht="158.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="57"/>
-      <c r="G100" s="57"/>
-      <c r="H100" s="57"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="57"/>
-      <c r="K100" s="57"/>
+      <c r="C100" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D100" s="38" t="s">
+        <v>489</v>
+      </c>
+      <c r="E100" s="49" t="s">
+        <v>539</v>
+      </c>
+      <c r="F100" s="49"/>
+      <c r="G100" s="49"/>
+      <c r="H100" s="49"/>
+      <c r="I100" s="49" t="s">
+        <v>540</v>
+      </c>
+      <c r="J100" s="49"/>
+      <c r="K100" s="49"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M100" s="10"/>
     </row>
+    <row r="101" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="34" t="s">
+        <v>499</v>
+      </c>
+      <c r="C101" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D101" s="38" t="s">
+        <v>541</v>
+      </c>
+      <c r="E101" s="49" t="s">
+        <v>542</v>
+      </c>
+      <c r="F101" s="49"/>
+      <c r="G101" s="49"/>
+      <c r="H101" s="49"/>
+      <c r="I101" s="49" t="s">
+        <v>543</v>
+      </c>
+      <c r="J101" s="49"/>
+      <c r="K101" s="49"/>
+      <c r="L101" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M101" s="10"/>
+    </row>
+    <row r="102" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="C102" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D102" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="E102" s="49" t="s">
+        <v>544</v>
+      </c>
+      <c r="F102" s="49"/>
+      <c r="G102" s="49"/>
+      <c r="H102" s="49"/>
+      <c r="I102" s="49" t="s">
+        <v>545</v>
+      </c>
+      <c r="J102" s="49"/>
+      <c r="K102" s="49"/>
+      <c r="L102" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M102" s="10"/>
+    </row>
+    <row r="103" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C103" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D103" s="9"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="48"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="48"/>
+      <c r="K103" s="48"/>
+      <c r="L103" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M103" s="10"/>
+    </row>
+    <row r="104" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C104" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D104" s="9"/>
+      <c r="E104" s="48"/>
+      <c r="F104" s="48"/>
+      <c r="G104" s="48"/>
+      <c r="H104" s="48"/>
+      <c r="I104" s="48"/>
+      <c r="J104" s="48"/>
+      <c r="K104" s="48"/>
+      <c r="L104" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M104" s="10"/>
+    </row>
+    <row r="105" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="C105" s="37">
+        <v>46182</v>
+      </c>
+      <c r="D105" s="9"/>
+      <c r="E105" s="48"/>
+      <c r="F105" s="48"/>
+      <c r="G105" s="48"/>
+      <c r="H105" s="48"/>
+      <c r="I105" s="48"/>
+      <c r="J105" s="48"/>
+      <c r="K105" s="48"/>
+      <c r="L105" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M105" s="10"/>
+    </row>
+    <row r="106" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B106" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="48"/>
+      <c r="F106" s="48"/>
+      <c r="G106" s="48"/>
+      <c r="H106" s="48"/>
+      <c r="I106" s="48"/>
+      <c r="J106" s="48"/>
+      <c r="K106" s="48"/>
+      <c r="L106" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M106" s="10"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B107" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="48"/>
+      <c r="F107" s="48"/>
+      <c r="G107" s="48"/>
+      <c r="H107" s="48"/>
+      <c r="I107" s="48"/>
+      <c r="J107" s="48"/>
+      <c r="K107" s="48"/>
+      <c r="L107" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M107" s="10"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B108" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="48"/>
+      <c r="F108" s="48"/>
+      <c r="G108" s="48"/>
+      <c r="H108" s="48"/>
+      <c r="I108" s="48"/>
+      <c r="J108" s="48"/>
+      <c r="K108" s="48"/>
+      <c r="L108" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M108" s="10"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B109" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="48"/>
+      <c r="F109" s="48"/>
+      <c r="G109" s="48"/>
+      <c r="H109" s="48"/>
+      <c r="I109" s="48"/>
+      <c r="J109" s="48"/>
+      <c r="K109" s="48"/>
+      <c r="L109" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M109" s="10"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B110" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="48"/>
+      <c r="F110" s="48"/>
+      <c r="G110" s="48"/>
+      <c r="H110" s="48"/>
+      <c r="I110" s="48"/>
+      <c r="J110" s="48"/>
+      <c r="K110" s="48"/>
+      <c r="L110" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M110" s="10"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B111" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="48"/>
+      <c r="F111" s="48"/>
+      <c r="G111" s="48"/>
+      <c r="H111" s="48"/>
+      <c r="I111" s="48"/>
+      <c r="J111" s="48"/>
+      <c r="K111" s="48"/>
+      <c r="L111" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M111" s="10"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B112" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="48"/>
+      <c r="F112" s="48"/>
+      <c r="G112" s="48"/>
+      <c r="H112" s="48"/>
+      <c r="I112" s="48"/>
+      <c r="J112" s="48"/>
+      <c r="K112" s="48"/>
+      <c r="L112" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M112" s="10"/>
+    </row>
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B113" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="48"/>
+      <c r="F113" s="48"/>
+      <c r="G113" s="48"/>
+      <c r="H113" s="48"/>
+      <c r="I113" s="48"/>
+      <c r="J113" s="48"/>
+      <c r="K113" s="48"/>
+      <c r="L113" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M113" s="10"/>
+    </row>
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B114" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="48"/>
+      <c r="F114" s="48"/>
+      <c r="G114" s="48"/>
+      <c r="H114" s="48"/>
+      <c r="I114" s="48"/>
+      <c r="J114" s="48"/>
+      <c r="K114" s="48"/>
+      <c r="L114" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M114" s="10"/>
+    </row>
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B115" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="48"/>
+      <c r="F115" s="48"/>
+      <c r="G115" s="48"/>
+      <c r="H115" s="48"/>
+      <c r="I115" s="48"/>
+      <c r="J115" s="48"/>
+      <c r="K115" s="48"/>
+      <c r="L115" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M115" s="10"/>
+    </row>
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B116" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="48"/>
+      <c r="F116" s="48"/>
+      <c r="G116" s="48"/>
+      <c r="H116" s="48"/>
+      <c r="I116" s="48"/>
+      <c r="J116" s="48"/>
+      <c r="K116" s="48"/>
+      <c r="L116" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M116" s="10"/>
+    </row>
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B117" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="48"/>
+      <c r="F117" s="48"/>
+      <c r="G117" s="48"/>
+      <c r="H117" s="48"/>
+      <c r="I117" s="48"/>
+      <c r="J117" s="48"/>
+      <c r="K117" s="48"/>
+      <c r="L117" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M117" s="10"/>
+    </row>
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B118" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="48"/>
+      <c r="F118" s="48"/>
+      <c r="G118" s="48"/>
+      <c r="H118" s="48"/>
+      <c r="I118" s="48"/>
+      <c r="J118" s="48"/>
+      <c r="K118" s="48"/>
+      <c r="L118" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M118" s="10"/>
+    </row>
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B119" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="48"/>
+      <c r="F119" s="48"/>
+      <c r="G119" s="48"/>
+      <c r="H119" s="48"/>
+      <c r="I119" s="48"/>
+      <c r="J119" s="48"/>
+      <c r="K119" s="48"/>
+      <c r="L119" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M119" s="10"/>
+    </row>
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B120" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
+      <c r="E120" s="48"/>
+      <c r="F120" s="48"/>
+      <c r="G120" s="48"/>
+      <c r="H120" s="48"/>
+      <c r="I120" s="48"/>
+      <c r="J120" s="48"/>
+      <c r="K120" s="48"/>
+      <c r="L120" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M120" s="10"/>
+    </row>
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B121" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="48"/>
+      <c r="F121" s="48"/>
+      <c r="G121" s="48"/>
+      <c r="H121" s="48"/>
+      <c r="I121" s="48"/>
+      <c r="J121" s="48"/>
+      <c r="K121" s="48"/>
+      <c r="L121" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M121" s="10"/>
+    </row>
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B122" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="48"/>
+      <c r="F122" s="48"/>
+      <c r="G122" s="48"/>
+      <c r="H122" s="48"/>
+      <c r="I122" s="48"/>
+      <c r="J122" s="48"/>
+      <c r="K122" s="48"/>
+      <c r="L122" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M122" s="10"/>
+    </row>
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B123" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="48"/>
+      <c r="F123" s="48"/>
+      <c r="G123" s="48"/>
+      <c r="H123" s="48"/>
+      <c r="I123" s="48"/>
+      <c r="J123" s="48"/>
+      <c r="K123" s="48"/>
+      <c r="L123" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M123" s="10"/>
+    </row>
+    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B124" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="48"/>
+      <c r="F124" s="48"/>
+      <c r="G124" s="48"/>
+      <c r="H124" s="48"/>
+      <c r="I124" s="48"/>
+      <c r="J124" s="48"/>
+      <c r="K124" s="48"/>
+      <c r="L124" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M124" s="10"/>
+    </row>
+    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B125" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="48"/>
+      <c r="F125" s="48"/>
+      <c r="G125" s="48"/>
+      <c r="H125" s="48"/>
+      <c r="I125" s="48"/>
+      <c r="J125" s="48"/>
+      <c r="K125" s="48"/>
+      <c r="L125" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M125" s="10"/>
+    </row>
+    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B126" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="48"/>
+      <c r="F126" s="48"/>
+      <c r="G126" s="48"/>
+      <c r="H126" s="48"/>
+      <c r="I126" s="48"/>
+      <c r="J126" s="48"/>
+      <c r="K126" s="48"/>
+      <c r="L126" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M126" s="10"/>
+    </row>
+    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B127" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="48"/>
+      <c r="F127" s="48"/>
+      <c r="G127" s="48"/>
+      <c r="H127" s="48"/>
+      <c r="I127" s="48"/>
+      <c r="J127" s="48"/>
+      <c r="K127" s="48"/>
+      <c r="L127" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M127" s="10"/>
+    </row>
+    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B128" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="48"/>
+      <c r="F128" s="48"/>
+      <c r="G128" s="48"/>
+      <c r="H128" s="48"/>
+      <c r="I128" s="48"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="48"/>
+      <c r="L128" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M128" s="10"/>
+    </row>
+    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B129" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="48"/>
+      <c r="F129" s="48"/>
+      <c r="G129" s="48"/>
+      <c r="H129" s="48"/>
+      <c r="I129" s="48"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="48"/>
+      <c r="L129" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M129" s="10"/>
+    </row>
+    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B130" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="48"/>
+      <c r="F130" s="48"/>
+      <c r="G130" s="48"/>
+      <c r="H130" s="48"/>
+      <c r="I130" s="48"/>
+      <c r="J130" s="48"/>
+      <c r="K130" s="48"/>
+      <c r="L130" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M130" s="10"/>
+    </row>
+    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B131" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="48"/>
+      <c r="F131" s="48"/>
+      <c r="G131" s="48"/>
+      <c r="H131" s="48"/>
+      <c r="I131" s="48"/>
+      <c r="J131" s="48"/>
+      <c r="K131" s="48"/>
+      <c r="L131" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M131" s="10"/>
+    </row>
+    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B132" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="48"/>
+      <c r="F132" s="48"/>
+      <c r="G132" s="48"/>
+      <c r="H132" s="48"/>
+      <c r="I132" s="48"/>
+      <c r="J132" s="48"/>
+      <c r="K132" s="48"/>
+      <c r="L132" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M132" s="10"/>
+    </row>
+    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B133" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="48"/>
+      <c r="F133" s="48"/>
+      <c r="G133" s="48"/>
+      <c r="H133" s="48"/>
+      <c r="I133" s="48"/>
+      <c r="J133" s="48"/>
+      <c r="K133" s="48"/>
+      <c r="L133" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M133" s="10"/>
+    </row>
+    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B134" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
+      <c r="E134" s="48"/>
+      <c r="F134" s="48"/>
+      <c r="G134" s="48"/>
+      <c r="H134" s="48"/>
+      <c r="I134" s="48"/>
+      <c r="J134" s="48"/>
+      <c r="K134" s="48"/>
+      <c r="L134" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M134" s="10"/>
+    </row>
+    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B135" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="48"/>
+      <c r="F135" s="48"/>
+      <c r="G135" s="48"/>
+      <c r="H135" s="48"/>
+      <c r="I135" s="48"/>
+      <c r="J135" s="48"/>
+      <c r="K135" s="48"/>
+      <c r="L135" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M135" s="10"/>
+    </row>
+    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B136" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
+      <c r="E136" s="48"/>
+      <c r="F136" s="48"/>
+      <c r="G136" s="48"/>
+      <c r="H136" s="48"/>
+      <c r="I136" s="48"/>
+      <c r="J136" s="48"/>
+      <c r="K136" s="48"/>
+      <c r="L136" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M136" s="10"/>
+    </row>
+    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B137" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="48"/>
+      <c r="F137" s="48"/>
+      <c r="G137" s="48"/>
+      <c r="H137" s="48"/>
+      <c r="I137" s="48"/>
+      <c r="J137" s="48"/>
+      <c r="K137" s="48"/>
+      <c r="L137" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M137" s="10"/>
+    </row>
+    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B138" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9"/>
+      <c r="E138" s="48"/>
+      <c r="F138" s="48"/>
+      <c r="G138" s="48"/>
+      <c r="H138" s="48"/>
+      <c r="I138" s="48"/>
+      <c r="J138" s="48"/>
+      <c r="K138" s="48"/>
+      <c r="L138" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M138" s="10"/>
+    </row>
+    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B139" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9"/>
+      <c r="E139" s="48"/>
+      <c r="F139" s="48"/>
+      <c r="G139" s="48"/>
+      <c r="H139" s="48"/>
+      <c r="I139" s="48"/>
+      <c r="J139" s="48"/>
+      <c r="K139" s="48"/>
+      <c r="L139" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M139" s="10"/>
+    </row>
+    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B140" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="C140" s="9"/>
+      <c r="D140" s="9"/>
+      <c r="E140" s="48"/>
+      <c r="F140" s="48"/>
+      <c r="G140" s="48"/>
+      <c r="H140" s="48"/>
+      <c r="I140" s="48"/>
+      <c r="J140" s="48"/>
+      <c r="K140" s="48"/>
+      <c r="L140" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M140" s="10"/>
+    </row>
+    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B141" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="48"/>
+      <c r="F141" s="48"/>
+      <c r="G141" s="48"/>
+      <c r="H141" s="48"/>
+      <c r="I141" s="48"/>
+      <c r="J141" s="48"/>
+      <c r="K141" s="48"/>
+      <c r="L141" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M141" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="197">
+  <mergeCells count="279">
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -6019,182 +7113,91 @@
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E104:H104"/>
+    <mergeCell ref="I104:K104"/>
+    <mergeCell ref="E105:H105"/>
+    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="I106:K106"/>
+    <mergeCell ref="E107:H107"/>
+    <mergeCell ref="I107:K107"/>
+    <mergeCell ref="E108:H108"/>
+    <mergeCell ref="I108:K108"/>
+    <mergeCell ref="E109:H109"/>
+    <mergeCell ref="I109:K109"/>
+    <mergeCell ref="E110:H110"/>
+    <mergeCell ref="I110:K110"/>
+    <mergeCell ref="E111:H111"/>
+    <mergeCell ref="I111:K111"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="I112:K112"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:K113"/>
+    <mergeCell ref="E114:H114"/>
+    <mergeCell ref="I114:K114"/>
+    <mergeCell ref="E115:H115"/>
+    <mergeCell ref="I115:K115"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="I116:K116"/>
+    <mergeCell ref="E117:H117"/>
+    <mergeCell ref="I117:K117"/>
+    <mergeCell ref="E118:H118"/>
+    <mergeCell ref="I118:K118"/>
+    <mergeCell ref="E119:H119"/>
+    <mergeCell ref="I119:K119"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="I120:K120"/>
+    <mergeCell ref="E121:H121"/>
+    <mergeCell ref="I121:K121"/>
+    <mergeCell ref="E122:H122"/>
+    <mergeCell ref="I122:K122"/>
+    <mergeCell ref="E123:H123"/>
+    <mergeCell ref="I123:K123"/>
+    <mergeCell ref="E124:H124"/>
+    <mergeCell ref="I124:K124"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:K125"/>
+    <mergeCell ref="E126:H126"/>
+    <mergeCell ref="I126:K126"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="I127:K127"/>
+    <mergeCell ref="E128:H128"/>
+    <mergeCell ref="I128:K128"/>
+    <mergeCell ref="E129:H129"/>
+    <mergeCell ref="I129:K129"/>
+    <mergeCell ref="E130:H130"/>
+    <mergeCell ref="I130:K130"/>
+    <mergeCell ref="E131:H131"/>
+    <mergeCell ref="I131:K131"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="I132:K132"/>
+    <mergeCell ref="E133:H133"/>
+    <mergeCell ref="I133:K133"/>
+    <mergeCell ref="E134:H134"/>
+    <mergeCell ref="I134:K134"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:K135"/>
+    <mergeCell ref="E141:H141"/>
+    <mergeCell ref="I141:K141"/>
+    <mergeCell ref="E136:H136"/>
+    <mergeCell ref="I136:K136"/>
+    <mergeCell ref="E137:H137"/>
+    <mergeCell ref="I137:K137"/>
+    <mergeCell ref="E138:H138"/>
+    <mergeCell ref="I138:K138"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:K139"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="I140:K140"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="L4:L100">
+  <conditionalFormatting sqref="L4:L141">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"검토 중"</formula>
     </cfRule>
@@ -6206,7 +7209,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L100" xr:uid="{67F1A76A-0B79-4B7A-9E00-9C36B025E07D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L141" xr:uid="{67F1A76A-0B79-4B7A-9E00-9C36B025E07D}">
       <formula1>"승인,거부,검토 중,-"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6232,36 +7235,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -6274,17 +7277,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -6303,17 +7306,17 @@
       <c r="D4" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="74" t="s">
         <v>463</v>
       </c>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="80" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="74" t="s">
         <v>464</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="82"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="76"/>
       <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
@@ -6330,17 +7333,17 @@
       <c r="D5" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="70" t="s">
         <v>468</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76" t="s">
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70" t="s">
         <v>469</v>
       </c>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -6357,17 +7360,17 @@
       <c r="D6" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="56" t="s">
         <v>466</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59" t="s">
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56" t="s">
         <v>467</v>
       </c>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -6384,17 +7387,17 @@
       <c r="D7" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="70" t="s">
         <v>470</v>
       </c>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76" t="s">
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70" t="s">
         <v>471</v>
       </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -6411,17 +7414,17 @@
       <c r="D8" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="71" t="s">
         <v>483</v>
       </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="77" t="s">
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="71" t="s">
         <v>484</v>
       </c>
-      <c r="J8" s="78"/>
-      <c r="K8" s="79"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="73"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -6438,17 +7441,17 @@
       <c r="D9" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="56" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59" t="s">
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56" t="s">
         <v>486</v>
       </c>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -6465,17 +7468,17 @@
       <c r="D10" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="70" t="s">
         <v>487</v>
       </c>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76" t="s">
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70" t="s">
         <v>488</v>
       </c>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -6488,13 +7491,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -6507,13 +7510,13 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="75"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="79"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -6526,13 +7529,13 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -6545,13 +7548,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -6564,13 +7567,13 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -6583,13 +7586,13 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -6602,13 +7605,13 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -6621,13 +7624,13 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -6640,13 +7643,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="75"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="79"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -6659,13 +7662,13 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -6678,13 +7681,13 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -6697,13 +7700,13 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -6716,13 +7719,13 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="75"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="79"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -6735,13 +7738,13 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -6754,13 +7757,13 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -6773,13 +7776,13 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -6807,13 +7810,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="75"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="79"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="79"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -6832,13 +7835,13 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -6854,13 +7857,13 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -6876,13 +7879,13 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -6898,13 +7901,13 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -6917,13 +7920,13 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="57"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -6936,13 +7939,13 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -6955,13 +7958,13 @@
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="75"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="79"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -6974,13 +7977,13 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -6993,13 +7996,13 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -7012,13 +8015,13 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -7031,13 +8034,13 @@
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="73"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="75"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="79"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -7050,13 +8053,13 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -7069,13 +8072,13 @@
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -7088,13 +8091,13 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -7107,13 +8110,13 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="75"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="79"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -7126,13 +8129,13 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -7145,13 +8148,13 @@
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -7164,13 +8167,13 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -7183,13 +8186,13 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -7202,13 +8205,13 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -7221,13 +8224,13 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="57"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -7240,13 +8243,13 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="57"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -7259,13 +8262,13 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="73"/>
-      <c r="J50" s="74"/>
-      <c r="K50" s="75"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="78"/>
+      <c r="H50" s="79"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="78"/>
+      <c r="K50" s="79"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -7278,13 +8281,13 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -7297,13 +8300,13 @@
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="57"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -7316,13 +8319,13 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="57"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -7335,13 +8338,13 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="74"/>
-      <c r="K54" s="75"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="79"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="78"/>
+      <c r="K54" s="79"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -7354,13 +8357,13 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="57"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -7373,13 +8376,13 @@
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="57"/>
-      <c r="K56" s="57"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -7392,13 +8395,13 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="57"/>
-      <c r="J57" s="57"/>
-      <c r="K57" s="57"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -7411,13 +8414,13 @@
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="74"/>
-      <c r="K58" s="75"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="78"/>
+      <c r="G58" s="78"/>
+      <c r="H58" s="79"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="78"/>
+      <c r="K58" s="79"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -7430,13 +8433,13 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="57"/>
-      <c r="J59" s="57"/>
-      <c r="K59" s="57"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -7449,13 +8452,13 @@
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="57"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="57"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="57"/>
-      <c r="K60" s="57"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -7468,13 +8471,13 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57"/>
-      <c r="K61" s="57"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -7487,13 +8490,13 @@
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="57"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="57"/>
-      <c r="K62" s="57"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -7506,13 +8509,13 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="57"/>
-      <c r="K63" s="57"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -7525,13 +8528,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
-      <c r="K64" s="57"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -7544,13 +8547,13 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="74"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="74"/>
-      <c r="K65" s="75"/>
+      <c r="E65" s="77"/>
+      <c r="F65" s="78"/>
+      <c r="G65" s="78"/>
+      <c r="H65" s="79"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="78"/>
+      <c r="K65" s="79"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -7563,13 +8566,13 @@
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="57"/>
-      <c r="J66" s="57"/>
-      <c r="K66" s="57"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -7582,13 +8585,13 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
-      <c r="J67" s="57"/>
-      <c r="K67" s="57"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -7601,13 +8604,13 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="57"/>
-      <c r="K68" s="57"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -7620,13 +8623,13 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="74"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="73"/>
-      <c r="J69" s="74"/>
-      <c r="K69" s="75"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="79"/>
+      <c r="I69" s="77"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="79"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -7639,13 +8642,13 @@
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
-      <c r="K70" s="57"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -7658,13 +8661,13 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
-      <c r="I71" s="57"/>
-      <c r="J71" s="57"/>
-      <c r="K71" s="57"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -7677,13 +8680,13 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
-      <c r="K72" s="57"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -7696,13 +8699,13 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="73"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="73"/>
-      <c r="J73" s="74"/>
-      <c r="K73" s="75"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="79"/>
+      <c r="I73" s="77"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="79"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -7715,13 +8718,13 @@
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
-      <c r="K74" s="57"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="48"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -7734,13 +8737,13 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
-      <c r="K75" s="57"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -7753,13 +8756,13 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="57"/>
-      <c r="K76" s="57"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -7772,13 +8775,13 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="57"/>
-      <c r="K77" s="57"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="48"/>
+      <c r="K77" s="48"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -7791,13 +8794,13 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="57"/>
-      <c r="K78" s="57"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -7810,13 +8813,13 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="57"/>
-      <c r="K79" s="57"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -7829,13 +8832,13 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="70"/>
-      <c r="J80" s="71"/>
-      <c r="K80" s="72"/>
+      <c r="E80" s="80"/>
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="82"/>
+      <c r="I80" s="80"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="82"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -7848,13 +8851,13 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="72"/>
+      <c r="E81" s="80"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="82"/>
+      <c r="I81" s="80"/>
+      <c r="J81" s="81"/>
+      <c r="K81" s="82"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -7867,13 +8870,13 @@
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="70"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="72"/>
+      <c r="E82" s="80"/>
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
+      <c r="H82" s="82"/>
+      <c r="I82" s="80"/>
+      <c r="J82" s="81"/>
+      <c r="K82" s="82"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -7886,13 +8889,13 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="72"/>
+      <c r="E83" s="80"/>
+      <c r="F83" s="81"/>
+      <c r="G83" s="81"/>
+      <c r="H83" s="82"/>
+      <c r="I83" s="80"/>
+      <c r="J83" s="81"/>
+      <c r="K83" s="82"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -7905,13 +8908,13 @@
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="70"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="70"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="72"/>
+      <c r="E84" s="80"/>
+      <c r="F84" s="81"/>
+      <c r="G84" s="81"/>
+      <c r="H84" s="82"/>
+      <c r="I84" s="80"/>
+      <c r="J84" s="81"/>
+      <c r="K84" s="82"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -7924,13 +8927,13 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="70"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="72"/>
-      <c r="I85" s="70"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="72"/>
+      <c r="E85" s="80"/>
+      <c r="F85" s="81"/>
+      <c r="G85" s="81"/>
+      <c r="H85" s="82"/>
+      <c r="I85" s="80"/>
+      <c r="J85" s="81"/>
+      <c r="K85" s="82"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -7943,13 +8946,13 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="70"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="71"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="70"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="72"/>
+      <c r="E86" s="80"/>
+      <c r="F86" s="81"/>
+      <c r="G86" s="81"/>
+      <c r="H86" s="82"/>
+      <c r="I86" s="80"/>
+      <c r="J86" s="81"/>
+      <c r="K86" s="82"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -7962,13 +8965,13 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="70"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="70"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="72"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="81"/>
+      <c r="G87" s="81"/>
+      <c r="H87" s="82"/>
+      <c r="I87" s="80"/>
+      <c r="J87" s="81"/>
+      <c r="K87" s="82"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -7981,13 +8984,13 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="70"/>
-      <c r="F88" s="71"/>
-      <c r="G88" s="71"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="70"/>
-      <c r="J88" s="71"/>
-      <c r="K88" s="72"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
+      <c r="H88" s="82"/>
+      <c r="I88" s="80"/>
+      <c r="J88" s="81"/>
+      <c r="K88" s="82"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -8000,13 +9003,13 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="70"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="71"/>
-      <c r="H89" s="72"/>
-      <c r="I89" s="70"/>
-      <c r="J89" s="71"/>
-      <c r="K89" s="72"/>
+      <c r="E89" s="80"/>
+      <c r="F89" s="81"/>
+      <c r="G89" s="81"/>
+      <c r="H89" s="82"/>
+      <c r="I89" s="80"/>
+      <c r="J89" s="81"/>
+      <c r="K89" s="82"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -8019,13 +9022,13 @@
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="71"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="70"/>
-      <c r="J90" s="71"/>
-      <c r="K90" s="72"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="81"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="80"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="82"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -8038,13 +9041,13 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="57"/>
-      <c r="G91" s="57"/>
-      <c r="H91" s="57"/>
-      <c r="I91" s="57"/>
-      <c r="J91" s="57"/>
-      <c r="K91" s="57"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -8057,13 +9060,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="57"/>
-      <c r="H92" s="57"/>
-      <c r="I92" s="57"/>
-      <c r="J92" s="57"/>
-      <c r="K92" s="57"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="48"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -8076,13 +9079,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="57"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="48"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -8095,13 +9098,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="57"/>
-      <c r="G94" s="57"/>
-      <c r="H94" s="57"/>
-      <c r="I94" s="57"/>
-      <c r="J94" s="57"/>
-      <c r="K94" s="57"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="48"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -8114,13 +9117,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="57"/>
-      <c r="F95" s="57"/>
-      <c r="G95" s="57"/>
-      <c r="H95" s="57"/>
-      <c r="I95" s="57"/>
-      <c r="J95" s="57"/>
-      <c r="K95" s="57"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="48"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -8133,13 +9136,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="57"/>
-      <c r="F96" s="57"/>
-      <c r="G96" s="57"/>
-      <c r="H96" s="57"/>
-      <c r="I96" s="57"/>
-      <c r="J96" s="57"/>
-      <c r="K96" s="57"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="48"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -8152,13 +9155,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="57"/>
-      <c r="J97" s="57"/>
-      <c r="K97" s="57"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="48"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -8171,13 +9174,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="57"/>
-      <c r="G98" s="57"/>
-      <c r="H98" s="57"/>
-      <c r="I98" s="57"/>
-      <c r="J98" s="57"/>
-      <c r="K98" s="57"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -8190,13 +9193,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="57"/>
-      <c r="F99" s="57"/>
-      <c r="G99" s="57"/>
-      <c r="H99" s="57"/>
-      <c r="I99" s="57"/>
-      <c r="J99" s="57"/>
-      <c r="K99" s="57"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -8209,13 +9212,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="57"/>
-      <c r="G100" s="57"/>
-      <c r="H100" s="57"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="57"/>
-      <c r="K100" s="57"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -8227,13 +9230,13 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="57"/>
-      <c r="F101" s="57"/>
-      <c r="G101" s="57"/>
-      <c r="H101" s="57"/>
-      <c r="I101" s="57"/>
-      <c r="J101" s="57"/>
-      <c r="K101" s="57"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
+      <c r="J101" s="48"/>
+      <c r="K101" s="48"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -8245,13 +9248,13 @@
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="57"/>
-      <c r="I102" s="57"/>
-      <c r="J102" s="57"/>
-      <c r="K102" s="57"/>
+      <c r="E102" s="48"/>
+      <c r="F102" s="48"/>
+      <c r="G102" s="48"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="48"/>
+      <c r="K102" s="48"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -8263,13 +9266,13 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="57"/>
-      <c r="F103" s="57"/>
-      <c r="G103" s="57"/>
-      <c r="H103" s="57"/>
-      <c r="I103" s="57"/>
-      <c r="J103" s="57"/>
-      <c r="K103" s="57"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="48"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="48"/>
+      <c r="K103" s="48"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -8277,6 +9280,196 @@
     </row>
   </sheetData>
   <mergeCells count="203">
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -8290,196 +9483,6 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -8889,140 +9892,148 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="91" t="s">
+      <c r="F2" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="93"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="89"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="90" t="s">
+      <c r="N2" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="89" t="e" vm="2">
+      <c r="B3" s="85" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="96" t="s">
+      <c r="F3" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="96" t="s">
+      <c r="J3" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="89" t="e" vm="3">
+      <c r="N3" s="85" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="96" t="s">
+      <c r="F4" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="96" t="s">
+      <c r="J4" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="95"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85" t="s">
+      <c r="C8" s="94"/>
+      <c r="D8" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="95" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="87" t="s">
+      <c r="C9" s="95"/>
+      <c r="D9" s="91" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="91" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87" t="s">
+      <c r="C11" s="91"/>
+      <c r="D11" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -9033,14 +10044,6 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB1DB3F-1FFE-4E52-8877-C2A1DE399F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3227478B-E38E-4AF7-B752-00CEB7A3372C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -2800,28 +2800,34 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2839,31 +2845,43 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2887,29 +2905,23 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2929,23 +2941,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3445,36 +3445,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3487,17 +3487,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52" t="s">
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3516,17 +3516,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51" t="s">
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3543,17 +3543,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51" t="s">
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3570,17 +3570,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51" t="s">
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3597,17 +3597,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="51" t="s">
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3624,17 +3624,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="51" t="s">
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3651,17 +3651,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="51" t="s">
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3678,17 +3678,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="51" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3705,17 +3705,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51" t="s">
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3732,17 +3732,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51" t="s">
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3759,17 +3759,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51" t="s">
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3786,17 +3786,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51" t="s">
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3813,17 +3813,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51" t="s">
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3840,17 +3840,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="51" t="s">
+      <c r="E16" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3867,17 +3867,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="51" t="s">
+      <c r="E17" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51" t="s">
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3894,17 +3894,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51" t="s">
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3921,17 +3921,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56" t="s">
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3948,17 +3948,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56" t="s">
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="56"/>
-      <c r="K20" s="56"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3975,17 +3975,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56" t="s">
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -4002,17 +4002,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56" t="s">
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -4029,17 +4029,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56" t="s">
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="56"/>
-      <c r="K23" s="56"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -4056,17 +4056,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56" t="s">
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -4083,17 +4083,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56" t="s">
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -4110,17 +4110,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57" t="s">
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -4152,17 +4152,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="62" t="s">
+      <c r="E27" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="62" t="s">
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="63"/>
-      <c r="K27" s="64"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -4185,17 +4185,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="62" t="s">
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="63"/>
-      <c r="K28" s="64"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="54"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -4215,17 +4215,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="62" t="s">
+      <c r="E29" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="62" t="s">
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="63"/>
-      <c r="K29" s="64"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="54"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4245,17 +4245,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57" t="s">
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4275,17 +4275,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49" t="s">
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4302,17 +4302,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="49" t="s">
+      <c r="E32" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49" t="s">
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4329,17 +4329,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="49" t="s">
+      <c r="E33" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49" t="s">
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4356,17 +4356,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="65" t="s">
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="66"/>
-      <c r="K34" s="67"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="51"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4383,17 +4383,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="68" t="s">
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="49" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4410,17 +4410,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="68" t="s">
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4437,17 +4437,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="65" t="s">
+      <c r="E37" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="68" t="s">
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4464,17 +4464,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="65" t="s">
+      <c r="E38" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="68" t="s">
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="49" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="66"/>
-      <c r="K38" s="67"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="51"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4491,17 +4491,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="61" t="s">
+      <c r="E39" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61" t="s">
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4518,17 +4518,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="61" t="s">
+      <c r="E40" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61" t="s">
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4545,17 +4545,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="61" t="s">
+      <c r="E41" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61" t="s">
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4572,17 +4572,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61" t="s">
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4599,17 +4599,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="E43" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61" t="s">
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="61"/>
-      <c r="K43" s="61"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4626,17 +4626,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="61" t="s">
+      <c r="E44" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="61" t="s">
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="61"/>
-      <c r="K44" s="61"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4653,17 +4653,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="61" t="s">
+      <c r="E45" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="61" t="s">
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="61"/>
-      <c r="K45" s="61"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4680,17 +4680,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61" t="s">
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4707,17 +4707,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="61" t="s">
+      <c r="E47" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="61" t="s">
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="61"/>
-      <c r="K47" s="61"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4734,17 +4734,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="61" t="s">
+      <c r="E48" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="61" t="s">
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="61"/>
-      <c r="K48" s="61"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4761,17 +4761,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="61" t="s">
+      <c r="E49" s="48" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61" t="s">
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4788,17 +4788,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61" t="s">
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="61"/>
-      <c r="K50" s="61"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="48"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4815,17 +4815,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="61" t="s">
+      <c r="E51" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="61" t="s">
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="61"/>
-      <c r="K51" s="61"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4842,17 +4842,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="61" t="s">
+      <c r="E52" s="48" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61" t="s">
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4869,17 +4869,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="61" t="s">
+      <c r="E53" s="48" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="61" t="s">
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="61"/>
-      <c r="K53" s="61"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4896,17 +4896,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="68" t="s">
+      <c r="E54" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="68"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="68"/>
-      <c r="I54" s="68" t="s">
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="68"/>
-      <c r="K54" s="68"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4923,17 +4923,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="68" t="s">
+      <c r="E55" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="68" t="s">
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="68"/>
-      <c r="K55" s="68"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4950,17 +4950,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="68" t="s">
+      <c r="E56" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="68"/>
-      <c r="G56" s="68"/>
-      <c r="H56" s="68"/>
-      <c r="I56" s="68" t="s">
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="68"/>
-      <c r="K56" s="68"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4977,17 +4977,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="61" t="s">
+      <c r="E57" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="61" t="s">
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="61"/>
-      <c r="K57" s="61"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -5004,17 +5004,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="61" t="s">
+      <c r="E58" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="61" t="s">
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="61"/>
-      <c r="K58" s="61"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -5031,17 +5031,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="61" t="s">
+      <c r="E59" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61" t="s">
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="61"/>
-      <c r="K59" s="61"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -5058,17 +5058,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="61" t="s">
+      <c r="E60" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61" t="s">
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -5085,17 +5085,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="61" t="s">
+      <c r="E61" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61" t="s">
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -5112,17 +5112,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="61" t="s">
+      <c r="E62" s="48" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="61" t="s">
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="61"/>
-      <c r="K62" s="61"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -5139,17 +5139,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="61" t="s">
+      <c r="E63" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61" t="e" vm="1">
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="61"/>
-      <c r="K63" s="61"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -5166,17 +5166,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="61" t="s">
+      <c r="E64" s="48" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="61"/>
-      <c r="I64" s="61" t="s">
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="61"/>
-      <c r="K64" s="61"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -5193,17 +5193,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="61" t="s">
+      <c r="E65" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="61"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="61"/>
-      <c r="I65" s="61" t="s">
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="61"/>
-      <c r="K65" s="61"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -5220,17 +5220,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="61" t="s">
+      <c r="E66" s="48" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61"/>
-      <c r="I66" s="61" t="s">
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5247,17 +5247,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="69" t="s">
+      <c r="E67" s="57" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69"/>
-      <c r="H67" s="69"/>
-      <c r="I67" s="61" t="s">
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="61"/>
-      <c r="K67" s="61"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5274,17 +5274,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="68" t="s">
+      <c r="E68" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="68"/>
-      <c r="I68" s="68" t="s">
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="68"/>
-      <c r="K68" s="68"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5301,17 +5301,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="68" t="s">
+      <c r="E69" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="68"/>
-      <c r="I69" s="68" t="s">
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="68"/>
-      <c r="K69" s="68"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5328,17 +5328,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="68" t="s">
+      <c r="E70" s="49" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="68"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="68"/>
-      <c r="I70" s="68" t="s">
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="68"/>
-      <c r="K70" s="68"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5355,17 +5355,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="68" t="s">
+      <c r="E71" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="68"/>
-      <c r="G71" s="68"/>
-      <c r="H71" s="68"/>
-      <c r="I71" s="68" t="s">
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="68"/>
-      <c r="K71" s="68"/>
+      <c r="J71" s="49"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5382,17 +5382,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="68" t="s">
+      <c r="E72" s="49" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="68"/>
-      <c r="G72" s="68"/>
-      <c r="H72" s="68"/>
-      <c r="I72" s="68" t="s">
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="68"/>
-      <c r="K72" s="68"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5409,17 +5409,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="68" t="s">
+      <c r="E73" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="68"/>
-      <c r="G73" s="68"/>
-      <c r="H73" s="68"/>
-      <c r="I73" s="68" t="s">
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="68"/>
-      <c r="K73" s="68"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5436,17 +5436,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="68" t="s">
+      <c r="E74" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="68"/>
-      <c r="G74" s="68"/>
-      <c r="H74" s="68"/>
-      <c r="I74" s="68" t="s">
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="68"/>
-      <c r="K74" s="68"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5463,17 +5463,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="68" t="s">
+      <c r="E75" s="49" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="68"/>
-      <c r="G75" s="68"/>
-      <c r="H75" s="68"/>
-      <c r="I75" s="68" t="s">
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="68"/>
-      <c r="K75" s="68"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5490,17 +5490,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="68" t="s">
+      <c r="E76" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="68"/>
-      <c r="G76" s="68"/>
-      <c r="H76" s="68"/>
-      <c r="I76" s="68" t="s">
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="68"/>
-      <c r="K76" s="68"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5517,17 +5517,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="68" t="s">
+      <c r="E77" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="68"/>
-      <c r="G77" s="68"/>
-      <c r="H77" s="68"/>
-      <c r="I77" s="68" t="s">
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="68"/>
-      <c r="K77" s="68"/>
+      <c r="J77" s="49"/>
+      <c r="K77" s="49"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5544,17 +5544,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="68" t="s">
+      <c r="E78" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="68"/>
-      <c r="G78" s="68"/>
-      <c r="H78" s="68"/>
-      <c r="I78" s="68" t="s">
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="68"/>
-      <c r="K78" s="68"/>
+      <c r="J78" s="49"/>
+      <c r="K78" s="49"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5571,17 +5571,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="68" t="s">
+      <c r="E79" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="68"/>
-      <c r="G79" s="68"/>
-      <c r="H79" s="68"/>
-      <c r="I79" s="68" t="s">
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="68"/>
-      <c r="K79" s="68"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5598,17 +5598,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="68" t="s">
+      <c r="E80" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="68"/>
-      <c r="G80" s="68"/>
-      <c r="H80" s="68"/>
-      <c r="I80" s="68" t="s">
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="68"/>
-      <c r="K80" s="68"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5625,17 +5625,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="61" t="s">
+      <c r="E81" s="48" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61" t="s">
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="61"/>
-      <c r="K81" s="61"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5652,17 +5652,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="61" t="s">
+      <c r="E82" s="48" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61" t="s">
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="61"/>
-      <c r="K82" s="61"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5679,17 +5679,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="61" t="s">
+      <c r="E83" s="48" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="61"/>
-      <c r="G83" s="61"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61" t="s">
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="61"/>
-      <c r="K83" s="61"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5706,17 +5706,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="61" t="s">
+      <c r="E84" s="48" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="61" t="s">
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="61"/>
-      <c r="K84" s="61"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5733,17 +5733,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="61" t="s">
+      <c r="E85" s="48" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="61" t="s">
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="61"/>
-      <c r="K85" s="61"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5760,17 +5760,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="61" t="s">
+      <c r="E86" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="61"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="61"/>
-      <c r="I86" s="61" t="s">
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="61"/>
-      <c r="K86" s="61"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5787,17 +5787,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="61" t="s">
+      <c r="E87" s="48" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="61"/>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61"/>
-      <c r="I87" s="61" t="s">
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="61"/>
-      <c r="K87" s="61"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5814,17 +5814,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="68" t="s">
+      <c r="E88" s="49" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="68"/>
-      <c r="I88" s="68" t="s">
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="68"/>
-      <c r="K88" s="68"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5841,17 +5841,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="68" t="s">
+      <c r="E89" s="49" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="68"/>
-      <c r="G89" s="68"/>
-      <c r="H89" s="68"/>
-      <c r="I89" s="68" t="s">
+      <c r="F89" s="49"/>
+      <c r="G89" s="49"/>
+      <c r="H89" s="49"/>
+      <c r="I89" s="49" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="68"/>
-      <c r="K89" s="68"/>
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5868,17 +5868,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="68" t="s">
+      <c r="E90" s="49" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
-      <c r="H90" s="68"/>
-      <c r="I90" s="68" t="s">
+      <c r="F90" s="49"/>
+      <c r="G90" s="49"/>
+      <c r="H90" s="49"/>
+      <c r="I90" s="49" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="68"/>
-      <c r="K90" s="68"/>
+      <c r="J90" s="49"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5895,17 +5895,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="68" t="s">
+      <c r="E91" s="49" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
-      <c r="H91" s="68"/>
-      <c r="I91" s="68" t="s">
+      <c r="F91" s="49"/>
+      <c r="G91" s="49"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="68"/>
-      <c r="K91" s="68"/>
+      <c r="J91" s="49"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5922,17 +5922,17 @@
       <c r="D92" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="E92" s="49" t="s">
+      <c r="E92" s="55" t="s">
         <v>474</v>
       </c>
-      <c r="F92" s="49"/>
-      <c r="G92" s="49"/>
-      <c r="H92" s="49"/>
-      <c r="I92" s="49" t="s">
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55" t="s">
         <v>475</v>
       </c>
-      <c r="J92" s="49"/>
-      <c r="K92" s="49"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
       <c r="L92" s="9" t="s">
         <v>164</v>
       </c>
@@ -5949,17 +5949,17 @@
       <c r="D93" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E93" s="49" t="s">
+      <c r="E93" s="55" t="s">
         <v>476</v>
       </c>
-      <c r="F93" s="49"/>
-      <c r="G93" s="49"/>
-      <c r="H93" s="49"/>
-      <c r="I93" s="49" t="s">
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55" t="s">
         <v>477</v>
       </c>
-      <c r="J93" s="49"/>
-      <c r="K93" s="49"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
       <c r="L93" s="9" t="s">
         <v>164</v>
       </c>
@@ -5976,17 +5976,17 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="49" t="s">
+      <c r="E94" s="55" t="s">
         <v>478</v>
       </c>
-      <c r="F94" s="49"/>
-      <c r="G94" s="49"/>
-      <c r="H94" s="49"/>
-      <c r="I94" s="49" t="s">
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55" t="s">
         <v>479</v>
       </c>
-      <c r="J94" s="49"/>
-      <c r="K94" s="49"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
       <c r="L94" s="9" t="s">
         <v>164</v>
       </c>
@@ -6003,17 +6003,17 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="49" t="s">
+      <c r="E95" s="55" t="s">
         <v>480</v>
       </c>
-      <c r="F95" s="49"/>
-      <c r="G95" s="49"/>
-      <c r="H95" s="49"/>
-      <c r="I95" s="49" t="s">
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55" t="s">
         <v>481</v>
       </c>
-      <c r="J95" s="49"/>
-      <c r="K95" s="49"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="55"/>
       <c r="L95" s="9" t="s">
         <v>164</v>
       </c>
@@ -6030,17 +6030,17 @@
       <c r="D96" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E96" s="49" t="s">
+      <c r="E96" s="55" t="s">
         <v>490</v>
       </c>
-      <c r="F96" s="49"/>
-      <c r="G96" s="49"/>
-      <c r="H96" s="49"/>
-      <c r="I96" s="49" t="s">
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55" t="s">
         <v>491</v>
       </c>
-      <c r="J96" s="49"/>
-      <c r="K96" s="49"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -6057,17 +6057,17 @@
       <c r="D97" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="E97" s="49" t="s">
+      <c r="E97" s="55" t="s">
         <v>492</v>
       </c>
-      <c r="F97" s="49"/>
-      <c r="G97" s="49"/>
-      <c r="H97" s="49"/>
-      <c r="I97" s="49" t="s">
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55" t="s">
         <v>493</v>
       </c>
-      <c r="J97" s="49"/>
-      <c r="K97" s="49"/>
+      <c r="J97" s="55"/>
+      <c r="K97" s="55"/>
       <c r="L97" s="9" t="s">
         <v>164</v>
       </c>
@@ -6084,19 +6084,19 @@
       <c r="D98" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="E98" s="49" t="s">
+      <c r="E98" s="55" t="s">
         <v>494</v>
       </c>
-      <c r="F98" s="49"/>
-      <c r="G98" s="49"/>
-      <c r="H98" s="49"/>
-      <c r="I98" s="49" t="s">
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55" t="s">
         <v>495</v>
       </c>
-      <c r="J98" s="49"/>
-      <c r="K98" s="49"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
       <c r="L98" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M98" s="10"/>
     </row>
@@ -6111,19 +6111,19 @@
       <c r="D99" s="38" t="s">
         <v>496</v>
       </c>
-      <c r="E99" s="49" t="s">
+      <c r="E99" s="55" t="s">
         <v>497</v>
       </c>
-      <c r="F99" s="49"/>
-      <c r="G99" s="49"/>
-      <c r="H99" s="49"/>
-      <c r="I99" s="49" t="s">
+      <c r="F99" s="55"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="55"/>
+      <c r="I99" s="55" t="s">
         <v>498</v>
       </c>
-      <c r="J99" s="49"/>
-      <c r="K99" s="49"/>
+      <c r="J99" s="55"/>
+      <c r="K99" s="55"/>
       <c r="L99" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M99" s="10"/>
     </row>
@@ -6138,19 +6138,19 @@
       <c r="D100" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E100" s="49" t="s">
+      <c r="E100" s="55" t="s">
         <v>539</v>
       </c>
-      <c r="F100" s="49"/>
-      <c r="G100" s="49"/>
-      <c r="H100" s="49"/>
-      <c r="I100" s="49" t="s">
+      <c r="F100" s="55"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="55"/>
+      <c r="I100" s="55" t="s">
         <v>540</v>
       </c>
-      <c r="J100" s="49"/>
-      <c r="K100" s="49"/>
+      <c r="J100" s="55"/>
+      <c r="K100" s="55"/>
       <c r="L100" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M100" s="10"/>
     </row>
@@ -6164,19 +6164,19 @@
       <c r="D101" s="38" t="s">
         <v>541</v>
       </c>
-      <c r="E101" s="49" t="s">
+      <c r="E101" s="55" t="s">
         <v>542</v>
       </c>
-      <c r="F101" s="49"/>
-      <c r="G101" s="49"/>
-      <c r="H101" s="49"/>
-      <c r="I101" s="49" t="s">
+      <c r="F101" s="55"/>
+      <c r="G101" s="55"/>
+      <c r="H101" s="55"/>
+      <c r="I101" s="55" t="s">
         <v>543</v>
       </c>
-      <c r="J101" s="49"/>
-      <c r="K101" s="49"/>
+      <c r="J101" s="55"/>
+      <c r="K101" s="55"/>
       <c r="L101" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M101" s="10"/>
     </row>
@@ -6190,19 +6190,19 @@
       <c r="D102" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="E102" s="49" t="s">
+      <c r="E102" s="55" t="s">
         <v>544</v>
       </c>
-      <c r="F102" s="49"/>
-      <c r="G102" s="49"/>
-      <c r="H102" s="49"/>
-      <c r="I102" s="49" t="s">
+      <c r="F102" s="55"/>
+      <c r="G102" s="55"/>
+      <c r="H102" s="55"/>
+      <c r="I102" s="55" t="s">
         <v>545</v>
       </c>
-      <c r="J102" s="49"/>
-      <c r="K102" s="49"/>
+      <c r="J102" s="55"/>
+      <c r="K102" s="55"/>
       <c r="L102" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M102" s="10"/>
     </row>
@@ -6214,13 +6214,13 @@
         <v>46182</v>
       </c>
       <c r="D103" s="9"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="48"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="48"/>
-      <c r="K103" s="48"/>
+      <c r="E103" s="69"/>
+      <c r="F103" s="69"/>
+      <c r="G103" s="69"/>
+      <c r="H103" s="69"/>
+      <c r="I103" s="69"/>
+      <c r="J103" s="69"/>
+      <c r="K103" s="69"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -6234,13 +6234,13 @@
         <v>46182</v>
       </c>
       <c r="D104" s="9"/>
-      <c r="E104" s="48"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="48"/>
-      <c r="H104" s="48"/>
-      <c r="I104" s="48"/>
-      <c r="J104" s="48"/>
-      <c r="K104" s="48"/>
+      <c r="E104" s="69"/>
+      <c r="F104" s="69"/>
+      <c r="G104" s="69"/>
+      <c r="H104" s="69"/>
+      <c r="I104" s="69"/>
+      <c r="J104" s="69"/>
+      <c r="K104" s="69"/>
       <c r="L104" s="9" t="s">
         <v>52</v>
       </c>
@@ -6254,13 +6254,13 @@
         <v>46182</v>
       </c>
       <c r="D105" s="9"/>
-      <c r="E105" s="48"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="48"/>
-      <c r="H105" s="48"/>
-      <c r="I105" s="48"/>
-      <c r="J105" s="48"/>
-      <c r="K105" s="48"/>
+      <c r="E105" s="69"/>
+      <c r="F105" s="69"/>
+      <c r="G105" s="69"/>
+      <c r="H105" s="69"/>
+      <c r="I105" s="69"/>
+      <c r="J105" s="69"/>
+      <c r="K105" s="69"/>
       <c r="L105" s="9" t="s">
         <v>52</v>
       </c>
@@ -6272,13 +6272,13 @@
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="48"/>
-      <c r="H106" s="48"/>
-      <c r="I106" s="48"/>
-      <c r="J106" s="48"/>
-      <c r="K106" s="48"/>
+      <c r="E106" s="69"/>
+      <c r="F106" s="69"/>
+      <c r="G106" s="69"/>
+      <c r="H106" s="69"/>
+      <c r="I106" s="69"/>
+      <c r="J106" s="69"/>
+      <c r="K106" s="69"/>
       <c r="L106" s="9" t="s">
         <v>52</v>
       </c>
@@ -6290,13 +6290,13 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
-      <c r="E107" s="48"/>
-      <c r="F107" s="48"/>
-      <c r="G107" s="48"/>
-      <c r="H107" s="48"/>
-      <c r="I107" s="48"/>
-      <c r="J107" s="48"/>
-      <c r="K107" s="48"/>
+      <c r="E107" s="69"/>
+      <c r="F107" s="69"/>
+      <c r="G107" s="69"/>
+      <c r="H107" s="69"/>
+      <c r="I107" s="69"/>
+      <c r="J107" s="69"/>
+      <c r="K107" s="69"/>
       <c r="L107" s="9" t="s">
         <v>52</v>
       </c>
@@ -6308,13 +6308,13 @@
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
-      <c r="E108" s="48"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="48"/>
-      <c r="H108" s="48"/>
-      <c r="I108" s="48"/>
-      <c r="J108" s="48"/>
-      <c r="K108" s="48"/>
+      <c r="E108" s="69"/>
+      <c r="F108" s="69"/>
+      <c r="G108" s="69"/>
+      <c r="H108" s="69"/>
+      <c r="I108" s="69"/>
+      <c r="J108" s="69"/>
+      <c r="K108" s="69"/>
       <c r="L108" s="9" t="s">
         <v>52</v>
       </c>
@@ -6326,13 +6326,13 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
-      <c r="E109" s="48"/>
-      <c r="F109" s="48"/>
-      <c r="G109" s="48"/>
-      <c r="H109" s="48"/>
-      <c r="I109" s="48"/>
-      <c r="J109" s="48"/>
-      <c r="K109" s="48"/>
+      <c r="E109" s="69"/>
+      <c r="F109" s="69"/>
+      <c r="G109" s="69"/>
+      <c r="H109" s="69"/>
+      <c r="I109" s="69"/>
+      <c r="J109" s="69"/>
+      <c r="K109" s="69"/>
       <c r="L109" s="9" t="s">
         <v>52</v>
       </c>
@@ -6344,13 +6344,13 @@
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
-      <c r="E110" s="48"/>
-      <c r="F110" s="48"/>
-      <c r="G110" s="48"/>
-      <c r="H110" s="48"/>
-      <c r="I110" s="48"/>
-      <c r="J110" s="48"/>
-      <c r="K110" s="48"/>
+      <c r="E110" s="69"/>
+      <c r="F110" s="69"/>
+      <c r="G110" s="69"/>
+      <c r="H110" s="69"/>
+      <c r="I110" s="69"/>
+      <c r="J110" s="69"/>
+      <c r="K110" s="69"/>
       <c r="L110" s="9" t="s">
         <v>52</v>
       </c>
@@ -6362,13 +6362,13 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
-      <c r="E111" s="48"/>
-      <c r="F111" s="48"/>
-      <c r="G111" s="48"/>
-      <c r="H111" s="48"/>
-      <c r="I111" s="48"/>
-      <c r="J111" s="48"/>
-      <c r="K111" s="48"/>
+      <c r="E111" s="69"/>
+      <c r="F111" s="69"/>
+      <c r="G111" s="69"/>
+      <c r="H111" s="69"/>
+      <c r="I111" s="69"/>
+      <c r="J111" s="69"/>
+      <c r="K111" s="69"/>
       <c r="L111" s="9" t="s">
         <v>52</v>
       </c>
@@ -6380,13 +6380,13 @@
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
-      <c r="E112" s="48"/>
-      <c r="F112" s="48"/>
-      <c r="G112" s="48"/>
-      <c r="H112" s="48"/>
-      <c r="I112" s="48"/>
-      <c r="J112" s="48"/>
-      <c r="K112" s="48"/>
+      <c r="E112" s="69"/>
+      <c r="F112" s="69"/>
+      <c r="G112" s="69"/>
+      <c r="H112" s="69"/>
+      <c r="I112" s="69"/>
+      <c r="J112" s="69"/>
+      <c r="K112" s="69"/>
       <c r="L112" s="9" t="s">
         <v>52</v>
       </c>
@@ -6398,13 +6398,13 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
-      <c r="E113" s="48"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="48"/>
-      <c r="H113" s="48"/>
-      <c r="I113" s="48"/>
-      <c r="J113" s="48"/>
-      <c r="K113" s="48"/>
+      <c r="E113" s="69"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="69"/>
+      <c r="H113" s="69"/>
+      <c r="I113" s="69"/>
+      <c r="J113" s="69"/>
+      <c r="K113" s="69"/>
       <c r="L113" s="9" t="s">
         <v>52</v>
       </c>
@@ -6416,13 +6416,13 @@
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
-      <c r="E114" s="48"/>
-      <c r="F114" s="48"/>
-      <c r="G114" s="48"/>
-      <c r="H114" s="48"/>
-      <c r="I114" s="48"/>
-      <c r="J114" s="48"/>
-      <c r="K114" s="48"/>
+      <c r="E114" s="69"/>
+      <c r="F114" s="69"/>
+      <c r="G114" s="69"/>
+      <c r="H114" s="69"/>
+      <c r="I114" s="69"/>
+      <c r="J114" s="69"/>
+      <c r="K114" s="69"/>
       <c r="L114" s="9" t="s">
         <v>52</v>
       </c>
@@ -6434,13 +6434,13 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
-      <c r="E115" s="48"/>
-      <c r="F115" s="48"/>
-      <c r="G115" s="48"/>
-      <c r="H115" s="48"/>
-      <c r="I115" s="48"/>
-      <c r="J115" s="48"/>
-      <c r="K115" s="48"/>
+      <c r="E115" s="69"/>
+      <c r="F115" s="69"/>
+      <c r="G115" s="69"/>
+      <c r="H115" s="69"/>
+      <c r="I115" s="69"/>
+      <c r="J115" s="69"/>
+      <c r="K115" s="69"/>
       <c r="L115" s="9" t="s">
         <v>52</v>
       </c>
@@ -6452,13 +6452,13 @@
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
-      <c r="E116" s="48"/>
-      <c r="F116" s="48"/>
-      <c r="G116" s="48"/>
-      <c r="H116" s="48"/>
-      <c r="I116" s="48"/>
-      <c r="J116" s="48"/>
-      <c r="K116" s="48"/>
+      <c r="E116" s="69"/>
+      <c r="F116" s="69"/>
+      <c r="G116" s="69"/>
+      <c r="H116" s="69"/>
+      <c r="I116" s="69"/>
+      <c r="J116" s="69"/>
+      <c r="K116" s="69"/>
       <c r="L116" s="9" t="s">
         <v>52</v>
       </c>
@@ -6470,13 +6470,13 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
-      <c r="E117" s="48"/>
-      <c r="F117" s="48"/>
-      <c r="G117" s="48"/>
-      <c r="H117" s="48"/>
-      <c r="I117" s="48"/>
-      <c r="J117" s="48"/>
-      <c r="K117" s="48"/>
+      <c r="E117" s="69"/>
+      <c r="F117" s="69"/>
+      <c r="G117" s="69"/>
+      <c r="H117" s="69"/>
+      <c r="I117" s="69"/>
+      <c r="J117" s="69"/>
+      <c r="K117" s="69"/>
       <c r="L117" s="9" t="s">
         <v>52</v>
       </c>
@@ -6488,13 +6488,13 @@
       </c>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
-      <c r="E118" s="48"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="48"/>
-      <c r="H118" s="48"/>
-      <c r="I118" s="48"/>
-      <c r="J118" s="48"/>
-      <c r="K118" s="48"/>
+      <c r="E118" s="69"/>
+      <c r="F118" s="69"/>
+      <c r="G118" s="69"/>
+      <c r="H118" s="69"/>
+      <c r="I118" s="69"/>
+      <c r="J118" s="69"/>
+      <c r="K118" s="69"/>
       <c r="L118" s="9" t="s">
         <v>52</v>
       </c>
@@ -6506,13 +6506,13 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
-      <c r="E119" s="48"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="48"/>
-      <c r="H119" s="48"/>
-      <c r="I119" s="48"/>
-      <c r="J119" s="48"/>
-      <c r="K119" s="48"/>
+      <c r="E119" s="69"/>
+      <c r="F119" s="69"/>
+      <c r="G119" s="69"/>
+      <c r="H119" s="69"/>
+      <c r="I119" s="69"/>
+      <c r="J119" s="69"/>
+      <c r="K119" s="69"/>
       <c r="L119" s="9" t="s">
         <v>52</v>
       </c>
@@ -6524,13 +6524,13 @@
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="48"/>
-      <c r="I120" s="48"/>
-      <c r="J120" s="48"/>
-      <c r="K120" s="48"/>
+      <c r="E120" s="69"/>
+      <c r="F120" s="69"/>
+      <c r="G120" s="69"/>
+      <c r="H120" s="69"/>
+      <c r="I120" s="69"/>
+      <c r="J120" s="69"/>
+      <c r="K120" s="69"/>
       <c r="L120" s="9" t="s">
         <v>52</v>
       </c>
@@ -6542,13 +6542,13 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
-      <c r="E121" s="48"/>
-      <c r="F121" s="48"/>
-      <c r="G121" s="48"/>
-      <c r="H121" s="48"/>
-      <c r="I121" s="48"/>
-      <c r="J121" s="48"/>
-      <c r="K121" s="48"/>
+      <c r="E121" s="69"/>
+      <c r="F121" s="69"/>
+      <c r="G121" s="69"/>
+      <c r="H121" s="69"/>
+      <c r="I121" s="69"/>
+      <c r="J121" s="69"/>
+      <c r="K121" s="69"/>
       <c r="L121" s="9" t="s">
         <v>52</v>
       </c>
@@ -6560,13 +6560,13 @@
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
-      <c r="E122" s="48"/>
-      <c r="F122" s="48"/>
-      <c r="G122" s="48"/>
-      <c r="H122" s="48"/>
-      <c r="I122" s="48"/>
-      <c r="J122" s="48"/>
-      <c r="K122" s="48"/>
+      <c r="E122" s="69"/>
+      <c r="F122" s="69"/>
+      <c r="G122" s="69"/>
+      <c r="H122" s="69"/>
+      <c r="I122" s="69"/>
+      <c r="J122" s="69"/>
+      <c r="K122" s="69"/>
       <c r="L122" s="9" t="s">
         <v>52</v>
       </c>
@@ -6578,13 +6578,13 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="48"/>
-      <c r="H123" s="48"/>
-      <c r="I123" s="48"/>
-      <c r="J123" s="48"/>
-      <c r="K123" s="48"/>
+      <c r="E123" s="69"/>
+      <c r="F123" s="69"/>
+      <c r="G123" s="69"/>
+      <c r="H123" s="69"/>
+      <c r="I123" s="69"/>
+      <c r="J123" s="69"/>
+      <c r="K123" s="69"/>
       <c r="L123" s="9" t="s">
         <v>52</v>
       </c>
@@ -6596,13 +6596,13 @@
       </c>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="48"/>
-      <c r="G124" s="48"/>
-      <c r="H124" s="48"/>
-      <c r="I124" s="48"/>
-      <c r="J124" s="48"/>
-      <c r="K124" s="48"/>
+      <c r="E124" s="69"/>
+      <c r="F124" s="69"/>
+      <c r="G124" s="69"/>
+      <c r="H124" s="69"/>
+      <c r="I124" s="69"/>
+      <c r="J124" s="69"/>
+      <c r="K124" s="69"/>
       <c r="L124" s="9" t="s">
         <v>52</v>
       </c>
@@ -6614,13 +6614,13 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="48"/>
-      <c r="H125" s="48"/>
-      <c r="I125" s="48"/>
-      <c r="J125" s="48"/>
-      <c r="K125" s="48"/>
+      <c r="E125" s="69"/>
+      <c r="F125" s="69"/>
+      <c r="G125" s="69"/>
+      <c r="H125" s="69"/>
+      <c r="I125" s="69"/>
+      <c r="J125" s="69"/>
+      <c r="K125" s="69"/>
       <c r="L125" s="9" t="s">
         <v>52</v>
       </c>
@@ -6632,13 +6632,13 @@
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
-      <c r="E126" s="48"/>
-      <c r="F126" s="48"/>
-      <c r="G126" s="48"/>
-      <c r="H126" s="48"/>
-      <c r="I126" s="48"/>
-      <c r="J126" s="48"/>
-      <c r="K126" s="48"/>
+      <c r="E126" s="69"/>
+      <c r="F126" s="69"/>
+      <c r="G126" s="69"/>
+      <c r="H126" s="69"/>
+      <c r="I126" s="69"/>
+      <c r="J126" s="69"/>
+      <c r="K126" s="69"/>
       <c r="L126" s="9" t="s">
         <v>52</v>
       </c>
@@ -6650,13 +6650,13 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
-      <c r="E127" s="48"/>
-      <c r="F127" s="48"/>
-      <c r="G127" s="48"/>
-      <c r="H127" s="48"/>
-      <c r="I127" s="48"/>
-      <c r="J127" s="48"/>
-      <c r="K127" s="48"/>
+      <c r="E127" s="69"/>
+      <c r="F127" s="69"/>
+      <c r="G127" s="69"/>
+      <c r="H127" s="69"/>
+      <c r="I127" s="69"/>
+      <c r="J127" s="69"/>
+      <c r="K127" s="69"/>
       <c r="L127" s="9" t="s">
         <v>52</v>
       </c>
@@ -6668,13 +6668,13 @@
       </c>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
-      <c r="E128" s="48"/>
-      <c r="F128" s="48"/>
-      <c r="G128" s="48"/>
-      <c r="H128" s="48"/>
-      <c r="I128" s="48"/>
-      <c r="J128" s="48"/>
-      <c r="K128" s="48"/>
+      <c r="E128" s="69"/>
+      <c r="F128" s="69"/>
+      <c r="G128" s="69"/>
+      <c r="H128" s="69"/>
+      <c r="I128" s="69"/>
+      <c r="J128" s="69"/>
+      <c r="K128" s="69"/>
       <c r="L128" s="9" t="s">
         <v>52</v>
       </c>
@@ -6686,13 +6686,13 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
-      <c r="E129" s="48"/>
-      <c r="F129" s="48"/>
-      <c r="G129" s="48"/>
-      <c r="H129" s="48"/>
-      <c r="I129" s="48"/>
-      <c r="J129" s="48"/>
-      <c r="K129" s="48"/>
+      <c r="E129" s="69"/>
+      <c r="F129" s="69"/>
+      <c r="G129" s="69"/>
+      <c r="H129" s="69"/>
+      <c r="I129" s="69"/>
+      <c r="J129" s="69"/>
+      <c r="K129" s="69"/>
       <c r="L129" s="9" t="s">
         <v>52</v>
       </c>
@@ -6704,13 +6704,13 @@
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
-      <c r="E130" s="48"/>
-      <c r="F130" s="48"/>
-      <c r="G130" s="48"/>
-      <c r="H130" s="48"/>
-      <c r="I130" s="48"/>
-      <c r="J130" s="48"/>
-      <c r="K130" s="48"/>
+      <c r="E130" s="69"/>
+      <c r="F130" s="69"/>
+      <c r="G130" s="69"/>
+      <c r="H130" s="69"/>
+      <c r="I130" s="69"/>
+      <c r="J130" s="69"/>
+      <c r="K130" s="69"/>
       <c r="L130" s="9" t="s">
         <v>52</v>
       </c>
@@ -6722,13 +6722,13 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
-      <c r="E131" s="48"/>
-      <c r="F131" s="48"/>
-      <c r="G131" s="48"/>
-      <c r="H131" s="48"/>
-      <c r="I131" s="48"/>
-      <c r="J131" s="48"/>
-      <c r="K131" s="48"/>
+      <c r="E131" s="69"/>
+      <c r="F131" s="69"/>
+      <c r="G131" s="69"/>
+      <c r="H131" s="69"/>
+      <c r="I131" s="69"/>
+      <c r="J131" s="69"/>
+      <c r="K131" s="69"/>
       <c r="L131" s="9" t="s">
         <v>52</v>
       </c>
@@ -6740,13 +6740,13 @@
       </c>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
-      <c r="E132" s="48"/>
-      <c r="F132" s="48"/>
-      <c r="G132" s="48"/>
-      <c r="H132" s="48"/>
-      <c r="I132" s="48"/>
-      <c r="J132" s="48"/>
-      <c r="K132" s="48"/>
+      <c r="E132" s="69"/>
+      <c r="F132" s="69"/>
+      <c r="G132" s="69"/>
+      <c r="H132" s="69"/>
+      <c r="I132" s="69"/>
+      <c r="J132" s="69"/>
+      <c r="K132" s="69"/>
       <c r="L132" s="9" t="s">
         <v>52</v>
       </c>
@@ -6758,13 +6758,13 @@
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
-      <c r="E133" s="48"/>
-      <c r="F133" s="48"/>
-      <c r="G133" s="48"/>
-      <c r="H133" s="48"/>
-      <c r="I133" s="48"/>
-      <c r="J133" s="48"/>
-      <c r="K133" s="48"/>
+      <c r="E133" s="69"/>
+      <c r="F133" s="69"/>
+      <c r="G133" s="69"/>
+      <c r="H133" s="69"/>
+      <c r="I133" s="69"/>
+      <c r="J133" s="69"/>
+      <c r="K133" s="69"/>
       <c r="L133" s="9" t="s">
         <v>52</v>
       </c>
@@ -6776,13 +6776,13 @@
       </c>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
-      <c r="E134" s="48"/>
-      <c r="F134" s="48"/>
-      <c r="G134" s="48"/>
-      <c r="H134" s="48"/>
-      <c r="I134" s="48"/>
-      <c r="J134" s="48"/>
-      <c r="K134" s="48"/>
+      <c r="E134" s="69"/>
+      <c r="F134" s="69"/>
+      <c r="G134" s="69"/>
+      <c r="H134" s="69"/>
+      <c r="I134" s="69"/>
+      <c r="J134" s="69"/>
+      <c r="K134" s="69"/>
       <c r="L134" s="9" t="s">
         <v>52</v>
       </c>
@@ -6794,13 +6794,13 @@
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
-      <c r="E135" s="48"/>
-      <c r="F135" s="48"/>
-      <c r="G135" s="48"/>
-      <c r="H135" s="48"/>
-      <c r="I135" s="48"/>
-      <c r="J135" s="48"/>
-      <c r="K135" s="48"/>
+      <c r="E135" s="69"/>
+      <c r="F135" s="69"/>
+      <c r="G135" s="69"/>
+      <c r="H135" s="69"/>
+      <c r="I135" s="69"/>
+      <c r="J135" s="69"/>
+      <c r="K135" s="69"/>
       <c r="L135" s="9" t="s">
         <v>52</v>
       </c>
@@ -6812,13 +6812,13 @@
       </c>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
-      <c r="E136" s="48"/>
-      <c r="F136" s="48"/>
-      <c r="G136" s="48"/>
-      <c r="H136" s="48"/>
-      <c r="I136" s="48"/>
-      <c r="J136" s="48"/>
-      <c r="K136" s="48"/>
+      <c r="E136" s="69"/>
+      <c r="F136" s="69"/>
+      <c r="G136" s="69"/>
+      <c r="H136" s="69"/>
+      <c r="I136" s="69"/>
+      <c r="J136" s="69"/>
+      <c r="K136" s="69"/>
       <c r="L136" s="9" t="s">
         <v>52</v>
       </c>
@@ -6830,13 +6830,13 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
-      <c r="E137" s="48"/>
-      <c r="F137" s="48"/>
-      <c r="G137" s="48"/>
-      <c r="H137" s="48"/>
-      <c r="I137" s="48"/>
-      <c r="J137" s="48"/>
-      <c r="K137" s="48"/>
+      <c r="E137" s="69"/>
+      <c r="F137" s="69"/>
+      <c r="G137" s="69"/>
+      <c r="H137" s="69"/>
+      <c r="I137" s="69"/>
+      <c r="J137" s="69"/>
+      <c r="K137" s="69"/>
       <c r="L137" s="9" t="s">
         <v>52</v>
       </c>
@@ -6848,13 +6848,13 @@
       </c>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
-      <c r="E138" s="48"/>
-      <c r="F138" s="48"/>
-      <c r="G138" s="48"/>
-      <c r="H138" s="48"/>
-      <c r="I138" s="48"/>
-      <c r="J138" s="48"/>
-      <c r="K138" s="48"/>
+      <c r="E138" s="69"/>
+      <c r="F138" s="69"/>
+      <c r="G138" s="69"/>
+      <c r="H138" s="69"/>
+      <c r="I138" s="69"/>
+      <c r="J138" s="69"/>
+      <c r="K138" s="69"/>
       <c r="L138" s="9" t="s">
         <v>52</v>
       </c>
@@ -6866,13 +6866,13 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
-      <c r="E139" s="48"/>
-      <c r="F139" s="48"/>
-      <c r="G139" s="48"/>
-      <c r="H139" s="48"/>
-      <c r="I139" s="48"/>
-      <c r="J139" s="48"/>
-      <c r="K139" s="48"/>
+      <c r="E139" s="69"/>
+      <c r="F139" s="69"/>
+      <c r="G139" s="69"/>
+      <c r="H139" s="69"/>
+      <c r="I139" s="69"/>
+      <c r="J139" s="69"/>
+      <c r="K139" s="69"/>
       <c r="L139" s="9" t="s">
         <v>52</v>
       </c>
@@ -6884,13 +6884,13 @@
       </c>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
-      <c r="E140" s="48"/>
-      <c r="F140" s="48"/>
-      <c r="G140" s="48"/>
-      <c r="H140" s="48"/>
-      <c r="I140" s="48"/>
-      <c r="J140" s="48"/>
-      <c r="K140" s="48"/>
+      <c r="E140" s="69"/>
+      <c r="F140" s="69"/>
+      <c r="G140" s="69"/>
+      <c r="H140" s="69"/>
+      <c r="I140" s="69"/>
+      <c r="J140" s="69"/>
+      <c r="K140" s="69"/>
       <c r="L140" s="9" t="s">
         <v>52</v>
       </c>
@@ -6902,13 +6902,13 @@
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
-      <c r="E141" s="48"/>
-      <c r="F141" s="48"/>
-      <c r="G141" s="48"/>
-      <c r="H141" s="48"/>
-      <c r="I141" s="48"/>
-      <c r="J141" s="48"/>
-      <c r="K141" s="48"/>
+      <c r="E141" s="69"/>
+      <c r="F141" s="69"/>
+      <c r="G141" s="69"/>
+      <c r="H141" s="69"/>
+      <c r="I141" s="69"/>
+      <c r="J141" s="69"/>
+      <c r="K141" s="69"/>
       <c r="L141" s="9" t="s">
         <v>52</v>
       </c>
@@ -6916,45 +6916,222 @@
     </row>
   </sheetData>
   <mergeCells count="279">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E141:H141"/>
+    <mergeCell ref="I141:K141"/>
+    <mergeCell ref="E136:H136"/>
+    <mergeCell ref="I136:K136"/>
+    <mergeCell ref="E137:H137"/>
+    <mergeCell ref="I137:K137"/>
+    <mergeCell ref="E138:H138"/>
+    <mergeCell ref="I138:K138"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:K139"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="I140:K140"/>
+    <mergeCell ref="E131:H131"/>
+    <mergeCell ref="I131:K131"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="I132:K132"/>
+    <mergeCell ref="E133:H133"/>
+    <mergeCell ref="I133:K133"/>
+    <mergeCell ref="E134:H134"/>
+    <mergeCell ref="I134:K134"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:K135"/>
+    <mergeCell ref="E126:H126"/>
+    <mergeCell ref="I126:K126"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="I127:K127"/>
+    <mergeCell ref="E128:H128"/>
+    <mergeCell ref="I128:K128"/>
+    <mergeCell ref="E129:H129"/>
+    <mergeCell ref="I129:K129"/>
+    <mergeCell ref="E130:H130"/>
+    <mergeCell ref="I130:K130"/>
+    <mergeCell ref="E121:H121"/>
+    <mergeCell ref="I121:K121"/>
+    <mergeCell ref="E122:H122"/>
+    <mergeCell ref="I122:K122"/>
+    <mergeCell ref="E123:H123"/>
+    <mergeCell ref="I123:K123"/>
+    <mergeCell ref="E124:H124"/>
+    <mergeCell ref="I124:K124"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:K125"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="I116:K116"/>
+    <mergeCell ref="E117:H117"/>
+    <mergeCell ref="I117:K117"/>
+    <mergeCell ref="E118:H118"/>
+    <mergeCell ref="I118:K118"/>
+    <mergeCell ref="E119:H119"/>
+    <mergeCell ref="I119:K119"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="I120:K120"/>
+    <mergeCell ref="E111:H111"/>
+    <mergeCell ref="I111:K111"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="I112:K112"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:K113"/>
+    <mergeCell ref="E114:H114"/>
+    <mergeCell ref="I114:K114"/>
+    <mergeCell ref="E115:H115"/>
+    <mergeCell ref="I115:K115"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="I106:K106"/>
+    <mergeCell ref="E107:H107"/>
+    <mergeCell ref="I107:K107"/>
+    <mergeCell ref="E108:H108"/>
+    <mergeCell ref="I108:K108"/>
+    <mergeCell ref="E109:H109"/>
+    <mergeCell ref="I109:K109"/>
+    <mergeCell ref="E110:H110"/>
+    <mergeCell ref="I110:K110"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E104:H104"/>
+    <mergeCell ref="I104:K104"/>
+    <mergeCell ref="E105:H105"/>
+    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -6979,222 +7156,45 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E104:H104"/>
-    <mergeCell ref="I104:K104"/>
-    <mergeCell ref="E105:H105"/>
-    <mergeCell ref="I105:K105"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="I106:K106"/>
-    <mergeCell ref="E107:H107"/>
-    <mergeCell ref="I107:K107"/>
-    <mergeCell ref="E108:H108"/>
-    <mergeCell ref="I108:K108"/>
-    <mergeCell ref="E109:H109"/>
-    <mergeCell ref="I109:K109"/>
-    <mergeCell ref="E110:H110"/>
-    <mergeCell ref="I110:K110"/>
-    <mergeCell ref="E111:H111"/>
-    <mergeCell ref="I111:K111"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="I112:K112"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:K113"/>
-    <mergeCell ref="E114:H114"/>
-    <mergeCell ref="I114:K114"/>
-    <mergeCell ref="E115:H115"/>
-    <mergeCell ref="I115:K115"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="I116:K116"/>
-    <mergeCell ref="E117:H117"/>
-    <mergeCell ref="I117:K117"/>
-    <mergeCell ref="E118:H118"/>
-    <mergeCell ref="I118:K118"/>
-    <mergeCell ref="E119:H119"/>
-    <mergeCell ref="I119:K119"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="I120:K120"/>
-    <mergeCell ref="E121:H121"/>
-    <mergeCell ref="I121:K121"/>
-    <mergeCell ref="E122:H122"/>
-    <mergeCell ref="I122:K122"/>
-    <mergeCell ref="E123:H123"/>
-    <mergeCell ref="I123:K123"/>
-    <mergeCell ref="E124:H124"/>
-    <mergeCell ref="I124:K124"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:K125"/>
-    <mergeCell ref="E126:H126"/>
-    <mergeCell ref="I126:K126"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="I127:K127"/>
-    <mergeCell ref="E128:H128"/>
-    <mergeCell ref="I128:K128"/>
-    <mergeCell ref="E129:H129"/>
-    <mergeCell ref="I129:K129"/>
-    <mergeCell ref="E130:H130"/>
-    <mergeCell ref="I130:K130"/>
-    <mergeCell ref="E131:H131"/>
-    <mergeCell ref="I131:K131"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="I132:K132"/>
-    <mergeCell ref="E133:H133"/>
-    <mergeCell ref="I133:K133"/>
-    <mergeCell ref="E134:H134"/>
-    <mergeCell ref="I134:K134"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:K135"/>
-    <mergeCell ref="E141:H141"/>
-    <mergeCell ref="I141:K141"/>
-    <mergeCell ref="E136:H136"/>
-    <mergeCell ref="I136:K136"/>
-    <mergeCell ref="E137:H137"/>
-    <mergeCell ref="I137:K137"/>
-    <mergeCell ref="E138:H138"/>
-    <mergeCell ref="I138:K138"/>
-    <mergeCell ref="E139:H139"/>
-    <mergeCell ref="I139:K139"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="I140:K140"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L141">
@@ -7235,36 +7235,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -7277,17 +7277,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52" t="s">
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -7306,17 +7306,17 @@
       <c r="D4" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E4" s="74" t="s">
+      <c r="E4" s="80" t="s">
         <v>463</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="74" t="s">
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="80" t="s">
         <v>464</v>
       </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="76"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="82"/>
       <c r="L4" s="9" t="s">
         <v>52</v>
       </c>
@@ -7333,17 +7333,17 @@
       <c r="D5" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E5" s="70" t="s">
+      <c r="E5" s="76" t="s">
         <v>468</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70" t="s">
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76" t="s">
         <v>469</v>
       </c>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -7360,17 +7360,17 @@
       <c r="D6" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="58" t="s">
         <v>466</v>
       </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56" t="s">
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58" t="s">
         <v>467</v>
       </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -7387,17 +7387,17 @@
       <c r="D7" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="76" t="s">
         <v>470</v>
       </c>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70" t="s">
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76" t="s">
         <v>471</v>
       </c>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -7414,17 +7414,17 @@
       <c r="D8" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="77" t="s">
         <v>483</v>
       </c>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="71" t="s">
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="77" t="s">
         <v>484</v>
       </c>
-      <c r="J8" s="72"/>
-      <c r="K8" s="73"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="79"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -7441,17 +7441,17 @@
       <c r="D9" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E9" s="56" t="s">
+      <c r="E9" s="58" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56" t="s">
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58" t="s">
         <v>486</v>
       </c>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -7468,17 +7468,17 @@
       <c r="D10" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="76" t="s">
         <v>487</v>
       </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70" t="s">
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76" t="s">
         <v>488</v>
       </c>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -7491,13 +7491,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -7510,13 +7510,13 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="79"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="75"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -7529,13 +7529,13 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -7548,13 +7548,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -7567,13 +7567,13 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -7586,13 +7586,13 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -7605,13 +7605,13 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -7624,13 +7624,13 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -7643,13 +7643,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="79"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="75"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -7662,13 +7662,13 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -7681,13 +7681,13 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -7700,13 +7700,13 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -7719,13 +7719,13 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="79"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="74"/>
+      <c r="K23" s="75"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -7738,13 +7738,13 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -7757,13 +7757,13 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -7776,13 +7776,13 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -7810,13 +7810,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="79"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="75"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -7835,13 +7835,13 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -7857,13 +7857,13 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -7879,13 +7879,13 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -7901,13 +7901,13 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -7920,13 +7920,13 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -7939,13 +7939,13 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -7958,13 +7958,13 @@
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="79"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="75"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -7977,13 +7977,13 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -7996,13 +7996,13 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -8015,13 +8015,13 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -8034,13 +8034,13 @@
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="79"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="75"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -8053,13 +8053,13 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -8072,13 +8072,13 @@
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -8091,13 +8091,13 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -8110,13 +8110,13 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="79"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="75"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -8129,13 +8129,13 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="69"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -8148,13 +8148,13 @@
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -8167,13 +8167,13 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -8186,13 +8186,13 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -8205,13 +8205,13 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -8224,13 +8224,13 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -8243,13 +8243,13 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -8262,13 +8262,13 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="78"/>
-      <c r="H50" s="79"/>
-      <c r="I50" s="77"/>
-      <c r="J50" s="78"/>
-      <c r="K50" s="79"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="73"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="75"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -8281,13 +8281,13 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="69"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="69"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -8300,13 +8300,13 @@
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="E52" s="69"/>
+      <c r="F52" s="69"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="69"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="69"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -8319,13 +8319,13 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -8338,13 +8338,13 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="77"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="78"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="77"/>
-      <c r="J54" s="78"/>
-      <c r="K54" s="79"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="75"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -8357,13 +8357,13 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -8376,13 +8376,13 @@
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="69"/>
+      <c r="G56" s="69"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="69"/>
+      <c r="J56" s="69"/>
+      <c r="K56" s="69"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -8395,13 +8395,13 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -8414,13 +8414,13 @@
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="77"/>
-      <c r="F58" s="78"/>
-      <c r="G58" s="78"/>
-      <c r="H58" s="79"/>
-      <c r="I58" s="77"/>
-      <c r="J58" s="78"/>
-      <c r="K58" s="79"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="75"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="75"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -8433,13 +8433,13 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="69"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="69"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -8452,13 +8452,13 @@
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="E60" s="69"/>
+      <c r="F60" s="69"/>
+      <c r="G60" s="69"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="69"/>
+      <c r="J60" s="69"/>
+      <c r="K60" s="69"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -8471,13 +8471,13 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="69"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -8490,13 +8490,13 @@
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="E62" s="69"/>
+      <c r="F62" s="69"/>
+      <c r="G62" s="69"/>
+      <c r="H62" s="69"/>
+      <c r="I62" s="69"/>
+      <c r="J62" s="69"/>
+      <c r="K62" s="69"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -8509,13 +8509,13 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="69"/>
+      <c r="K63" s="69"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -8528,13 +8528,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="69"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="69"/>
+      <c r="K64" s="69"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -8547,13 +8547,13 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="77"/>
-      <c r="F65" s="78"/>
-      <c r="G65" s="78"/>
-      <c r="H65" s="79"/>
-      <c r="I65" s="77"/>
-      <c r="J65" s="78"/>
-      <c r="K65" s="79"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="73"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="75"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -8566,13 +8566,13 @@
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="69"/>
+      <c r="J66" s="69"/>
+      <c r="K66" s="69"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -8585,13 +8585,13 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="48"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="E67" s="69"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="69"/>
+      <c r="J67" s="69"/>
+      <c r="K67" s="69"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -8604,13 +8604,13 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="69"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="69"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -8623,13 +8623,13 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="79"/>
-      <c r="I69" s="77"/>
-      <c r="J69" s="78"/>
-      <c r="K69" s="79"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="73"/>
+      <c r="J69" s="74"/>
+      <c r="K69" s="75"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -8642,13 +8642,13 @@
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
+      <c r="E70" s="69"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="69"/>
+      <c r="J70" s="69"/>
+      <c r="K70" s="69"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -8661,13 +8661,13 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
+      <c r="E71" s="69"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="69"/>
+      <c r="J71" s="69"/>
+      <c r="K71" s="69"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -8680,13 +8680,13 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="48"/>
+      <c r="E72" s="69"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="69"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="69"/>
+      <c r="J72" s="69"/>
+      <c r="K72" s="69"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -8699,13 +8699,13 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="77"/>
-      <c r="F73" s="78"/>
-      <c r="G73" s="78"/>
-      <c r="H73" s="79"/>
-      <c r="I73" s="77"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="79"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="73"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="75"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -8718,13 +8718,13 @@
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="69"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="69"/>
+      <c r="J74" s="69"/>
+      <c r="K74" s="69"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -8737,13 +8737,13 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
+      <c r="E75" s="69"/>
+      <c r="F75" s="69"/>
+      <c r="G75" s="69"/>
+      <c r="H75" s="69"/>
+      <c r="I75" s="69"/>
+      <c r="J75" s="69"/>
+      <c r="K75" s="69"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -8756,13 +8756,13 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-      <c r="K76" s="48"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="69"/>
+      <c r="I76" s="69"/>
+      <c r="J76" s="69"/>
+      <c r="K76" s="69"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -8775,13 +8775,13 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="69"/>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="69"/>
+      <c r="J77" s="69"/>
+      <c r="K77" s="69"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -8794,13 +8794,13 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
+      <c r="E78" s="69"/>
+      <c r="F78" s="69"/>
+      <c r="G78" s="69"/>
+      <c r="H78" s="69"/>
+      <c r="I78" s="69"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="69"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -8813,13 +8813,13 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
+      <c r="E79" s="69"/>
+      <c r="F79" s="69"/>
+      <c r="G79" s="69"/>
+      <c r="H79" s="69"/>
+      <c r="I79" s="69"/>
+      <c r="J79" s="69"/>
+      <c r="K79" s="69"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -8832,13 +8832,13 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="81"/>
-      <c r="G80" s="81"/>
-      <c r="H80" s="82"/>
-      <c r="I80" s="80"/>
-      <c r="J80" s="81"/>
-      <c r="K80" s="82"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="72"/>
+      <c r="I80" s="70"/>
+      <c r="J80" s="71"/>
+      <c r="K80" s="72"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -8851,13 +8851,13 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="80"/>
-      <c r="F81" s="81"/>
-      <c r="G81" s="81"/>
-      <c r="H81" s="82"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="81"/>
-      <c r="K81" s="82"/>
+      <c r="E81" s="70"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="70"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="72"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -8870,13 +8870,13 @@
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="81"/>
-      <c r="G82" s="81"/>
-      <c r="H82" s="82"/>
-      <c r="I82" s="80"/>
-      <c r="J82" s="81"/>
-      <c r="K82" s="82"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="71"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="70"/>
+      <c r="J82" s="71"/>
+      <c r="K82" s="72"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -8889,13 +8889,13 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="80"/>
-      <c r="F83" s="81"/>
-      <c r="G83" s="81"/>
-      <c r="H83" s="82"/>
-      <c r="I83" s="80"/>
-      <c r="J83" s="81"/>
-      <c r="K83" s="82"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="70"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="72"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -8908,13 +8908,13 @@
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="80"/>
-      <c r="F84" s="81"/>
-      <c r="G84" s="81"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="80"/>
-      <c r="J84" s="81"/>
-      <c r="K84" s="82"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="71"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="71"/>
+      <c r="K84" s="72"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -8927,13 +8927,13 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="80"/>
-      <c r="F85" s="81"/>
-      <c r="G85" s="81"/>
-      <c r="H85" s="82"/>
-      <c r="I85" s="80"/>
-      <c r="J85" s="81"/>
-      <c r="K85" s="82"/>
+      <c r="E85" s="70"/>
+      <c r="F85" s="71"/>
+      <c r="G85" s="71"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="71"/>
+      <c r="K85" s="72"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -8946,13 +8946,13 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="80"/>
-      <c r="F86" s="81"/>
-      <c r="G86" s="81"/>
-      <c r="H86" s="82"/>
-      <c r="I86" s="80"/>
-      <c r="J86" s="81"/>
-      <c r="K86" s="82"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="71"/>
+      <c r="H86" s="72"/>
+      <c r="I86" s="70"/>
+      <c r="J86" s="71"/>
+      <c r="K86" s="72"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -8965,13 +8965,13 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="80"/>
-      <c r="F87" s="81"/>
-      <c r="G87" s="81"/>
-      <c r="H87" s="82"/>
-      <c r="I87" s="80"/>
-      <c r="J87" s="81"/>
-      <c r="K87" s="82"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="72"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -8984,13 +8984,13 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="80"/>
-      <c r="F88" s="81"/>
-      <c r="G88" s="81"/>
-      <c r="H88" s="82"/>
-      <c r="I88" s="80"/>
-      <c r="J88" s="81"/>
-      <c r="K88" s="82"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="71"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="70"/>
+      <c r="J88" s="71"/>
+      <c r="K88" s="72"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -9003,13 +9003,13 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="80"/>
-      <c r="F89" s="81"/>
-      <c r="G89" s="81"/>
-      <c r="H89" s="82"/>
-      <c r="I89" s="80"/>
-      <c r="J89" s="81"/>
-      <c r="K89" s="82"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="70"/>
+      <c r="J89" s="71"/>
+      <c r="K89" s="72"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -9022,13 +9022,13 @@
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="81"/>
-      <c r="G90" s="81"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="80"/>
-      <c r="J90" s="81"/>
-      <c r="K90" s="82"/>
+      <c r="E90" s="70"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="71"/>
+      <c r="K90" s="72"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -9041,13 +9041,13 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
+      <c r="E91" s="69"/>
+      <c r="F91" s="69"/>
+      <c r="G91" s="69"/>
+      <c r="H91" s="69"/>
+      <c r="I91" s="69"/>
+      <c r="J91" s="69"/>
+      <c r="K91" s="69"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -9060,13 +9060,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="48"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="69"/>
+      <c r="H92" s="69"/>
+      <c r="I92" s="69"/>
+      <c r="J92" s="69"/>
+      <c r="K92" s="69"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -9079,13 +9079,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="48"/>
-      <c r="J93" s="48"/>
-      <c r="K93" s="48"/>
+      <c r="E93" s="69"/>
+      <c r="F93" s="69"/>
+      <c r="G93" s="69"/>
+      <c r="H93" s="69"/>
+      <c r="I93" s="69"/>
+      <c r="J93" s="69"/>
+      <c r="K93" s="69"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -9098,13 +9098,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="48"/>
+      <c r="E94" s="69"/>
+      <c r="F94" s="69"/>
+      <c r="G94" s="69"/>
+      <c r="H94" s="69"/>
+      <c r="I94" s="69"/>
+      <c r="J94" s="69"/>
+      <c r="K94" s="69"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -9117,13 +9117,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="48"/>
+      <c r="E95" s="69"/>
+      <c r="F95" s="69"/>
+      <c r="G95" s="69"/>
+      <c r="H95" s="69"/>
+      <c r="I95" s="69"/>
+      <c r="J95" s="69"/>
+      <c r="K95" s="69"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -9136,13 +9136,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="48"/>
-      <c r="K96" s="48"/>
+      <c r="E96" s="69"/>
+      <c r="F96" s="69"/>
+      <c r="G96" s="69"/>
+      <c r="H96" s="69"/>
+      <c r="I96" s="69"/>
+      <c r="J96" s="69"/>
+      <c r="K96" s="69"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -9155,13 +9155,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="48"/>
+      <c r="E97" s="69"/>
+      <c r="F97" s="69"/>
+      <c r="G97" s="69"/>
+      <c r="H97" s="69"/>
+      <c r="I97" s="69"/>
+      <c r="J97" s="69"/>
+      <c r="K97" s="69"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -9174,13 +9174,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
+      <c r="E98" s="69"/>
+      <c r="F98" s="69"/>
+      <c r="G98" s="69"/>
+      <c r="H98" s="69"/>
+      <c r="I98" s="69"/>
+      <c r="J98" s="69"/>
+      <c r="K98" s="69"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -9193,13 +9193,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
+      <c r="E99" s="69"/>
+      <c r="F99" s="69"/>
+      <c r="G99" s="69"/>
+      <c r="H99" s="69"/>
+      <c r="I99" s="69"/>
+      <c r="J99" s="69"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -9212,13 +9212,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
+      <c r="E100" s="69"/>
+      <c r="F100" s="69"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="69"/>
+      <c r="I100" s="69"/>
+      <c r="J100" s="69"/>
+      <c r="K100" s="69"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -9230,13 +9230,13 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
-      <c r="J101" s="48"/>
-      <c r="K101" s="48"/>
+      <c r="E101" s="69"/>
+      <c r="F101" s="69"/>
+      <c r="G101" s="69"/>
+      <c r="H101" s="69"/>
+      <c r="I101" s="69"/>
+      <c r="J101" s="69"/>
+      <c r="K101" s="69"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -9248,13 +9248,13 @@
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="48"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="48"/>
-      <c r="H102" s="48"/>
-      <c r="I102" s="48"/>
-      <c r="J102" s="48"/>
-      <c r="K102" s="48"/>
+      <c r="E102" s="69"/>
+      <c r="F102" s="69"/>
+      <c r="G102" s="69"/>
+      <c r="H102" s="69"/>
+      <c r="I102" s="69"/>
+      <c r="J102" s="69"/>
+      <c r="K102" s="69"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -9266,13 +9266,13 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="48"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="48"/>
-      <c r="K103" s="48"/>
+      <c r="E103" s="69"/>
+      <c r="F103" s="69"/>
+      <c r="G103" s="69"/>
+      <c r="H103" s="69"/>
+      <c r="I103" s="69"/>
+      <c r="J103" s="69"/>
+      <c r="K103" s="69"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -9280,196 +9280,6 @@
     </row>
   </sheetData>
   <mergeCells count="203">
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -9483,6 +9293,196 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -9892,148 +9892,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="87" t="s">
+      <c r="F2" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="89"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="93"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="86" t="s">
+      <c r="N2" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="85" t="e" vm="2">
+      <c r="B3" s="89" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="85" t="e" vm="3">
+      <c r="N3" s="89" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="93" t="s">
+      <c r="F4" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="93" t="s">
+      <c r="J4" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="85"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="90" t="s">
+      <c r="F5" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="92"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="95"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="85" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94" t="s">
+      <c r="C8" s="85"/>
+      <c r="D8" s="85" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="95"/>
-      <c r="D9" s="91" t="s">
+      <c r="C9" s="86"/>
+      <c r="D9" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91" t="s">
+      <c r="C10" s="87"/>
+      <c r="D10" s="87" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="87" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -10044,6 +10036,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3227478B-E38E-4AF7-B752-00CEB7A3372C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F7055E-1334-4793-B5FD-DAB77E9F1BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="551">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2367,6 +2367,27 @@
   <si>
     <t>기존 이미지가 다시 안보이게 변경
 해결방안으로 그림에 이미지 투명도(알파값)을 변동하는 것으로 해결이 가능함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retry버튼이 클릭되지 않는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retry버튼이 다시 작동할 수 있게 스크립트를 추가할 것
+현재 스크립트가 빠져있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인홀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중앙 홀에 네임 택에 밑단이 보이는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomName에 들어가 있는 Animetor에서 RoomName : Anchored Position에 찍혀있는 키들을 각각 640과 430으로 수정하면 해결 가능함</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6211,16 +6232,22 @@
         <v>461</v>
       </c>
       <c r="C103" s="37">
-        <v>46182</v>
-      </c>
-      <c r="D103" s="9"/>
-      <c r="E103" s="69"/>
-      <c r="F103" s="69"/>
-      <c r="G103" s="69"/>
-      <c r="H103" s="69"/>
-      <c r="I103" s="69"/>
-      <c r="J103" s="69"/>
-      <c r="K103" s="69"/>
+        <v>46184</v>
+      </c>
+      <c r="D103" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="E103" s="55" t="s">
+        <v>546</v>
+      </c>
+      <c r="F103" s="55"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="55"/>
+      <c r="I103" s="55" t="s">
+        <v>547</v>
+      </c>
+      <c r="J103" s="55"/>
+      <c r="K103" s="55"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -6231,16 +6258,22 @@
         <v>501</v>
       </c>
       <c r="C104" s="37">
-        <v>46182</v>
-      </c>
-      <c r="D104" s="9"/>
-      <c r="E104" s="69"/>
-      <c r="F104" s="69"/>
-      <c r="G104" s="69"/>
-      <c r="H104" s="69"/>
-      <c r="I104" s="69"/>
-      <c r="J104" s="69"/>
-      <c r="K104" s="69"/>
+        <v>46184</v>
+      </c>
+      <c r="D104" s="38" t="s">
+        <v>548</v>
+      </c>
+      <c r="E104" s="55" t="s">
+        <v>549</v>
+      </c>
+      <c r="F104" s="55"/>
+      <c r="G104" s="55"/>
+      <c r="H104" s="55"/>
+      <c r="I104" s="55" t="s">
+        <v>550</v>
+      </c>
+      <c r="J104" s="55"/>
+      <c r="K104" s="55"/>
       <c r="L104" s="9" t="s">
         <v>52</v>
       </c>
@@ -7318,7 +7351,7 @@
       <c r="J4" s="81"/>
       <c r="K4" s="82"/>
       <c r="L4" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M4" s="31"/>
     </row>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F7055E-1334-4793-B5FD-DAB77E9F1BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95ED24FF-CE9A-48D1-9532-0CBBB6796810}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -28,28 +28,28 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2"/>
         </ext>
       </extLst>
@@ -2387,7 +2387,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RoomName에 들어가 있는 Animetor에서 RoomName : Anchored Position에 찍혀있는 키들을 각각 640과 430으로 수정하면 해결 가능함</t>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2821,34 +2821,28 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2866,43 +2860,31 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2926,23 +2908,29 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2962,11 +2950,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3466,36 +3466,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -3508,17 +3508,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3537,17 +3537,17 @@
       <c r="D4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -3564,17 +3564,17 @@
       <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63" t="s">
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
       <c r="L5" s="9" t="s">
         <v>164</v>
       </c>
@@ -3591,17 +3591,17 @@
       <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63" t="s">
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
       <c r="L6" s="9" t="s">
         <v>164</v>
       </c>
@@ -3618,17 +3618,17 @@
       <c r="D7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="63" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
       <c r="L7" s="9" t="s">
         <v>164</v>
       </c>
@@ -3645,17 +3645,17 @@
       <c r="D8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="64" t="s">
+      <c r="E8" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="63" t="s">
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
       <c r="L8" s="9" t="s">
         <v>164</v>
       </c>
@@ -3672,17 +3672,17 @@
       <c r="D9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="64" t="s">
+      <c r="E9" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="63" t="s">
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
       <c r="L9" s="9" t="s">
         <v>164</v>
       </c>
@@ -3699,17 +3699,17 @@
       <c r="D10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="64" t="s">
+      <c r="E10" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="63" t="s">
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
       <c r="L10" s="9" t="s">
         <v>164</v>
       </c>
@@ -3726,17 +3726,17 @@
       <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
       <c r="L11" s="9" t="s">
         <v>164</v>
       </c>
@@ -3753,17 +3753,17 @@
       <c r="D12" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63" t="s">
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
       <c r="L12" s="9" t="s">
         <v>54</v>
       </c>
@@ -3780,17 +3780,17 @@
       <c r="D13" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -3807,17 +3807,17 @@
       <c r="D14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63" t="s">
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
       <c r="L14" s="9" t="s">
         <v>54</v>
       </c>
@@ -3834,17 +3834,17 @@
       <c r="D15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
       <c r="L15" s="9" t="s">
         <v>164</v>
       </c>
@@ -3861,17 +3861,17 @@
       <c r="D16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63" t="s">
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
       <c r="L16" s="9" t="s">
         <v>164</v>
       </c>
@@ -3888,17 +3888,17 @@
       <c r="D17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
       <c r="L17" s="9" t="s">
         <v>164</v>
       </c>
@@ -3915,17 +3915,17 @@
       <c r="D18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63" t="s">
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
       <c r="L18" s="9" t="s">
         <v>164</v>
       </c>
@@ -3942,17 +3942,17 @@
       <c r="D19" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58" t="s">
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -3969,17 +3969,17 @@
       <c r="D20" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58" t="s">
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -3996,17 +3996,17 @@
       <c r="D21" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58" t="s">
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
       <c r="L21" s="9" t="s">
         <v>164</v>
       </c>
@@ -4023,17 +4023,17 @@
       <c r="D22" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58" t="s">
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
       <c r="L22" s="9" t="s">
         <v>164</v>
       </c>
@@ -4050,17 +4050,17 @@
       <c r="D23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58" t="s">
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -4077,17 +4077,17 @@
       <c r="D24" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="58" t="s">
+      <c r="E24" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58" t="s">
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -4104,17 +4104,17 @@
       <c r="D25" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="58" t="s">
+      <c r="E25" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58" t="s">
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -4131,17 +4131,17 @@
       <c r="D26" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59" t="s">
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
       <c r="L26" s="9" t="s">
         <v>54</v>
       </c>
@@ -4173,17 +4173,17 @@
       <c r="D27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="62" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="52" t="s">
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="62" t="s">
         <v>182</v>
       </c>
-      <c r="J27" s="53"/>
-      <c r="K27" s="54"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="64"/>
       <c r="L27" s="9" t="s">
         <v>164</v>
       </c>
@@ -4206,17 +4206,17 @@
       <c r="D28" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="52" t="s">
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="53"/>
-      <c r="K28" s="54"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="64"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -4236,17 +4236,17 @@
       <c r="D29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="52" t="s">
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="62" t="s">
         <v>190</v>
       </c>
-      <c r="J29" s="53"/>
-      <c r="K29" s="54"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="64"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -4266,17 +4266,17 @@
       <c r="D30" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59" t="s">
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -4296,17 +4296,17 @@
       <c r="D31" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55" t="s">
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -4323,17 +4323,17 @@
       <c r="D32" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55" t="s">
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -4350,17 +4350,17 @@
       <c r="D33" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55" t="s">
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -4377,17 +4377,17 @@
       <c r="D34" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="56" t="s">
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="50"/>
-      <c r="K34" s="51"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="67"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -4404,17 +4404,17 @@
       <c r="D35" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="60" t="s">
+      <c r="E35" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="49" t="s">
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -4431,17 +4431,17 @@
       <c r="D36" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="60" t="s">
+      <c r="E36" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="49" t="s">
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="68"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -4458,17 +4458,17 @@
       <c r="D37" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="49" t="s">
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="68"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -4485,17 +4485,17 @@
       <c r="D38" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="E38" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="49" t="s">
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="50"/>
-      <c r="K38" s="51"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="67"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -4512,17 +4512,17 @@
       <c r="D39" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="48" t="s">
+      <c r="E39" s="61" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48" t="s">
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61" t="s">
         <v>220</v>
       </c>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -4539,17 +4539,17 @@
       <c r="D40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="61" t="s">
         <v>228</v>
       </c>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48" t="s">
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -4566,17 +4566,17 @@
       <c r="D41" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="E41" s="61" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48" t="s">
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -4593,17 +4593,17 @@
       <c r="D42" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="E42" s="48" t="s">
+      <c r="E42" s="61" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48" t="s">
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -4620,17 +4620,17 @@
       <c r="D43" s="43" t="s">
         <v>237</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="61" t="s">
         <v>247</v>
       </c>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48" t="s">
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -4647,17 +4647,17 @@
       <c r="D44" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48" t="s">
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="61" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="J44" s="61"/>
+      <c r="K44" s="61"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -4674,17 +4674,17 @@
       <c r="D45" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E45" s="48" t="s">
+      <c r="E45" s="61" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48" t="s">
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="61" t="s">
         <v>241</v>
       </c>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="61"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -4701,17 +4701,17 @@
       <c r="D46" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="61" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48" t="s">
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -4728,17 +4728,17 @@
       <c r="D47" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="48" t="s">
+      <c r="E47" s="61" t="s">
         <v>249</v>
       </c>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48" t="s">
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61" t="s">
         <v>250</v>
       </c>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -4755,17 +4755,17 @@
       <c r="D48" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="48" t="s">
+      <c r="E48" s="61" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48" t="s">
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="61" t="s">
         <v>252</v>
       </c>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -4782,17 +4782,17 @@
       <c r="D49" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48" t="s">
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -4809,17 +4809,17 @@
       <c r="D50" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48" t="s">
+      <c r="F50" s="61"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61" t="s">
         <v>257</v>
       </c>
-      <c r="J50" s="48"/>
-      <c r="K50" s="48"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -4836,17 +4836,17 @@
       <c r="D51" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="61" t="s">
         <v>258</v>
       </c>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48" t="s">
+      <c r="F51" s="61"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -4863,17 +4863,17 @@
       <c r="D52" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="48" t="s">
+      <c r="E52" s="61" t="s">
         <v>261</v>
       </c>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48" t="s">
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61" t="s">
         <v>262</v>
       </c>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -4890,17 +4890,17 @@
       <c r="D53" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48" t="s">
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61" t="s">
         <v>266</v>
       </c>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="J53" s="61"/>
+      <c r="K53" s="61"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -4917,17 +4917,17 @@
       <c r="D54" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="49" t="s">
+      <c r="E54" s="68" t="s">
         <v>268</v>
       </c>
-      <c r="F54" s="49"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="49" t="s">
+      <c r="F54" s="68"/>
+      <c r="G54" s="68"/>
+      <c r="H54" s="68"/>
+      <c r="I54" s="68" t="s">
         <v>269</v>
       </c>
-      <c r="J54" s="49"/>
-      <c r="K54" s="49"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="68"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -4944,17 +4944,17 @@
       <c r="D55" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="49" t="s">
+      <c r="E55" s="68" t="s">
         <v>271</v>
       </c>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49" t="s">
+      <c r="F55" s="68"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="68" t="s">
         <v>272</v>
       </c>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
+      <c r="J55" s="68"/>
+      <c r="K55" s="68"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -4971,17 +4971,17 @@
       <c r="D56" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="49" t="s">
+      <c r="E56" s="68" t="s">
         <v>274</v>
       </c>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49" t="s">
+      <c r="F56" s="68"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="68"/>
+      <c r="I56" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="J56" s="49"/>
-      <c r="K56" s="49"/>
+      <c r="J56" s="68"/>
+      <c r="K56" s="68"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -4998,17 +4998,17 @@
       <c r="D57" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48" t="s">
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61" t="s">
         <v>277</v>
       </c>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
       <c r="L57" s="43" t="s">
         <v>52</v>
       </c>
@@ -5025,17 +5025,17 @@
       <c r="D58" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="E58" s="48" t="s">
+      <c r="E58" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48" t="s">
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61" t="s">
         <v>282</v>
       </c>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
       <c r="L58" s="43" t="s">
         <v>52</v>
       </c>
@@ -5052,17 +5052,17 @@
       <c r="D59" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="E59" s="48" t="s">
+      <c r="E59" s="61" t="s">
         <v>278</v>
       </c>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48" t="s">
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61" t="s">
         <v>279</v>
       </c>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
       <c r="L59" s="43" t="s">
         <v>52</v>
       </c>
@@ -5079,17 +5079,17 @@
       <c r="D60" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="48" t="s">
+      <c r="E60" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48" t="s">
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61" t="s">
         <v>285</v>
       </c>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
       <c r="L60" s="43" t="s">
         <v>52</v>
       </c>
@@ -5106,17 +5106,17 @@
       <c r="D61" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E61" s="48" t="s">
+      <c r="E61" s="61" t="s">
         <v>286</v>
       </c>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48" t="s">
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="J61" s="61"/>
+      <c r="K61" s="61"/>
       <c r="L61" s="43" t="s">
         <v>52</v>
       </c>
@@ -5133,17 +5133,17 @@
       <c r="D62" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="61" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48" t="s">
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="61"/>
       <c r="L62" s="43" t="s">
         <v>52</v>
       </c>
@@ -5160,17 +5160,17 @@
       <c r="D63" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="48" t="s">
+      <c r="E63" s="61" t="s">
         <v>291</v>
       </c>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48" t="e" vm="1">
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
       <c r="L63" s="43" t="s">
         <v>52</v>
       </c>
@@ -5187,17 +5187,17 @@
       <c r="D64" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48" t="s">
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="61"/>
+      <c r="I64" s="61" t="s">
         <v>294</v>
       </c>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="J64" s="61"/>
+      <c r="K64" s="61"/>
       <c r="L64" s="43" t="s">
         <v>52</v>
       </c>
@@ -5214,17 +5214,17 @@
       <c r="D65" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="61" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48" t="s">
+      <c r="F65" s="61"/>
+      <c r="G65" s="61"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="61" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
       <c r="L65" s="43" t="s">
         <v>52</v>
       </c>
@@ -5241,17 +5241,17 @@
       <c r="D66" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48" t="s">
+      <c r="F66" s="61"/>
+      <c r="G66" s="61"/>
+      <c r="H66" s="61"/>
+      <c r="I66" s="61" t="s">
         <v>299</v>
       </c>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="J66" s="61"/>
+      <c r="K66" s="61"/>
       <c r="L66" s="43" t="s">
         <v>52</v>
       </c>
@@ -5268,17 +5268,17 @@
       <c r="D67" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="57" t="s">
+      <c r="E67" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="48" t="s">
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="61" t="s">
         <v>302</v>
       </c>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="J67" s="61"/>
+      <c r="K67" s="61"/>
       <c r="L67" s="43" t="s">
         <v>52</v>
       </c>
@@ -5295,17 +5295,17 @@
       <c r="D68" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="49" t="s">
+      <c r="E68" s="68" t="s">
         <v>303</v>
       </c>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="49" t="s">
+      <c r="F68" s="68"/>
+      <c r="G68" s="68"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="J68" s="49"/>
-      <c r="K68" s="49"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="68"/>
       <c r="L68" s="27" t="s">
         <v>52</v>
       </c>
@@ -5322,17 +5322,17 @@
       <c r="D69" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E69" s="49" t="s">
+      <c r="E69" s="68" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="49" t="s">
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="68" t="s">
         <v>307</v>
       </c>
-      <c r="J69" s="49"/>
-      <c r="K69" s="49"/>
+      <c r="J69" s="68"/>
+      <c r="K69" s="68"/>
       <c r="L69" s="27" t="s">
         <v>52</v>
       </c>
@@ -5349,17 +5349,17 @@
       <c r="D70" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="49" t="s">
+      <c r="E70" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49" t="s">
+      <c r="F70" s="68"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="68"/>
+      <c r="I70" s="68" t="s">
         <v>308</v>
       </c>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
+      <c r="J70" s="68"/>
+      <c r="K70" s="68"/>
       <c r="L70" s="27" t="s">
         <v>52</v>
       </c>
@@ -5376,17 +5376,17 @@
       <c r="D71" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E71" s="49" t="s">
+      <c r="E71" s="68" t="s">
         <v>310</v>
       </c>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="49" t="s">
+      <c r="F71" s="68"/>
+      <c r="G71" s="68"/>
+      <c r="H71" s="68"/>
+      <c r="I71" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="J71" s="49"/>
-      <c r="K71" s="49"/>
+      <c r="J71" s="68"/>
+      <c r="K71" s="68"/>
       <c r="L71" s="27" t="s">
         <v>52</v>
       </c>
@@ -5403,17 +5403,17 @@
       <c r="D72" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="E72" s="49" t="s">
+      <c r="E72" s="68" t="s">
         <v>313</v>
       </c>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49" t="s">
+      <c r="F72" s="68"/>
+      <c r="G72" s="68"/>
+      <c r="H72" s="68"/>
+      <c r="I72" s="68" t="s">
         <v>314</v>
       </c>
-      <c r="J72" s="49"/>
-      <c r="K72" s="49"/>
+      <c r="J72" s="68"/>
+      <c r="K72" s="68"/>
       <c r="L72" s="27" t="s">
         <v>52</v>
       </c>
@@ -5430,17 +5430,17 @@
       <c r="D73" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="E73" s="49" t="s">
+      <c r="E73" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49" t="s">
+      <c r="F73" s="68"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="68" t="s">
         <v>316</v>
       </c>
-      <c r="J73" s="49"/>
-      <c r="K73" s="49"/>
+      <c r="J73" s="68"/>
+      <c r="K73" s="68"/>
       <c r="L73" s="27" t="s">
         <v>52</v>
       </c>
@@ -5457,17 +5457,17 @@
       <c r="D74" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="49" t="s">
+      <c r="E74" s="68" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49" t="s">
+      <c r="F74" s="68"/>
+      <c r="G74" s="68"/>
+      <c r="H74" s="68"/>
+      <c r="I74" s="68" t="s">
         <v>319</v>
       </c>
-      <c r="J74" s="49"/>
-      <c r="K74" s="49"/>
+      <c r="J74" s="68"/>
+      <c r="K74" s="68"/>
       <c r="L74" s="27" t="s">
         <v>52</v>
       </c>
@@ -5484,17 +5484,17 @@
       <c r="D75" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="49" t="s">
+      <c r="E75" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49" t="s">
+      <c r="F75" s="68"/>
+      <c r="G75" s="68"/>
+      <c r="H75" s="68"/>
+      <c r="I75" s="68" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="49"/>
-      <c r="K75" s="49"/>
+      <c r="J75" s="68"/>
+      <c r="K75" s="68"/>
       <c r="L75" s="27" t="s">
         <v>52</v>
       </c>
@@ -5511,17 +5511,17 @@
       <c r="D76" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="49" t="s">
+      <c r="E76" s="68" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49" t="s">
+      <c r="F76" s="68"/>
+      <c r="G76" s="68"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="68" t="s">
         <v>332</v>
       </c>
-      <c r="J76" s="49"/>
-      <c r="K76" s="49"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="68"/>
       <c r="L76" s="27" t="s">
         <v>52</v>
       </c>
@@ -5538,17 +5538,17 @@
       <c r="D77" s="27" t="s">
         <v>321</v>
       </c>
-      <c r="E77" s="49" t="s">
+      <c r="E77" s="68" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="49"/>
-      <c r="G77" s="49"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="49" t="s">
+      <c r="F77" s="68"/>
+      <c r="G77" s="68"/>
+      <c r="H77" s="68"/>
+      <c r="I77" s="68" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="49"/>
-      <c r="K77" s="49"/>
+      <c r="J77" s="68"/>
+      <c r="K77" s="68"/>
       <c r="L77" s="27" t="s">
         <v>52</v>
       </c>
@@ -5565,17 +5565,17 @@
       <c r="D78" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="49" t="s">
+      <c r="E78" s="68" t="s">
         <v>325</v>
       </c>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49" t="s">
+      <c r="F78" s="68"/>
+      <c r="G78" s="68"/>
+      <c r="H78" s="68"/>
+      <c r="I78" s="68" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
+      <c r="J78" s="68"/>
+      <c r="K78" s="68"/>
       <c r="L78" s="27" t="s">
         <v>52</v>
       </c>
@@ -5592,17 +5592,17 @@
       <c r="D79" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="E79" s="49" t="s">
+      <c r="E79" s="68" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49" t="s">
+      <c r="F79" s="68"/>
+      <c r="G79" s="68"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="68" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
+      <c r="J79" s="68"/>
+      <c r="K79" s="68"/>
       <c r="L79" s="27" t="s">
         <v>52</v>
       </c>
@@ -5619,17 +5619,17 @@
       <c r="D80" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="49" t="s">
+      <c r="E80" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49" t="s">
+      <c r="F80" s="68"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="68" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="49"/>
-      <c r="K80" s="49"/>
+      <c r="J80" s="68"/>
+      <c r="K80" s="68"/>
       <c r="L80" s="27" t="s">
         <v>52</v>
       </c>
@@ -5646,17 +5646,17 @@
       <c r="D81" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="E81" s="48" t="s">
+      <c r="E81" s="61" t="s">
         <v>336</v>
       </c>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48" t="s">
+      <c r="F81" s="61"/>
+      <c r="G81" s="61"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="61" t="s">
         <v>335</v>
       </c>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="J81" s="61"/>
+      <c r="K81" s="61"/>
       <c r="L81" s="43" t="s">
         <v>52</v>
       </c>
@@ -5673,17 +5673,17 @@
       <c r="D82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E82" s="48" t="s">
+      <c r="E82" s="61" t="s">
         <v>338</v>
       </c>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48" t="s">
+      <c r="F82" s="61"/>
+      <c r="G82" s="61"/>
+      <c r="H82" s="61"/>
+      <c r="I82" s="61" t="s">
         <v>339</v>
       </c>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="J82" s="61"/>
+      <c r="K82" s="61"/>
       <c r="L82" s="43" t="s">
         <v>52</v>
       </c>
@@ -5700,17 +5700,17 @@
       <c r="D83" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="E83" s="48" t="s">
+      <c r="E83" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48" t="s">
+      <c r="F83" s="61"/>
+      <c r="G83" s="61"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61" t="s">
         <v>342</v>
       </c>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="J83" s="61"/>
+      <c r="K83" s="61"/>
       <c r="L83" s="43" t="s">
         <v>52</v>
       </c>
@@ -5727,17 +5727,17 @@
       <c r="D84" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E84" s="48" t="s">
+      <c r="E84" s="61" t="s">
         <v>344</v>
       </c>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48" t="s">
+      <c r="F84" s="61"/>
+      <c r="G84" s="61"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61" t="s">
         <v>343</v>
       </c>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="J84" s="61"/>
+      <c r="K84" s="61"/>
       <c r="L84" s="43" t="s">
         <v>52</v>
       </c>
@@ -5754,17 +5754,17 @@
       <c r="D85" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="E85" s="48" t="s">
+      <c r="E85" s="61" t="s">
         <v>346</v>
       </c>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48" t="s">
+      <c r="F85" s="61"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="61" t="s">
         <v>347</v>
       </c>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="J85" s="61"/>
+      <c r="K85" s="61"/>
       <c r="L85" s="43" t="s">
         <v>52</v>
       </c>
@@ -5781,17 +5781,17 @@
       <c r="D86" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="E86" s="48" t="s">
+      <c r="E86" s="61" t="s">
         <v>348</v>
       </c>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48" t="s">
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
+      <c r="I86" s="61" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
+      <c r="J86" s="61"/>
+      <c r="K86" s="61"/>
       <c r="L86" s="43" t="s">
         <v>52</v>
       </c>
@@ -5808,17 +5808,17 @@
       <c r="D87" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E87" s="48" t="s">
+      <c r="E87" s="61" t="s">
         <v>350</v>
       </c>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48" t="s">
+      <c r="F87" s="61"/>
+      <c r="G87" s="61"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="61" t="s">
         <v>352</v>
       </c>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
+      <c r="J87" s="61"/>
+      <c r="K87" s="61"/>
       <c r="L87" s="43" t="s">
         <v>52</v>
       </c>
@@ -5835,17 +5835,17 @@
       <c r="D88" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="49" t="s">
+      <c r="E88" s="68" t="s">
         <v>355</v>
       </c>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49" t="s">
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
+      <c r="H88" s="68"/>
+      <c r="I88" s="68" t="s">
         <v>358</v>
       </c>
-      <c r="J88" s="49"/>
-      <c r="K88" s="49"/>
+      <c r="J88" s="68"/>
+      <c r="K88" s="68"/>
       <c r="L88" s="27" t="s">
         <v>52</v>
       </c>
@@ -5862,17 +5862,17 @@
       <c r="D89" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="49" t="s">
+      <c r="E89" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="F89" s="49"/>
-      <c r="G89" s="49"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="49" t="s">
+      <c r="F89" s="68"/>
+      <c r="G89" s="68"/>
+      <c r="H89" s="68"/>
+      <c r="I89" s="68" t="s">
         <v>357</v>
       </c>
-      <c r="J89" s="49"/>
-      <c r="K89" s="49"/>
+      <c r="J89" s="68"/>
+      <c r="K89" s="68"/>
       <c r="L89" s="27" t="s">
         <v>164</v>
       </c>
@@ -5889,17 +5889,17 @@
       <c r="D90" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="49" t="s">
+      <c r="E90" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="49"/>
-      <c r="G90" s="49"/>
-      <c r="H90" s="49"/>
-      <c r="I90" s="49" t="s">
+      <c r="F90" s="68"/>
+      <c r="G90" s="68"/>
+      <c r="H90" s="68"/>
+      <c r="I90" s="68" t="s">
         <v>360</v>
       </c>
-      <c r="J90" s="49"/>
-      <c r="K90" s="49"/>
+      <c r="J90" s="68"/>
+      <c r="K90" s="68"/>
       <c r="L90" s="27" t="s">
         <v>164</v>
       </c>
@@ -5916,17 +5916,17 @@
       <c r="D91" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="E91" s="49" t="s">
+      <c r="E91" s="68" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="49"/>
-      <c r="G91" s="49"/>
-      <c r="H91" s="49"/>
-      <c r="I91" s="49" t="s">
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
+      <c r="H91" s="68"/>
+      <c r="I91" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="J91" s="49"/>
-      <c r="K91" s="49"/>
+      <c r="J91" s="68"/>
+      <c r="K91" s="68"/>
       <c r="L91" s="27" t="s">
         <v>164</v>
       </c>
@@ -5943,17 +5943,17 @@
       <c r="D92" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="E92" s="55" t="s">
+      <c r="E92" s="49" t="s">
         <v>474</v>
       </c>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="55"/>
-      <c r="I92" s="55" t="s">
+      <c r="F92" s="49"/>
+      <c r="G92" s="49"/>
+      <c r="H92" s="49"/>
+      <c r="I92" s="49" t="s">
         <v>475</v>
       </c>
-      <c r="J92" s="55"/>
-      <c r="K92" s="55"/>
+      <c r="J92" s="49"/>
+      <c r="K92" s="49"/>
       <c r="L92" s="9" t="s">
         <v>164</v>
       </c>
@@ -5970,17 +5970,17 @@
       <c r="D93" s="38" t="s">
         <v>473</v>
       </c>
-      <c r="E93" s="55" t="s">
+      <c r="E93" s="49" t="s">
         <v>476</v>
       </c>
-      <c r="F93" s="55"/>
-      <c r="G93" s="55"/>
-      <c r="H93" s="55"/>
-      <c r="I93" s="55" t="s">
+      <c r="F93" s="49"/>
+      <c r="G93" s="49"/>
+      <c r="H93" s="49"/>
+      <c r="I93" s="49" t="s">
         <v>477</v>
       </c>
-      <c r="J93" s="55"/>
-      <c r="K93" s="55"/>
+      <c r="J93" s="49"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="9" t="s">
         <v>164</v>
       </c>
@@ -5997,17 +5997,17 @@
       <c r="D94" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="E94" s="55" t="s">
+      <c r="E94" s="49" t="s">
         <v>478</v>
       </c>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55" t="s">
+      <c r="F94" s="49"/>
+      <c r="G94" s="49"/>
+      <c r="H94" s="49"/>
+      <c r="I94" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="J94" s="55"/>
-      <c r="K94" s="55"/>
+      <c r="J94" s="49"/>
+      <c r="K94" s="49"/>
       <c r="L94" s="9" t="s">
         <v>164</v>
       </c>
@@ -6024,17 +6024,17 @@
       <c r="D95" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="E95" s="55" t="s">
+      <c r="E95" s="49" t="s">
         <v>480</v>
       </c>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="55"/>
-      <c r="I95" s="55" t="s">
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="J95" s="55"/>
-      <c r="K95" s="55"/>
+      <c r="J95" s="49"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="9" t="s">
         <v>164</v>
       </c>
@@ -6051,19 +6051,19 @@
       <c r="D96" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E96" s="55" t="s">
+      <c r="E96" s="49" t="s">
         <v>490</v>
       </c>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="55"/>
-      <c r="I96" s="55" t="s">
+      <c r="F96" s="49"/>
+      <c r="G96" s="49"/>
+      <c r="H96" s="49"/>
+      <c r="I96" s="49" t="s">
         <v>491</v>
       </c>
-      <c r="J96" s="55"/>
-      <c r="K96" s="55"/>
+      <c r="J96" s="49"/>
+      <c r="K96" s="49"/>
       <c r="L96" s="9" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="M96" s="10"/>
     </row>
@@ -6078,17 +6078,17 @@
       <c r="D97" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="E97" s="55" t="s">
+      <c r="E97" s="49" t="s">
         <v>492</v>
       </c>
-      <c r="F97" s="55"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="55"/>
-      <c r="I97" s="55" t="s">
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
+      <c r="H97" s="49"/>
+      <c r="I97" s="49" t="s">
         <v>493</v>
       </c>
-      <c r="J97" s="55"/>
-      <c r="K97" s="55"/>
+      <c r="J97" s="49"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="9" t="s">
         <v>164</v>
       </c>
@@ -6105,17 +6105,17 @@
       <c r="D98" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="E98" s="55" t="s">
+      <c r="E98" s="49" t="s">
         <v>494</v>
       </c>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="55"/>
-      <c r="I98" s="55" t="s">
+      <c r="F98" s="49"/>
+      <c r="G98" s="49"/>
+      <c r="H98" s="49"/>
+      <c r="I98" s="49" t="s">
         <v>495</v>
       </c>
-      <c r="J98" s="55"/>
-      <c r="K98" s="55"/>
+      <c r="J98" s="49"/>
+      <c r="K98" s="49"/>
       <c r="L98" s="9" t="s">
         <v>164</v>
       </c>
@@ -6132,17 +6132,17 @@
       <c r="D99" s="38" t="s">
         <v>496</v>
       </c>
-      <c r="E99" s="55" t="s">
+      <c r="E99" s="49" t="s">
         <v>497</v>
       </c>
-      <c r="F99" s="55"/>
-      <c r="G99" s="55"/>
-      <c r="H99" s="55"/>
-      <c r="I99" s="55" t="s">
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
+      <c r="H99" s="49"/>
+      <c r="I99" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="J99" s="55"/>
-      <c r="K99" s="55"/>
+      <c r="J99" s="49"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="9" t="s">
         <v>164</v>
       </c>
@@ -6159,17 +6159,17 @@
       <c r="D100" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="E100" s="55" t="s">
+      <c r="E100" s="49" t="s">
         <v>539</v>
       </c>
-      <c r="F100" s="55"/>
-      <c r="G100" s="55"/>
-      <c r="H100" s="55"/>
-      <c r="I100" s="55" t="s">
+      <c r="F100" s="49"/>
+      <c r="G100" s="49"/>
+      <c r="H100" s="49"/>
+      <c r="I100" s="49" t="s">
         <v>540</v>
       </c>
-      <c r="J100" s="55"/>
-      <c r="K100" s="55"/>
+      <c r="J100" s="49"/>
+      <c r="K100" s="49"/>
       <c r="L100" s="9" t="s">
         <v>164</v>
       </c>
@@ -6185,17 +6185,17 @@
       <c r="D101" s="38" t="s">
         <v>541</v>
       </c>
-      <c r="E101" s="55" t="s">
+      <c r="E101" s="49" t="s">
         <v>542</v>
       </c>
-      <c r="F101" s="55"/>
-      <c r="G101" s="55"/>
-      <c r="H101" s="55"/>
-      <c r="I101" s="55" t="s">
+      <c r="F101" s="49"/>
+      <c r="G101" s="49"/>
+      <c r="H101" s="49"/>
+      <c r="I101" s="49" t="s">
         <v>543</v>
       </c>
-      <c r="J101" s="55"/>
-      <c r="K101" s="55"/>
+      <c r="J101" s="49"/>
+      <c r="K101" s="49"/>
       <c r="L101" s="9" t="s">
         <v>164</v>
       </c>
@@ -6211,17 +6211,17 @@
       <c r="D102" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="E102" s="55" t="s">
+      <c r="E102" s="49" t="s">
         <v>544</v>
       </c>
-      <c r="F102" s="55"/>
-      <c r="G102" s="55"/>
-      <c r="H102" s="55"/>
-      <c r="I102" s="55" t="s">
+      <c r="F102" s="49"/>
+      <c r="G102" s="49"/>
+      <c r="H102" s="49"/>
+      <c r="I102" s="49" t="s">
         <v>545</v>
       </c>
-      <c r="J102" s="55"/>
-      <c r="K102" s="55"/>
+      <c r="J102" s="49"/>
+      <c r="K102" s="49"/>
       <c r="L102" s="9" t="s">
         <v>164</v>
       </c>
@@ -6237,17 +6237,17 @@
       <c r="D103" s="38" t="s">
         <v>334</v>
       </c>
-      <c r="E103" s="55" t="s">
+      <c r="E103" s="49" t="s">
         <v>546</v>
       </c>
-      <c r="F103" s="55"/>
-      <c r="G103" s="55"/>
-      <c r="H103" s="55"/>
-      <c r="I103" s="55" t="s">
+      <c r="F103" s="49"/>
+      <c r="G103" s="49"/>
+      <c r="H103" s="49"/>
+      <c r="I103" s="49" t="s">
         <v>547</v>
       </c>
-      <c r="J103" s="55"/>
-      <c r="K103" s="55"/>
+      <c r="J103" s="49"/>
+      <c r="K103" s="49"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -6263,17 +6263,17 @@
       <c r="D104" s="38" t="s">
         <v>548</v>
       </c>
-      <c r="E104" s="55" t="s">
+      <c r="E104" s="49" t="s">
         <v>549</v>
       </c>
-      <c r="F104" s="55"/>
-      <c r="G104" s="55"/>
-      <c r="H104" s="55"/>
-      <c r="I104" s="55" t="s">
+      <c r="F104" s="49"/>
+      <c r="G104" s="49"/>
+      <c r="H104" s="49"/>
+      <c r="I104" s="49" t="s">
         <v>550</v>
       </c>
-      <c r="J104" s="55"/>
-      <c r="K104" s="55"/>
+      <c r="J104" s="49"/>
+      <c r="K104" s="49"/>
       <c r="L104" s="9" t="s">
         <v>52</v>
       </c>
@@ -6287,13 +6287,13 @@
         <v>46182</v>
       </c>
       <c r="D105" s="9"/>
-      <c r="E105" s="69"/>
-      <c r="F105" s="69"/>
-      <c r="G105" s="69"/>
-      <c r="H105" s="69"/>
-      <c r="I105" s="69"/>
-      <c r="J105" s="69"/>
-      <c r="K105" s="69"/>
+      <c r="E105" s="48"/>
+      <c r="F105" s="48"/>
+      <c r="G105" s="48"/>
+      <c r="H105" s="48"/>
+      <c r="I105" s="48"/>
+      <c r="J105" s="48"/>
+      <c r="K105" s="48"/>
       <c r="L105" s="9" t="s">
         <v>52</v>
       </c>
@@ -6305,13 +6305,13 @@
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
-      <c r="E106" s="69"/>
-      <c r="F106" s="69"/>
-      <c r="G106" s="69"/>
-      <c r="H106" s="69"/>
-      <c r="I106" s="69"/>
-      <c r="J106" s="69"/>
-      <c r="K106" s="69"/>
+      <c r="E106" s="48"/>
+      <c r="F106" s="48"/>
+      <c r="G106" s="48"/>
+      <c r="H106" s="48"/>
+      <c r="I106" s="48"/>
+      <c r="J106" s="48"/>
+      <c r="K106" s="48"/>
       <c r="L106" s="9" t="s">
         <v>52</v>
       </c>
@@ -6323,13 +6323,13 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
-      <c r="E107" s="69"/>
-      <c r="F107" s="69"/>
-      <c r="G107" s="69"/>
-      <c r="H107" s="69"/>
-      <c r="I107" s="69"/>
-      <c r="J107" s="69"/>
-      <c r="K107" s="69"/>
+      <c r="E107" s="48"/>
+      <c r="F107" s="48"/>
+      <c r="G107" s="48"/>
+      <c r="H107" s="48"/>
+      <c r="I107" s="48"/>
+      <c r="J107" s="48"/>
+      <c r="K107" s="48"/>
       <c r="L107" s="9" t="s">
         <v>52</v>
       </c>
@@ -6341,13 +6341,13 @@
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
-      <c r="E108" s="69"/>
-      <c r="F108" s="69"/>
-      <c r="G108" s="69"/>
-      <c r="H108" s="69"/>
-      <c r="I108" s="69"/>
-      <c r="J108" s="69"/>
-      <c r="K108" s="69"/>
+      <c r="E108" s="48"/>
+      <c r="F108" s="48"/>
+      <c r="G108" s="48"/>
+      <c r="H108" s="48"/>
+      <c r="I108" s="48"/>
+      <c r="J108" s="48"/>
+      <c r="K108" s="48"/>
       <c r="L108" s="9" t="s">
         <v>52</v>
       </c>
@@ -6359,13 +6359,13 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
-      <c r="E109" s="69"/>
-      <c r="F109" s="69"/>
-      <c r="G109" s="69"/>
-      <c r="H109" s="69"/>
-      <c r="I109" s="69"/>
-      <c r="J109" s="69"/>
-      <c r="K109" s="69"/>
+      <c r="E109" s="48"/>
+      <c r="F109" s="48"/>
+      <c r="G109" s="48"/>
+      <c r="H109" s="48"/>
+      <c r="I109" s="48"/>
+      <c r="J109" s="48"/>
+      <c r="K109" s="48"/>
       <c r="L109" s="9" t="s">
         <v>52</v>
       </c>
@@ -6377,13 +6377,13 @@
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
-      <c r="E110" s="69"/>
-      <c r="F110" s="69"/>
-      <c r="G110" s="69"/>
-      <c r="H110" s="69"/>
-      <c r="I110" s="69"/>
-      <c r="J110" s="69"/>
-      <c r="K110" s="69"/>
+      <c r="E110" s="48"/>
+      <c r="F110" s="48"/>
+      <c r="G110" s="48"/>
+      <c r="H110" s="48"/>
+      <c r="I110" s="48"/>
+      <c r="J110" s="48"/>
+      <c r="K110" s="48"/>
       <c r="L110" s="9" t="s">
         <v>52</v>
       </c>
@@ -6395,13 +6395,13 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
-      <c r="E111" s="69"/>
-      <c r="F111" s="69"/>
-      <c r="G111" s="69"/>
-      <c r="H111" s="69"/>
-      <c r="I111" s="69"/>
-      <c r="J111" s="69"/>
-      <c r="K111" s="69"/>
+      <c r="E111" s="48"/>
+      <c r="F111" s="48"/>
+      <c r="G111" s="48"/>
+      <c r="H111" s="48"/>
+      <c r="I111" s="48"/>
+      <c r="J111" s="48"/>
+      <c r="K111" s="48"/>
       <c r="L111" s="9" t="s">
         <v>52</v>
       </c>
@@ -6413,13 +6413,13 @@
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
-      <c r="E112" s="69"/>
-      <c r="F112" s="69"/>
-      <c r="G112" s="69"/>
-      <c r="H112" s="69"/>
-      <c r="I112" s="69"/>
-      <c r="J112" s="69"/>
-      <c r="K112" s="69"/>
+      <c r="E112" s="48"/>
+      <c r="F112" s="48"/>
+      <c r="G112" s="48"/>
+      <c r="H112" s="48"/>
+      <c r="I112" s="48"/>
+      <c r="J112" s="48"/>
+      <c r="K112" s="48"/>
       <c r="L112" s="9" t="s">
         <v>52</v>
       </c>
@@ -6431,13 +6431,13 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
-      <c r="E113" s="69"/>
-      <c r="F113" s="69"/>
-      <c r="G113" s="69"/>
-      <c r="H113" s="69"/>
-      <c r="I113" s="69"/>
-      <c r="J113" s="69"/>
-      <c r="K113" s="69"/>
+      <c r="E113" s="48"/>
+      <c r="F113" s="48"/>
+      <c r="G113" s="48"/>
+      <c r="H113" s="48"/>
+      <c r="I113" s="48"/>
+      <c r="J113" s="48"/>
+      <c r="K113" s="48"/>
       <c r="L113" s="9" t="s">
         <v>52</v>
       </c>
@@ -6449,13 +6449,13 @@
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
-      <c r="E114" s="69"/>
-      <c r="F114" s="69"/>
-      <c r="G114" s="69"/>
-      <c r="H114" s="69"/>
-      <c r="I114" s="69"/>
-      <c r="J114" s="69"/>
-      <c r="K114" s="69"/>
+      <c r="E114" s="48"/>
+      <c r="F114" s="48"/>
+      <c r="G114" s="48"/>
+      <c r="H114" s="48"/>
+      <c r="I114" s="48"/>
+      <c r="J114" s="48"/>
+      <c r="K114" s="48"/>
       <c r="L114" s="9" t="s">
         <v>52</v>
       </c>
@@ -6467,13 +6467,13 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
-      <c r="E115" s="69"/>
-      <c r="F115" s="69"/>
-      <c r="G115" s="69"/>
-      <c r="H115" s="69"/>
-      <c r="I115" s="69"/>
-      <c r="J115" s="69"/>
-      <c r="K115" s="69"/>
+      <c r="E115" s="48"/>
+      <c r="F115" s="48"/>
+      <c r="G115" s="48"/>
+      <c r="H115" s="48"/>
+      <c r="I115" s="48"/>
+      <c r="J115" s="48"/>
+      <c r="K115" s="48"/>
       <c r="L115" s="9" t="s">
         <v>52</v>
       </c>
@@ -6485,13 +6485,13 @@
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
-      <c r="E116" s="69"/>
-      <c r="F116" s="69"/>
-      <c r="G116" s="69"/>
-      <c r="H116" s="69"/>
-      <c r="I116" s="69"/>
-      <c r="J116" s="69"/>
-      <c r="K116" s="69"/>
+      <c r="E116" s="48"/>
+      <c r="F116" s="48"/>
+      <c r="G116" s="48"/>
+      <c r="H116" s="48"/>
+      <c r="I116" s="48"/>
+      <c r="J116" s="48"/>
+      <c r="K116" s="48"/>
       <c r="L116" s="9" t="s">
         <v>52</v>
       </c>
@@ -6503,13 +6503,13 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
-      <c r="E117" s="69"/>
-      <c r="F117" s="69"/>
-      <c r="G117" s="69"/>
-      <c r="H117" s="69"/>
-      <c r="I117" s="69"/>
-      <c r="J117" s="69"/>
-      <c r="K117" s="69"/>
+      <c r="E117" s="48"/>
+      <c r="F117" s="48"/>
+      <c r="G117" s="48"/>
+      <c r="H117" s="48"/>
+      <c r="I117" s="48"/>
+      <c r="J117" s="48"/>
+      <c r="K117" s="48"/>
       <c r="L117" s="9" t="s">
         <v>52</v>
       </c>
@@ -6521,13 +6521,13 @@
       </c>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
-      <c r="E118" s="69"/>
-      <c r="F118" s="69"/>
-      <c r="G118" s="69"/>
-      <c r="H118" s="69"/>
-      <c r="I118" s="69"/>
-      <c r="J118" s="69"/>
-      <c r="K118" s="69"/>
+      <c r="E118" s="48"/>
+      <c r="F118" s="48"/>
+      <c r="G118" s="48"/>
+      <c r="H118" s="48"/>
+      <c r="I118" s="48"/>
+      <c r="J118" s="48"/>
+      <c r="K118" s="48"/>
       <c r="L118" s="9" t="s">
         <v>52</v>
       </c>
@@ -6539,13 +6539,13 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
-      <c r="E119" s="69"/>
-      <c r="F119" s="69"/>
-      <c r="G119" s="69"/>
-      <c r="H119" s="69"/>
-      <c r="I119" s="69"/>
-      <c r="J119" s="69"/>
-      <c r="K119" s="69"/>
+      <c r="E119" s="48"/>
+      <c r="F119" s="48"/>
+      <c r="G119" s="48"/>
+      <c r="H119" s="48"/>
+      <c r="I119" s="48"/>
+      <c r="J119" s="48"/>
+      <c r="K119" s="48"/>
       <c r="L119" s="9" t="s">
         <v>52</v>
       </c>
@@ -6557,13 +6557,13 @@
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
-      <c r="E120" s="69"/>
-      <c r="F120" s="69"/>
-      <c r="G120" s="69"/>
-      <c r="H120" s="69"/>
-      <c r="I120" s="69"/>
-      <c r="J120" s="69"/>
-      <c r="K120" s="69"/>
+      <c r="E120" s="48"/>
+      <c r="F120" s="48"/>
+      <c r="G120" s="48"/>
+      <c r="H120" s="48"/>
+      <c r="I120" s="48"/>
+      <c r="J120" s="48"/>
+      <c r="K120" s="48"/>
       <c r="L120" s="9" t="s">
         <v>52</v>
       </c>
@@ -6575,13 +6575,13 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
-      <c r="E121" s="69"/>
-      <c r="F121" s="69"/>
-      <c r="G121" s="69"/>
-      <c r="H121" s="69"/>
-      <c r="I121" s="69"/>
-      <c r="J121" s="69"/>
-      <c r="K121" s="69"/>
+      <c r="E121" s="48"/>
+      <c r="F121" s="48"/>
+      <c r="G121" s="48"/>
+      <c r="H121" s="48"/>
+      <c r="I121" s="48"/>
+      <c r="J121" s="48"/>
+      <c r="K121" s="48"/>
       <c r="L121" s="9" t="s">
         <v>52</v>
       </c>
@@ -6593,13 +6593,13 @@
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
-      <c r="E122" s="69"/>
-      <c r="F122" s="69"/>
-      <c r="G122" s="69"/>
-      <c r="H122" s="69"/>
-      <c r="I122" s="69"/>
-      <c r="J122" s="69"/>
-      <c r="K122" s="69"/>
+      <c r="E122" s="48"/>
+      <c r="F122" s="48"/>
+      <c r="G122" s="48"/>
+      <c r="H122" s="48"/>
+      <c r="I122" s="48"/>
+      <c r="J122" s="48"/>
+      <c r="K122" s="48"/>
       <c r="L122" s="9" t="s">
         <v>52</v>
       </c>
@@ -6611,13 +6611,13 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
-      <c r="E123" s="69"/>
-      <c r="F123" s="69"/>
-      <c r="G123" s="69"/>
-      <c r="H123" s="69"/>
-      <c r="I123" s="69"/>
-      <c r="J123" s="69"/>
-      <c r="K123" s="69"/>
+      <c r="E123" s="48"/>
+      <c r="F123" s="48"/>
+      <c r="G123" s="48"/>
+      <c r="H123" s="48"/>
+      <c r="I123" s="48"/>
+      <c r="J123" s="48"/>
+      <c r="K123" s="48"/>
       <c r="L123" s="9" t="s">
         <v>52</v>
       </c>
@@ -6629,13 +6629,13 @@
       </c>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
-      <c r="E124" s="69"/>
-      <c r="F124" s="69"/>
-      <c r="G124" s="69"/>
-      <c r="H124" s="69"/>
-      <c r="I124" s="69"/>
-      <c r="J124" s="69"/>
-      <c r="K124" s="69"/>
+      <c r="E124" s="48"/>
+      <c r="F124" s="48"/>
+      <c r="G124" s="48"/>
+      <c r="H124" s="48"/>
+      <c r="I124" s="48"/>
+      <c r="J124" s="48"/>
+      <c r="K124" s="48"/>
       <c r="L124" s="9" t="s">
         <v>52</v>
       </c>
@@ -6647,13 +6647,13 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
-      <c r="E125" s="69"/>
-      <c r="F125" s="69"/>
-      <c r="G125" s="69"/>
-      <c r="H125" s="69"/>
-      <c r="I125" s="69"/>
-      <c r="J125" s="69"/>
-      <c r="K125" s="69"/>
+      <c r="E125" s="48"/>
+      <c r="F125" s="48"/>
+      <c r="G125" s="48"/>
+      <c r="H125" s="48"/>
+      <c r="I125" s="48"/>
+      <c r="J125" s="48"/>
+      <c r="K125" s="48"/>
       <c r="L125" s="9" t="s">
         <v>52</v>
       </c>
@@ -6665,13 +6665,13 @@
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
-      <c r="E126" s="69"/>
-      <c r="F126" s="69"/>
-      <c r="G126" s="69"/>
-      <c r="H126" s="69"/>
-      <c r="I126" s="69"/>
-      <c r="J126" s="69"/>
-      <c r="K126" s="69"/>
+      <c r="E126" s="48"/>
+      <c r="F126" s="48"/>
+      <c r="G126" s="48"/>
+      <c r="H126" s="48"/>
+      <c r="I126" s="48"/>
+      <c r="J126" s="48"/>
+      <c r="K126" s="48"/>
       <c r="L126" s="9" t="s">
         <v>52</v>
       </c>
@@ -6683,13 +6683,13 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
-      <c r="E127" s="69"/>
-      <c r="F127" s="69"/>
-      <c r="G127" s="69"/>
-      <c r="H127" s="69"/>
-      <c r="I127" s="69"/>
-      <c r="J127" s="69"/>
-      <c r="K127" s="69"/>
+      <c r="E127" s="48"/>
+      <c r="F127" s="48"/>
+      <c r="G127" s="48"/>
+      <c r="H127" s="48"/>
+      <c r="I127" s="48"/>
+      <c r="J127" s="48"/>
+      <c r="K127" s="48"/>
       <c r="L127" s="9" t="s">
         <v>52</v>
       </c>
@@ -6701,13 +6701,13 @@
       </c>
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
-      <c r="E128" s="69"/>
-      <c r="F128" s="69"/>
-      <c r="G128" s="69"/>
-      <c r="H128" s="69"/>
-      <c r="I128" s="69"/>
-      <c r="J128" s="69"/>
-      <c r="K128" s="69"/>
+      <c r="E128" s="48"/>
+      <c r="F128" s="48"/>
+      <c r="G128" s="48"/>
+      <c r="H128" s="48"/>
+      <c r="I128" s="48"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="48"/>
       <c r="L128" s="9" t="s">
         <v>52</v>
       </c>
@@ -6719,13 +6719,13 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
-      <c r="E129" s="69"/>
-      <c r="F129" s="69"/>
-      <c r="G129" s="69"/>
-      <c r="H129" s="69"/>
-      <c r="I129" s="69"/>
-      <c r="J129" s="69"/>
-      <c r="K129" s="69"/>
+      <c r="E129" s="48"/>
+      <c r="F129" s="48"/>
+      <c r="G129" s="48"/>
+      <c r="H129" s="48"/>
+      <c r="I129" s="48"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="48"/>
       <c r="L129" s="9" t="s">
         <v>52</v>
       </c>
@@ -6737,13 +6737,13 @@
       </c>
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
-      <c r="E130" s="69"/>
-      <c r="F130" s="69"/>
-      <c r="G130" s="69"/>
-      <c r="H130" s="69"/>
-      <c r="I130" s="69"/>
-      <c r="J130" s="69"/>
-      <c r="K130" s="69"/>
+      <c r="E130" s="48"/>
+      <c r="F130" s="48"/>
+      <c r="G130" s="48"/>
+      <c r="H130" s="48"/>
+      <c r="I130" s="48"/>
+      <c r="J130" s="48"/>
+      <c r="K130" s="48"/>
       <c r="L130" s="9" t="s">
         <v>52</v>
       </c>
@@ -6755,13 +6755,13 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
-      <c r="E131" s="69"/>
-      <c r="F131" s="69"/>
-      <c r="G131" s="69"/>
-      <c r="H131" s="69"/>
-      <c r="I131" s="69"/>
-      <c r="J131" s="69"/>
-      <c r="K131" s="69"/>
+      <c r="E131" s="48"/>
+      <c r="F131" s="48"/>
+      <c r="G131" s="48"/>
+      <c r="H131" s="48"/>
+      <c r="I131" s="48"/>
+      <c r="J131" s="48"/>
+      <c r="K131" s="48"/>
       <c r="L131" s="9" t="s">
         <v>52</v>
       </c>
@@ -6773,13 +6773,13 @@
       </c>
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
-      <c r="E132" s="69"/>
-      <c r="F132" s="69"/>
-      <c r="G132" s="69"/>
-      <c r="H132" s="69"/>
-      <c r="I132" s="69"/>
-      <c r="J132" s="69"/>
-      <c r="K132" s="69"/>
+      <c r="E132" s="48"/>
+      <c r="F132" s="48"/>
+      <c r="G132" s="48"/>
+      <c r="H132" s="48"/>
+      <c r="I132" s="48"/>
+      <c r="J132" s="48"/>
+      <c r="K132" s="48"/>
       <c r="L132" s="9" t="s">
         <v>52</v>
       </c>
@@ -6791,13 +6791,13 @@
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
-      <c r="E133" s="69"/>
-      <c r="F133" s="69"/>
-      <c r="G133" s="69"/>
-      <c r="H133" s="69"/>
-      <c r="I133" s="69"/>
-      <c r="J133" s="69"/>
-      <c r="K133" s="69"/>
+      <c r="E133" s="48"/>
+      <c r="F133" s="48"/>
+      <c r="G133" s="48"/>
+      <c r="H133" s="48"/>
+      <c r="I133" s="48"/>
+      <c r="J133" s="48"/>
+      <c r="K133" s="48"/>
       <c r="L133" s="9" t="s">
         <v>52</v>
       </c>
@@ -6809,13 +6809,13 @@
       </c>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
-      <c r="E134" s="69"/>
-      <c r="F134" s="69"/>
-      <c r="G134" s="69"/>
-      <c r="H134" s="69"/>
-      <c r="I134" s="69"/>
-      <c r="J134" s="69"/>
-      <c r="K134" s="69"/>
+      <c r="E134" s="48"/>
+      <c r="F134" s="48"/>
+      <c r="G134" s="48"/>
+      <c r="H134" s="48"/>
+      <c r="I134" s="48"/>
+      <c r="J134" s="48"/>
+      <c r="K134" s="48"/>
       <c r="L134" s="9" t="s">
         <v>52</v>
       </c>
@@ -6827,13 +6827,13 @@
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
-      <c r="E135" s="69"/>
-      <c r="F135" s="69"/>
-      <c r="G135" s="69"/>
-      <c r="H135" s="69"/>
-      <c r="I135" s="69"/>
-      <c r="J135" s="69"/>
-      <c r="K135" s="69"/>
+      <c r="E135" s="48"/>
+      <c r="F135" s="48"/>
+      <c r="G135" s="48"/>
+      <c r="H135" s="48"/>
+      <c r="I135" s="48"/>
+      <c r="J135" s="48"/>
+      <c r="K135" s="48"/>
       <c r="L135" s="9" t="s">
         <v>52</v>
       </c>
@@ -6845,13 +6845,13 @@
       </c>
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
-      <c r="E136" s="69"/>
-      <c r="F136" s="69"/>
-      <c r="G136" s="69"/>
-      <c r="H136" s="69"/>
-      <c r="I136" s="69"/>
-      <c r="J136" s="69"/>
-      <c r="K136" s="69"/>
+      <c r="E136" s="48"/>
+      <c r="F136" s="48"/>
+      <c r="G136" s="48"/>
+      <c r="H136" s="48"/>
+      <c r="I136" s="48"/>
+      <c r="J136" s="48"/>
+      <c r="K136" s="48"/>
       <c r="L136" s="9" t="s">
         <v>52</v>
       </c>
@@ -6863,13 +6863,13 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
-      <c r="E137" s="69"/>
-      <c r="F137" s="69"/>
-      <c r="G137" s="69"/>
-      <c r="H137" s="69"/>
-      <c r="I137" s="69"/>
-      <c r="J137" s="69"/>
-      <c r="K137" s="69"/>
+      <c r="E137" s="48"/>
+      <c r="F137" s="48"/>
+      <c r="G137" s="48"/>
+      <c r="H137" s="48"/>
+      <c r="I137" s="48"/>
+      <c r="J137" s="48"/>
+      <c r="K137" s="48"/>
       <c r="L137" s="9" t="s">
         <v>52</v>
       </c>
@@ -6881,13 +6881,13 @@
       </c>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
-      <c r="E138" s="69"/>
-      <c r="F138" s="69"/>
-      <c r="G138" s="69"/>
-      <c r="H138" s="69"/>
-      <c r="I138" s="69"/>
-      <c r="J138" s="69"/>
-      <c r="K138" s="69"/>
+      <c r="E138" s="48"/>
+      <c r="F138" s="48"/>
+      <c r="G138" s="48"/>
+      <c r="H138" s="48"/>
+      <c r="I138" s="48"/>
+      <c r="J138" s="48"/>
+      <c r="K138" s="48"/>
       <c r="L138" s="9" t="s">
         <v>52</v>
       </c>
@@ -6899,13 +6899,13 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
-      <c r="E139" s="69"/>
-      <c r="F139" s="69"/>
-      <c r="G139" s="69"/>
-      <c r="H139" s="69"/>
-      <c r="I139" s="69"/>
-      <c r="J139" s="69"/>
-      <c r="K139" s="69"/>
+      <c r="E139" s="48"/>
+      <c r="F139" s="48"/>
+      <c r="G139" s="48"/>
+      <c r="H139" s="48"/>
+      <c r="I139" s="48"/>
+      <c r="J139" s="48"/>
+      <c r="K139" s="48"/>
       <c r="L139" s="9" t="s">
         <v>52</v>
       </c>
@@ -6917,13 +6917,13 @@
       </c>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
-      <c r="E140" s="69"/>
-      <c r="F140" s="69"/>
-      <c r="G140" s="69"/>
-      <c r="H140" s="69"/>
-      <c r="I140" s="69"/>
-      <c r="J140" s="69"/>
-      <c r="K140" s="69"/>
+      <c r="E140" s="48"/>
+      <c r="F140" s="48"/>
+      <c r="G140" s="48"/>
+      <c r="H140" s="48"/>
+      <c r="I140" s="48"/>
+      <c r="J140" s="48"/>
+      <c r="K140" s="48"/>
       <c r="L140" s="9" t="s">
         <v>52</v>
       </c>
@@ -6935,13 +6935,13 @@
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
-      <c r="E141" s="69"/>
-      <c r="F141" s="69"/>
-      <c r="G141" s="69"/>
-      <c r="H141" s="69"/>
-      <c r="I141" s="69"/>
-      <c r="J141" s="69"/>
-      <c r="K141" s="69"/>
+      <c r="E141" s="48"/>
+      <c r="F141" s="48"/>
+      <c r="G141" s="48"/>
+      <c r="H141" s="48"/>
+      <c r="I141" s="48"/>
+      <c r="J141" s="48"/>
+      <c r="K141" s="48"/>
       <c r="L141" s="9" t="s">
         <v>52</v>
       </c>
@@ -6949,88 +6949,179 @@
     </row>
   </sheetData>
   <mergeCells count="279">
-    <mergeCell ref="E141:H141"/>
-    <mergeCell ref="I141:K141"/>
-    <mergeCell ref="E136:H136"/>
-    <mergeCell ref="I136:K136"/>
-    <mergeCell ref="E137:H137"/>
-    <mergeCell ref="I137:K137"/>
-    <mergeCell ref="E138:H138"/>
-    <mergeCell ref="I138:K138"/>
-    <mergeCell ref="E139:H139"/>
-    <mergeCell ref="I139:K139"/>
-    <mergeCell ref="E140:H140"/>
-    <mergeCell ref="I140:K140"/>
-    <mergeCell ref="E131:H131"/>
-    <mergeCell ref="I131:K131"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="I132:K132"/>
-    <mergeCell ref="E133:H133"/>
-    <mergeCell ref="I133:K133"/>
-    <mergeCell ref="E134:H134"/>
-    <mergeCell ref="I134:K134"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:K135"/>
-    <mergeCell ref="E126:H126"/>
-    <mergeCell ref="I126:K126"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="I127:K127"/>
-    <mergeCell ref="E128:H128"/>
-    <mergeCell ref="I128:K128"/>
-    <mergeCell ref="E129:H129"/>
-    <mergeCell ref="I129:K129"/>
-    <mergeCell ref="E130:H130"/>
-    <mergeCell ref="I130:K130"/>
-    <mergeCell ref="E121:H121"/>
-    <mergeCell ref="I121:K121"/>
-    <mergeCell ref="E122:H122"/>
-    <mergeCell ref="I122:K122"/>
-    <mergeCell ref="E123:H123"/>
-    <mergeCell ref="I123:K123"/>
-    <mergeCell ref="E124:H124"/>
-    <mergeCell ref="I124:K124"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:K125"/>
-    <mergeCell ref="E116:H116"/>
-    <mergeCell ref="I116:K116"/>
-    <mergeCell ref="E117:H117"/>
-    <mergeCell ref="I117:K117"/>
-    <mergeCell ref="E118:H118"/>
-    <mergeCell ref="I118:K118"/>
-    <mergeCell ref="E119:H119"/>
-    <mergeCell ref="I119:K119"/>
-    <mergeCell ref="E120:H120"/>
-    <mergeCell ref="I120:K120"/>
-    <mergeCell ref="E111:H111"/>
-    <mergeCell ref="I111:K111"/>
-    <mergeCell ref="E112:H112"/>
-    <mergeCell ref="I112:K112"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:K113"/>
-    <mergeCell ref="E114:H114"/>
-    <mergeCell ref="I114:K114"/>
-    <mergeCell ref="E115:H115"/>
-    <mergeCell ref="I115:K115"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="I106:K106"/>
-    <mergeCell ref="E107:H107"/>
-    <mergeCell ref="I107:K107"/>
-    <mergeCell ref="E108:H108"/>
-    <mergeCell ref="I108:K108"/>
-    <mergeCell ref="E109:H109"/>
-    <mergeCell ref="I109:K109"/>
-    <mergeCell ref="E110:H110"/>
-    <mergeCell ref="I110:K110"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E104:H104"/>
-    <mergeCell ref="I104:K104"/>
-    <mergeCell ref="E105:H105"/>
-    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -7055,179 +7146,88 @@
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E104:H104"/>
+    <mergeCell ref="I104:K104"/>
+    <mergeCell ref="E105:H105"/>
+    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="I106:K106"/>
+    <mergeCell ref="E107:H107"/>
+    <mergeCell ref="I107:K107"/>
+    <mergeCell ref="E108:H108"/>
+    <mergeCell ref="I108:K108"/>
+    <mergeCell ref="E109:H109"/>
+    <mergeCell ref="I109:K109"/>
+    <mergeCell ref="E110:H110"/>
+    <mergeCell ref="I110:K110"/>
+    <mergeCell ref="E111:H111"/>
+    <mergeCell ref="I111:K111"/>
+    <mergeCell ref="E112:H112"/>
+    <mergeCell ref="I112:K112"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:K113"/>
+    <mergeCell ref="E114:H114"/>
+    <mergeCell ref="I114:K114"/>
+    <mergeCell ref="E115:H115"/>
+    <mergeCell ref="I115:K115"/>
+    <mergeCell ref="E116:H116"/>
+    <mergeCell ref="I116:K116"/>
+    <mergeCell ref="E117:H117"/>
+    <mergeCell ref="I117:K117"/>
+    <mergeCell ref="E118:H118"/>
+    <mergeCell ref="I118:K118"/>
+    <mergeCell ref="E119:H119"/>
+    <mergeCell ref="I119:K119"/>
+    <mergeCell ref="E120:H120"/>
+    <mergeCell ref="I120:K120"/>
+    <mergeCell ref="E121:H121"/>
+    <mergeCell ref="I121:K121"/>
+    <mergeCell ref="E122:H122"/>
+    <mergeCell ref="I122:K122"/>
+    <mergeCell ref="E123:H123"/>
+    <mergeCell ref="I123:K123"/>
+    <mergeCell ref="E124:H124"/>
+    <mergeCell ref="I124:K124"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:K125"/>
+    <mergeCell ref="E126:H126"/>
+    <mergeCell ref="I126:K126"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="I127:K127"/>
+    <mergeCell ref="E128:H128"/>
+    <mergeCell ref="I128:K128"/>
+    <mergeCell ref="E129:H129"/>
+    <mergeCell ref="I129:K129"/>
+    <mergeCell ref="E130:H130"/>
+    <mergeCell ref="I130:K130"/>
+    <mergeCell ref="E131:H131"/>
+    <mergeCell ref="I131:K131"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="I132:K132"/>
+    <mergeCell ref="E133:H133"/>
+    <mergeCell ref="I133:K133"/>
+    <mergeCell ref="E134:H134"/>
+    <mergeCell ref="I134:K134"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:K135"/>
+    <mergeCell ref="E141:H141"/>
+    <mergeCell ref="I141:K141"/>
+    <mergeCell ref="E136:H136"/>
+    <mergeCell ref="I136:K136"/>
+    <mergeCell ref="E137:H137"/>
+    <mergeCell ref="I137:K137"/>
+    <mergeCell ref="E138:H138"/>
+    <mergeCell ref="I138:K138"/>
+    <mergeCell ref="E139:H139"/>
+    <mergeCell ref="I139:K139"/>
+    <mergeCell ref="E140:H140"/>
+    <mergeCell ref="I140:K140"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L141">
@@ -7268,36 +7268,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
@@ -7310,17 +7310,17 @@
       <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68" t="s">
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
       <c r="L3" s="5" t="s">
         <v>51</v>
       </c>
@@ -7339,17 +7339,17 @@
       <c r="D4" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="74" t="s">
         <v>463</v>
       </c>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="80" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="74" t="s">
         <v>464</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="82"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="76"/>
       <c r="L4" s="9" t="s">
         <v>164</v>
       </c>
@@ -7366,17 +7366,17 @@
       <c r="D5" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E5" s="76" t="s">
+      <c r="E5" s="70" t="s">
         <v>468</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76" t="s">
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70" t="s">
         <v>469</v>
       </c>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
       <c r="L5" s="9" t="s">
         <v>52</v>
       </c>
@@ -7393,17 +7393,17 @@
       <c r="D6" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="56" t="s">
         <v>466</v>
       </c>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58" t="s">
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56" t="s">
         <v>467</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
       <c r="L6" s="9" t="s">
         <v>52</v>
       </c>
@@ -7420,17 +7420,17 @@
       <c r="D7" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="70" t="s">
         <v>470</v>
       </c>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76" t="s">
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70" t="s">
         <v>471</v>
       </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
       <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
@@ -7447,17 +7447,17 @@
       <c r="D8" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="71" t="s">
         <v>483</v>
       </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="77" t="s">
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="71" t="s">
         <v>484</v>
       </c>
-      <c r="J8" s="78"/>
-      <c r="K8" s="79"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="73"/>
       <c r="L8" s="9" t="s">
         <v>52</v>
       </c>
@@ -7474,17 +7474,17 @@
       <c r="D9" s="24" t="s">
         <v>465</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="56" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58" t="s">
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56" t="s">
         <v>486</v>
       </c>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
       <c r="L9" s="9" t="s">
         <v>52</v>
       </c>
@@ -7501,17 +7501,17 @@
       <c r="D10" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="70" t="s">
         <v>487</v>
       </c>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76" t="s">
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70" t="s">
         <v>488</v>
       </c>
-      <c r="J10" s="76"/>
-      <c r="K10" s="76"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
       <c r="L10" s="9" t="s">
         <v>52</v>
       </c>
@@ -7524,13 +7524,13 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
@@ -7543,13 +7543,13 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="75"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="79"/>
       <c r="L12" s="9" t="s">
         <v>52</v>
       </c>
@@ -7562,13 +7562,13 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
       <c r="L13" s="9" t="s">
         <v>52</v>
       </c>
@@ -7581,13 +7581,13 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
       <c r="L14" s="9" t="s">
         <v>52</v>
       </c>
@@ -7600,13 +7600,13 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
       <c r="L15" s="9" t="s">
         <v>52</v>
       </c>
@@ -7619,13 +7619,13 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
       <c r="L16" s="9" t="s">
         <v>52</v>
       </c>
@@ -7638,13 +7638,13 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
       <c r="L17" s="9" t="s">
         <v>52</v>
       </c>
@@ -7657,13 +7657,13 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
       <c r="L18" s="9" t="s">
         <v>52</v>
       </c>
@@ -7676,13 +7676,13 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="75"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="79"/>
       <c r="L19" s="9" t="s">
         <v>52</v>
       </c>
@@ -7695,13 +7695,13 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
       <c r="L20" s="9" t="s">
         <v>52</v>
       </c>
@@ -7714,13 +7714,13 @@
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
       <c r="L21" s="9" t="s">
         <v>52</v>
       </c>
@@ -7733,13 +7733,13 @@
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
       <c r="L22" s="9" t="s">
         <v>52</v>
       </c>
@@ -7752,13 +7752,13 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="75"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="79"/>
       <c r="L23" s="9" t="s">
         <v>52</v>
       </c>
@@ -7771,13 +7771,13 @@
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
       <c r="L24" s="9" t="s">
         <v>52</v>
       </c>
@@ -7790,13 +7790,13 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
       <c r="L25" s="9" t="s">
         <v>52</v>
       </c>
@@ -7809,13 +7809,13 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
       <c r="L26" s="9" t="s">
         <v>52</v>
       </c>
@@ -7843,13 +7843,13 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="75"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="79"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="79"/>
       <c r="L27" s="9" t="s">
         <v>52</v>
       </c>
@@ -7868,13 +7868,13 @@
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
       <c r="L28" s="9" t="s">
         <v>52</v>
       </c>
@@ -7890,13 +7890,13 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
       <c r="L29" s="9" t="s">
         <v>52</v>
       </c>
@@ -7912,13 +7912,13 @@
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
       <c r="L30" s="9" t="s">
         <v>52</v>
       </c>
@@ -7934,13 +7934,13 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
       <c r="L31" s="9" t="s">
         <v>52</v>
       </c>
@@ -7953,13 +7953,13 @@
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
       <c r="L32" s="9" t="s">
         <v>52</v>
       </c>
@@ -7972,13 +7972,13 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
       <c r="L33" s="9" t="s">
         <v>52</v>
       </c>
@@ -7991,13 +7991,13 @@
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="75"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="79"/>
       <c r="L34" s="9" t="s">
         <v>52</v>
       </c>
@@ -8010,13 +8010,13 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
       <c r="L35" s="9" t="s">
         <v>52</v>
       </c>
@@ -8029,13 +8029,13 @@
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
       <c r="L36" s="9" t="s">
         <v>52</v>
       </c>
@@ -8048,13 +8048,13 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
       <c r="L37" s="9" t="s">
         <v>52</v>
       </c>
@@ -8067,13 +8067,13 @@
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="73"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="75"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="79"/>
       <c r="L38" s="9" t="s">
         <v>52</v>
       </c>
@@ -8086,13 +8086,13 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="9" t="s">
         <v>52</v>
       </c>
@@ -8105,13 +8105,13 @@
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="69"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="9" t="s">
         <v>52</v>
       </c>
@@ -8124,13 +8124,13 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="9" t="s">
         <v>52</v>
       </c>
@@ -8143,13 +8143,13 @@
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="75"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="79"/>
       <c r="L42" s="9" t="s">
         <v>52</v>
       </c>
@@ -8162,13 +8162,13 @@
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="69"/>
-      <c r="K43" s="69"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="9" t="s">
         <v>52</v>
       </c>
@@ -8181,13 +8181,13 @@
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="69"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="69"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="9" t="s">
         <v>52</v>
       </c>
@@ -8200,13 +8200,13 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="69"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="9" t="s">
         <v>52</v>
       </c>
@@ -8219,13 +8219,13 @@
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="9" t="s">
         <v>52</v>
       </c>
@@ -8238,13 +8238,13 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="9" t="s">
         <v>52</v>
       </c>
@@ -8257,13 +8257,13 @@
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="69"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="9" t="s">
         <v>52</v>
       </c>
@@ -8276,13 +8276,13 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="9" t="s">
         <v>52</v>
       </c>
@@ -8295,13 +8295,13 @@
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="73"/>
-      <c r="J50" s="74"/>
-      <c r="K50" s="75"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="78"/>
+      <c r="G50" s="78"/>
+      <c r="H50" s="79"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="78"/>
+      <c r="K50" s="79"/>
       <c r="L50" s="9" t="s">
         <v>52</v>
       </c>
@@ -8314,13 +8314,13 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="69"/>
-      <c r="I51" s="69"/>
-      <c r="J51" s="69"/>
-      <c r="K51" s="69"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="9" t="s">
         <v>52</v>
       </c>
@@ -8333,13 +8333,13 @@
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="69"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="69"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="9" t="s">
         <v>52</v>
       </c>
@@ -8352,13 +8352,13 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="69"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="69"/>
-      <c r="I53" s="69"/>
-      <c r="J53" s="69"/>
-      <c r="K53" s="69"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="9" t="s">
         <v>52</v>
       </c>
@@ -8371,13 +8371,13 @@
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="74"/>
-      <c r="K54" s="75"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="79"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="78"/>
+      <c r="K54" s="79"/>
       <c r="L54" s="9" t="s">
         <v>52</v>
       </c>
@@ -8390,13 +8390,13 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
-      <c r="E55" s="69"/>
-      <c r="F55" s="69"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="69"/>
-      <c r="J55" s="69"/>
-      <c r="K55" s="69"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
       <c r="L55" s="9" t="s">
         <v>52</v>
       </c>
@@ -8409,13 +8409,13 @@
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
-      <c r="E56" s="69"/>
-      <c r="F56" s="69"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="69"/>
-      <c r="J56" s="69"/>
-      <c r="K56" s="69"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
       <c r="L56" s="9" t="s">
         <v>52</v>
       </c>
@@ -8428,13 +8428,13 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
-      <c r="E57" s="69"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="69"/>
-      <c r="J57" s="69"/>
-      <c r="K57" s="69"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="9" t="s">
         <v>52</v>
       </c>
@@ -8447,13 +8447,13 @@
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="74"/>
-      <c r="K58" s="75"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="78"/>
+      <c r="G58" s="78"/>
+      <c r="H58" s="79"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="78"/>
+      <c r="K58" s="79"/>
       <c r="L58" s="9" t="s">
         <v>52</v>
       </c>
@@ -8466,13 +8466,13 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="69"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="69"/>
-      <c r="I59" s="69"/>
-      <c r="J59" s="69"/>
-      <c r="K59" s="69"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="9" t="s">
         <v>52</v>
       </c>
@@ -8485,13 +8485,13 @@
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="69"/>
-      <c r="F60" s="69"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="69"/>
-      <c r="K60" s="69"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="9" t="s">
         <v>52</v>
       </c>
@@ -8504,13 +8504,13 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="69"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="9" t="s">
         <v>52</v>
       </c>
@@ -8523,13 +8523,13 @@
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="69"/>
-      <c r="K62" s="69"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="9" t="s">
         <v>52</v>
       </c>
@@ -8542,13 +8542,13 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="69"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="69"/>
-      <c r="K63" s="69"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="9" t="s">
         <v>52</v>
       </c>
@@ -8561,13 +8561,13 @@
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="69"/>
-      <c r="F64" s="69"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="69"/>
-      <c r="K64" s="69"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="9" t="s">
         <v>52</v>
       </c>
@@ -8580,13 +8580,13 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="74"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="74"/>
-      <c r="K65" s="75"/>
+      <c r="E65" s="77"/>
+      <c r="F65" s="78"/>
+      <c r="G65" s="78"/>
+      <c r="H65" s="79"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="78"/>
+      <c r="K65" s="79"/>
       <c r="L65" s="9" t="s">
         <v>52</v>
       </c>
@@ -8599,13 +8599,13 @@
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="69"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="9" t="s">
         <v>52</v>
       </c>
@@ -8618,13 +8618,13 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69"/>
-      <c r="H67" s="69"/>
-      <c r="I67" s="69"/>
-      <c r="J67" s="69"/>
-      <c r="K67" s="69"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="9" t="s">
         <v>52</v>
       </c>
@@ -8637,13 +8637,13 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
-      <c r="E68" s="69"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="69"/>
-      <c r="J68" s="69"/>
-      <c r="K68" s="69"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
       <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
@@ -8656,13 +8656,13 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="74"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="73"/>
-      <c r="J69" s="74"/>
-      <c r="K69" s="75"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="79"/>
+      <c r="I69" s="77"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="79"/>
       <c r="L69" s="9" t="s">
         <v>52</v>
       </c>
@@ -8675,13 +8675,13 @@
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="69"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="69"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="69"/>
-      <c r="K70" s="69"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
       <c r="L70" s="9" t="s">
         <v>52</v>
       </c>
@@ -8694,13 +8694,13 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="69"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="69"/>
-      <c r="H71" s="69"/>
-      <c r="I71" s="69"/>
-      <c r="J71" s="69"/>
-      <c r="K71" s="69"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
       <c r="L71" s="9" t="s">
         <v>52</v>
       </c>
@@ -8713,13 +8713,13 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="69"/>
-      <c r="K72" s="69"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48"/>
       <c r="L72" s="9" t="s">
         <v>52</v>
       </c>
@@ -8732,13 +8732,13 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
-      <c r="E73" s="73"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="73"/>
-      <c r="J73" s="74"/>
-      <c r="K73" s="75"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="79"/>
+      <c r="I73" s="77"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="79"/>
       <c r="L73" s="9" t="s">
         <v>52</v>
       </c>
@@ -8751,13 +8751,13 @@
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="69"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="69"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="48"/>
       <c r="L74" s="9" t="s">
         <v>52</v>
       </c>
@@ -8770,13 +8770,13 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
-      <c r="E75" s="69"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="69"/>
-      <c r="H75" s="69"/>
-      <c r="I75" s="69"/>
-      <c r="J75" s="69"/>
-      <c r="K75" s="69"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
       <c r="L75" s="9" t="s">
         <v>52</v>
       </c>
@@ -8789,13 +8789,13 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
-      <c r="E76" s="69"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="69"/>
-      <c r="H76" s="69"/>
-      <c r="I76" s="69"/>
-      <c r="J76" s="69"/>
-      <c r="K76" s="69"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48"/>
       <c r="L76" s="9" t="s">
         <v>52</v>
       </c>
@@ -8808,13 +8808,13 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="69"/>
-      <c r="H77" s="69"/>
-      <c r="I77" s="69"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="69"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="48"/>
+      <c r="K77" s="48"/>
       <c r="L77" s="9" t="s">
         <v>52</v>
       </c>
@@ -8827,13 +8827,13 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="69"/>
-      <c r="F78" s="69"/>
-      <c r="G78" s="69"/>
-      <c r="H78" s="69"/>
-      <c r="I78" s="69"/>
-      <c r="J78" s="69"/>
-      <c r="K78" s="69"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
       <c r="L78" s="9" t="s">
         <v>52</v>
       </c>
@@ -8846,13 +8846,13 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="69"/>
-      <c r="F79" s="69"/>
-      <c r="G79" s="69"/>
-      <c r="H79" s="69"/>
-      <c r="I79" s="69"/>
-      <c r="J79" s="69"/>
-      <c r="K79" s="69"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
       <c r="L79" s="9" t="s">
         <v>52</v>
       </c>
@@ -8865,13 +8865,13 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="72"/>
-      <c r="I80" s="70"/>
-      <c r="J80" s="71"/>
-      <c r="K80" s="72"/>
+      <c r="E80" s="80"/>
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="82"/>
+      <c r="I80" s="80"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="82"/>
       <c r="L80" s="9" t="s">
         <v>52</v>
       </c>
@@ -8884,13 +8884,13 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="72"/>
+      <c r="E81" s="80"/>
+      <c r="F81" s="81"/>
+      <c r="G81" s="81"/>
+      <c r="H81" s="82"/>
+      <c r="I81" s="80"/>
+      <c r="J81" s="81"/>
+      <c r="K81" s="82"/>
       <c r="L81" s="9" t="s">
         <v>52</v>
       </c>
@@ -8903,13 +8903,13 @@
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="72"/>
-      <c r="I82" s="70"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="72"/>
+      <c r="E82" s="80"/>
+      <c r="F82" s="81"/>
+      <c r="G82" s="81"/>
+      <c r="H82" s="82"/>
+      <c r="I82" s="80"/>
+      <c r="J82" s="81"/>
+      <c r="K82" s="82"/>
       <c r="L82" s="9" t="s">
         <v>52</v>
       </c>
@@ -8922,13 +8922,13 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="72"/>
+      <c r="E83" s="80"/>
+      <c r="F83" s="81"/>
+      <c r="G83" s="81"/>
+      <c r="H83" s="82"/>
+      <c r="I83" s="80"/>
+      <c r="J83" s="81"/>
+      <c r="K83" s="82"/>
       <c r="L83" s="9" t="s">
         <v>52</v>
       </c>
@@ -8941,13 +8941,13 @@
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
-      <c r="E84" s="70"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="70"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="72"/>
+      <c r="E84" s="80"/>
+      <c r="F84" s="81"/>
+      <c r="G84" s="81"/>
+      <c r="H84" s="82"/>
+      <c r="I84" s="80"/>
+      <c r="J84" s="81"/>
+      <c r="K84" s="82"/>
       <c r="L84" s="9" t="s">
         <v>52</v>
       </c>
@@ -8960,13 +8960,13 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
-      <c r="E85" s="70"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="72"/>
-      <c r="I85" s="70"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="72"/>
+      <c r="E85" s="80"/>
+      <c r="F85" s="81"/>
+      <c r="G85" s="81"/>
+      <c r="H85" s="82"/>
+      <c r="I85" s="80"/>
+      <c r="J85" s="81"/>
+      <c r="K85" s="82"/>
       <c r="L85" s="9" t="s">
         <v>52</v>
       </c>
@@ -8979,13 +8979,13 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
-      <c r="E86" s="70"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="71"/>
-      <c r="H86" s="72"/>
-      <c r="I86" s="70"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="72"/>
+      <c r="E86" s="80"/>
+      <c r="F86" s="81"/>
+      <c r="G86" s="81"/>
+      <c r="H86" s="82"/>
+      <c r="I86" s="80"/>
+      <c r="J86" s="81"/>
+      <c r="K86" s="82"/>
       <c r="L86" s="9" t="s">
         <v>52</v>
       </c>
@@ -8998,13 +8998,13 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="70"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="70"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="72"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="81"/>
+      <c r="G87" s="81"/>
+      <c r="H87" s="82"/>
+      <c r="I87" s="80"/>
+      <c r="J87" s="81"/>
+      <c r="K87" s="82"/>
       <c r="L87" s="9" t="s">
         <v>52</v>
       </c>
@@ -9017,13 +9017,13 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
-      <c r="E88" s="70"/>
-      <c r="F88" s="71"/>
-      <c r="G88" s="71"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="70"/>
-      <c r="J88" s="71"/>
-      <c r="K88" s="72"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
+      <c r="H88" s="82"/>
+      <c r="I88" s="80"/>
+      <c r="J88" s="81"/>
+      <c r="K88" s="82"/>
       <c r="L88" s="9" t="s">
         <v>52</v>
       </c>
@@ -9036,13 +9036,13 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
-      <c r="E89" s="70"/>
-      <c r="F89" s="71"/>
-      <c r="G89" s="71"/>
-      <c r="H89" s="72"/>
-      <c r="I89" s="70"/>
-      <c r="J89" s="71"/>
-      <c r="K89" s="72"/>
+      <c r="E89" s="80"/>
+      <c r="F89" s="81"/>
+      <c r="G89" s="81"/>
+      <c r="H89" s="82"/>
+      <c r="I89" s="80"/>
+      <c r="J89" s="81"/>
+      <c r="K89" s="82"/>
       <c r="L89" s="9" t="s">
         <v>52</v>
       </c>
@@ -9055,13 +9055,13 @@
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="71"/>
-      <c r="H90" s="72"/>
-      <c r="I90" s="70"/>
-      <c r="J90" s="71"/>
-      <c r="K90" s="72"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="81"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="80"/>
+      <c r="J90" s="81"/>
+      <c r="K90" s="82"/>
       <c r="L90" s="9" t="s">
         <v>52</v>
       </c>
@@ -9074,13 +9074,13 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
-      <c r="E91" s="69"/>
-      <c r="F91" s="69"/>
-      <c r="G91" s="69"/>
-      <c r="H91" s="69"/>
-      <c r="I91" s="69"/>
-      <c r="J91" s="69"/>
-      <c r="K91" s="69"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
       <c r="L91" s="9" t="s">
         <v>52</v>
       </c>
@@ -9093,13 +9093,13 @@
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
-      <c r="E92" s="69"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="69"/>
-      <c r="H92" s="69"/>
-      <c r="I92" s="69"/>
-      <c r="J92" s="69"/>
-      <c r="K92" s="69"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="48"/>
       <c r="L92" s="9" t="s">
         <v>52</v>
       </c>
@@ -9112,13 +9112,13 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
-      <c r="E93" s="69"/>
-      <c r="F93" s="69"/>
-      <c r="G93" s="69"/>
-      <c r="H93" s="69"/>
-      <c r="I93" s="69"/>
-      <c r="J93" s="69"/>
-      <c r="K93" s="69"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="48"/>
       <c r="L93" s="9" t="s">
         <v>52</v>
       </c>
@@ -9131,13 +9131,13 @@
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
-      <c r="E94" s="69"/>
-      <c r="F94" s="69"/>
-      <c r="G94" s="69"/>
-      <c r="H94" s="69"/>
-      <c r="I94" s="69"/>
-      <c r="J94" s="69"/>
-      <c r="K94" s="69"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="48"/>
       <c r="L94" s="9" t="s">
         <v>52</v>
       </c>
@@ -9150,13 +9150,13 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
-      <c r="E95" s="69"/>
-      <c r="F95" s="69"/>
-      <c r="G95" s="69"/>
-      <c r="H95" s="69"/>
-      <c r="I95" s="69"/>
-      <c r="J95" s="69"/>
-      <c r="K95" s="69"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="48"/>
       <c r="L95" s="9" t="s">
         <v>52</v>
       </c>
@@ -9169,13 +9169,13 @@
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="69"/>
-      <c r="F96" s="69"/>
-      <c r="G96" s="69"/>
-      <c r="H96" s="69"/>
-      <c r="I96" s="69"/>
-      <c r="J96" s="69"/>
-      <c r="K96" s="69"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="48"/>
       <c r="L96" s="9" t="s">
         <v>52</v>
       </c>
@@ -9188,13 +9188,13 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
-      <c r="E97" s="69"/>
-      <c r="F97" s="69"/>
-      <c r="G97" s="69"/>
-      <c r="H97" s="69"/>
-      <c r="I97" s="69"/>
-      <c r="J97" s="69"/>
-      <c r="K97" s="69"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="48"/>
       <c r="L97" s="9" t="s">
         <v>52</v>
       </c>
@@ -9207,13 +9207,13 @@
       </c>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
-      <c r="E98" s="69"/>
-      <c r="F98" s="69"/>
-      <c r="G98" s="69"/>
-      <c r="H98" s="69"/>
-      <c r="I98" s="69"/>
-      <c r="J98" s="69"/>
-      <c r="K98" s="69"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
       <c r="L98" s="9" t="s">
         <v>52</v>
       </c>
@@ -9226,13 +9226,13 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="9"/>
-      <c r="E99" s="69"/>
-      <c r="F99" s="69"/>
-      <c r="G99" s="69"/>
-      <c r="H99" s="69"/>
-      <c r="I99" s="69"/>
-      <c r="J99" s="69"/>
-      <c r="K99" s="69"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
       <c r="L99" s="9" t="s">
         <v>52</v>
       </c>
@@ -9245,13 +9245,13 @@
       </c>
       <c r="C100" s="9"/>
       <c r="D100" s="9"/>
-      <c r="E100" s="69"/>
-      <c r="F100" s="69"/>
-      <c r="G100" s="69"/>
-      <c r="H100" s="69"/>
-      <c r="I100" s="69"/>
-      <c r="J100" s="69"/>
-      <c r="K100" s="69"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
       <c r="L100" s="9" t="s">
         <v>52</v>
       </c>
@@ -9263,13 +9263,13 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="9"/>
-      <c r="E101" s="69"/>
-      <c r="F101" s="69"/>
-      <c r="G101" s="69"/>
-      <c r="H101" s="69"/>
-      <c r="I101" s="69"/>
-      <c r="J101" s="69"/>
-      <c r="K101" s="69"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
+      <c r="J101" s="48"/>
+      <c r="K101" s="48"/>
       <c r="L101" s="9" t="s">
         <v>52</v>
       </c>
@@ -9281,13 +9281,13 @@
       </c>
       <c r="C102" s="9"/>
       <c r="D102" s="9"/>
-      <c r="E102" s="69"/>
-      <c r="F102" s="69"/>
-      <c r="G102" s="69"/>
-      <c r="H102" s="69"/>
-      <c r="I102" s="69"/>
-      <c r="J102" s="69"/>
-      <c r="K102" s="69"/>
+      <c r="E102" s="48"/>
+      <c r="F102" s="48"/>
+      <c r="G102" s="48"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="48"/>
+      <c r="K102" s="48"/>
       <c r="L102" s="9" t="s">
         <v>52</v>
       </c>
@@ -9299,13 +9299,13 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="9"/>
-      <c r="E103" s="69"/>
-      <c r="F103" s="69"/>
-      <c r="G103" s="69"/>
-      <c r="H103" s="69"/>
-      <c r="I103" s="69"/>
-      <c r="J103" s="69"/>
-      <c r="K103" s="69"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="48"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="48"/>
+      <c r="K103" s="48"/>
       <c r="L103" s="9" t="s">
         <v>52</v>
       </c>
@@ -9313,6 +9313,196 @@
     </row>
   </sheetData>
   <mergeCells count="203">
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="E102:H102"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="E103:H103"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="E7:H7"/>
@@ -9326,196 +9516,6 @@
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="E102:H102"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="E103:H103"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I100:K100"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L103">
@@ -9925,140 +9925,148 @@
   <sheetData>
     <row r="1" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="91" t="s">
+      <c r="F2" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="93"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="89"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="90" t="s">
+      <c r="N2" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="89" t="e" vm="2">
+      <c r="B3" s="85" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="19"/>
-      <c r="F3" s="96" t="s">
+      <c r="F3" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="96" t="s">
+      <c r="J3" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
       <c r="M3" s="19"/>
-      <c r="N3" s="89" t="e" vm="3">
+      <c r="N3" s="85" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="19"/>
-      <c r="F4" s="96" t="s">
+      <c r="F4" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="19"/>
-      <c r="J4" s="96" t="s">
+      <c r="J4" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
       <c r="M4" s="19"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="19"/>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="95"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="92"/>
       <c r="M5" s="19"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="89"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
     </row>
     <row r="6" spans="2:16" s="18" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85" t="s">
+      <c r="C8" s="94"/>
+      <c r="D8" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="95" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="87" t="s">
+      <c r="C9" s="95"/>
+      <c r="D9" s="91" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="91" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="91" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87" t="s">
+      <c r="C11" s="91"/>
+      <c r="D11" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -10069,14 +10077,6 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/temporary QA.xlsx
+++ b/QA문서/temporary QA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F7055E-1334-4793-B5FD-DAB77E9F1BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5537CEE-0F77-4A17-A134-F61B5D2B1451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="870" windowWidth="23880" windowHeight="13170" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="버그피드백" sheetId="7" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="557">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2388,6 +2388,31 @@
   </si>
   <si>
     <t>RoomName에 들어가 있는 Animetor에서 RoomName : Anchored Position에 찍혀있는 키들을 각각 640과 430으로 수정하면 해결 가능함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 다용도실에 플레이가 있을 경우 지도를 열어서 위치를 확인하면 안방으로 되어 있는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hall_playerble에서 하이라아키 부분에 있는 맵을 확인하여 그 중 Map Player Location Marker 스크립으 부분에서 Marker Location에 Element 15번을 보면 다용도실(UtilityRoom)으로 되어 있는 것이 확인이 가능하나 나머지 Floor 부분을 1로 수정하고 포지션 부분에 좌표를 X-823 Y-35.5 수정하는 것으로 해결이 가능함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱크대에서 물을 켜도 이미지에 가려지는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">이미지가 다시 보일 수 있도록 수정
+해결방도 찾아보고 있는 상태 현재 Canvas, Water, Particle System을 다 건드려봐도 해결법이 안나오고 있는 상태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캔버스에 프라이팬 패널에 버너 부분을 클릭해도 불이 안켜지는 상태하고 반대로 캔버스 내부가 아닌 외부에 있는 Fripan을 클릭하면 불을 키겠냐고 문구가 나오는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해결방안으로 먼저 외부에 있는 Fripan에서 레이어를  Igonre Raycast로 변경 이후 firpan_Panel안에 있는 버너 오브젝트가 활성화 되게 변경 이후 Image에서 Raycast Target을 체크해서 키는 것으로 해결 가능한 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6228,7 +6253,7 @@
       <c r="M102" s="10"/>
     </row>
     <row r="103" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="34" t="s">
         <v>461</v>
       </c>
       <c r="C103" s="37">
@@ -6254,7 +6279,7 @@
       <c r="M103" s="10"/>
     </row>
     <row r="104" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="34" t="s">
         <v>501</v>
       </c>
       <c r="C104" s="37">
@@ -6280,80 +6305,104 @@
       <c r="M104" s="10"/>
     </row>
     <row r="105" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="34" t="s">
         <v>502</v>
       </c>
       <c r="C105" s="37">
-        <v>46182</v>
-      </c>
-      <c r="D105" s="9"/>
-      <c r="E105" s="69"/>
-      <c r="F105" s="69"/>
-      <c r="G105" s="69"/>
-      <c r="H105" s="69"/>
-      <c r="I105" s="69"/>
-      <c r="J105" s="69"/>
-      <c r="K105" s="69"/>
+        <v>46184</v>
+      </c>
+      <c r="D105" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="E105" s="55" t="s">
+        <v>551</v>
+      </c>
+      <c r="F105" s="55"/>
+      <c r="G105" s="55"/>
+      <c r="H105" s="55"/>
+      <c r="I105" s="55" t="s">
+        <v>552</v>
+      </c>
+      <c r="J105" s="55"/>
+      <c r="K105" s="55"/>
       <c r="L105" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M105" s="10"/>
     </row>
     <row r="106" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="34" t="s">
         <v>503</v>
       </c>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="69"/>
-      <c r="F106" s="69"/>
-      <c r="G106" s="69"/>
-      <c r="H106" s="69"/>
-      <c r="I106" s="69"/>
-      <c r="J106" s="69"/>
-      <c r="K106" s="69"/>
+      <c r="C106" s="37">
+        <v>46185</v>
+      </c>
+      <c r="D106" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="E106" s="55" t="s">
+        <v>553</v>
+      </c>
+      <c r="F106" s="55"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="55" t="s">
+        <v>554</v>
+      </c>
+      <c r="J106" s="55"/>
+      <c r="K106" s="55"/>
       <c r="L106" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M106" s="10"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B107" s="7" t="s">
+    <row r="107" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B107" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="C107" s="9"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="69"/>
-      <c r="F107" s="69"/>
-      <c r="G107" s="69"/>
-      <c r="H107" s="69"/>
-      <c r="I107" s="69"/>
-      <c r="J107" s="69"/>
-      <c r="K107" s="69"/>
+      <c r="C107" s="37">
+        <v>46185</v>
+      </c>
+      <c r="D107" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="E107" s="55" t="s">
+        <v>555</v>
+      </c>
+      <c r="F107" s="55"/>
+      <c r="G107" s="55"/>
+      <c r="H107" s="55"/>
+      <c r="I107" s="55" t="s">
+        <v>556</v>
+      </c>
+      <c r="J107" s="55"/>
+      <c r="K107" s="55"/>
       <c r="L107" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M107" s="10"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B108" s="7" t="s">
+    <row r="108" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="34" t="s">
         <v>505</v>
       </c>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="69"/>
-      <c r="F108" s="69"/>
-      <c r="G108" s="69"/>
-      <c r="H108" s="69"/>
-      <c r="I108" s="69"/>
-      <c r="J108" s="69"/>
-      <c r="K108" s="69"/>
+      <c r="C108" s="37">
+        <v>46185</v>
+      </c>
+      <c r="D108" s="38"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="55"/>
+      <c r="G108" s="55"/>
+      <c r="H108" s="55"/>
+      <c r="I108" s="55"/>
+      <c r="J108" s="55"/>
+      <c r="K108" s="55"/>
       <c r="L108" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M108" s="10"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="7" t="s">
         <v>506</v>
       </c>
@@ -6371,7 +6420,7 @@
       </c>
       <c r="M109" s="10"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="7" t="s">
         <v>507</v>
       </c>
@@ -6389,7 +6438,7 @@
       </c>
       <c r="M110" s="10"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="7" t="s">
         <v>508</v>
       </c>
@@ -6407,7 +6456,7 @@
       </c>
       <c r="M111" s="10"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="7" t="s">
         <v>509</v>
       </c>
@@ -6425,7 +6474,7 @@
       </c>
       <c r="M112" s="10"/>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="7" t="s">
         <v>510</v>
       </c>
@@ -6443,7 +6492,7 @@
       </c>
       <c r="M113" s="10"/>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="7" t="s">
         <v>511</v>
       </c>
@@ -6461,7 +6510,7 @@
       </c>
       <c r="M114" s="10"/>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="7" t="s">
         <v>512</v>
       </c>
@@ -6479,7 +6528,7 @@
       </c>
       <c r="M115" s="10"/>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="7" t="s">
         <v>513</v>
       </c>
@@ -6497,7 +6546,7 @@
       </c>
       <c r="M116" s="10"/>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
         <v>514</v>
       </c>
@@ -6515,7 +6564,7 @@
       </c>
       <c r="M117" s="10"/>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="7" t="s">
         <v>515</v>
       </c>
@@ -6533,7 +6582,7 @@
       </c>
       <c r="M118" s="10"/>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="7" t="s">
         <v>516</v>
       </c>
@@ -6551,7 +6600,7 @@
       </c>
       <c r="M119" s="10"/>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="7" t="s">
         <v>517</v>
       </c>
@@ -6569,7 +6618,7 @@
       </c>
       <c r="M120" s="10"/>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="7" t="s">
         <v>518</v>
       </c>
@@ -6587,7 +6636,7 @@
       </c>
       <c r="M121" s="10"/>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="7" t="s">
         <v>519</v>
       </c>
@@ -6605,7 +6654,7 @@
       </c>
       <c r="M122" s="10"/>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="7" t="s">
         <v>520</v>
       </c>
@@ -6623,7 +6672,7 @@
       </c>
       <c r="M123" s="10"/>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="7" t="s">
         <v>521</v>
       </c>
@@ -6641,7 +6690,7 @@
       </c>
       <c r="M124" s="10"/>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="7" t="s">
         <v>522</v>
       </c>
@@ -6659,7 +6708,7 @@
       </c>
       <c r="M125" s="10"/>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="7" t="s">
         <v>523</v>
       </c>
@@ -6677,7 +6726,7 @@
       </c>
       <c r="M126" s="10"/>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="7" t="s">
         <v>524</v>
       </c>
@@ -6695,7 +6744,7 @@
       </c>
       <c r="M127" s="10"/>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="7" t="s">
         <v>525</v>
       </c>
@@ -6713,7 +6762,7 @@
       </c>
       <c r="M128" s="10"/>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="7" t="s">
         <v>526</v>
       </c>
@@ -6731,7 +6780,7 @@
       </c>
       <c r="M129" s="10"/>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="7" t="s">
         <v>527</v>
       </c>
@@ -6749,7 +6798,7 @@
       </c>
       <c r="M130" s="10"/>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="7" t="s">
         <v>528</v>
       </c>
@@ -6767,7 +6816,7 @@
       </c>
       <c r="M131" s="10"/>
     </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="7" t="s">
         <v>529</v>
       </c>
@@ -6785,7 +6834,7 @@
       </c>
       <c r="M132" s="10"/>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="7" t="s">
         <v>530</v>
       </c>
@@ -6803,7 +6852,7 @@
       </c>
       <c r="M133" s="10"/>
     </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="7" t="s">
         <v>531</v>
       </c>
@@ -6821,7 +6870,7 @@
       </c>
       <c r="M134" s="10"/>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="7" t="s">
         <v>532</v>
       </c>
@@ -6839,7 +6888,7 @@
       </c>
       <c r="M135" s="10"/>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="7" t="s">
         <v>533</v>
       </c>
@@ -6857,7 +6906,7 @@
       </c>
       <c r="M136" s="10"/>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="7" t="s">
         <v>534</v>
       </c>
@@ -6875,7 +6924,7 @@
       </c>
       <c r="M137" s="10"/>
     </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="7" t="s">
         <v>535</v>
       </c>
@@ -6893,7 +6942,7 @@
       </c>
       <c r="M138" s="10"/>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="7" t="s">
         <v>536</v>
       </c>
@@ -6911,7 +6960,7 @@
       </c>
       <c r="M139" s="10"/>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="7" t="s">
         <v>537</v>
       </c>
@@ -6929,7 +6978,7 @@
       </c>
       <c r="M140" s="10"/>
     </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="7" t="s">
         <v>538</v>
       </c>
